--- a/myapp/data_idx_gabung.xlsx
+++ b/myapp/data_idx_gabung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SENTIMENT ANALYSIS UGI AQIS 2026\PROJECT SHINY DASHBOARD ANALISIS SENTIMEN 2026 TERBARU\myapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{838B4110-65EA-4B42-89B7-6DC1EAF3F391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC585D6C-BAC4-4CFF-A38B-447984B893AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="159">
   <si>
     <t>No</t>
   </si>
@@ -85,6 +85,150 @@
     <t>Journal Information</t>
   </si>
   <si>
+    <t>High Performance of Polynomial Kernel at SVM Algorithm for Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>Lailil Muflikhah; Dimas Joko Haryanto</t>
+  </si>
+  <si>
+    <t>JITeCS (Journal of Information Technology and Computer Science)</t>
+  </si>
+  <si>
+    <t>https://jitecs.ub.ac.id/index.php/jitecs/article/view/60</t>
+  </si>
+  <si>
+    <t>sentiment analysis; SVM; kernel; RBF; polynomial; performance</t>
+  </si>
+  <si>
+    <t>Sinta 2</t>
+  </si>
+  <si>
+    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/3497</t>
+  </si>
+  <si>
+    <t>Sentiment analysis is a text mining based on the opinion collection towards the review of online product. Support Vector Machine (SVM) is an algorithm of classification that applicable to review the analysis of product. The hyperplane kernel function of SVM has importance role to classify the certain category. Therefore, this research is address to investigate the performance between Polynomial and Radial Basis Function (RBF) kernel functions for sentiment analysis of review product. They are examined to 200 comments using 10-fold validation and various parameter values (learning rate, lambda, c value, epsilon and iteration). As general, the performance for polynomial kernel of 88.75% is slightly higher than RBF kernel of 83.25%.</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of Visitor Reviews on Star Hotels in Manado City</t>
+  </si>
+  <si>
+    <t>Jeniver Petronela Matrutty; Angelia Melani Adrian; Apriandy Angdresey</t>
+  </si>
+  <si>
+    <t>https://jitecs.ub.ac.id/index.php/jitecs/article/view/403</t>
+  </si>
+  <si>
+    <t>Text Mining; Sentiment Analysis; Naive Bayes; Hotels</t>
+  </si>
+  <si>
+    <t>Abstract. Sentiment analysis is a technique of extracting the text data to analyze the opinions and evaluate to obtain the information. Sentiment analysis is performed by internet users on social media or online applications or websites to provide assessments or personal opinions. Tourism in North Sulawesi has grown by 600% in the past four years, and the rise of tourism has sent tourists flocking to the city of Manado. These travelers need a hotel that satisfies their desires, so they need to read about the hotel in the reviews on the hotel reservation service website. This takes a lot of time. To overcome existing problems, sentiment analysis applications were developed to make it easier for potential hotel users to find previous user responses. Additionally, data mining classification techniques are used to help hotel managers determine the satisfaction of previous hotel users using a Naive Bayes algorithm. There were 640 reviews data from January to March 2019 obtained from TripAdvisor website used in this study with the proportion of 70:30 for data training and testing respectively. The classification results are divided into five classes, namely excellent, good, average, poor, terrible. This classification is based on categories from the TripAdvisor website. The experimental result for five consecutive runs shows that Naïve Bayes obtained 76.20% accuracy, with an average of 70.55%. While the average precision is 70.57% and 99.85% for the recall.</t>
+  </si>
+  <si>
+    <t>Multilingual Sentiment Analysis of RCTI+ Reviews Utilising Orange, ChatGPT, and Naïve Bayes</t>
+  </si>
+  <si>
+    <t>Meilani Mega Juita; Rahmi Rahmi</t>
+  </si>
+  <si>
+    <t>https://jitecs.ub.ac.id/index.php/jitecs/article/view/787</t>
+  </si>
+  <si>
+    <t>sentiment analysis; multilingual reviews; generative AI; ChatGPT; Orange Data Mining; Naive Bayes; user feedback; RCTI+</t>
+  </si>
+  <si>
+    <t>Abstract. Low user ratings of mobile applications often reflect underlying dissatisfaction that is not immediately apparent through quantitative scores alone. To uncover the sentiment dynamics behind such evaluations, this study analyzed user reviews of the RCTI+ Superapp in both the original Indonesian and English translated forms. Using the CRISP-DM framework, reviews were scraped from Google Play, normalized and translated via ChatGPT, and classified using Orange Data Mining with a Naïve Bayes algorithm. The analysis reveals that English-translated reviews yield sharper sentiment polarity and higher classification accuracy (100%) than the original Indonesian texts (99.1%), albeit with reduced lexical nuance. These findings suggest that generative AI-assisted translation enhances sentiment clarity in informal, low-resource language data while potentially simplifying cultural or emotional expression. This study offers methodological insights into multilingual sentiment analysis and practical implications for app developers seeking to interpret user feedback more effectively across languages.</t>
+  </si>
+  <si>
+    <t>Sentiment Anlysis On Customer Reviews Using Support Vector Machine and Usability Scoring Using System Usability Scale</t>
+  </si>
+  <si>
+    <t>Novira Azpiranda; Ahmad Afif Supianto; Nanang Yudi Setiawan; Endang Suryawati; R. Sandra Yuwana; Arafat Febriandirza</t>
+  </si>
+  <si>
+    <t>https://jitecs.ub.ac.id/index.php/jitecs/article/view/330</t>
+  </si>
+  <si>
+    <t>sentiment analysis; text mining; support vector machine; tf-idf; web scraping</t>
+  </si>
+  <si>
+    <t>Abstract. Al-Ghiff Steak is a restaurant located in Cirebon City that offers quality steaks at affordable prices. For maintaining a competitive Al-Ghiff Steak advantage and reputation, it is important to build a good relationship with customers and have a business strategy that considers customer opinions. However, in its implementation, Al-Ghiff Steak has difficulty when collecting and processing customer review data manually. Therefore, it is necessary to conduct sentiment analysis by utilizing Google Reviews to determine customer perspectives regarding Al-Ghiff Steak products and services. This analysis was conducted on 968 Google Review reviews from 2016 to 2020 using the Support Vector Machine (SVM) and Term Frequency-Inverse Document Frequency (TF-IDF) methods. Classification testing is done with a confusion matrix against four parameters: accuracy, precision, recall, and f1-score. SVM with TF-IDF gets accuracy value 83%, precision 64%, recall 60% and f1-score 59%. The sentiment classification result is then visualized in the form of a dashboard. We utilize the System Usability Scale (SUS) for usability testing, which produces a value of 77.5. This result achieve the Acceptable category and an Excellent rating.</t>
+  </si>
+  <si>
+    <t>Analysis of Indonesian Public Satisfaction Towards Goods Delivery Services using the CNN-LSTM Model</t>
+  </si>
+  <si>
+    <t>Anak Agung Istri Prabhaisvari Sadhaka; I Made Agus Dwi Suarjaya; Putu Wira Buana</t>
+  </si>
+  <si>
+    <t>https://jitecs.ub.ac.id/index.php/jitecs/article/view/507</t>
+  </si>
+  <si>
+    <t>sentiment analysis; delivery service; expedition; CNN; LSTM</t>
+  </si>
+  <si>
+    <t>Abstract. The fast-paced development of e-commerce in Indonesia has driven the expansion and rising demand for goods delivery services. Every goods delivery service offers consultations or Q&amp;A sessions about their services through Twitter. The number of tweets from users of goods delivery services can be used to determine the level of public satisfaction with these delivery services. The sentiment analysis process is conducted using a CNN-LSTM deep learning model. Evaluation of the CNN-LSTM model resulted in an accuracy of 0.838, an F1-score of 0.838 for the macro average and micro average, a precision of 0.840 for the macro average and 0.838 for the micro average, and a recall of 0.840 for the macro average and 0.838 for the micro average. Based on the results of analysis, it was found that Indonesian people tend to be dissatisfied with existing delivery services.</t>
+  </si>
+  <si>
+    <t>Sentiment Visualization of Covid-19 Vaccine Based On Naive Bayes Analysis</t>
+  </si>
+  <si>
+    <t>Nabilah Putri Aprilia; Dian Pratiwi; Anung Barlianto</t>
+  </si>
+  <si>
+    <t>https://jitecs.ub.ac.id/index.php/jitecs/article/view/353</t>
+  </si>
+  <si>
+    <t>sentiment analysis; naive bayes; lexicon-based; twitter</t>
+  </si>
+  <si>
+    <t>COVID-19 is one of the topics that is being discussed intensively. The virus which was declared a global pandemic on March 11 by WHO caused around 2.09 million Indonesians to be infected with the COVID-19 virus. To overcome this, the government carried out a vaccination program. The data taken for this study is public opinion about the COVID-19 vaccine written on Twitter. The idea of this research is to classify the covid vaccination dataset using the naive Bayes classifier method and visualization using word cloud. Crawling to obtain the dataset from Twitter, text pre-processing and labelling to determine the positive and negative classes, TF-IDF feature extraction for word weighting, data splitting with a percentage of 80% for train data and 20% for data testing, and finally classification using nave Bayes are the stages in this research The system's sentiment analysis research yielded significant results, the accuracy value is 73.1%, the precision value is 73% and the recall value is 83%.</t>
+  </si>
+  <si>
+    <t>The Sentiment Analysis Of Indonesian Startup Application Reviews Using TF-IDF+SVM and FastText: A Comparative Study</t>
+  </si>
+  <si>
+    <t>Aini Nabilah; Nurlayli Indah Sari; Mira Afrina; Ali Ibrahim</t>
+  </si>
+  <si>
+    <t>https://jitecs.ub.ac.id/index.php/jitecs/article/view/807</t>
+  </si>
+  <si>
+    <t>fastText; Indonesian Startups; Sentiment Analysis; SVM; Technopreneurship; TF-IDF</t>
+  </si>
+  <si>
+    <t>Abstract. The rapid rise of startups in Indonesia makes user reviews on the Google Play Store a valuable data source for understanding user perceptions and satisfaction. These unstructured reviews contain insights supporting product development and business strategies. This study analyzes sentiments in Indonesian startup app reviews and compares two classification methods: TF-IDF + Linear SVM and fastText, implemented using Google Colab. Reviews were collected in September 2025 using google-play-scraper; 4,000 reviews were retrieved and refined into 3,152 unique reviews after cleaning and preprocessing. Sentiment labeling used ratings (1–2 negative, 4–5 positive); because the neutral class was limited, this study focuses on balanced binary classification with 1576 positive and 1576 negative reviews. The process involves data scraping, text preprocessing, model training, and evaluation using accuracy, precision, recall, and F1-score metrics, with Linear SVM chosen as an efficient baseline for high-dimensional sparse TF-IDF features. Results show that fastText achieves 91.88% accuracy and an F1-macro of 0.9184, slightly outperforming TF-IDF + SVM (F1-macro 0.9103), suggesting that the embedding-based approach better captures semantic nuances of Indonesian text. Future work may extend this study to ABSA to assess sentiments toward price, UI/UX, and customer service for deeper technopreneurship insights in Indonesia.</t>
+  </si>
+  <si>
+    <t>Comparison of Bagging Ensemble Combination Rules for Imbalanced Text Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>Reiza Adi Cahya; Fitra A. Bachtiar; Wayan Firdaus Mahmudy</t>
+  </si>
+  <si>
+    <t>https://jitecs.ub.ac.id/index.php/jitecs/article/view/206</t>
+  </si>
+  <si>
+    <t>ensemble; SUM; SR; classifier; dataset</t>
+  </si>
+  <si>
+    <t>Abstract. The wealth of opinions expressed by users on micro-blogging sites can be beneficial for product manufacturers of service providers, as they can gain insights about certain aspects of their products or services. The most common approach for analyzing text opinion is using machine learning. However. opinion data are often imbalanced, e.g. the number of positive sentiments heavily outnumbered the negative sentiments. Ensemble technique, which combines multiple classification algorithms to make decisions, can be used to tackle imbalanced data to learn from multiple balanced datasets. The decision of ensemble is obtained by combining the decisions of individual classifiers using a certain rule. Therefore, rule selection is an important factor in ensemble design. This research aims to investigate the best decision combination rule for imbalanced text data. Multinomial Naïve Bayes, Complement Naïve Bayes, Support Vector Machine, and Softmax Regression are used for base classifiers, and max, min, product, sum, vote, and meta-classifier rules are considered for decision combination. The experiment is done on several Twitter datasets. From the experimental results, it is found that the Softmax Regression ensemble with meta-classifier combination rule performs the best in all except in one dataset. However, it is also found that the training of the Softmax Regression ensemble requires intensive computational resources.</t>
+  </si>
+  <si>
+    <t>Event Recommendation System using Hybrid Method Based on Mobile Device</t>
+  </si>
+  <si>
+    <t>Dio Saputra Kudori</t>
+  </si>
+  <si>
+    <t>https://jitecs.ub.ac.id/index.php/jitecs/article/view/221</t>
+  </si>
+  <si>
+    <t>event; sentiment; accuracy; filtering</t>
+  </si>
+  <si>
+    <t>Abstract. In everyday life there are many events are held. These events use various ways in announcing the event for attracting people to participate come in the event. Because there are many events that are held in everyday life, an event recommendation system can be implemented to provide event recommendations that are appropriate for the user. In developing event recommendation systems, there are many methods that can be used, the one that frequently used is collaborative filtering. The event recommendation system has a unique character compared to other recommendation systems. This is because the event recommendation system does not use the classic scenario of a recommendation system. In this study we tried to use a hybrid method that combines collaborative filtering with sentiment analysis. The experiment show that the results of the event recommendations have an accuracy value of 82%. It shows that the hybrid method can be utilized for developing event recommendation systems.</t>
+  </si>
+  <si>
     <t>Analisis Sentimen Sosial Media Twitter Dengan Algoritma Machine Learning Menggunakan Software R</t>
   </si>
   <si>
@@ -109,9 +253,7 @@
     <t>R</t>
   </si>
   <si>
-    <t>Penelitian ini akan menggunakan metode Machine Learning pada analisis sentimen pengguna layanan jejaring social Twitter terhadap Donald Trump dan Barack Obama dalam 20000 tweets
-"Penelitian ini akan menggunakan metode Machine Learning pada analisis sentimen pengguna layanan jejaring social Twitter terhadap Donald Trump dan Barack Obama dalam 20000 tweets. Nilai akurasi metode Machine Learning yang diperoleh cukup tinggi yaitu 87.52% untuk Data Training dan 87.4% untuk Data Testing.
-Penelitian ini bertujuan untuk menerapkan analisis sentiment dan Text Mining pada layanan jejaring sosial Twitter menggunakan algoritma Machine Learning dengan contoh kasus sentimen pengguna Twitter berbahasa inggris kepada Donald Trump dan Barack Obama selama bulan Agustus 2017 hingga September 2017 dengan menggunakan software R."</t>
+    <t>Social media is a place to express opinions on a particular topic. The availability of information and opinions from social media users is a collection of data documents in the form of very large textual data and its useful for the research purposes and make a decision for certain parties. Text Mining can be defined as a process of extracting information in which the user interacts with the documents over time using an analysis tool. Opinion Mining analysis is one of computational studies related to public case concerning opinion, judgment, attitude, and emotion. This study will use the method of Machine Learning algorithm on the analysis of Twitter user sentiment toward Donald Trump and Barack Obama in 20000 tweets. The accuracy of Machine Learning method obtained is high enough that is 87.52% for Data Training and 87.4% for Data Testing.</t>
   </si>
   <si>
     <t>Publication Fee (Author Fees): Jurnal Fourier does not charge APCs, submission charges, or another fee. All processes of article publication are free of charge.
@@ -130,8 +272,7 @@
     <t>Sentiment Analysis; Stratified 10-Fold Cross Validation; SMOTE; Class Weighting</t>
   </si>
   <si>
-    <t>Penelitian ini bertujuan untuk membandingkan performa tiga pendekatan analisis sentimen, yaitu Naïve Bayes, Support Vector Machine (SVM), dan Indonesian Bidirectional Encoder Representations from Transformers (IndoBERT), pada layanan IndiHome menggunakan data Twitter. Keterbatasan model tradisional melatarbelakangi penelitian ini dalam mengenali opini positif dan tantangan ketidakseimbangan data yang sering muncul dalam analisis berbasis media sosial. Data penelitian berupa 7393 tweet (Januari 2019–Agustus 2024) yang dilabeli secara manual menjadi sentimen positif dan negatif.
-Pelabelan data dilakukan secara manual untuk memastikan akurasi dalam klasifikasi sentimen. Penelitian ini hanya menggunakan dua kategori sentimen, yaitu positif dan negative. Sentimen netral tidak disertakan karena sering kali sulit diinterpretasikan secara konsisten. Tweet dengan sentimen netral umumnya bersifat informatif atau ambigu, sehingga tidak secara tegas mencerminkan sikap pengguna terhadap layanan, baik berupa kepuasan maupun ketidakpuasan. Kondisi tersebut dapat menurunkan reliabilitas pelabelan. Oleh karena itu, pembatasan analisis pada dua kelas utama memungkinkan proses klasifikasi yang lebih efisien serta menghasilkan interpretasi hasil yang lebih reliabel.</t>
+    <t>This study aims to compare the performance of three sentiment analysis approaches, namely Naïve Bayes, Support Vector Machine (SVM), and Indonesian Bidirectional Encoder Representations from Transformers (IndoBERT), on IndiHome services using Twitter data. The limitations of traditional models underlie this study in recognizing positive opinions and the challenge of data imbalance that often arises in social media based analysis. The research data consist of 7,393 tweets (January 2019–August 2024) manually labeled into positive and negative sentiments. Models were evaluated using stratified 10-fold cross validation and test data, with the application of imbalance handling techniques such as Synthetic Minority Oversampling Technique (SMOTE) and class weighting. Results show IndoBERT excels with 0.96 accuracy and 0.95 macro F1-score without special handling, while SVM reaches 0.95 accuracy with class weighting, and Naïve Bayes improves from 0.89 to 0.92 accuracy after SMOTE. Sentiment trend analysis indicates negative opinions dominate, mainly regarding speed and service stability. These findings confirm IndoBERT is more effective in understanding Indonesian context, while data handling remains relevant for improving traditional models. This study’s results are important because they offer an empirical foundation for choosing sentiment analysis models that are more accurate, adaptive to Indonesian language, and useful for improving service quality.</t>
   </si>
   <si>
     <t>Analisis Sentimen Berbasis Aspek Ulasan Pelanggan Restoran Menggunakan LSTM Dengan Adam Optimizer</t>
@@ -155,7 +296,7 @@
     <t>Python</t>
   </si>
   <si>
-    <t>opini pelanggan restoran berbasis aspek (makanan, tempat, pelayanan, harga), berdasarkan ulasan pelanggan restoran pada TripAdvisor berbahasa Indonesia</t>
+    <t>Abstract Consumers believe that restaurant reviews are very important when choosing a restaurant. Due to the fact that reviews have become one of the most effective ways to influence customer decisions, research that has been done on restaurant customer reviews is about sentiment analysis. Previous studies have only used sentiment analysis at the sentence or document level, while a better level uses Aspect-Based Sentiment Analysis (ABSA), or a type of aspect-based sentiment analysis. LSTM is a variant of RNN that stores long-term information in memory cells. Use of global max pooling to reduce output resolution features and prevent overfitting. In addition, the optimization method used by Adam Optimizer is an adaptive learning rate optimization algorithm specifically designed to train deep neural networks. This study aims to classify restaurant customer opinions based on aspects (food, place, service, and price) based on restaurant customer reviews on Indonesian-language TripAdvisor with LSTM and global max pooling for sentiment classification (negative, half negative, neutral, half positive, positive). The results of this study indicate that the ABSA in restaurant customer reviews for sentiment classification accuracy is 78.7% and the aspect category accuracy is 78%, both are interconnected and can help understand restaurant customer opinions on TripAdvisor.</t>
   </si>
   <si>
     <t>Biaya Pemrosesan Artikel (Article Processing Charge - APC); Untuk mendukung keberlangsungan operasional dan pengelolaan penerbitan, JOINTECS: Journal of Information Technology and Computer Science menerapkan biaya pemrosesan artikel (Article Processing Charge - APC) sebesar Rp. 750.000,00,-. Besaran biaya ini mencakup seluruh proses pengelolaan naskah, mulai dari administrasi, penelaahan sejawat (peer review), penyuntingan, hingga penerbitan artikel secara daring dengan akses terbuka. Link: https://publishing-widyagama.ac.id/ejournal-v2/index.php/jointecs/charge</t>
@@ -173,7 +314,7 @@
     <t>Debat Calon Presiden; Twitter; Sentiment Analysis; Twitter API; Pemrograman R</t>
   </si>
   <si>
-    <t>Media sosial, Twitter, saat ini telah banyak memberikan dampak besar dalam membangun opini, pandangan, sentimen, dan preferensi politik publik (menjelang Pemilihan Umum) berlangsung. Penelitian ini dilakukan untuk mengetahui percakapan di Twitter pada debat pertama calon presiden Republik Indonesia melalui hashtag dari kedua pasang calon. Selain itu, juga untuk mengetahui tentang kecenderungan masyarakat di Twitter terkait dengan debat yang sedang berlangsung tersebut cenderung positif, negatif, atau netral. Data percakapan di Twitter didapatkan melalui Twitter API yang diambil dengan bahasa Pemrograman R. Proses analisis sentimen ini menggunakan metode Fined-grained Sentiment Analysis yaitu, Jika satu tweet berisi lebih banyak kalimat positif daripada negatif, maka hasil keseluruhan akan positif dan bernilai (+1). Jika jumlah kalimat negatif lebih besar dari kalimat positif, maka hasil keseluruhan negatif dan bernilai (-1). Jika ada jumlah yang sama dari kalimat positif dan negatif dalam paragraf, maka hasilnya adalah netral dan bernilai (0). Hasil dari penelitian ini menunjukkan bahwa tweet sentimen dari kedua hashtag cenderung positif, lebih banyak daripada sentimen negatif dan netral.</t>
+    <t>Abstract — Social media, Twitter, these days has a great impact in building public opinion, views, sentiments, and political preferences (ahead of the general election). This research is to find out the conversations on Twitter at the First Candidate Debate of the President of the Republic of Indonesia through the hashtag of the two pairs of candidates. Besides that, also to find out about the tendency of people on Twitter related to the ongoing debate tends to be positive, negative, or neutral. Conversation data on Twitter is obtained through the Twitter API taken with the R programming language and uses the Fine-grained Sentiment Analysis method. If one tweet contains more positive than negative sentences, then the overall result will be positive and worth (+1). If the number of negative sentences is greater than the positive sentence, then the overall result is negative and is worth (-1). If there is an equal number of positive and negative sentences in the input paragraph, then the result is neutral and worth (0). The results of this study indicate that sentiment tweets from both hashtags tend to be positive, more than negative and neutral sentiments.</t>
   </si>
   <si>
     <t>Analisis Sentimen dan Topic Modelling Pada Pembelajaran Online di Indonesia Melalui Twitter</t>
@@ -191,7 +332,7 @@
     <t>Orange Machine Learning</t>
   </si>
   <si>
-    <t>Penelitian ini bertujuan untuk mengetahui komentar dan respon dari berbagai pihak mengenai pembelajaran online yang dilakukan selama berlangsungnya pandemi COVID-19 yang masih terjadi di Indonesia menggunakan metode analisis sentimen dan topic modeling dengan machine learning Orange. Dimana untuk data yang berupa komentar dan reaksi dari berbagai pihak mengenai pembelajaran online diambil pada 18 April 2020 dan 21 Januari 2021 dari media sosial Twitter menggunakan API (Aplication Programming Interface). Hasil olahan data yang diambil pada 18 April 2020 dapat diketahui bahwa dari komentar dan respon yang muncul, paling banyak mengandung emosi surprise dengan nilai 44.5%. Emosi surprise menjadi yang paling banyak muncul karena pada awal pelaksanaannya, masyarakat Indonesia masih belum siap dengan pembelajaran online yang diterapkan.</t>
+    <t>This study aims to determine the comments and responses of various parties regarding the online learning carried out during the COVID-19 pandemic in Indonesia using sentiment analysis and topic modeling methods with Orange's machine learning. Data in the form of comments and reactions from various parties regarding online learning was taken on April 18, 2020 and January 21, 2021 from Twitter using the API (Application Programming Interface). The results of the processed data taken on April 18, 2020, revealed that of the comments and responses that appeared, most of them contained the emotion of surprise with a value of 44.5%. The excitement of surprise arose mostly because Indonesians weren't ready for online learning. And the data collection on January 21, 2021 contains the highest amount of joy emotions with a value of 48.4%. Joy's emotions arise due to the tale of the task rider. Information from this research is that the e-learning system that has been implemented to date is still experiencing problems. These can be seen from the complaints where the word assignment was used 481 times. In addition, complaints with the word abandonment reappeared 330 times in the second period.</t>
   </si>
   <si>
     <t>CNN-LSTM with Transformer-Based Fusion (CLIP: Contrastive Language-Image Pretraining) for Sentiment and Emotion</t>
@@ -206,6 +347,9 @@
     <t>Multimodal Sentiment Analysis; CNN-LSTM; CLIP; Emotion Classification; Internet Memes; Deep Learning</t>
   </si>
   <si>
+    <t>Sentiment analysis on multimodal data presents significant challenges due to the complex integration of textual and visual information, especially in internet memes where meaning often emerges from the interplay between image and text. This study proposes a hybrid deep learning model that combines Convolutional Neural Networks (CNN) for visual feature extraction, Long Short-Term Memory (LSTM) networks for contextual text understanding, and Contrastive Language–Image Pretraining (CLIP) as a transformer-based fusion mechanism to align both modalities in a shared semantic space. Evaluated on the Memotion 7K dataset, the proposed model achieves an accuracy of 85.6%, outperforming baseline architectures such as CNN-LSTM (78.3%) and BERT-DenseNet (81.2%). Experimental results demonstrate that CLIP’s contrastive learning significantly enhances the model’s ability to interpret ambiguous and sarcastic content by capturing nuanced text-image relationships. The system shows balanced performance across sentiment classes, with strong precision and recall metrics, confirming its robustness. This research contributes a methodologically sound framework for multimodal sentiment analysis and offers practical implications for real-world applications such as social media monitoring, digital marketing, and cross-cultural content understanding. Future work includes multilingual dataset expansion, computational optimization for deployment, and integration of additional modalities like audio or video to further enrich emotional context.</t>
+  </si>
+  <si>
     <t>Analisis Sentimen Dewan Perwakilan Rakyat Dengan Algoritma Klasifikasi Berbasis Particle Swarm Optimization</t>
   </si>
   <si>
@@ -218,6 +362,30 @@
     <t>legislative member; analysis sentiment; support vector machine; naive bayes; particle swarm optimization</t>
   </si>
   <si>
+    <t>The use of the internet, especially social media, has become a part of national life. This is partly because many members of the House of Representatives of the Republic of Indonesia (DPR RI) convey ideas, policies and provide comments on government policies through social media. This research was conducted to measure opinions or separate positive and negative sentiments towards the DPR RI. The data used in this study was obtained by crawling on social media twitter. The study was conducted using two algorithms namely Support Vector Machine (SVM) and Naive Bayes (NB).Two algorithms are used in this study, Support Vector Machine (SVM), Naive Bayes (NB), and each is optimized using Particle Swarm Optimization (PSO). The accuracy values of cross-validation test of SVM and NB without PSO are 71.04% and 70.69% with Area Under the Curve (AUC) values of 0.817 and 0.661. The accuracy values of cross-validation test using PSO, for SVM and NB are 75.03% and 73.49%, with AUC values of 0.808 and 0.719. The use of PSO can increase the accuracy of SVM 3.99% and 2.8% for NB. The highest value of accuracy recorded, come from SVM using PSO, measured at 75.03%.</t>
+  </si>
+  <si>
+    <t>Design of Sentiment Analysis on Indodax Instagram Social Media Comments About Cryptocurrency Using Naïve Bayes Classifier</t>
+  </si>
+  <si>
+    <t>Dimas Prayoga</t>
+  </si>
+  <si>
+    <t>Al'Adzkiya International of Computer Science and Information Technology Journal</t>
+  </si>
+  <si>
+    <t>https://aladzkiyajournal.com/index.php/AIoCSIT/article/view/325</t>
+  </si>
+  <si>
+    <t>User Sentiment; Indodax; Instagram; Naive Bayes Classifier; Application Service Quality</t>
+  </si>
+  <si>
+    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/15418</t>
+  </si>
+  <si>
+    <t>In today's digital era, social media such as Instagram has become the main platform for many individuals to interact and express opinions online. One application that is often the subject of conversation is Indodax, a well-known digital asset trading platform in Indonesia. This research aims to evaluate the sentiment of Instagram users towards Indodax services through a sentiment analysis approach using Naive Bayes Classifier. The data collected consists of Instagram users' comments, which are analyzed to assess the tendency of their sentiments, whether positive or negative towards Indodax services. This method applies probability and statistical concepts to classify sentiments based on the words present in the comments. It is hoped that the results of this study can provide insights for Indodax to improve the quality of their services based on the perceptions of users. Based on the experiments conducted, the Naive Bayes Classifier method shows fairly accurate classification results, so it can support sentiment analysis related to the Indodax application.</t>
+  </si>
+  <si>
     <t>AlgoDM: algorithm to perform aspect-based sentiment analysis using IDistance matrix</t>
   </si>
   <si>
@@ -239,10 +407,97 @@
     <t>https://sinta.kemdiktisaintek.go.id/journals/profile/693</t>
   </si>
   <si>
+    <t>Sentiment analysis is a method of analyzing data to identify its intent. It identifies the emotional tone of a text body. Aspect-based sentiment analysis is a text analysis technique that identifies the aspect and the sentiment associated with each aspect. Different organizations use aspect-based sentiment analysis to analyze opinions about a product, service, or idea. Traditional sentiment analysis methods analyze the complete text and assign a single sentiment label to it. They do not handle the tasks of aspect association, dealing with multiple aspects and inclusion of linguistic concepts together as a system. In this article, AlgoDM, an algorithm to perform aspect-based sentiment analysis is proposed. AlgoDM uses a novel concept of IDistance matrix to extract aspects, associate aspects with sentiment words, and determine the sentiment associated with each aspect. The IDistance matrix is constructed to calculate the distance between aspects and the words expressing the sentiment related to the aspect. It works at the sentence level and identifies the opinion expressed on each aspect appearing in the sentence. It also evaluates the overall sentiment expressed in the sentence. The proposed algorithm can perform sentiment analysis of any opinionated text.</t>
+  </si>
+  <si>
     <t>https://www.scopus.com/sourceid/21100373959</t>
   </si>
   <si>
     <t>Article Submission: 0.00 (USD); Authors are not required to pay an Article Submission Fee as part of the submission process to contribute to review costs.; Article Publication: 215.00 (USD). Link: https://ijece.iaescore.com/index.php/IJECE/about/submissions#authorFees</t>
+  </si>
+  <si>
+    <t>Analyzing Public Sentiment Toward Makanan Bergizi Gratis Program Using Machine Learning</t>
+  </si>
+  <si>
+    <t>Musriatun Napiah; Sujiliani Heristian; Mugi Raharjo; Rachmat Adi Purnama</t>
+  </si>
+  <si>
+    <t>Computer Science (CO-SCIENCE)</t>
+  </si>
+  <si>
+    <t>https://jurnal.bsi.ac.id/index.php/co-science/article/view/10445</t>
+  </si>
+  <si>
+    <t>MBG; Machine Learning; Natural Language Processing</t>
+  </si>
+  <si>
+    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/9948</t>
+  </si>
+  <si>
+    <t>Makanan Bergizi Gratis (MBG) program is a strategic initiative of the Indonesian government to improve the nutritional quality of schoolchildren. This research seeks to examine public sentiment regarding the MBG program by leveraging 10,000 tweets obtained from Kaggle. The method used combines Natural Language Processing (NLP) and Machine Learning approaches, several algorithms such as Logistic Regression, Support Vector Machine (SVM), Random Forest, Naive Bayes, XGBoost, and LightGBM were tested to compare classification performance. The dataset contains a collection of public reviews categorized into three sentiment classes: positive, negative, and neutral. The analysis process includes text cleaning, tokenization, stopword removal, and stemming to obtain a cleaner text representation. Text features were then extracted using the Term Frequency–Inverse Document Frequency (TF-IDF) method. The results showed that the Logistic Regression 97% with an F1-score of 0.9552 models showed the most optimal performance. Sentiment analysis revealed 65% positive responses, 25% neutral, and 10% negative, with the dominant keywords being "nutrisi," "sehat," "anak sekolah," and "gratis." The results visualization, in the form of a Word Cloud and a bar chart, indicate that public opinion tends to be positive towards the implementation of the MBG program, particularly regarding improving the nutrition of schoolchildren. This research is expected to provide input for policymakers in evaluating public perceptions of the implementation of food-based social programs.</t>
+  </si>
+  <si>
+    <t>Article Publication Fee (Domestic Authors): IDR 500,000; (This fee is charged only if the manuscript is accepted for publication after completing the peer-review process.); Article Publication Fee (Foreign Authors): IDR 0 (FREE); (No publication fee is charged for international authors whose manuscripts are accepted after peer review.); Link: https://jurnal.bsi.ac.id/index.php/co-science/APC</t>
+  </si>
+  <si>
+    <t>Analisis Sentimen Terhadap Aplikasi Canva Menggunakan Algoritma Naive Bayes Dan K-Nearest Neighbors</t>
+  </si>
+  <si>
+    <t>Dany Pratmanto; Fabriyan Fandi Dwi Imaniawan</t>
+  </si>
+  <si>
+    <t>https://jurnal.bsi.ac.id/index.php/co-science/article/view/1917</t>
+  </si>
+  <si>
+    <t>Sentiment analysis; Canva; KNN algorithm; Naive Bayes algorithm</t>
+  </si>
+  <si>
+    <t>Abstracts - The sentiment analysis used in the Canva application involves collecting user reviews or feedback. Then, a sentiment analysis algorithm is applied to classify the reviews as positive or negative. Sentiment analysis can help the company understand user opinions about the Canva application and how the application can meet user needs. The process of sentiment analysis in the Canva application involves collecting user reviews or feedback, which are then classified using a sentiment analysis algorithm. The research results show that the KNN algorithm has an accuracy rate of 83.92%, while Naive Bayes only has an accuracy rate of 77.41%. The KNN algorithm also has higher recall and precision values than Naive Bayes, namely 83.66% and 84.49%, respectively. In addition, the AUC value generated by the KNN algorithm is also higher than Naive Bayes, namely 95.00% compared to 94.50%. Therefore, it can be concluded that the KNN algorithm is more suitable for data classification in this research. This research can contribute to the development of the Canva application and improve the quality of service for its users.</t>
+  </si>
+  <si>
+    <t>Analisis Sentimen Pemanfaatan Artificial Intelligence di Dunia Pendidikan Menggunakan SVM Berbasis Particle Swarm Optimization</t>
+  </si>
+  <si>
+    <t>Atang Saepudin; Riska Aryanti; Eka Fitriani; Royadi Royadi; Dian Ardiansyah</t>
+  </si>
+  <si>
+    <t>https://jurnal.bsi.ac.id/index.php/co-science/article/view/2921</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis; Artificial Intelligence; Media Social; Support Vector Machine; PSO</t>
+  </si>
+  <si>
+    <t>The utilization of Artificial Intelligence (AI) in the field of education in Indonesia has witnessed significant developments in recent years. The advancements in AI technology have opened up new opportunities to enhance the quality of education, and address various challenges faced by the Indonesian education system. This has naturally sparked diverse opinions and comments from the public, particularly on the social media platform X/Twitter. This research focuses on sentiment analysis of reviews expressed on the X/Twitter social media platform. The primary goal of this study is to develop an effective sentiment analysis method by leveraging the Support Vector Machine (SVM) algorithm optimized with Particle Swarm Optimization (PSO) for feature selection. In this research, user reviews from X/Twitter were collected and analyzed to identify positive or negative sentiments within the context of each comment. The SVM algorithm was used to classify sentiments based on similarity to comments with known sentiments. Feature Selection PSO was employed to optimize the parameters within SVM to enhance sentiment analysis accuracy. The results of sentiment analysis on comments or tweets on the X/Twitter social media platform using both SVM and PSO-based SVM algorithms indicated that the PSO based SVM algorithm achieved a higher accuracy. The SVM algorithm with feature selection PSO produced accuracy 89.50%, precision 86.98%, recall 93.00%, and AUC 0.964. Meanwhile, the SVM algorithm had accuracy 87.50%, precision 85.46%, recall 90.50%, and AUC 0.956. This demonstrates that the use of feature selection PSO in the SVM algorithm is capable of improving the accuracy of the results.</t>
+  </si>
+  <si>
+    <t>Analisis Sentimen Ulasan Aplikasi Identitas Kependudukan Digital Pada Play Store Menggunakan Metode Naïve Bayes</t>
+  </si>
+  <si>
+    <t>Ahmad Komarudin; Atiqah Meutia Hilda</t>
+  </si>
+  <si>
+    <t>https://jurnal.bsi.ac.id/index.php/co-science/article/view/2955</t>
+  </si>
+  <si>
+    <t>Digital ID; Sentiment Analysis; Naive Bayes</t>
+  </si>
+  <si>
+    <t>One of the government's new innovations is the implementation of Digital Population Identity which is to bring transformation in the way people prove their own identity, making it easier, safer, and more efficient in various contexts of everyday life. It is known that on October 20, 2023 the Digital Population Identity application only received 3.3 stars from 32.7 thousand reviews, this shows that the application still has not reached the maximum level of satisfaction in serving the needs of the community. Therefore, sentiment analysis of user reviews is needed to gain deeper insight into how people respond to this application, so this research aims to obtain sentiment data from the Digital Population Identity application on the Play Store in the form of reviews from users and the results of the analysis can be used as evaluation material for application developers. Data collection is done using the scrapping method through Google Colab as many as 1000 reviews whose results will be labeled negative and positive. Then the data will be cleaned and simplified through preprocessing, and will be classified with the Naïve Bayes algorithm with 90% test data and 10% training data for each iteration. The classification results are then calculated performance with confusion matrix and obtained an accuracy value of 85,06%, precission of 80,31%, and recall of 92,89%.</t>
+  </si>
+  <si>
+    <t>Analisis Sentimen Ulasan Pelanggan Menggunakan Algoritma Naive Bayes pada Aplikasi Gojek</t>
+  </si>
+  <si>
+    <t>Sujiliani Heristian; Musriatun Napiah; Wati Erawati</t>
+  </si>
+  <si>
+    <t>https://jurnal.bsi.ac.id/index.php/co-science/article/view/7775</t>
+  </si>
+  <si>
+    <t>Gojek; Sentiment analysis; Naive Bayes</t>
+  </si>
+  <si>
+    <t>Transportation is a means that a person uses to move from one place to another. One mode of transportation that is popular among the public is online motorcycle taxis, such as Gojek. Gojek continues to innovate to meet customer needs more effectively, as well as expand the scope of its services. This research aims to identify the number of positive and negative sentiments in the user review dataset, evaluate the performance of the algorithm used, and measure the level of customer satisfaction with Gojek services. Analysis was carried out on 6,485 customer reviews, which resulted in 4,387 positive sentiments and 2,098 negative sentiments. The classification model used, namely Naive Bayes, shows an accuracy of 88.5%, precision of 88.1%, and recall of 89.0%. The results of this research indicate that the Naive Bayes method provides good performance in analyzing the sentiment of user reviews of Gojek services</t>
   </si>
 </sst>
 </file>
@@ -298,8 +553,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:U9" totalsRowShown="0">
-  <autoFilter ref="A1:U9" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:U24" totalsRowShown="0">
+  <autoFilter ref="A1:U24" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Title of Article"/>
@@ -606,7 +861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
@@ -685,10 +940,10 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -697,7 +952,7 @@
         <v>23</v>
       </c>
       <c r="H2">
-        <v>25415239</v>
+        <v>25409824</v>
       </c>
       <c r="I2" t="s">
         <v>24</v>
@@ -711,14 +966,8 @@
       <c r="L2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="P2" t="s">
         <v>28</v>
-      </c>
-      <c r="P2" t="s">
-        <v>29</v>
-      </c>
-      <c r="U2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -726,16 +975,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -744,13 +993,13 @@
         <v>23</v>
       </c>
       <c r="H3">
-        <v>25415239</v>
+        <v>25409824</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
         <v>26</v>
@@ -759,277 +1008,916 @@
         <v>27</v>
       </c>
       <c r="P3" t="s">
-        <v>35</v>
-      </c>
-      <c r="U3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4">
+        <v>2025</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4">
+        <v>25409824</v>
+      </c>
+      <c r="I4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" t="s">
+      <c r="J4" t="s">
         <v>37</v>
-      </c>
-      <c r="D4">
-        <v>2023</v>
-      </c>
-      <c r="E4">
-        <v>8</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4">
-        <v>25416448</v>
-      </c>
-      <c r="I4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" t="s">
-        <v>40</v>
       </c>
       <c r="K4" t="s">
         <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="P4" t="s">
-        <v>43</v>
-      </c>
-      <c r="U4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H5">
-        <v>25416448</v>
+        <v>25409824</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K5" t="s">
         <v>26</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P5" t="s">
-        <v>49</v>
-      </c>
-      <c r="U5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D6">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H6">
-        <v>25416448</v>
+        <v>25409824</v>
       </c>
       <c r="I6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="J6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="K6" t="s">
         <v>26</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="P6" t="s">
-        <v>55</v>
-      </c>
-      <c r="U6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D7">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H7">
-        <v>25416448</v>
+        <v>25409824</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J7" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="K7" t="s">
         <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
-      </c>
-      <c r="U7" t="s">
-        <v>44</v>
+        <v>27</v>
+      </c>
+      <c r="P7" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D8">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H8">
-        <v>25416448</v>
+        <v>25409824</v>
       </c>
       <c r="I8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="J8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="K8" t="s">
         <v>26</v>
       </c>
       <c r="L8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U8" t="s">
-        <v>44</v>
+        <v>27</v>
+      </c>
+      <c r="P8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9">
+        <v>2021</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
         <v>1</v>
       </c>
-      <c r="B9" t="s">
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9">
+        <v>25409824</v>
+      </c>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
         <v>64</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>65</v>
       </c>
-      <c r="D9">
+      <c r="D10">
+        <v>2021</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10">
+        <v>25409824</v>
+      </c>
+      <c r="I10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11">
+        <v>2017</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11">
+        <v>25415239</v>
+      </c>
+      <c r="I11" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11" t="s">
+        <v>75</v>
+      </c>
+      <c r="M11" t="s">
+        <v>76</v>
+      </c>
+      <c r="P11" t="s">
+        <v>77</v>
+      </c>
+      <c r="U11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12">
+        <v>2025</v>
+      </c>
+      <c r="E12">
+        <v>14</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12">
+        <v>25415239</v>
+      </c>
+      <c r="I12" t="s">
+        <v>81</v>
+      </c>
+      <c r="J12" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12" t="s">
+        <v>75</v>
+      </c>
+      <c r="P12" t="s">
+        <v>83</v>
+      </c>
+      <c r="U12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13">
+        <v>2023</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13">
+        <v>25416448</v>
+      </c>
+      <c r="I13" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13" t="s">
+        <v>88</v>
+      </c>
+      <c r="K13" t="s">
+        <v>74</v>
+      </c>
+      <c r="L13" t="s">
+        <v>89</v>
+      </c>
+      <c r="M13" t="s">
+        <v>90</v>
+      </c>
+      <c r="P13" t="s">
+        <v>91</v>
+      </c>
+      <c r="U13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14">
+        <v>2019</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14">
+        <v>25416448</v>
+      </c>
+      <c r="I14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J14" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" t="s">
+        <v>74</v>
+      </c>
+      <c r="L14" t="s">
+        <v>89</v>
+      </c>
+      <c r="M14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P14" t="s">
+        <v>97</v>
+      </c>
+      <c r="U14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15">
+        <v>2021</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15">
+        <v>25416448</v>
+      </c>
+      <c r="I15" t="s">
+        <v>100</v>
+      </c>
+      <c r="J15" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" t="s">
+        <v>74</v>
+      </c>
+      <c r="L15" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15" t="s">
+        <v>102</v>
+      </c>
+      <c r="P15" t="s">
+        <v>103</v>
+      </c>
+      <c r="U15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16">
+        <v>2025</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16">
+        <v>25416448</v>
+      </c>
+      <c r="I16" t="s">
+        <v>106</v>
+      </c>
+      <c r="J16" t="s">
+        <v>107</v>
+      </c>
+      <c r="K16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L16" t="s">
+        <v>89</v>
+      </c>
+      <c r="P16" t="s">
+        <v>108</v>
+      </c>
+      <c r="U16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17">
+        <v>2020</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17">
+        <v>25416448</v>
+      </c>
+      <c r="I17" t="s">
+        <v>111</v>
+      </c>
+      <c r="J17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" t="s">
+        <v>74</v>
+      </c>
+      <c r="L17" t="s">
+        <v>89</v>
+      </c>
+      <c r="P17" t="s">
+        <v>113</v>
+      </c>
+      <c r="U17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18">
         <v>2024</v>
       </c>
-      <c r="E9">
+      <c r="E18">
+        <v>5</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18">
+        <v>27220001</v>
+      </c>
+      <c r="I18" t="s">
+        <v>117</v>
+      </c>
+      <c r="J18" t="s">
+        <v>118</v>
+      </c>
+      <c r="K18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" t="s">
+        <v>119</v>
+      </c>
+      <c r="P18" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19">
+        <v>2024</v>
+      </c>
+      <c r="E19">
         <v>14</v>
       </c>
-      <c r="F9">
+      <c r="F19">
         <v>4</v>
       </c>
-      <c r="G9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9">
+      <c r="G19" t="s">
+        <v>123</v>
+      </c>
+      <c r="H19">
         <v>27222578</v>
       </c>
-      <c r="I9" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" t="s">
-        <v>68</v>
-      </c>
-      <c r="K9" t="s">
-        <v>69</v>
-      </c>
-      <c r="L9" t="s">
-        <v>70</v>
-      </c>
-      <c r="R9" t="s">
-        <v>71</v>
-      </c>
-      <c r="U9" t="s">
-        <v>72</v>
+      <c r="I19" t="s">
+        <v>124</v>
+      </c>
+      <c r="J19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K19" t="s">
+        <v>126</v>
+      </c>
+      <c r="L19" t="s">
+        <v>127</v>
+      </c>
+      <c r="P19" t="s">
+        <v>128</v>
+      </c>
+      <c r="R19" t="s">
+        <v>129</v>
+      </c>
+      <c r="U19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20">
+        <v>2026</v>
+      </c>
+      <c r="E20">
+        <v>6</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>133</v>
+      </c>
+      <c r="H20">
+        <v>27749711</v>
+      </c>
+      <c r="I20" t="s">
+        <v>134</v>
+      </c>
+      <c r="J20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K20" t="s">
+        <v>74</v>
+      </c>
+      <c r="L20" t="s">
+        <v>136</v>
+      </c>
+      <c r="P20" t="s">
+        <v>137</v>
+      </c>
+      <c r="U20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21">
+        <v>2023</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" t="s">
+        <v>133</v>
+      </c>
+      <c r="H21">
+        <v>27749711</v>
+      </c>
+      <c r="I21" t="s">
+        <v>141</v>
+      </c>
+      <c r="J21" t="s">
+        <v>142</v>
+      </c>
+      <c r="K21" t="s">
+        <v>74</v>
+      </c>
+      <c r="L21" t="s">
+        <v>136</v>
+      </c>
+      <c r="P21" t="s">
+        <v>143</v>
+      </c>
+      <c r="U21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22">
+        <v>2024</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>133</v>
+      </c>
+      <c r="H22">
+        <v>27749711</v>
+      </c>
+      <c r="I22" t="s">
+        <v>146</v>
+      </c>
+      <c r="J22" t="s">
+        <v>147</v>
+      </c>
+      <c r="K22" t="s">
+        <v>74</v>
+      </c>
+      <c r="L22" t="s">
+        <v>136</v>
+      </c>
+      <c r="P22" t="s">
+        <v>148</v>
+      </c>
+      <c r="U22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23">
+        <v>2024</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>133</v>
+      </c>
+      <c r="H23">
+        <v>27749711</v>
+      </c>
+      <c r="I23" t="s">
+        <v>151</v>
+      </c>
+      <c r="J23" t="s">
+        <v>152</v>
+      </c>
+      <c r="K23" t="s">
+        <v>74</v>
+      </c>
+      <c r="L23" t="s">
+        <v>136</v>
+      </c>
+      <c r="P23" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24">
+        <v>2025</v>
+      </c>
+      <c r="E24">
+        <v>5</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>133</v>
+      </c>
+      <c r="H24">
+        <v>27749711</v>
+      </c>
+      <c r="I24" t="s">
+        <v>156</v>
+      </c>
+      <c r="J24" t="s">
+        <v>157</v>
+      </c>
+      <c r="K24" t="s">
+        <v>74</v>
+      </c>
+      <c r="L24" t="s">
+        <v>136</v>
+      </c>
+      <c r="P24" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/myapp/data_idx_gabung.xlsx
+++ b/myapp/data_idx_gabung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SENTIMENT ANALYSIS UGI AQIS 2026\PROJECT SHINY DASHBOARD ANALISIS SENTIMEN 2026 TERBARU\myapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC585D6C-BAC4-4CFF-A38B-447984B893AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B4744F6-FB88-4393-8E7A-D9E4DE89F2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="335">
   <si>
     <t>No</t>
   </si>
@@ -416,6 +416,60 @@
     <t>Article Submission: 0.00 (USD); Authors are not required to pay an Article Submission Fee as part of the submission process to contribute to review costs.; Article Publication: 215.00 (USD). Link: https://ijece.iaescore.com/index.php/IJECE/about/submissions#authorFees</t>
   </si>
   <si>
+    <t>Systematic Literature Review: Analisa Sentimen Masyarakat terhadap Penerapan Peraturan ETLE</t>
+  </si>
+  <si>
+    <t>Syafrial Fachri Pane; Muhammad Syiarul Amrullah</t>
+  </si>
+  <si>
+    <t>Journal of Applied Computer Science and Technology (JACOST)</t>
+  </si>
+  <si>
+    <t>https://journal.isas.or.id/index.php/JACOST/article/view/493</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis; Systematic Literature Review; Machine Learning; Natural Language Processing; ETLE</t>
+  </si>
+  <si>
+    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/10014</t>
+  </si>
+  <si>
+    <t>This study examines the efforts to develop a model for analyzing public sentiment regarding applying ETLE (Electronic Traffic Law Enforcement) regulations. The method used is the systematic literature review. A systematic literature review (SLR) consists of three stages: planning, conducting, and reporting. The planning stage is the determination of the SLR procedure. This stage includes preparing topics, research questions, article search criteria &amp; inclusion and exclusion criteria. The conducting stage, namely the implementation, includes searching for articles and filtering articles. The reporting stage is the final stage of SLR. This stage includes writing the SLR results according to the article format. The explanation follows: First, hybrid is the most widely used method in developing sentiment analysis models. Apart from hybrid, several methods are used to develop sentiment analysis models, including multi-task, deep, and machine learning. Each has its advantages and disadvantages in the development of sentiment analysis models. Second, this study shows the development of a model with superior performance, namely using XGBoost as a sentiment analysis model, and the stages it goes through are preprocessing data, handling imbalanced data, and optimizing the model. Therefore, the model for analyzing public sentiment regarding the application of ETLE regulations can be an option for hybrid methods, multi-task learning, deep learning, machine learning, and the XGBoost model to obtain superior performance with preprocessing data stages, handling imbalanced data and optimization models.</t>
+  </si>
+  <si>
+    <t>Submision dan review naskah tidak dipungut biaya, namun jika naskah Anda diterima untuk diterbitkan, Anda diharuskan membayar biaya penerbitan sejumlah Rp.750.000,- karena jurnal JACOST dikelola secara independen. Link: https://journal.isas.or.id/index.php/JACOST/biaya</t>
+  </si>
+  <si>
+    <t>Membangun Model Machine Learning Untuk Meninjau Layanan Indosat Ooredoo Dari Twitter Menggunakan Naive Bayes Classifier</t>
+  </si>
+  <si>
+    <t>Febri Astiko; Achmad Khodar</t>
+  </si>
+  <si>
+    <t>https://journal.isas.or.id/index.php/JACOST/article/view/79</t>
+  </si>
+  <si>
+    <t>sentiment analysis; indosat Ooredoo; twitter; naive bayes classifier; positive negative</t>
+  </si>
+  <si>
+    <t>This study aims to design a machine learning model of sentiment analysis on Indosat Ooredoo service reviews on social media twitter using the Naive Bayes algorithm as a classifier of positive and negative labels. This sentiment analysis uses machine learning to get patterns an model that can be used again to predict new data.</t>
+  </si>
+  <si>
+    <t>Analisis Sentimen: Pengaruh Jam Kerja Terhadap Kesehatan Mental Generasi Z</t>
+  </si>
+  <si>
+    <t>Muhammad Daffa Al Fahreza; Ardytha Luthfiarta; Muhammad Rafid; Michael Indrawan</t>
+  </si>
+  <si>
+    <t>https://journal.isas.or.id/index.php/JACOST/article/view/715</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis; Gaussian Naive Bayes; Support Vector Machine; Stemming Algorithm; Mental Health; Generation Z</t>
+  </si>
+  <si>
+    <t>Mental health is a significant concern in society today, particularly for Generation Z, who are vulnerable to experiencing mental health problems that can disrupt daily productivity. The influence of working hours also contributes to the mental health of this generation. To assess public opinion on this issue, sentiment analysis is needed on social media, especially twitter. This research uses the Gaussian Naïve Bayes algorithm and Support Vector Machine with various stemming algorithms such as Nazief-Adriani, Arifin Setiono, and Sastrawi. The sentiment analysis method is used to assess positive, negative, and neutral sentiment in related tweets. The research results show that the Sastrawi stemming algorithm on the Gaussian Naïve Bayes model achieves 84% precision, 84% recall, and 84% f1-score, with 84% accuracy. Meanwhile, Support Vector Machine achieved 91% precision, 90% recall, 90% f1-score, and 91% accuracy. The Nazief-Adriani stemming algorithm on the Gaussian Naïve Bayes model has 80% precision, 80% recall, and 80% f1-score, with 80% accuracy. Meanwhile, on the Support Vector Machine, precision is 87%, recall is 85%, f1-score is 86%, and accuracy is 85%. Arifin Setiono's stemming algorithm on the Gaussian Naïve Bayes model achieved 81% precision, 81% recall, 81% f1-score, with 82% accuracy, while on Support Vector Machine, 88% precision, 86% recall, 86% f1-score, with 86% accuracy. Public opinion was recorded as 33% positive, 9% neutral, and 58% negative. This research aims to increase public awareness of the importance of mental health, especially regarding the influence of working hours, to create a healthy work environment for Generation Z and society in general, as well as improving the quality of mental health.</t>
+  </si>
+  <si>
     <t>Analyzing Public Sentiment Toward Makanan Bergizi Gratis Program Using Machine Learning</t>
   </si>
   <si>
@@ -498,6 +552,480 @@
   </si>
   <si>
     <t>Transportation is a means that a person uses to move from one place to another. One mode of transportation that is popular among the public is online motorcycle taxis, such as Gojek. Gojek continues to innovate to meet customer needs more effectively, as well as expand the scope of its services. This research aims to identify the number of positive and negative sentiments in the user review dataset, evaluate the performance of the algorithm used, and measure the level of customer satisfaction with Gojek services. Analysis was carried out on 6,485 customer reviews, which resulted in 4,387 positive sentiments and 2,098 negative sentiments. The classification model used, namely Naive Bayes, shows an accuracy of 88.5%, precision of 88.1%, and recall of 89.0%. The results of this research indicate that the Naive Bayes method provides good performance in analyzing the sentiment of user reviews of Gojek services</t>
+  </si>
+  <si>
+    <t>Analysis of Public Opinion Sentiment About Covid-19 Vaccination in Indonesia Using Naïve Bayes and Decission Tree</t>
+  </si>
+  <si>
+    <t>Ahmad Harun; Dea Putri Ananda</t>
+  </si>
+  <si>
+    <t>Malcom: Indonesian Journal of Machine Learning and Computer Science</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/63</t>
+  </si>
+  <si>
+    <t>Covid-19; Decision Tree; Facebook; NBC; Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/11292</t>
+  </si>
+  <si>
+    <t>COVID-19 is a new disease reported in Wuhan China in December 2019. Based on www.covid19.go.id, in Indonesia as of January 20, 2021 there were more than 939 thousand cases and more than 26 thousand cases which resulted in death. The rapid spread of COVID-19 and the dangers it causes, the Indonesian government is taking precautions with vaccination, the information of which has been spread across various social media, including the facebook page owned by the Ministry of Health. Facebook pages that have a comment feature on their posts have not been able to determine the amount of user sentiment about positive or negative comments automatically. Sentiment analysis is part of text mining for grouping text polarity in knowing the polarity of an opinion given is positive or negative using a certain algorithm. This study aims to provide results of public opinion about the sentiment analysis of COVID-19 vaccination using the Naïve Bayes Classifier (NBC) algorithm and the Decision Tree and to compare the accuracy of the two algorithms. The results of the research on the analysis of public opinion about the COVID-19 vaccination that have been carried out, tend to be negative responses with an accuracy value of 100.00% using the NBC algorithm and 50.39% using the Decision Tree algorithm.</t>
+  </si>
+  <si>
+    <t>MALCOM: Indonesian Journal of Machine Learning and Computer Science charges the following author fees. Article Submission: 0.00 (IDR); Article Publication: 1.000.000 (IDR) or 75 (USD); From February 3, 2026, MALCOM's APC will be 1.000,000 IDR od 75 USD; Link: https://journal.irpi.or.id/index.php/malcom/fees</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of Cash Direct Assistance Distribution for Fuel Oil Using Support Vector Machine</t>
+  </si>
+  <si>
+    <t>Rizky Rahman Salam; Muhammad Fajri Jamil; Yusril Ibrahim; Rahmaddeni Rahmaddeni; Soni Soni; Herianto Herianto</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/590</t>
+  </si>
+  <si>
+    <t>Economic Burden; Fuel; Government; Sentiment; Support Vector Machine</t>
+  </si>
+  <si>
+    <t>Fuel oil (BBM) is one of the basic needs of society. However, the high price of fuel can create an economic burden for the poor. To overcome this, the government implemented the Direct Cash Assistance (BLT) program as a form of assistance for people who experience economic imbalance. The purpose of this research is to analyze people's sentiment towards the Direct Cash Assistance (BLT) Fuel Oil (BBM) program. This research uses scraping data collection techniques, which is taking data from social media Instagram. The amount used was 356 data. The classification process used is based on the Support Vector Machine (SVM) learning model and evaluation with confusion matrix. From the calculation results, it can be seen that the sentiment classification process using the SVM method obtained an accuracy rate of 85.98%, an average precision value of 82.25%, an average recall value of 66.35%, and an average f-measure value of 73.44%. The results obtained show that negative sentiment is more than positive sentiment, with a percentage of 78.61% and 21.34% respectively. From the sentiment analysis conducted, it was found that negative sentiments were the most prevalent, indicating that people were dissatisfied with the BBM Direct cash assistance (BLT) program. In response to the dominant negative sentiment, it is necessary to implement a structured distribution and data collection strategy so that the level of community disappointment can be minimized.</t>
+  </si>
+  <si>
+    <t>Comparative Evaluation of SVM Kernels for Sentiment Classification in Fuel Price Increase Analysis</t>
+  </si>
+  <si>
+    <t>Salsabila Rabbani; Dea Safitri; Nadila Rahmadhani; Al Amin Fadillah Sani; M. Khairul Anam</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/897</t>
+  </si>
+  <si>
+    <t>Classification; Fuel Oil; Sentiment Analysis; SMOTE; Support Vector Machine</t>
+  </si>
+  <si>
+    <t>The policy of changing the price of fuel oil (BBM) by the government in September 2022 caused controversy among social media users including Twitter. To understand how the change in fuel price increase affects people's perceptions and emotions on Twitter, this study conducted sentiment analysis using the Support Vector Machine (SVM) algorithm with three different kernel types, namely linear, RBF (Radial Basis Function), and polynomial. This research aims to classify tweets as positive, negative, or neutral, and compare the performance of the three SVM kernels. This research also tries to overcome class imbalance by applying the SMOTE (Synthetic Minority Over-sampling Technique) oversampling technique to the dataset. The results showed that Twitter users predominantly gave negative reactions to the fuel price increase. In applying the SVM algorithm, the RBF kernel produces the best performance of 87% using TF-IDF word weighting. In addition, the use of TF-IDF word weighting has the best accuracy results compared to the BoW word weighting model. The application of SMOTE oversampling technique in the polynomial kernel of TF-IDF word weighting on 70:30 and 80:20 data division successfully improved the algorithm performance by 2%. The results of this study provide an in-depth insight into the public's views on fuel price policy and enable public decision-makers and industry to design more responsive and pro-people policies.</t>
+  </si>
+  <si>
+    <t>Comparison of Support Vector Machine and Naïve Bayes Algorithms for Sentiment Analysis of the Metaverse</t>
+  </si>
+  <si>
+    <t>Dea Nurmastin Novianti; Diqy Fakhrun Shiddieq; Fikri Fahru Roji; Wati Susilawati</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1061</t>
+  </si>
+  <si>
+    <t>Metaverse; Naive Bayes; Sentiment Analysis; SVM</t>
+  </si>
+  <si>
+    <t>The Metaverse has captured the world's attention due to its ability to merge the real and virtual worlds. Interest in the Metaverse has been on the rise, fueled due to the effects of the COVID-19, the development project the National Capital Integrated Coastal Development (IKN), and the growing usage of digital platforms. Discussions about the Metaverse escalated further after Facebook rebranded itself as Meta. The objective oh study is to evaluate and contrast the maximum level accuracy levels between the SVM and the Naïve Bayes in analyzing public responses to the Metaverse. This study utilizes sentiment analysis method. The use of these two algorithms adds novelty to this research. The study utilizes data collected from Twitter (x) and simulates sentiment analysis using SVM and Naïve Bayes algorithms. Derived from the study findings, is revealed that SVM algorithm achieves concerning prepecision 90.32%, precision of 0.90, and recall of 0.86, during the implementation the Naïve Bayes reaches concerning precision of 84.23%, precision of 0.87, and recall of 0.84. This research provides insights into Metaverse trends and compares the highest accuracy results between two algorithms.</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of PLN Mobile Application Review Using Naïve Bayes Classifier and K-Nearest Neighbor Algorithm</t>
+  </si>
+  <si>
+    <t>Syafrizal Syafrizal; M. Afdal; Rice Novita</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/983</t>
+  </si>
+  <si>
+    <t>Classification; K-Nearest Neighbor; Naive Bayes Classifier; PLN Mobile; Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>The real proof that PLN continues to improve its services is by launching an application, namely PLN Mobile. Many customers feel the convenience of the application. But now, some customers are encountering problems such as failing to load locations when making complaints and purchasing tokens with virtual accounts. The balance has been deducted, but the token code does not appear. This research conducts sentiment analysis of PLN Mobile application user reviews using a text mining approach. This approach can perform sentiment classification on user reviews quickly. Data was collected using scrapping techniques on the Google Play Store, and obtained 3000 data lines. The data was then labelled by an expert, resulting in 2099 positive sentiments (69.97%), 368 neutral (12.27%) and 533 negatives (17.77%). Furthermore, modelling uses the NBC and KNN algorithms with K-Fold Cross Validation as a validation technique. The results show that the NBC model is better than KNN with an accuracy of 77.69%, recall of 53.14%, precision of 59.84% and F1-Score of 54.09%. Furthermore, the analysis process is carried out using word cloud data visualization. The result is that the PLN Mobile application provides convenience to customers in using PLN services such as token purchases, complaints, and other features. However, the PLN Mobile application still has several problems often reviewed by users, one of which is when making token payments.</t>
+  </si>
+  <si>
+    <t>Comparison of Naive Bayes and SVM Algorithms in Twitter Sentiment Analysis on Electric Car Use in Indonesia</t>
+  </si>
+  <si>
+    <t>Widia Ningsih; Baginda Alfianda; Rahmaddeni Rahmaddeni; Denok Wulandari</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1253</t>
+  </si>
+  <si>
+    <t>Analisis; Electric Car; Naive Bayes; Support Vector Machine; Twitter</t>
+  </si>
+  <si>
+    <t>Sentiment analysis can classify sentiment based on the polarity of the text within a phrase and determine it as positive, negative, or neutral sentiment. This sentiment data was obtained from the social network Twitter based on Indonesian queries. The purpose of this study is to understand public opinion on specific topics communicated on Twitter in Indonesian and to support efforts to conduct market research on public opinion. The collected data goes through manual labeling, preprocessing, and modeling processes, and a classification model is created through a training process. The data collection technique was performed by searching for records using the search term “electric vehicle” on the website Kaggle.com. The algorithms used to build a classification model based on the data obtained in this study are Naive Bayes Algorithm and Support Vector Machine. The accuracy value of the classification implementation obtained by the Naive Bayes algorithm was 63.02%, and the accuracy of the support vector machine was 70.82%. We can conclude that the support vector machine algorithm has the highest accuracy value</t>
+  </si>
+  <si>
+    <t>Comparison of Sentiment Analysis Algorithms with SMOTE Oversampling and TF-IDF Implementation on Google Reviews for Public Health Centers</t>
+  </si>
+  <si>
+    <t>I Gede Bintang Arya Budaya; I Ketut Putu Suniantara</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1459</t>
+  </si>
+  <si>
+    <t>Binary Classification; Imbalanced Classes; Sentiment Classification; Supervised Learning; User Feedback</t>
+  </si>
+  <si>
+    <t>Sentiment analysis, or opinion mining, is a critical area of natural language processing that identifies sentiments in free text.  As  digital  business  services  expand  and user-generated  content  increases,  analyzing  sentiments  in  online  reviews becomes crucial for enhancing business operations and customer satisfaction. This study focuses on sentiment analysis of user reviews from Google Reviews for Public Health Centers (PHCs) in Bali, Indonesia, utilizing five machine learning models: Logistic Regression, Support Vector Machine (SVM), XGBoost, Naive Bayes, and Random Forest. These models classify sentiments into positive and negative categories using a dataset balanced with SMOTE to address class imbalance and improve accuracy. Additionally, TF-IDF (Term Frequency-Inverse Document Frequency) is employed to highlight key sentiment  indicators.  We  divided  a  total  of  1,834  reviews,  allocating  20%  for  testing  and  80%  for  training,  ensuring comprehensive evaluation under real-world conditions. Logistic Regression and Naive Bayes emerged as top performers, achieving  an  accuracy  of  0.89,  with  Logistic  Regression  demonstrating  balanced  precision  and  recall.  This  study contributes to advancing academic understanding of sentiment analysis in healthcare and provides practical insights for business administrators on leveraging online customer feedback. The findings underscore the importance of integrating SMOTE for class balance and TF-IDFfor identifying crucial sentiment markers, emphasizing the selection of appropriate machine learning techniques tailored to data characteristics and project objectives to optimize technological and business outcomes.</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of Online Services at the Engineering and Vocational Faculty of Ganesha Education University Using Naïve Bayes and LSTM Algorithms</t>
+  </si>
+  <si>
+    <t>Ni Kadek Tesya Ari Saputri; I Gede Aris Gunadi; I Made Gede Sunarya</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1336</t>
+  </si>
+  <si>
+    <t>COVID-19; LSTM; Naive Bayes; Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>One of the faculties at Ganesha Education University is the Technical and Vocational Faculty (FTK) which is implementing online services during the COVID-19 pandemic. Various comments emerged when this online service was carried out so that an analysis was needed. Students gave positive and negative opinions. To analyze student comments using the Naive Bayes method and long short-term memory (LSTM). The data used is information obtained from distributing questionnaires filled out by FTK students. Confusion matrix evaluation includes accuracy, precision, recall, and f-measure. This research aims to compare the two Naive Bayes and LSTM methods and detect words that frequently appear in FTK online services by comparing stopwords collected during questionnaire processing. Tested the accuracy of the Naïve Bayes classification method and the result was 83.69%. The classification results of the LSTM method achieved an accuracy of 53.12%. The resulting LSTM accuracy value is very low. Perhaps the main reason is that only positive comments are read when trying the LSTM method. Another cause is the dataset which can also influence. By comparing the performance of Naive Bayes and LSTM, results were obtained showing that the Naïve Bayes method was superior for analyzing FTK Undiksha student comments.</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of Alleged 2024 Election Fraud Based on Tweets Using the Naïve Bayes Classifier Algorithm</t>
+  </si>
+  <si>
+    <t>Dafa Setyo Nugroho; Isa Faqihuddin Hanif; Muhammad Adryan Hasbi; Fredianto Fredianto; Adrian Maulana Saputra; Rachmad Zildjian</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1496</t>
+  </si>
+  <si>
+    <t>Alleged Violations; Naive Bayes; Sentiment Analysis; Twitter; 2024 Election</t>
+  </si>
+  <si>
+    <t>Twitter is a social media that is the public's main source of information and opinion on various topics, including tragedies and current events. With its many users, Twitter provides researchers with valuable insights in analyzing public sentiment. However, the implementation of the elections in 2024 this time is colored by various issues and many people think there have been violations in the process of holding the 2024 elections. With various public opinions on this matter, we are trying to create an article that includes sentiment analysis. public. Sentiment analysis using Twitter data has become a popular approach, especially using the Naïve Bayes classification algorithm, extracting sentiment from text which has proven effective in conducting sentiment analysis. This research aims to analyze public sentiment regarding alleged violations of the 2024 election using Twitter data. The aim is to gain deeper insight into public opinion regarding alleged violations that occurred in holding elections in Indonesia</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of Using TikTok as a Learning Media Using the Naïve Bayes Classifiers Algorithm</t>
+  </si>
+  <si>
+    <t>Elsa Apriani; Falah Oktavianalisti; La Denna Hasri Monasari; Indah Winarni; Isa Faqihuddin Hanif</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1482</t>
+  </si>
+  <si>
+    <t>Learning Media; Naive Bayes Classifier; Sentiment Analysis; TikTok</t>
+  </si>
+  <si>
+    <t>Social media platforms such as TikTok have become popular among internet users, especially among the younger generation. On the other hand, social media also has the potential to be an effective learning medium. This study aims to analyze user sentiment regarding the use of TikTok as a learning medium by using the Naïve Bayes algorithm to analyze the sentiment data. A total of 176 data points were collected through a questionnaire distributed via Google Form. The obtained data were then analyzed using the Naïve Bayes Classifiers algorithm to categorize sentiments into positive, negative, and neutral. The analysis results showed that the model accuracy was 52.27%, with a precision value of 19.60% and a recall value of 50.83%. Although the accuracy and precision obtained are relatively low, these results provide an initial overview of users' perceptions of TikTok as a learning tool. This research is expected to provide further insights for developers of social media-based learning applications and help improve the quality of educational content on TikTok</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of the Indonesian Smart College Card Program on Social Media X Using the Naive Bayes Algorithm</t>
+  </si>
+  <si>
+    <t>Diky Pramudita; Yuma Akbar; Tri Wahyudi</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1565</t>
+  </si>
+  <si>
+    <t>CRISP-DM; Naive Bayes; Sentiment Analysis; Smart Indonesia Card</t>
+  </si>
+  <si>
+    <t>This study shows that the public has various responses to the Indonesia Smart Card Program for College (KIP-K) which can be categorized into positive and negative sentiments. The problem studied is how the public responds to the KIP-K program expressed through social media X. This study uses a sentiment method with the Naive Bayes algorithm and the CRISP-DM approach to ensure a systematic and structured analysis process. The data collected were 1,516 tweets containing the keyword "KIP-K" through data crawling techniques using API X. The results showed that the Naive Bayes algorithm was effective with an accuracy of 84.99%, a positive sentiment precision of 83.54%, and a negative sentiment precision of 87.25%. The solution offered is the use of machine learning techniques to automatically categorize sentiment from large and unstructured text data. The benefits of this study are to provide insight to the government and stakeholders about public perceptions of the KIP-K program, which can be used as a basis for evaluating and improving the program in the future. In conclusion, the Naive Bayes algorithm can classify sentiment well using data from tweets about KIP-K, with results showing a dominance of negative sentiment. This research also contributes to the development of machine learning-based sentiment analysis methods in the field of education.</t>
+  </si>
+  <si>
+    <t>Implementation of Support Vector Machine Algorithm for Sentiment Analysis of Online Loan Application Review Data on Google Play Store</t>
+  </si>
+  <si>
+    <t>Muhammad Iqbal; M Afdal; Rice Novita</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1435</t>
+  </si>
+  <si>
+    <t>Classification; Online Lending Application; Sentiment Analysis; Support Vector Machine; User Review</t>
+  </si>
+  <si>
+    <t>Online lending (pinjol) have sparked significant controversy due to their easy access and widespread advertising on social media. Pinjol also employs distressing collection methods, high-interest rates, and short repayment periods, especially for illegal loans. Based on these issues, this study conducts a sentiment analysis on five pinjol applications: Kredivo, Easycash, Rupiah Cepat, Kredit Pintar, and Ada Pundi. Application review data was collected from Google Play Store using scraping techniques. Sentiment labeling was then performed automatically using the Indonesian sentiment dictionary (Inset). The labeling results indicate that all pinjol applications predominantly have negative sentiments. Kredivo has the highest number of positive sentiments (46%), while Easycash has the most negative sentiments (65%). The labeled data was then used for classification modeling with the SVM algorithm. Evaluation results show that the SVM algorithm performs quite well with an average accuracy of 72%, precision of 76%, and recall of 85%. However, specifically, SVM excels in classifying sentiments for the Kredit Pintar application with an accuracy of 83%. Visualization analysis using word cloud was also conducted to understand the context of user reviews of the pinjol applications. Observations show that users almost always discuss loan limits in every sentiment across all five applications</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of Childfree Campaign on X Social Media Using NBC and SVM Algorithms</t>
+  </si>
+  <si>
+    <t>Moh Azlan Shah Putra; Inggih Permana; M. Afdal</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1356</t>
+  </si>
+  <si>
+    <t>Childfree; NBC; Sentiment Analysis; Social Media X; SVM</t>
+  </si>
+  <si>
+    <t>Children are one of the common entities in forming a family, but in recent years there has been discussion about childfree. With so many pro-con debates about childfree, it is necessary to analyze sentiment related to this issue. This research aims to analyze public sentiment regarding the childfree movement on social media X using the Naïve Bayes Classifier (NBC) and Support Vector Machine (SVM) algorithms. Sentiment is divided into 3 classes: positive, negative, and neutral. This research collects data by crawling data on social media X with the keyword childfree. The data obtained is raw text data so that a pre-process stage is needed. The pre-process stage carried out is tokenizing, case folding, stopword filter, stemming, TF-IDF, and data balancing. Based on simulation, the performance of the NBC algorithm is: accuracy = 56.36%, precision = 56.41%, and recall = 56.35%, while the performance of the SVM algorithm is: 76.12% accuracy, 76.36% precision, and 76.13% recall. So it can be concluded that SVM has better performance than NBC in sentiment analysis in this study. In this study, it was found that the majority of people on social media X are still against the childfree movement, but many people are more concerned about who is doing and how to communicate their opinions about childfree.</t>
+  </si>
+  <si>
+    <t>Sentiment Analyst of Cyber Bullying in X Using Naïve Bayes Algorithm</t>
+  </si>
+  <si>
+    <t>Ibnu Soffi Arfan; Sifa Fauziah; Ismasari Nawangsih</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1550</t>
+  </si>
+  <si>
+    <t>Cyberbullying; Comments; Naive Bayes Classifier; Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>X is one of the most popular social media in the world, users can express their thoughts to the public and quickly get information and responses from various points of view. Apart from the many positive sides of x, it certainly doesn't escape its negative sides, one of which is Cyberbullying on social media. Cyberbullying itself is a criminal act and the perpetrators can be prosecuted in accordance with applicable laws. Therefore, sentiment analysis research on Cyberbullying on social media x to classify tweets and comments that have negative and positive content using the method and Naïve Bayes classifier. The input data for this analysis is in the form of tweets obtained from open data for analysis to look for potential Cyberbullying acts. The output in this research is a classification of Cyberbullying sentiments that have gone through preprocessing. From the test results, the accuracy using the Naïve Bayes method was 86%, producing evidence for the Cyberbullying topic, so that the algorithm can be applied for sentiment analysis classification on other data</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of The Performance of Medan Mayor Program on Social Media X Using Support Vector Machine</t>
+  </si>
+  <si>
+    <t>Desliana Sari; Rakhmat Kurniawan</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1685</t>
+  </si>
+  <si>
+    <t>Performance; Python; Sentiment Analysis; Social Media X; Support Vector Machine</t>
+  </si>
+  <si>
+    <t>Leadership is the process and art of creating interactions that influence followers to achieve predetermined goals. Leadership is important to create order and compatibility between leaders and followers. This research raises the performance of the Mayor of Medan, Mr. Muhammad Bobby Afif Nasution, S.E., M.M.. There are 5 priority programs of the Mayor of Medan, namely Health, Infrastructure Handling, Flood Handling, Cleanliness, and Revamping Heritage Areas as well as Empowering MSMEs. The application of the Support Vector Machine (SVM) technique aims to find the most optimal separation function among the various functions available to distinguish two types of objects. Sentiment analysis or opinion mining is an automated process for understanding, extracting, and processing textual data to obtain information about the sentiment contained in opinion sentences. The results of this study show that SVM is able to achieve a very good level of accuracy in processing sentiment data, so that it can help students and writers in analyzing public views on this application. Sentiment analysis of data in application X regarding the performance of the Medan Mayor's program can be done using the Support Vector Machine method with accuracy 81%, precission 84%, recall 90% and f1-score 87%</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis on Sirekap App Reviews on Google Play Using Naive Bayes Algorithm</t>
+  </si>
+  <si>
+    <t>Muhammad Rizky Hanafi; Rakhmat Kurniawan R</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1693</t>
+  </si>
+  <si>
+    <t>Application Review; Classification; Naive Bayes; Sentiment Analysis; SIREKAP</t>
+  </si>
+  <si>
+    <t>Alongside the advancement and use of technological developments. SIREKAP is an auxiliary application that the KPU developed and uses in the tiered manual recapitulation process. As per the decision number 66 of the general election commission in 2024, the electronic recapitulation information system, or SIREKAP, is an IT-based application tool used to publish vote count results, make the process of recapitulating vote count results easier, and help with the implementation of recapitulating election vote count results. Using scraping methods, SIREKAP gets information from Google Play about app reviews. The researchers then recognized the sentiment by hand. The labeling results show that 93.3% of SIREKAP applications have bad feelings and only 6.7% have good feelings. The labeled data are then used with the Naive Bayes method to model classification. Based on the results of the test, the Naive Bayes algorithm does pretty well overall, with 90% accuracy, 98% precision, and 81% recall. Word cloud visualization analysis is another way to look at the background of SIREKAP app user reviews</t>
+  </si>
+  <si>
+    <t>Public Sentiment Analysis of the Public Housing Savings Program Using the IndoBERT Lite Model on YouTube Comments</t>
+  </si>
+  <si>
+    <t>Mutiara Puspita Firdaus; Dedi Trisnawarman</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1744</t>
+  </si>
+  <si>
+    <t>IndoBERT Lite Large; Sentiment Analysis; Social Media; TAPERA</t>
+  </si>
+  <si>
+    <t>In the digital era, social media has become the primary platform for the public to express opinions on public policies, including Public Housing Savings (TAPERA), a government program aimed at providing housing access for low-income communities. This study analyzes public sentiment toward TAPERA using the IndoBERT Lite Large model, optimized for handling large datasets with efficient computational resources. Out of 14,618 YouTube comments collected, 13,766 comments were processed after the preprocessing stage. Sentiment labeling results revealed a dominance of negative sentiment with 9,571 comments, reflecting concerns about transparency, implementation, and program communication. Positive sentiment reached 2,485 comments, indicating limited appreciation for the program, while neutral sentiment totaled 1,710 comments, suggesting a need for clearer information. Visualization using bar charts and word clouds highlighted sentiment patterns and frequently occurring keywords. Based on evaluation using a confusion matrix, the model achieved an accuracy of 78%. While effective in handling large-scale data, this study has limitations in performing a more in-depth evaluation of the model's performance. Future research is recommended to expand the analysis with data from various social media platforms to enhance overall sentiment analysis.</t>
+  </si>
+  <si>
+    <t>Public Sentiment Analysis Towards Mayor Teddy Indra Wijaya with Logistic Regression Approach</t>
+  </si>
+  <si>
+    <t>Antonius Steven Dimas Prasetya Sinaga; Adam Sekti Aji</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1752</t>
+  </si>
+  <si>
+    <t>Logistic Regression; Major Teddy; Sentiment Analysis; Social Media; Twitter</t>
+  </si>
+  <si>
+    <t>This study aims to analyze public sentiment toward Mayor Teddy Indra Wijaya, an aide to Prabowo Subianto, using the Logistic Regression algorithm. Sentiment analysis is essential as public figures like Mayor Teddy, who are closely associated with prominent political leaders, significantly shape public perceptions. Understanding these sentiments is crucial to identifying positive and negative public responses, which serve as indicators of public perception regarding Prabowo Subianto's political image. This research utilizes data from the Twitter social media platform, collected through web crawling from January 2024 until the time of this report. The primary objective of this study is to explore the effectiveness of the Logistic Regression algorithm in mapping public sentiment based on complex and diverse textual data. The research process includes data collection, preprocessing, labeling, model training, and performance evaluation using metrics such as accuracy, precision, recall, and F1 score. The findings reveal that the Logistic Regression model achieved an accuracy of 73.68%, a precision of 75%, a recall of 71%, and an F1 score of 0.73. These results demonstrate the model's considerable effectiveness in predicting public sentiment. This study contributes to the development of sentiment analysis methodologies in socio-political contexts and provides strategic insights for managing public communication and reputation in the digital era</t>
+  </si>
+  <si>
+    <t>Telkom Stock Price Prediction Using Prophet: Analysis of the Effect of Public Sentiment on the Presence of Starlink</t>
+  </si>
+  <si>
+    <t>Hendra Taofiqurrohman; Wufron Wufron; Fikri Fahru Roji</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1796</t>
+  </si>
+  <si>
+    <t>Prophet; Sentiment Analysis; Stock Price; Starlink; Telkom</t>
+  </si>
+  <si>
+    <t>Stock price fluctuations pose a significant challenge for investors and companies as they are influenced by various factors, including public sentiment on social media. Most of the traditional prediction models rely solely on historical data and thus are less able to capture external dynamics that affect stock prices. This study aims to predict the share price of PT Telkom Indonesia Tbk (TLKM) by integrating public sentiment related to the presence of Starlink as an external variable at the Prophet model. Sentiment data is obtained from Twitter with the Valence Aware Dictionary and sEntiment Reasoner VADER algorithm, while stock price data is taken from Yahoo Finance for the period May to October 2024. The results showed that the integration of public sentiment improved prediction accuracy, with a Mean Absolute Percentage Error (MAPE) value of 2.927%, Mean Squared Error (MSE) of 12102.43, and Root Mean Square Error (RMSE) of 110.01. Positive sentiment, such as on October 27, 2024 with a compound score of 0.5106, resulted in a prediction of 3030.75 compared to the actual price of 2910.0. Conversely, negative sentiment on September 20, 2024 with a compound score of -0.3613 lowered the prediction to 3137.48 compared to the actual price of 3150.0. This research highlights the impact of public opinion on stock prices and recommends expanding data sources, integrating external variables, and employing deep learning methods for more accurate future predictions.</t>
+  </si>
+  <si>
+    <t>Utilization of Machine Learning in Analyzing Sentiment Towards the TAPERA Program on Digital X Platform</t>
+  </si>
+  <si>
+    <t>Aziz Musthafa; Triana Harmini; Abid Rafiq; Nurhana Marantika</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1801</t>
+  </si>
+  <si>
+    <t>Machine Learning; Random Forest; Platform Digital; Support Vector Machine; TAPERA</t>
+  </si>
+  <si>
+    <t>Tabungan Perumahan Rakyat (TAPERA) is an Indonesian government program aimed at addressing housing issues for low- and middle-income communities but has received mixed responses due to policy changes. This study analyzes social media user sentiment on Platform X regarding the TAPERA policy to determine whether the dominant sentiment is positive, negative, or neutral. Sentiment analysis was conducted using the Crisp-DM method with Machine Learning algorithms, namely Support Vector Machine (SVM) and Random Forest. A total of 2,936 comments were collected from the Digital X Platform, with the labeling process validated by Communication Science experts to ensure accuracy. Evaluation results using the confusion matrix show that the SVM model outperforms with an accuracy of 88%, compared to 86% for Random Forest. The classification results indicate that the majority of public responses are negative, with 1,874 comments (63.9%). This dominance of negative sentiment reflects public dissatisfaction with the TAPERA program overall. Meanwhile, positive sentiment accounts for only 527 comments (18%), indicating limited appreciation, while neutral sentiment comprises 534 comments (18.1%), highlighting the need for further public awareness efforts. This study is expected to serve as a foundation for recommendations to improve TAPERA management, particularly in terms of service, transparency, and communication.</t>
+  </si>
+  <si>
+    <t>Application of the Naive Bayes Algorithm with TF-IDF and Cross Validation Techniques for Sentiment Analysis Towards Starlink</t>
+  </si>
+  <si>
+    <t>Suci Khoerunnisa; Diqy Fakhrun Shiddieq; Dwi Nurhayati</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1852</t>
+  </si>
+  <si>
+    <t>Cross Validation; Naive Bayes; Sentiment Analysis; Starlink; TF-IDF</t>
+  </si>
+  <si>
+    <t>Starlink, a satellite internet service from SpaceX, will begin operations in Indonesia in 2024 to address the digital divide in remote areas. However, its presence poses challenges such as high prices, potential impact on local providers, and regulatory issues. This research analyzes public sentiment towards Starlink using Naïve Bayes algorithm combined with TF-IDF and Cross Validation techniques which are still rarely applied in similar studies in Indonesia. The data used are Indonesian tweets from users of platform X during May-November 2024. The analysis results show that the Naïve Bayes model has optimal performance in detecting positive sentiment compared to negative or neutral, as measured using confusion matrix. The main findings showed that Naïve Bayes 49.38% of tweets had positive sentiment, 32.94% were neutral, and 17.68% were negative. The positive sentiment was dominated by appreciation of the speed and stability of the service, while the negative sentiment criticized the high price and its impact on local providers. While the model performed well on positive sentiments, the classification accuracy of negative and neutral sentiments still needs to be improved. The results of this study provide strategic insights for Starlink's business development as well as a basis for consideration for the government regarding satellite-based internet services in Indonesia</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of Coretax: A Comparison of Manual, Transformers-Based, and Lexicon-Based Data Labeling on IndoBERT Performance</t>
+  </si>
+  <si>
+    <t>Agnia Suci Rizkia; Wufron Wufron; Fikri Fahru Roji</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2151</t>
+  </si>
+  <si>
+    <t>Coretax; Data Labeling; Indobert; Sentiment Analysis; Transformers</t>
+  </si>
+  <si>
+    <t>Sentiment analysis of public opinion on social media presents significant challenges due to informal language and large data volume. This study aims to evaluate the impact of five labeling approaches manual, IndoBERT , IndoBERT weet, RoBERTa , and InSet Lexicon on the performance of the Indonesian Bidirectional Encoder Representations from Transformers (IndoBERT) model in classifying sentiments related to the Coretax issue. A total of 8.035 tweets were collected, processed, and labeled using each method. The labeled datasets were then used to retrain the IndoBERT model and evaluated using accuracy, F1-Score, confusion matrix, and Receiver Operating Characteristic-Area Under the Curve (ROC-AUC) curve. Results show that Indonesian Bidirectional Encoder Representations from Transformers for Tweet (IndoBERTweet) achieved the highest metric performance F1-Score (0.9802) but suffered from a strong dominance of the neutral class, indicating a potential model bias towards that class or significant data imbalance. Manual labeling produced a more balanced class distribution despite lower performance F1-Score (0.8684), while Robustly Optimized BERT Pretraining Approach (RoBERTa) demonstrated the best balance between metric performance and label distribution. In contrast, InSet Lexicon and IndoBERT tended to overpredict specific sentiment classes. The study concludes that labeling effectiveness should not be assessed solely by metric scores, but also by the fairness and balance of class distribution to produce reliable and generalizable models.</t>
+  </si>
+  <si>
+    <t>Comparison of Naïve Bayes and Support Vector Machine in Sentiment Analysis of Confiscation of Corrupt Assets on Twitter</t>
+  </si>
+  <si>
+    <t>Ananda sholekhah; Muntahanah Muntahanah</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2068</t>
+  </si>
+  <si>
+    <t>Asset Forfeiture; Corruptors; Naive Bayes; Sentiment Analysis; Support Vector Machine</t>
+  </si>
+  <si>
+    <t>Sentiment analysis is one approach used to understand public perception of social issues and government policies through textual data. This study examines Indonesian public opinion toward President Prabowo Subianto’s statement regarding the confiscation of corruptors’ assets, which questioned, "Is it fair for the children to suffer?”. The dataset was collected from Twitter, comprising 1,561 tweets gathered between April 9 and April 25, 2025, using relevant keywords. The analysis involved preprocessing, TF-IDF vectorization, and classification using Naïve Bayes and Support Vector Machine (SVM) algorithms. Model performance was evaluated using a confusion matrix and four evaluation metrics: accuracy, precision, recall, and F1-score. The results indicate that SVM outperformed Naïve Bayes, achieving an accuracy of 70.51% and an F1-score of 0.69, while Naïve Bayes recorded 66.34% accuracy and 0.66 F1-score. Most of the sentiments were classified as positive, reflecting majority public support for the asset confiscation policy despite its impact on the perpetrators’ families. This research demonstrates the effectiveness of machine learning-based classification in mapping public opinion on controversial policy issues through social media platforms.</t>
+  </si>
+  <si>
+    <t>Comparison of Deep Learning Algorithm in Sentiment Analysis Ecotourism in Bogor</t>
+  </si>
+  <si>
+    <t>Peni Agustini; Muhammad Iqbal; Vicha Amalia Akbar; Robert Kurniawan</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2191</t>
+  </si>
+  <si>
+    <t>Bogor; Deep Learning; Ecotourism; Scraping; Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>Bogor has a leading ecotourism destination in Indonesia, offering pristine nature and easy access from Jakarta. However, the increasing number of tourists poses challenges to environmental management, such as waste management and pressure on natural resources. Social media, particularly Google Maps, plays a crucial role in promoting tourism and understanding tourist behavior through its review features. This study aims to conduct sentiment analysis on ecotourism reviews in Bogor collected from Google Maps using neural network-based deep learning methods, namely Convolutional Neural Network (CNN), Recurrent Neural Network (RNN), and Long Short-Term Memory (LSTM). The performance of these three models is compared to determine the best method for classifying visitor sentiment. The results of this study indicate that the CNN model has the highest accuracy of 72 percent, outperforming the RNN and LSTM models. The CNN model can be used as a primary reference in applying sentiment analysis to similar topics.</t>
+  </si>
+  <si>
+    <t>Sentiment Classification Using Multilayer Perceptron Algorithm with TF-IDF Features</t>
+  </si>
+  <si>
+    <t>Abdurrahman Arasy; Surya Agustian; Lestari Handayani; Iwan Iskandar</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2052</t>
+  </si>
+  <si>
+    <t>Classification; Multi-Layer Perceptron; Sentiment Analysis; Term Frequency-Inverse Document Frequency</t>
+  </si>
+  <si>
+    <t>Social media, particularly Twitter (X), has become the main platform for discussions on politics and government policy. The term used for messages sent on Twitter is a "tweet", which consists of a message with a maximum of 280 characters. Although Tweets are often just text, they can also include hyperlinks, videos, and other types of media that can be used to gauge public opinion. This study aims to classify public sentiment regarding the appointment of Kaesang Pangarep as Chairman of the Indonesian Solidarity Party (PSI) using the Multi-Layer Perceptron (MLP) Classifier method with the Term Frequency-Inverse Document Frequency (TF-IDF) approach, utilizing the Python programming language. The data used consists of 300 Tweets, with 100 Tweets per class or option for optimal results. The three categories are positive, neutral, and negative. Based on the research conducted, the best method achieved an F1-score of 0.6767 and an accuracy of 0.6667. These results indicate that the combination of the MLP Classifier and TF-IDF can overcome the limitations of the dataset to a certain extent compared to the baseline method. This study also provides insights into sentiment classification optimization under limited data conditions, which can be applied to other topics with similar issues.</t>
+  </si>
+  <si>
+    <t>Machine Learning-Based Sentiment Analysis of Public Opinion on Palm Oil Plantation Expansion in Papua</t>
+  </si>
+  <si>
+    <t>Ester Ayuk Pusvita; Deni Stefanus Paboy Ranggup; Usman Arfan</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2279</t>
+  </si>
+  <si>
+    <t>Machine Learning; Multilingual Sentiment; Papua; Public Emotion; Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>The expansion of palm oil plantations in Papua has generated diverse public responses on social media, particularly on the X (Twitter) platform. This study aims to analyze public sentiment and emotions toward the issue using a machine learning approach through the Orange Data Mining application. A total of 1,355 tweets were collected using Twitter API v2 and Google Colab integrated with the snscrape library to overcome data retrieval limitations. The analysis employed the Multilingual Sentiment model for sentiment polarity classification (positive, negative, neutral) and the Ekman Emotion model for identifying six basic emotions. The results show that neutral sentiment dominates (39.78%), followed by negative (32.16%) and positive (28.05%) sentiments. However, neutral sentiment is not always informative, as it may arise from linguistic ambiguity or model limitations in understanding the local context of the Indonesian language. The emotion Joy was found to be the most dominant, but also appeared in negative sentiment categories, indicating expressions of sarcasm and irony toward the palm oil issue. This reflects the limitations of automated models in detecting implicit meanings and satirical language styles. The study concludes that while the Multilingual Sentiment model effectively identifies general patterns of public opinion, contextual adaptation is required to enhance sensitivity to cultural and semantic nuances in the Indonesian language.</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of Papuan Public Perceptions Toward the Free Nutritional Meal Program in Indonesia</t>
+  </si>
+  <si>
+    <t>Usman Arfan; Evradus Badii</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2087</t>
+  </si>
+  <si>
+    <t>Free Nutritional Meal Program; Public Perception; Sentiment Analysis; Social Media X (Twitter); Text mining</t>
+  </si>
+  <si>
+    <t>This study aims to explore Papuan society's perceptions of Indonesia’s Free Nutritional Meal Program using a sentiment analysis approach based on text mining. Data were collected from the social media platform X (Twitter) between February 24 and 28, 2025. A total of 712 tweets were analyzed using the Orange software to classify public sentiment into three categories: positive, neutral, and negative. The results indicate that public perception is predominantly positive, with 70.08% of tweets expressing support for the program, 21.63% showing neutral sentiment, and 8.29% reflecting negative sentiment. Emotion mapping based on Ekman’s model revealed the dominance of Surprise and Joy, representing enthusiasm and optimism toward the policy. Negative emotions such as Anger and Sadness appeared in very small proportions, suggesting a generally favorable reception among social media users. These findings indicate that the Free Nutritional Meal Program is widely perceived as a constructive government initiative, although some concerns remain regarding its implementation effectiveness. The study highlights the importance of utilizing social media as a real-time tool for monitoring public perception and recommends integrating sentiment analysis into data-driven evaluations of social policy implementation</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of Shopee Product Reviews on the Instagram Application Using the K-Nearest Neighbors Algorithm</t>
+  </si>
+  <si>
+    <t>Sri Lestari; Syafira Febrianti</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/1595</t>
+  </si>
+  <si>
+    <t>CRISP-DM; K-Nearest Neighbors; Sentiment Analysis; Shoppe Product</t>
+  </si>
+  <si>
+    <t>This study examines various consumer responses to products sold on Shopee and promoted through Instagram, categorized into positive and negative sentiments. The main issue addressed is how the public perceives these products based on reviews posted on Instagram. The research employs sentiment analysis using the K-Nearest Neighbors (K-NN) algorithm and the CRISP-DM approach to ensure a systematic and structured analysis process. The dataset consists of a collection of reviews gathered through crawling techniques using automated data retrieval. The results indicate that the K-NN algorithm can classify sentiments with an accuracy of 82.80%, a positive sentiment precision of 83.54%, and a negative sentiment precision of 23.08%. These findings suggest that the majority of consumer reviews are positive, reflecting satisfaction with product quality, price, and service, although some negative reviews highlight certain shortcomings. The proposed solution in this study is the application of machine learning techniques to automate the sentiment classification process for large and unstructured review datasets. This research is expected to provide valuable insights for businesses and e-commerce platform managers to better understand consumer perceptions and use them as a basis for decision-making in marketing strategies and service quality improvements. In conclusion, the K-NN algorithm is effective for sentiment analysis of Shopee product reviews on Instagram, with results indicating a predominance of positive sentiment</t>
+  </si>
+  <si>
+    <t>Public Sentiment Analysis on Platform X Following the Mixed Fuel Scandal Using the Naïve Bayes Algorithm</t>
+  </si>
+  <si>
+    <t>Achmad Thaufik Chidayat; Diqy Fakhrun Shiddieq; Dwi Nurhayati</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2220</t>
+  </si>
+  <si>
+    <t>BBM Oplosan; Naive Bayes; TF-IDF; VADER; X/ Twitter</t>
+  </si>
+  <si>
+    <t>The adulterated fuel scandal that emerged in early 2025 triggered a wave of reactions from the public voiced through the X platform. This study aims to evaluate public sentiment regarding the case using the Naïve Bayes algorithm as an analysis method. The analysis process was carried out by scraping 2,351 relevant tweets, followed by text preprocessing. Sentiment labels were determined automatically using the VADER method, while feature representation was performed using the TF-IDF technique to improve classification quality. Next, the data was divided into training data and testing data with a ratio of 80:20, then classified using the Multinomial Naïve Bayes algorithm. The classification results showed that the algorithm was able to identify negative sentiments with the highest recall of 75%, although the overall accuracy only reached 57%. These findings indicate that this approach is quite reliable in capturing critical public opinion, but still needs development to accurately recognize positive and neutral sentiments. Further research is recommended to compare the Naïve Bayes algorithm with other models such as SVM or Random Forest to improve classification accuracy</t>
+  </si>
+  <si>
+    <t>Topic Modeling and Sentiment Analysis on Trans Jatim Application User Reviews</t>
+  </si>
+  <si>
+    <t>Maria Ulfa Yanuar; Wahyu Wibowo</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2410</t>
+  </si>
+  <si>
+    <t>IndoBERT; Public Transportation; Sentiment Analysis; Topic Modeling; Trans Jatim</t>
+  </si>
+  <si>
+    <t>Public transportation plays an important role in providing public mobility, reducing traffic congestion, and minimizing environmental impacts caused by private vehicles. To maintain service effectiveness, the Government of East Java Province has introduced the Trans Jatim Ajaib application as a digital platform that provides real-time information on schedules, routes, and bus tracking. The success of this application is not only determined by its technological features but also the user experience and perception as seen in digital platform reviews. This study aims to model user review topics in the Trans Jatim application using Latent Dirichlet Allocation (LDA) and to analyze sentiment using the IndoBERT model. The analysis results show that LDA successfully identified 5 main topics with the greatest focus on convenience and route scheduling aspects. Sentiment analysis using the IndoBERT model achieved an accuracy of 88.2%, indicating reliable performance in classifying user sentiments. Overall, most user reviews express positive sentiments, particularly regarding application information and route features, while priority improvements are required in the payment feature to enhance service quality</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of Jamsostek Mobile Application Reviews on Google Play Store Using Support Vector Machine and Naive Bayes Algorithms</t>
+  </si>
+  <si>
+    <t>Tria Setyani; Kevinda Sari; Helma Nopijani Heidy; Ryan Randy Suryono</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2526</t>
+  </si>
+  <si>
+    <t>Google Play Store; Jamsostek Mobile; Naive Bayes; Sentiment Analysis; Support Vector Machine</t>
+  </si>
+  <si>
+    <t>This study aims to analyze user sentiment toward the Jamsostek Mobile (JMO) application using Support Vector Machine (SVM) and Naive Bayes algorithms, based on reviews collected from the Google Play Store. A total of 6,000 user reviews were collected via web scraping. The research stages include text preprocessing (cleaning, case folding, normalization, tokenization, stopword removal, and stemming), feature weighting using Term Frequency–Inverse Document Frequency (TF-IDF), data labeling using a lexicon-based approach, and sentiment classification into three classes: positive, negative, and neutral. Model performance was evaluated using a confusion matrix and metrics such as accuracy, precision, recall, and F1-score. The results show that the SVM algorithm achieved superior performance with an accuracy of 88.9%, while Naive Bayes achieved 64.1%. SVM also demonstrated more consistent F1-score values across all sentiment classes. Therefore, SVM has been shown to be a more effective and reliable algorithm for sentiment classification of JMO application reviews.</t>
   </si>
 </sst>
 </file>
@@ -553,8 +1081,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:U24" totalsRowShown="0">
-  <autoFilter ref="A1:U24" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:U59" totalsRowShown="0">
+  <autoFilter ref="A1:U59" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Title of Article"/>
@@ -861,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
@@ -1717,10 +2245,10 @@
         <v>132</v>
       </c>
       <c r="D20">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1729,7 +2257,7 @@
         <v>133</v>
       </c>
       <c r="H20">
-        <v>27749711</v>
+        <v>27231453</v>
       </c>
       <c r="I20" t="s">
         <v>134</v>
@@ -1761,10 +2289,10 @@
         <v>140</v>
       </c>
       <c r="D21">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21">
         <v>2</v>
@@ -1773,7 +2301,7 @@
         <v>133</v>
       </c>
       <c r="H21">
-        <v>27749711</v>
+        <v>27231453</v>
       </c>
       <c r="I21" t="s">
         <v>141</v>
@@ -1808,7 +2336,7 @@
         <v>2024</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1817,7 +2345,7 @@
         <v>133</v>
       </c>
       <c r="H22">
-        <v>27749711</v>
+        <v>27231453</v>
       </c>
       <c r="I22" t="s">
         <v>146</v>
@@ -1840,7 +2368,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B23" t="s">
         <v>149</v>
@@ -1849,75 +2377,1615 @@
         <v>150</v>
       </c>
       <c r="D23">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="H23">
         <v>27749711</v>
       </c>
       <c r="I23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K23" t="s">
         <v>74</v>
       </c>
       <c r="L23" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="P23" t="s">
-        <v>153</v>
+        <v>155</v>
+      </c>
+      <c r="U23" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C24" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D24">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="H24">
         <v>27749711</v>
       </c>
       <c r="I24" t="s">
+        <v>159</v>
+      </c>
+      <c r="J24" t="s">
+        <v>160</v>
+      </c>
+      <c r="K24" t="s">
+        <v>74</v>
+      </c>
+      <c r="L24" t="s">
+        <v>154</v>
+      </c>
+      <c r="P24" t="s">
+        <v>161</v>
+      </c>
+      <c r="U24" t="s">
         <v>156</v>
       </c>
-      <c r="J24" t="s">
-        <v>157</v>
-      </c>
-      <c r="K24" t="s">
-        <v>74</v>
-      </c>
-      <c r="L24" t="s">
-        <v>136</v>
-      </c>
-      <c r="P24" t="s">
-        <v>158</v>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25">
+        <v>2024</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>151</v>
+      </c>
+      <c r="H25">
+        <v>27749711</v>
+      </c>
+      <c r="I25" t="s">
+        <v>164</v>
+      </c>
+      <c r="J25" t="s">
+        <v>165</v>
+      </c>
+      <c r="K25" t="s">
+        <v>74</v>
+      </c>
+      <c r="L25" t="s">
+        <v>154</v>
+      </c>
+      <c r="P25" t="s">
+        <v>166</v>
+      </c>
+      <c r="U25" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" t="s">
+        <v>168</v>
+      </c>
+      <c r="D26">
+        <v>2024</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>151</v>
+      </c>
+      <c r="H26">
+        <v>27749711</v>
+      </c>
+      <c r="I26" t="s">
+        <v>169</v>
+      </c>
+      <c r="J26" t="s">
+        <v>170</v>
+      </c>
+      <c r="K26" t="s">
+        <v>74</v>
+      </c>
+      <c r="L26" t="s">
+        <v>154</v>
+      </c>
+      <c r="P26" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C27" t="s">
+        <v>173</v>
+      </c>
+      <c r="D27">
+        <v>2025</v>
+      </c>
+      <c r="E27">
+        <v>5</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>151</v>
+      </c>
+      <c r="H27">
+        <v>27749711</v>
+      </c>
+      <c r="I27" t="s">
+        <v>174</v>
+      </c>
+      <c r="J27" t="s">
+        <v>175</v>
+      </c>
+      <c r="K27" t="s">
+        <v>74</v>
+      </c>
+      <c r="L27" t="s">
+        <v>154</v>
+      </c>
+      <c r="P27" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" t="s">
+        <v>178</v>
+      </c>
+      <c r="D28">
+        <v>2021</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H28">
+        <v>27758575</v>
+      </c>
+      <c r="I28" t="s">
+        <v>180</v>
+      </c>
+      <c r="J28" t="s">
+        <v>181</v>
+      </c>
+      <c r="K28" t="s">
+        <v>74</v>
+      </c>
+      <c r="L28" t="s">
+        <v>182</v>
+      </c>
+      <c r="P28" t="s">
+        <v>183</v>
+      </c>
+      <c r="U28" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29">
+        <v>2023</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>179</v>
+      </c>
+      <c r="H29">
+        <v>27758575</v>
+      </c>
+      <c r="I29" t="s">
+        <v>187</v>
+      </c>
+      <c r="J29" t="s">
+        <v>188</v>
+      </c>
+      <c r="K29" t="s">
+        <v>74</v>
+      </c>
+      <c r="L29" t="s">
+        <v>182</v>
+      </c>
+      <c r="P29" t="s">
+        <v>189</v>
+      </c>
+      <c r="U29" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>190</v>
+      </c>
+      <c r="C30" t="s">
+        <v>191</v>
+      </c>
+      <c r="D30">
+        <v>2023</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30" t="s">
+        <v>179</v>
+      </c>
+      <c r="H30">
+        <v>27758575</v>
+      </c>
+      <c r="I30" t="s">
+        <v>192</v>
+      </c>
+      <c r="J30" t="s">
+        <v>193</v>
+      </c>
+      <c r="K30" t="s">
+        <v>74</v>
+      </c>
+      <c r="L30" t="s">
+        <v>182</v>
+      </c>
+      <c r="P30" t="s">
+        <v>194</v>
+      </c>
+      <c r="U30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" t="s">
+        <v>196</v>
+      </c>
+      <c r="D31">
+        <v>2024</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>179</v>
+      </c>
+      <c r="H31">
+        <v>27758575</v>
+      </c>
+      <c r="I31" t="s">
+        <v>197</v>
+      </c>
+      <c r="J31" t="s">
+        <v>198</v>
+      </c>
+      <c r="K31" t="s">
+        <v>74</v>
+      </c>
+      <c r="L31" t="s">
+        <v>182</v>
+      </c>
+      <c r="P31" t="s">
+        <v>199</v>
+      </c>
+      <c r="U31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>5</v>
+      </c>
+      <c r="B32" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" t="s">
+        <v>201</v>
+      </c>
+      <c r="D32">
+        <v>2024</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>179</v>
+      </c>
+      <c r="H32">
+        <v>27758575</v>
+      </c>
+      <c r="I32" t="s">
+        <v>202</v>
+      </c>
+      <c r="J32" t="s">
+        <v>203</v>
+      </c>
+      <c r="K32" t="s">
+        <v>74</v>
+      </c>
+      <c r="L32" t="s">
+        <v>182</v>
+      </c>
+      <c r="P32" t="s">
+        <v>204</v>
+      </c>
+      <c r="U32" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>6</v>
+      </c>
+      <c r="B33" t="s">
+        <v>205</v>
+      </c>
+      <c r="C33" t="s">
+        <v>206</v>
+      </c>
+      <c r="D33">
+        <v>2024</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33" t="s">
+        <v>179</v>
+      </c>
+      <c r="H33">
+        <v>27758575</v>
+      </c>
+      <c r="I33" t="s">
+        <v>207</v>
+      </c>
+      <c r="J33" t="s">
+        <v>208</v>
+      </c>
+      <c r="K33" t="s">
+        <v>74</v>
+      </c>
+      <c r="L33" t="s">
+        <v>182</v>
+      </c>
+      <c r="P33" t="s">
+        <v>209</v>
+      </c>
+      <c r="U33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>210</v>
+      </c>
+      <c r="C34" t="s">
+        <v>211</v>
+      </c>
+      <c r="D34">
+        <v>2024</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34" t="s">
+        <v>179</v>
+      </c>
+      <c r="H34">
+        <v>27758575</v>
+      </c>
+      <c r="I34" t="s">
+        <v>212</v>
+      </c>
+      <c r="J34" t="s">
+        <v>213</v>
+      </c>
+      <c r="K34" t="s">
+        <v>74</v>
+      </c>
+      <c r="L34" t="s">
+        <v>182</v>
+      </c>
+      <c r="P34" t="s">
+        <v>214</v>
+      </c>
+      <c r="U34" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>8</v>
+      </c>
+      <c r="B35" t="s">
+        <v>215</v>
+      </c>
+      <c r="C35" t="s">
+        <v>216</v>
+      </c>
+      <c r="D35">
+        <v>2024</v>
+      </c>
+      <c r="E35">
+        <v>4</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35" t="s">
+        <v>179</v>
+      </c>
+      <c r="H35">
+        <v>27758575</v>
+      </c>
+      <c r="I35" t="s">
+        <v>217</v>
+      </c>
+      <c r="J35" t="s">
+        <v>218</v>
+      </c>
+      <c r="K35" t="s">
+        <v>74</v>
+      </c>
+      <c r="L35" t="s">
+        <v>182</v>
+      </c>
+      <c r="P35" t="s">
+        <v>219</v>
+      </c>
+      <c r="U35" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>220</v>
+      </c>
+      <c r="C36" t="s">
+        <v>221</v>
+      </c>
+      <c r="D36">
+        <v>2024</v>
+      </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
+      <c r="F36">
+        <v>3</v>
+      </c>
+      <c r="G36" t="s">
+        <v>179</v>
+      </c>
+      <c r="H36">
+        <v>27758575</v>
+      </c>
+      <c r="I36" t="s">
+        <v>222</v>
+      </c>
+      <c r="J36" t="s">
+        <v>223</v>
+      </c>
+      <c r="K36" t="s">
+        <v>74</v>
+      </c>
+      <c r="L36" t="s">
+        <v>182</v>
+      </c>
+      <c r="P36" t="s">
+        <v>224</v>
+      </c>
+      <c r="U36" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>10</v>
+      </c>
+      <c r="B37" t="s">
+        <v>225</v>
+      </c>
+      <c r="C37" t="s">
+        <v>226</v>
+      </c>
+      <c r="D37">
+        <v>2024</v>
+      </c>
+      <c r="E37">
+        <v>4</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" t="s">
+        <v>179</v>
+      </c>
+      <c r="H37">
+        <v>27758575</v>
+      </c>
+      <c r="I37" t="s">
+        <v>227</v>
+      </c>
+      <c r="J37" t="s">
+        <v>228</v>
+      </c>
+      <c r="K37" t="s">
+        <v>74</v>
+      </c>
+      <c r="L37" t="s">
+        <v>182</v>
+      </c>
+      <c r="P37" t="s">
+        <v>229</v>
+      </c>
+      <c r="U37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>230</v>
+      </c>
+      <c r="C38" t="s">
+        <v>231</v>
+      </c>
+      <c r="D38">
+        <v>2024</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+      <c r="F38">
+        <v>4</v>
+      </c>
+      <c r="G38" t="s">
+        <v>179</v>
+      </c>
+      <c r="H38">
+        <v>27758575</v>
+      </c>
+      <c r="I38" t="s">
+        <v>232</v>
+      </c>
+      <c r="J38" t="s">
+        <v>233</v>
+      </c>
+      <c r="K38" t="s">
+        <v>74</v>
+      </c>
+      <c r="L38" t="s">
+        <v>182</v>
+      </c>
+      <c r="P38" t="s">
+        <v>234</v>
+      </c>
+      <c r="U38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>12</v>
+      </c>
+      <c r="B39" t="s">
+        <v>235</v>
+      </c>
+      <c r="C39" t="s">
+        <v>236</v>
+      </c>
+      <c r="D39">
+        <v>2024</v>
+      </c>
+      <c r="E39">
+        <v>4</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39" t="s">
+        <v>179</v>
+      </c>
+      <c r="H39">
+        <v>27758575</v>
+      </c>
+      <c r="I39" t="s">
+        <v>237</v>
+      </c>
+      <c r="J39" t="s">
+        <v>238</v>
+      </c>
+      <c r="K39" t="s">
+        <v>74</v>
+      </c>
+      <c r="L39" t="s">
+        <v>182</v>
+      </c>
+      <c r="P39" t="s">
+        <v>239</v>
+      </c>
+      <c r="U39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>13</v>
+      </c>
+      <c r="B40" t="s">
+        <v>240</v>
+      </c>
+      <c r="C40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D40">
+        <v>2024</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>179</v>
+      </c>
+      <c r="H40">
+        <v>27758575</v>
+      </c>
+      <c r="I40" t="s">
+        <v>242</v>
+      </c>
+      <c r="J40" t="s">
+        <v>243</v>
+      </c>
+      <c r="K40" t="s">
+        <v>74</v>
+      </c>
+      <c r="L40" t="s">
+        <v>182</v>
+      </c>
+      <c r="P40" t="s">
+        <v>244</v>
+      </c>
+      <c r="U40" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>14</v>
+      </c>
+      <c r="B41" t="s">
+        <v>245</v>
+      </c>
+      <c r="C41" t="s">
+        <v>246</v>
+      </c>
+      <c r="D41">
+        <v>2024</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41" t="s">
+        <v>179</v>
+      </c>
+      <c r="H41">
+        <v>27758575</v>
+      </c>
+      <c r="I41" t="s">
+        <v>247</v>
+      </c>
+      <c r="J41" t="s">
+        <v>248</v>
+      </c>
+      <c r="K41" t="s">
+        <v>74</v>
+      </c>
+      <c r="L41" t="s">
+        <v>182</v>
+      </c>
+      <c r="P41" t="s">
+        <v>249</v>
+      </c>
+      <c r="U41" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>250</v>
+      </c>
+      <c r="C42" t="s">
+        <v>251</v>
+      </c>
+      <c r="D42">
+        <v>2024</v>
+      </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
+      </c>
+      <c r="G42" t="s">
+        <v>179</v>
+      </c>
+      <c r="H42">
+        <v>27758575</v>
+      </c>
+      <c r="I42" t="s">
+        <v>252</v>
+      </c>
+      <c r="J42" t="s">
+        <v>253</v>
+      </c>
+      <c r="K42" t="s">
+        <v>74</v>
+      </c>
+      <c r="L42" t="s">
+        <v>182</v>
+      </c>
+      <c r="P42" t="s">
+        <v>254</v>
+      </c>
+      <c r="U42" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>16</v>
+      </c>
+      <c r="B43" t="s">
+        <v>255</v>
+      </c>
+      <c r="C43" t="s">
+        <v>256</v>
+      </c>
+      <c r="D43">
+        <v>2024</v>
+      </c>
+      <c r="E43">
+        <v>4</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="G43" t="s">
+        <v>179</v>
+      </c>
+      <c r="H43">
+        <v>27758575</v>
+      </c>
+      <c r="I43" t="s">
+        <v>257</v>
+      </c>
+      <c r="J43" t="s">
+        <v>258</v>
+      </c>
+      <c r="K43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L43" t="s">
+        <v>182</v>
+      </c>
+      <c r="P43" t="s">
+        <v>259</v>
+      </c>
+      <c r="U43" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>17</v>
+      </c>
+      <c r="B44" t="s">
+        <v>260</v>
+      </c>
+      <c r="C44" t="s">
+        <v>261</v>
+      </c>
+      <c r="D44">
+        <v>2025</v>
+      </c>
+      <c r="E44">
+        <v>5</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
+        <v>179</v>
+      </c>
+      <c r="H44">
+        <v>27758575</v>
+      </c>
+      <c r="I44" t="s">
+        <v>262</v>
+      </c>
+      <c r="J44" t="s">
+        <v>263</v>
+      </c>
+      <c r="K44" t="s">
+        <v>74</v>
+      </c>
+      <c r="L44" t="s">
+        <v>182</v>
+      </c>
+      <c r="P44" t="s">
+        <v>264</v>
+      </c>
+      <c r="U44" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>18</v>
+      </c>
+      <c r="B45" t="s">
+        <v>265</v>
+      </c>
+      <c r="C45" t="s">
+        <v>266</v>
+      </c>
+      <c r="D45">
+        <v>2025</v>
+      </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45" t="s">
+        <v>179</v>
+      </c>
+      <c r="H45">
+        <v>27758575</v>
+      </c>
+      <c r="I45" t="s">
+        <v>267</v>
+      </c>
+      <c r="J45" t="s">
+        <v>268</v>
+      </c>
+      <c r="K45" t="s">
+        <v>74</v>
+      </c>
+      <c r="L45" t="s">
+        <v>182</v>
+      </c>
+      <c r="P45" t="s">
+        <v>269</v>
+      </c>
+      <c r="U45" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>19</v>
+      </c>
+      <c r="B46" t="s">
+        <v>270</v>
+      </c>
+      <c r="C46" t="s">
+        <v>271</v>
+      </c>
+      <c r="D46">
+        <v>2025</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
+      <c r="G46" t="s">
+        <v>179</v>
+      </c>
+      <c r="H46">
+        <v>27758575</v>
+      </c>
+      <c r="I46" t="s">
+        <v>272</v>
+      </c>
+      <c r="J46" t="s">
+        <v>273</v>
+      </c>
+      <c r="K46" t="s">
+        <v>74</v>
+      </c>
+      <c r="L46" t="s">
+        <v>182</v>
+      </c>
+      <c r="P46" t="s">
+        <v>274</v>
+      </c>
+      <c r="U46" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>20</v>
+      </c>
+      <c r="B47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C47" t="s">
+        <v>276</v>
+      </c>
+      <c r="D47">
+        <v>2025</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
+      <c r="G47" t="s">
+        <v>179</v>
+      </c>
+      <c r="H47">
+        <v>27758575</v>
+      </c>
+      <c r="I47" t="s">
+        <v>277</v>
+      </c>
+      <c r="J47" t="s">
+        <v>278</v>
+      </c>
+      <c r="K47" t="s">
+        <v>74</v>
+      </c>
+      <c r="L47" t="s">
+        <v>182</v>
+      </c>
+      <c r="P47" t="s">
+        <v>279</v>
+      </c>
+      <c r="U47" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>21</v>
+      </c>
+      <c r="B48" t="s">
+        <v>280</v>
+      </c>
+      <c r="C48" t="s">
+        <v>281</v>
+      </c>
+      <c r="D48">
+        <v>2025</v>
+      </c>
+      <c r="E48">
+        <v>5</v>
+      </c>
+      <c r="F48">
+        <v>2</v>
+      </c>
+      <c r="G48" t="s">
+        <v>179</v>
+      </c>
+      <c r="H48">
+        <v>27758575</v>
+      </c>
+      <c r="I48" t="s">
+        <v>282</v>
+      </c>
+      <c r="J48" t="s">
+        <v>283</v>
+      </c>
+      <c r="K48" t="s">
+        <v>74</v>
+      </c>
+      <c r="L48" t="s">
+        <v>182</v>
+      </c>
+      <c r="P48" t="s">
+        <v>284</v>
+      </c>
+      <c r="U48" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>22</v>
+      </c>
+      <c r="B49" t="s">
+        <v>285</v>
+      </c>
+      <c r="C49" t="s">
+        <v>286</v>
+      </c>
+      <c r="D49">
+        <v>2025</v>
+      </c>
+      <c r="E49">
+        <v>5</v>
+      </c>
+      <c r="F49">
+        <v>3</v>
+      </c>
+      <c r="G49" t="s">
+        <v>179</v>
+      </c>
+      <c r="H49">
+        <v>27758575</v>
+      </c>
+      <c r="I49" t="s">
+        <v>287</v>
+      </c>
+      <c r="J49" t="s">
+        <v>288</v>
+      </c>
+      <c r="K49" t="s">
+        <v>74</v>
+      </c>
+      <c r="L49" t="s">
+        <v>182</v>
+      </c>
+      <c r="P49" t="s">
+        <v>289</v>
+      </c>
+      <c r="U49" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>23</v>
+      </c>
+      <c r="B50" t="s">
+        <v>290</v>
+      </c>
+      <c r="C50" t="s">
+        <v>291</v>
+      </c>
+      <c r="D50">
+        <v>2025</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+      <c r="F50">
+        <v>3</v>
+      </c>
+      <c r="G50" t="s">
+        <v>179</v>
+      </c>
+      <c r="H50">
+        <v>27758575</v>
+      </c>
+      <c r="I50" t="s">
+        <v>292</v>
+      </c>
+      <c r="J50" t="s">
+        <v>293</v>
+      </c>
+      <c r="K50" t="s">
+        <v>74</v>
+      </c>
+      <c r="L50" t="s">
+        <v>182</v>
+      </c>
+      <c r="P50" t="s">
+        <v>294</v>
+      </c>
+      <c r="U50" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>24</v>
+      </c>
+      <c r="B51" t="s">
+        <v>295</v>
+      </c>
+      <c r="C51" t="s">
+        <v>296</v>
+      </c>
+      <c r="D51">
+        <v>2025</v>
+      </c>
+      <c r="E51">
+        <v>5</v>
+      </c>
+      <c r="F51">
+        <v>3</v>
+      </c>
+      <c r="G51" t="s">
+        <v>179</v>
+      </c>
+      <c r="H51">
+        <v>27758575</v>
+      </c>
+      <c r="I51" t="s">
+        <v>297</v>
+      </c>
+      <c r="J51" t="s">
+        <v>298</v>
+      </c>
+      <c r="K51" t="s">
+        <v>74</v>
+      </c>
+      <c r="L51" t="s">
+        <v>182</v>
+      </c>
+      <c r="P51" t="s">
+        <v>299</v>
+      </c>
+      <c r="U51" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>25</v>
+      </c>
+      <c r="B52" t="s">
+        <v>300</v>
+      </c>
+      <c r="C52" t="s">
+        <v>301</v>
+      </c>
+      <c r="D52">
+        <v>2025</v>
+      </c>
+      <c r="E52">
+        <v>5</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+      <c r="G52" t="s">
+        <v>179</v>
+      </c>
+      <c r="H52">
+        <v>27758575</v>
+      </c>
+      <c r="I52" t="s">
+        <v>302</v>
+      </c>
+      <c r="J52" t="s">
+        <v>303</v>
+      </c>
+      <c r="K52" t="s">
+        <v>74</v>
+      </c>
+      <c r="L52" t="s">
+        <v>182</v>
+      </c>
+      <c r="P52" t="s">
+        <v>304</v>
+      </c>
+      <c r="U52" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>26</v>
+      </c>
+      <c r="B53" t="s">
+        <v>285</v>
+      </c>
+      <c r="C53" t="s">
+        <v>286</v>
+      </c>
+      <c r="D53">
+        <v>2025</v>
+      </c>
+      <c r="E53">
+        <v>5</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53" t="s">
+        <v>179</v>
+      </c>
+      <c r="H53">
+        <v>27758575</v>
+      </c>
+      <c r="I53" t="s">
+        <v>287</v>
+      </c>
+      <c r="J53" t="s">
+        <v>288</v>
+      </c>
+      <c r="K53" t="s">
+        <v>74</v>
+      </c>
+      <c r="L53" t="s">
+        <v>182</v>
+      </c>
+      <c r="P53" t="s">
+        <v>289</v>
+      </c>
+      <c r="U53" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>27</v>
+      </c>
+      <c r="B54" t="s">
+        <v>305</v>
+      </c>
+      <c r="C54" t="s">
+        <v>306</v>
+      </c>
+      <c r="D54">
+        <v>2025</v>
+      </c>
+      <c r="E54">
+        <v>5</v>
+      </c>
+      <c r="F54">
+        <v>4</v>
+      </c>
+      <c r="G54" t="s">
+        <v>179</v>
+      </c>
+      <c r="H54">
+        <v>27758575</v>
+      </c>
+      <c r="I54" t="s">
+        <v>307</v>
+      </c>
+      <c r="J54" t="s">
+        <v>308</v>
+      </c>
+      <c r="K54" t="s">
+        <v>74</v>
+      </c>
+      <c r="L54" t="s">
+        <v>182</v>
+      </c>
+      <c r="P54" t="s">
+        <v>309</v>
+      </c>
+      <c r="U54" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>28</v>
+      </c>
+      <c r="B55" t="s">
+        <v>310</v>
+      </c>
+      <c r="C55" t="s">
+        <v>311</v>
+      </c>
+      <c r="D55">
+        <v>2025</v>
+      </c>
+      <c r="E55">
+        <v>5</v>
+      </c>
+      <c r="F55">
+        <v>4</v>
+      </c>
+      <c r="G55" t="s">
+        <v>179</v>
+      </c>
+      <c r="H55">
+        <v>27758575</v>
+      </c>
+      <c r="I55" t="s">
+        <v>312</v>
+      </c>
+      <c r="J55" t="s">
+        <v>313</v>
+      </c>
+      <c r="K55" t="s">
+        <v>74</v>
+      </c>
+      <c r="L55" t="s">
+        <v>182</v>
+      </c>
+      <c r="P55" t="s">
+        <v>314</v>
+      </c>
+      <c r="U55" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>29</v>
+      </c>
+      <c r="B56" t="s">
+        <v>315</v>
+      </c>
+      <c r="C56" t="s">
+        <v>316</v>
+      </c>
+      <c r="D56">
+        <v>2025</v>
+      </c>
+      <c r="E56">
+        <v>5</v>
+      </c>
+      <c r="F56">
+        <v>4</v>
+      </c>
+      <c r="G56" t="s">
+        <v>179</v>
+      </c>
+      <c r="H56">
+        <v>27758575</v>
+      </c>
+      <c r="I56" t="s">
+        <v>317</v>
+      </c>
+      <c r="J56" t="s">
+        <v>318</v>
+      </c>
+      <c r="K56" t="s">
+        <v>74</v>
+      </c>
+      <c r="L56" t="s">
+        <v>182</v>
+      </c>
+      <c r="P56" t="s">
+        <v>319</v>
+      </c>
+      <c r="U56" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>30</v>
+      </c>
+      <c r="B57" t="s">
+        <v>320</v>
+      </c>
+      <c r="C57" t="s">
+        <v>321</v>
+      </c>
+      <c r="D57">
+        <v>2025</v>
+      </c>
+      <c r="E57">
+        <v>5</v>
+      </c>
+      <c r="F57">
+        <v>4</v>
+      </c>
+      <c r="G57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H57">
+        <v>27758575</v>
+      </c>
+      <c r="I57" t="s">
+        <v>322</v>
+      </c>
+      <c r="J57" t="s">
+        <v>323</v>
+      </c>
+      <c r="K57" t="s">
+        <v>74</v>
+      </c>
+      <c r="L57" t="s">
+        <v>182</v>
+      </c>
+      <c r="P57" t="s">
+        <v>324</v>
+      </c>
+      <c r="U57" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>31</v>
+      </c>
+      <c r="B58" t="s">
+        <v>325</v>
+      </c>
+      <c r="C58" t="s">
+        <v>326</v>
+      </c>
+      <c r="D58">
+        <v>2026</v>
+      </c>
+      <c r="E58">
+        <v>6</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58" t="s">
+        <v>179</v>
+      </c>
+      <c r="H58">
+        <v>27758575</v>
+      </c>
+      <c r="I58" t="s">
+        <v>327</v>
+      </c>
+      <c r="J58" t="s">
+        <v>328</v>
+      </c>
+      <c r="K58" t="s">
+        <v>74</v>
+      </c>
+      <c r="L58" t="s">
+        <v>182</v>
+      </c>
+      <c r="P58" t="s">
+        <v>329</v>
+      </c>
+      <c r="U58" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>32</v>
+      </c>
+      <c r="B59" t="s">
+        <v>330</v>
+      </c>
+      <c r="C59" t="s">
+        <v>331</v>
+      </c>
+      <c r="D59">
+        <v>2026</v>
+      </c>
+      <c r="E59">
+        <v>6</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>179</v>
+      </c>
+      <c r="H59">
+        <v>27758575</v>
+      </c>
+      <c r="I59" t="s">
+        <v>332</v>
+      </c>
+      <c r="J59" t="s">
+        <v>333</v>
+      </c>
+      <c r="K59" t="s">
+        <v>74</v>
+      </c>
+      <c r="L59" t="s">
+        <v>182</v>
+      </c>
+      <c r="P59" t="s">
+        <v>334</v>
+      </c>
+      <c r="U59" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/myapp/data_idx_gabung.xlsx
+++ b/myapp/data_idx_gabung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SENTIMENT ANALYSIS UGI AQIS 2026\PROJECT SHINY DASHBOARD ANALISIS SENTIMEN 2026 TERBARU\myapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B4744F6-FB88-4393-8E7A-D9E4DE89F2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51853112-18CB-49BF-9EB0-C2980A8E9B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="393">
   <si>
     <t>No</t>
   </si>
@@ -1026,6 +1026,180 @@
   </si>
   <si>
     <t>This study aims to analyze user sentiment toward the Jamsostek Mobile (JMO) application using Support Vector Machine (SVM) and Naive Bayes algorithms, based on reviews collected from the Google Play Store. A total of 6,000 user reviews were collected via web scraping. The research stages include text preprocessing (cleaning, case folding, normalization, tokenization, stopword removal, and stemming), feature weighting using Term Frequency–Inverse Document Frequency (TF-IDF), data labeling using a lexicon-based approach, and sentiment classification into three classes: positive, negative, and neutral. Model performance was evaluated using a confusion matrix and metrics such as accuracy, precision, recall, and F1-score. The results show that the SVM algorithm achieved superior performance with an accuracy of 88.9%, while Naive Bayes achieved 64.1%. SVM also demonstrated more consistent F1-score values across all sentiment classes. Therefore, SVM has been shown to be a more effective and reliable algorithm for sentiment classification of JMO application reviews.</t>
+  </si>
+  <si>
+    <t>The Shopee Application User Reviews Sentiment Analysis Employing Naïve Bayes Algorithm</t>
+  </si>
+  <si>
+    <t>Nur Adha Pasaribu; Sriani</t>
+  </si>
+  <si>
+    <t>International Journal Software Engineering and Computer Science (IJSECS)</t>
+  </si>
+  <si>
+    <t>https://journal.lembagakita.org/ijsecs/article/view/1699</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis; Shopee; Naive Bayes</t>
+  </si>
+  <si>
+    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/11126</t>
+  </si>
+  <si>
+    <t>With the significant growth of internet use in Indonesia, there has been a surge in online business activity. The convenience offered by online platforms is increasingly in demand because it allows consumers to shop without being bound by a certain time or location. Before making a purchase, consumers tend to look for information first through various sources such as reviews on blogs, Instagram, TikTok, or reviews on the YouTube platform which is integrated in the application. This research adopted a method that included planning, literature study, data collection, and data processing using a dataset from the Play Store application which was taken using the Python library with an initial amount of 5000 data. After a manual filtering process which involved removing slang words, eliminating duplications, and normalizing punctuation marks, the remaining data was 3946. The application of the Naïve Bayes algorithm in this research uses probability methods to classify and predict 3141 training data and 805 test data, with Python library help. The accuracy calculation results show satisfactory performance, with an accuracy of 86.00%, precision of 80.74%, recall of 78.13%, and f1-score of 79.00% on a dataset of 3946. Analysis from this research shows the dominance of positive sentiment in 2050 data, while sentiment negative amounted to 1199 data. The amount and quality of training data plays an important role in system predictions, where high data quality provides better accuracy in predicting sentiment classes.</t>
+  </si>
+  <si>
+    <t>45.00 (USD) / 700.000 (IDR). This journal provides authors with the option to publish their research via subscription (without an Article Publishing Charge) or through open access. For open access publication, authors are required to cover a publication fee (APC), either personally or through funding from a research body. Link: https://journal.lembagakita.org/ijsecs/about/submissions</t>
+  </si>
+  <si>
+    <t>Application of the Naive Bayes Algorithm in Twitter Sentiment Analysis of 2024 Vice Presidential Candidate Gibran Rakabuming Raka using RapidMiner</t>
+  </si>
+  <si>
+    <t>Tasya Aisyah Amini; Kiki Setiawan</t>
+  </si>
+  <si>
+    <t>https://journal.lembagakita.org/ijsecs/article/view/2236</t>
+  </si>
+  <si>
+    <t>Sentiment; Twitter; Vice President; Naive Bayes; Rapidminer</t>
+  </si>
+  <si>
+    <t>In the current era of digital democracy, social media sentiment analysis has become a relevant method for understanding public views of political figures. As one of the leading social media platforms, Twitter provides a public space for sharing opinions and expressions regarding political issues. This research aims to classify and measure the accuracy of people's responses to the positive and negative sides. Sentiment analysis was carried out using the Naïve Bayes method using a dataset of 3223 tweets. The final results of this research show that implementing the Naïve Bayes Method in sentiment analysis regarding political dynasty polemics, especially regarding the 2024 Cawapres Gibran Rakabuming Raka, provides an accuracy value of 82.19%. Of the 1696 negative and 112 positive sentiments predicted, there were 462 harmful and 953 positive predicted data. These results indicate that most public responses tend to be detrimental to the Constitutional Court's (MK) decision, which grants political legitimacy to Gibran Rakabuming Raka as the 2024 vice-presidential candidate.</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of BMKG Weather Information Service Using K-Nearest Neighbor Method</t>
+  </si>
+  <si>
+    <t>Muhamad Fajar Sodiq; Fatkhul Amin</t>
+  </si>
+  <si>
+    <t>https://journal.lembagakita.org/ijsecs/article/view/2881</t>
+  </si>
+  <si>
+    <t>BMKG; Platform X; K-Nearest Neighbor (KNN)</t>
+  </si>
+  <si>
+    <t>The Meteorology, Climatology, and Geophysics Agency (BMKG) is a government institution that provides information related to air quality, climate, dry days, satellite imagery, wave forecasts, wind forecasts, and fire potential. This information is disseminated not only through BMKG's official website but also via the social media platform X, making it easier for the public to access up-to-date information. This study aims to classify user sentiment towards the weather information services provided by BMKG using the K-Nearest Neighbor (KNN) method. Data was collected through a web crawling technique, resulting in 1,031 data points analyzed in this research. The data processing stages included Pre-Processing and sentiment calculation using Vader's Sentiment and Random Forest. The classification results using the KNN algorithm showed an accuracy rate of 96%, with an average precision of 96%, an average recall of 96%, and an average f-measure of 96%. These findings indicate that the KNN model can effectively classify user sentiment towards BMKG's services</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of the Tapera Law on Platform X Using Naive Bayes Algorithm</t>
+  </si>
+  <si>
+    <t>Dava Sevtiandra Bimantoro; Rasiban</t>
+  </si>
+  <si>
+    <t>https://journal.lembagakita.org/ijsecs/article/view/3077</t>
+  </si>
+  <si>
+    <t>Tapera Law; Sentiment Analysis; Naive Bayes Method; Twitter</t>
+  </si>
+  <si>
+    <t>The implementation of the 2016 Public Housing Savings Law (UU Tapera) aims to help legal and informal workers have decent houses through the management of housing savings funds by BP Tapera. However, when implemented, this program experienced obstacles amidst various problems including the transparency of the fund collection and management system, the unevenness of benefit provision, and variations in public perception. Sentiment analysis was conducted on Twitter data for sentiment regarding the Tapera Law to obtain public perception with Naïve Bayes. This approach classifies sentiment into positive, negative, and neutral. The accuracy of the Analysis Results was 62.47% (343 negative sentiments, 23 neutral, and finally 32 positive sentiments). The public mostly has negative sentiment towards the Tapera Law, because many of them are afraid of losing justice and effectiveness with this policy. These results underline the need to intensify transparency and communication of the benefits of the Tapera Law and its mechanisms to increase public acceptance and trust.</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of Social Media X Users Towards Legislators Engaged in Online Gambling Using Naïve Bayes Algorithm</t>
+  </si>
+  <si>
+    <t>Vivi Nurmaylina; Yuma Akbar</t>
+  </si>
+  <si>
+    <t>https://journal.lembagakita.org/ijsecs/article/view/3079</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis; Twitter; Online Gambling; Legislative Members; Naive Bayes; RapidMiner</t>
+  </si>
+  <si>
+    <t>This research analyzes public feelings toward legislative members participating in online gambling applying the Naïve bayes classification technique. The collected data were processed, labeled, cleaned, preprocessed, and classified using RapidMiner Studio software, while conducting the sentiment analysis according to a systematic approach from each of those steps described above, namely, data crawling, cleaning, preprocessing, and classification of the Twitter data. Sentiment distribution yielded 286 negative and 90 positive sentiments with a prediction accuracy of 73.10%. These findings illustrate an overwhelmingly negative public response to this behavior and the expectation society has for legislators as public figures.</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of Kredivo App Users Using the K-Nearest Neighbor Algorithm</t>
+  </si>
+  <si>
+    <t>Saepudin; Sutisna</t>
+  </si>
+  <si>
+    <t>https://journal.lembagakita.org/ijsecs/article/view/3056</t>
+  </si>
+  <si>
+    <t>Analysis; Sentiment; Kredivo; CRISP-DM; K-Nearest Neighbors</t>
+  </si>
+  <si>
+    <t>In today's technological era, the internet has played an important role in all aspects of human life. This is also what drives various mobile applications to develop very rapidly. Kredivo is an instant credit solution that provides convenience to buy now pay later in a 1-month tenor or 3-month installment tenor with 0% interest. In addition, Kredivo is not only used for shopping purposes, but borrowers can also make withdrawals in the form of cash. However, not all users are satisfied with the service of the application. and the many comments submitted through the Kredivo application review feature on the Google Play Store. Therefore, in this study, researchers tried to conduct a sentiment analysis of Kredivo application users using the K-Nearest Neighbor algorithm. The purpose of this study was to determine the accuracy value produced by the K-Nearest Neighbor algorithm. From testing 1880 data using the cross-validation model, it was found that reviews containing positive sentiment were 62.55% and containing negative sentiment were 37.45%. Evaluation of the classification results using the Confusion Matrix test obtained an accuracy value of 79.36%, with a recall value of 83.08%, precision of 72.15%, and recall (Specificity) of 73.15%, so it can be concluded that the K-Nearest Neighbor algorithm can classify sentiments well using review data on Kredivo application users.</t>
+  </si>
+  <si>
+    <t>Public Sentiment Analysis on the Inauguration of President Prabowo Subianto on Platform X Using the Support Vector Machine (SVM) Algorithm</t>
+  </si>
+  <si>
+    <t>Rosalina Saputri; Sri Lestari</t>
+  </si>
+  <si>
+    <t>https://journal.lembagakita.org/ijsecs/article/view/3787</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis; Support Vector Machine; Presidential Inauguration; Public Opinion; Social Media Analysis</t>
+  </si>
+  <si>
+    <t>The inauguration of President Prabowo Subianto emerged as a pivotal political event that captured significant public interest and sparked a wide array of reactions across social media, particularly on the X platform (formerly known as Twitter). This research aims to categorize and analyze public sentiment regarding this historic moment by utilizing the Support Vector Machine (SVM) algorithm, a robust machine learning approach for classification tasks. A dataset comprising 1,000 tweets was initially gathered through targeted searches related to the inauguration. Subsequently, the data underwent a rigorous preprocessing phase, which included tokenization to break down text into individual components, stopword removal to eliminate irrelevant terms, filtering to exclude special characters and noise, and Term Frequency Inverse Document Frequency (TF-IDF) transformation to convert textual data into a numerical format suitable for algorithmic processing. After preprocessing, 909 data points were prepared for further analysis. The dataset was then divided into two subsets: 80% allocated for training the model (727 data points) and 20% reserved for testing its performance (182 data points). The results of sentiment classification indicated that, among the test data, 653 tweets conveyed a positive sentiment toward the inauguration, whereas 74 tweets expressed a negative sentiment. Performance evaluation of the model demonstrated a commendable accuracy rate of 89.82%, alongside a precision of 89.82%, a recall of 100%, and an F1-score of 94.63%. These metrics highlight the model’s strong capability to accurately discern and classify public opinions related to political developments. The elevated recall rate, in particular, signifies the model’s ability to identify all instances of positive sentiment without omission. However, the precision score suggests some room for refinement in reducing misclassifications. The findings underscore the effectiveness of the SVM algorithm in dissecting and interpreting consumer sentiment toward significant political events. This provides a reliable tool for such analyses. Moreover, the outcomes of this study are anticipated to offer a valuable reference point for stakeholders and policymakers in leveraging data-driven approaches to gauge public opinion and monitor economic trends in Indonesia. This research also lays the groundwork for future investigations into sentiment analysis within the digital sphere. This could guide strategic communications and policy formulation based on real-time societal feedback.</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of Public Comments on YouTube Regarding the Inaugural Speech of the 8th President of Indonesia Using VADER and BERT Methods</t>
+  </si>
+  <si>
+    <t>Alwi Ahmad Bastian; Andreas Perdana</t>
+  </si>
+  <si>
+    <t>https://journal.lembagakita.org/ijsecs/article/view/3472</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis; Public Opinion; Prabowo Subianto; YouTube Comments; Natural Language Processing</t>
+  </si>
+  <si>
+    <t>The research examines public reactions toward President Prabowo Subianto first presidential address in 2024 by studying YouTube comment sentiments. By utilizing sentiment analysis methods, this research combines two main approaches: The research combines VADER (Valence Aware Dictionary and Sentiment Reasoner) for initial sentiment labeling through predefined dictionary categories with BERT (Bidirectional Encoder Representations from Transformers) for more advanced classification. The dataset contains 10,306 comments which display a range of public opinions. Positive sentiment represents 4,943 comments which make up 49.26% of the total while neutral sentiment accounts for 4,336 comments at 43.21% and negative sentiment represents 756 comments at 7.53%. The BERT model reached an accuracy level of 97.01% which illustrates its capability to process contextual details and subtle data elements. VADER delivers rapid preliminary labeling results and BERT improves classification precision through its analysis of complex contexts. The study reveals how people perceive the new government while providing chances for creating public opinion monitoring techniques for social and political topics. Researchers, academics, and policymakers will find these findings valuable for comprehending public opinion dynamics during the digital age's continuous evolution</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of the TikTok Tokopedia Seller Center Application Using Support Vector Machine (SVM) and Naive Bayes Algorithms</t>
+  </si>
+  <si>
+    <t>Faddilla Aulia Dara; Irfan Pratama</t>
+  </si>
+  <si>
+    <t>https://journal.lembagakita.org/ijsecs/article/view/3463</t>
+  </si>
+  <si>
+    <t>Google Play Store; Naive Bayes; Sentiment Analysis; Support Vector Machine; TikTok Tokopedia Seller Center</t>
+  </si>
+  <si>
+    <t>The TikTok Tokopedia Seller Center application is a collaboration between TikTok and Tokopedia designed to help sellers manage their stores and boost sales. Despite offering various features, complaints about poor user experience often appear in reviews on the Google Play Store. This study aims to analyze user sentiment towards the TikTok Tokopedia Seller Center application using a dataset of 2,000 reviews, using the Support Vector Machine (SVM) and Naive Bayes algorithms to classify positive, negative, and neutral sentiments. In addition, this study also attempts to compare the effectiveness of these algorithms in sentiment analysis and evaluate the performance of two weighting methods: TF-IDF and Term Presence. The dataset used was taken by scraping review data on the Google Play Store in Python, as many as 2000 user review datasets. This study found 1,171 negative sentiments, 735 positive sentiments, and 94 neutral sentiments. The results showed that the accuracy of SVM (0.81 and 0.78) was higher than Naive Bayes (0.69 and 0.75). It is hoped that this research can help potential users to find user sentiment towards the application and provide valuable information for application developers to understand user needs and expectations so that developers can improve application features more appropriately and effectively</t>
+  </si>
+  <si>
+    <t>Social Media Sentiment Analysis of Twitter Regarding People's Housing Savings (TAPERA) Using Naïve Bayes</t>
+  </si>
+  <si>
+    <t>Avry Liyanah Dewy; Mia Kamayani</t>
+  </si>
+  <si>
+    <t>https://journal.lembagakita.org/ijsecs/article/view/4126</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis; Twitter; TAPERA; Naive Bayes</t>
+  </si>
+  <si>
+    <t>The advancement of technology has transformed how people interact and express opinions on social media platforms. This research examines Twitter conversations regarding Indonesia's governmentinitiated Housing Savings Program (TAPERA) through sentiment analysis. The study employed Naïve Bayes classification methodology, with data acquisition conducted via Google Colab platform utilizing the tweetharvest library. The collection process yielded 1,800 tweets matching predetermined search parameters. Data underwent rigorous preprocessing, including text cleaning and manual sentiment annotation to establish reliable training datasets. Examination of 720 test tweets revealed 473 (65.69%) expressed negative sentiment while 247 (34.31%) conveyed positive sentiment toward the program. The implemented Naïve Bayes model achieved 84.17% accuracy, with negative class precision at 88.71% and recall at 88.60%, while positive class precision reached 78.54% with 76.08% recall. Results indicate the Naïve Bayes approach effectively categorizes public sentiment regarding the TAPERA program, offering valuable feedback for stakeholders responsible for program assessment and enhancement.</t>
+  </si>
+  <si>
+    <t>Student Aspiration Processing Information System with Sentiment Analysis at Piksi Ganesha Polytechnic</t>
+  </si>
+  <si>
+    <t>Maulidia Tuzahra; Johni S Pasaribu</t>
+  </si>
+  <si>
+    <t>https://journal.lembagakita.org/ijsecs/article/view/5719</t>
+  </si>
+  <si>
+    <t>Information System; Student Aspiration; Sentiment Analysis; Waterfall; Black Box Testing</t>
+  </si>
+  <si>
+    <t>Student aspirations play an important role as a means of two-way communication to improve the quality of academic and non-academic services in higher education. However, manual aspiration submission systems often result in delays in follow-up and a lack of documentation. This study aims to design and implement a web-based student aspiration processing information system integrated with sentiment analysis. The development method used is Waterfall, with stages of requirements analysis, design, implementation, testing, and maintenance. The implementation was carried out using the PHP programming language and MySQL database. The main features of the system include registration, login, feedback form, feedback list, admin replies, and lexicon-based sentiment analysis. Testing using Black Box Testing showed that all functions ran according to user requirements (100% success rate), with an average system response time of 2.7 seconds and a user satisfaction rate of 92%. This system is capable of classifying aspirations into positive (46%), negative (38%), and neutral (16%) categories, thereby facilitating the evaluation of campus services. This research proves that the system is capable of accelerating the handling of aspirations by up to 40% compared to manual mechanisms and supports decision-making based on sentiment data.</t>
   </si>
 </sst>
 </file>
@@ -1081,8 +1255,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:U59" totalsRowShown="0">
-  <autoFilter ref="A1:U59" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:U70" totalsRowShown="0">
+  <autoFilter ref="A1:U70" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Title of Article"/>
@@ -1389,7 +1563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U59"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
@@ -3986,6 +4160,490 @@
       </c>
       <c r="U59" t="s">
         <v>184</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1</v>
+      </c>
+      <c r="B60" t="s">
+        <v>335</v>
+      </c>
+      <c r="C60" t="s">
+        <v>336</v>
+      </c>
+      <c r="D60">
+        <v>2023</v>
+      </c>
+      <c r="E60">
+        <v>3</v>
+      </c>
+      <c r="F60">
+        <v>3</v>
+      </c>
+      <c r="G60" t="s">
+        <v>337</v>
+      </c>
+      <c r="H60">
+        <v>27763242</v>
+      </c>
+      <c r="I60" t="s">
+        <v>338</v>
+      </c>
+      <c r="J60" t="s">
+        <v>339</v>
+      </c>
+      <c r="K60" t="s">
+        <v>74</v>
+      </c>
+      <c r="L60" t="s">
+        <v>340</v>
+      </c>
+      <c r="P60" t="s">
+        <v>341</v>
+      </c>
+      <c r="U60" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>2</v>
+      </c>
+      <c r="B61" t="s">
+        <v>343</v>
+      </c>
+      <c r="C61" t="s">
+        <v>344</v>
+      </c>
+      <c r="D61">
+        <v>2024</v>
+      </c>
+      <c r="E61">
+        <v>4</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" t="s">
+        <v>337</v>
+      </c>
+      <c r="H61">
+        <v>27763242</v>
+      </c>
+      <c r="I61" t="s">
+        <v>345</v>
+      </c>
+      <c r="J61" t="s">
+        <v>346</v>
+      </c>
+      <c r="K61" t="s">
+        <v>74</v>
+      </c>
+      <c r="L61" t="s">
+        <v>340</v>
+      </c>
+      <c r="P61" t="s">
+        <v>347</v>
+      </c>
+      <c r="U61" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s">
+        <v>348</v>
+      </c>
+      <c r="C62" t="s">
+        <v>349</v>
+      </c>
+      <c r="D62">
+        <v>2024</v>
+      </c>
+      <c r="E62">
+        <v>4</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62" t="s">
+        <v>337</v>
+      </c>
+      <c r="H62">
+        <v>27763242</v>
+      </c>
+      <c r="I62" t="s">
+        <v>350</v>
+      </c>
+      <c r="J62" t="s">
+        <v>351</v>
+      </c>
+      <c r="K62" t="s">
+        <v>74</v>
+      </c>
+      <c r="L62" t="s">
+        <v>340</v>
+      </c>
+      <c r="P62" t="s">
+        <v>352</v>
+      </c>
+      <c r="U62" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>4</v>
+      </c>
+      <c r="B63" t="s">
+        <v>353</v>
+      </c>
+      <c r="C63" t="s">
+        <v>354</v>
+      </c>
+      <c r="D63">
+        <v>2024</v>
+      </c>
+      <c r="E63">
+        <v>4</v>
+      </c>
+      <c r="F63">
+        <v>3</v>
+      </c>
+      <c r="G63" t="s">
+        <v>337</v>
+      </c>
+      <c r="H63">
+        <v>27763242</v>
+      </c>
+      <c r="I63" t="s">
+        <v>355</v>
+      </c>
+      <c r="J63" t="s">
+        <v>356</v>
+      </c>
+      <c r="K63" t="s">
+        <v>74</v>
+      </c>
+      <c r="L63" t="s">
+        <v>340</v>
+      </c>
+      <c r="P63" t="s">
+        <v>357</v>
+      </c>
+      <c r="U63" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64" t="s">
+        <v>358</v>
+      </c>
+      <c r="C64" t="s">
+        <v>359</v>
+      </c>
+      <c r="D64">
+        <v>2024</v>
+      </c>
+      <c r="E64">
+        <v>4</v>
+      </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+      <c r="G64" t="s">
+        <v>337</v>
+      </c>
+      <c r="H64">
+        <v>27763242</v>
+      </c>
+      <c r="I64" t="s">
+        <v>360</v>
+      </c>
+      <c r="J64" t="s">
+        <v>361</v>
+      </c>
+      <c r="K64" t="s">
+        <v>74</v>
+      </c>
+      <c r="L64" t="s">
+        <v>340</v>
+      </c>
+      <c r="P64" t="s">
+        <v>362</v>
+      </c>
+      <c r="U64" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>6</v>
+      </c>
+      <c r="B65" t="s">
+        <v>363</v>
+      </c>
+      <c r="C65" t="s">
+        <v>364</v>
+      </c>
+      <c r="D65">
+        <v>2024</v>
+      </c>
+      <c r="E65">
+        <v>4</v>
+      </c>
+      <c r="F65">
+        <v>3</v>
+      </c>
+      <c r="G65" t="s">
+        <v>337</v>
+      </c>
+      <c r="H65">
+        <v>27763242</v>
+      </c>
+      <c r="I65" t="s">
+        <v>365</v>
+      </c>
+      <c r="J65" t="s">
+        <v>366</v>
+      </c>
+      <c r="K65" t="s">
+        <v>74</v>
+      </c>
+      <c r="L65" t="s">
+        <v>340</v>
+      </c>
+      <c r="P65" t="s">
+        <v>367</v>
+      </c>
+      <c r="U65" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>7</v>
+      </c>
+      <c r="B66" t="s">
+        <v>368</v>
+      </c>
+      <c r="C66" t="s">
+        <v>369</v>
+      </c>
+      <c r="D66">
+        <v>2025</v>
+      </c>
+      <c r="E66">
+        <v>5</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>337</v>
+      </c>
+      <c r="H66">
+        <v>27763242</v>
+      </c>
+      <c r="I66" t="s">
+        <v>370</v>
+      </c>
+      <c r="J66" t="s">
+        <v>371</v>
+      </c>
+      <c r="K66" t="s">
+        <v>74</v>
+      </c>
+      <c r="L66" t="s">
+        <v>340</v>
+      </c>
+      <c r="P66" t="s">
+        <v>372</v>
+      </c>
+      <c r="U66" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>8</v>
+      </c>
+      <c r="B67" t="s">
+        <v>373</v>
+      </c>
+      <c r="C67" t="s">
+        <v>374</v>
+      </c>
+      <c r="D67">
+        <v>2025</v>
+      </c>
+      <c r="E67">
+        <v>5</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67" t="s">
+        <v>337</v>
+      </c>
+      <c r="H67">
+        <v>27763242</v>
+      </c>
+      <c r="I67" t="s">
+        <v>375</v>
+      </c>
+      <c r="J67" t="s">
+        <v>376</v>
+      </c>
+      <c r="K67" t="s">
+        <v>74</v>
+      </c>
+      <c r="L67" t="s">
+        <v>340</v>
+      </c>
+      <c r="P67" t="s">
+        <v>377</v>
+      </c>
+      <c r="U67" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>9</v>
+      </c>
+      <c r="B68" t="s">
+        <v>378</v>
+      </c>
+      <c r="C68" t="s">
+        <v>379</v>
+      </c>
+      <c r="D68">
+        <v>2025</v>
+      </c>
+      <c r="E68">
+        <v>5</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
+        <v>337</v>
+      </c>
+      <c r="H68">
+        <v>27763242</v>
+      </c>
+      <c r="I68" t="s">
+        <v>380</v>
+      </c>
+      <c r="J68" t="s">
+        <v>381</v>
+      </c>
+      <c r="K68" t="s">
+        <v>74</v>
+      </c>
+      <c r="L68" t="s">
+        <v>340</v>
+      </c>
+      <c r="P68" t="s">
+        <v>382</v>
+      </c>
+      <c r="U68" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>10</v>
+      </c>
+      <c r="B69" t="s">
+        <v>383</v>
+      </c>
+      <c r="C69" t="s">
+        <v>384</v>
+      </c>
+      <c r="D69">
+        <v>2025</v>
+      </c>
+      <c r="E69">
+        <v>5</v>
+      </c>
+      <c r="F69">
+        <v>2</v>
+      </c>
+      <c r="G69" t="s">
+        <v>337</v>
+      </c>
+      <c r="H69">
+        <v>27763242</v>
+      </c>
+      <c r="I69" t="s">
+        <v>385</v>
+      </c>
+      <c r="J69" t="s">
+        <v>386</v>
+      </c>
+      <c r="K69" t="s">
+        <v>74</v>
+      </c>
+      <c r="L69" t="s">
+        <v>340</v>
+      </c>
+      <c r="P69" t="s">
+        <v>387</v>
+      </c>
+      <c r="U69" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>11</v>
+      </c>
+      <c r="B70" t="s">
+        <v>388</v>
+      </c>
+      <c r="C70" t="s">
+        <v>389</v>
+      </c>
+      <c r="D70">
+        <v>2025</v>
+      </c>
+      <c r="E70">
+        <v>5</v>
+      </c>
+      <c r="F70">
+        <v>3</v>
+      </c>
+      <c r="G70" t="s">
+        <v>337</v>
+      </c>
+      <c r="H70">
+        <v>27763242</v>
+      </c>
+      <c r="I70" t="s">
+        <v>390</v>
+      </c>
+      <c r="J70" t="s">
+        <v>391</v>
+      </c>
+      <c r="K70" t="s">
+        <v>74</v>
+      </c>
+      <c r="L70" t="s">
+        <v>340</v>
+      </c>
+      <c r="P70" t="s">
+        <v>392</v>
+      </c>
+      <c r="U70" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/myapp/data_idx_gabung.xlsx
+++ b/myapp/data_idx_gabung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SENTIMENT ANALYSIS UGI AQIS 2026\PROJECT SHINY DASHBOARD ANALISIS SENTIMEN 2026 TERBARU\myapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51853112-18CB-49BF-9EB0-C2980A8E9B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8944BB26-DE2F-4096-BBBB-C84EA7E524AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="819">
   <si>
     <t>No</t>
   </si>
@@ -85,6 +85,336 @@
     <t>Journal Information</t>
   </si>
   <si>
+    <t>Investigating the Role of Logistics Delivery Services in Shaping Customer Satisfaction: LLM-Aspect-Based Sentiment Analysis of Perceived Quality in Indonesian E-Commerce</t>
+  </si>
+  <si>
+    <t>Arbi Setiyawan; Youshi He; Ray Sastri</t>
+  </si>
+  <si>
+    <t>Journal of Theoretical and Applied Electronic Commerce Research</t>
+  </si>
+  <si>
+    <t>0718-1876</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/0718-1876/20/4/345</t>
+  </si>
+  <si>
+    <t>perceived quality; logistics delivery service; customer satisfaction; online review; e-commerce; large language model; aspect-based sentiment analysis</t>
+  </si>
+  <si>
+    <t>A significant challenge in e-commerce is the inability of consumers to physically inspect products, forcing them to rely on perceived quality derived from other consumers’ experiences. However, gaps remain in understanding which dimensions of perceived quality are most frequently mentioned and influential for customer satisfaction, particularly in emerging markets like Indonesia. This study investigates these gaps by identifying key perceived quality aspects and examining their impact on satisfaction, with a specific focus on the moderating role of logistics delivery services. Using a large language model (LLM), specifically Google’s Gemma 2, we performed aspect-based sentiment analysis on 5000 smartphone reviews from Indonesian e-commerce. Logistic regression models incorporating interaction variables were employed to evaluate the relationships. The results identify the most frequently mentioned aspects of perceived quality: Logistics delivery services, Functionality, Originality, Responsiveness, and Packaging. While Logistics delivery services was the most mentioned aspect, Packaging had the most significant direct influence on satisfaction. Notably, Logistics delivery services also play a significant moderating role, enhancing the positive effect of other perceived quality aspects on satisfaction. These findings suggest that Logistics delivery services contribute directly to satisfaction and amplify other aspects, resulting in greater customer satisfaction. The study contributes to the literature by demonstrating LLM-driven aspect-based sentiment analysis methods and expanding the concept of perceived quality to include service aspects, thus promoting a more complete consideration of perceived quality in e-commerce.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=6300153121&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/6300153121?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Multidisciplinary Digital Publishing Institute (MDPI)</t>
+  </si>
+  <si>
+    <t>A hybrid stacked ensemble learning framework for multilabel text emotion detection</t>
+  </si>
+  <si>
+    <t>Hassan Adamu; Masrah Azrifah Azmi Murad; Nurul Amelina Nasharuddin</t>
+  </si>
+  <si>
+    <t>Scientific Reports</t>
+  </si>
+  <si>
+    <t>20452322</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-026-38172-9</t>
+  </si>
+  <si>
+    <t>Multi-label emotion detection; Hybrid stacking; Low-resource NLP; Ensemble learning; Transformer models; Hausa Language</t>
+  </si>
+  <si>
+    <t>Understanding emotions in text is an important part of sentiment analysis, especially in areas like mental health monitoring, customer feedback analysis, hate speech and disaster management. Unlike basic sentiment analysis that classifies text as positive or negative, real human emotions are complex and often overlapping, requiring multi-label classification to accurately capture multiple emotional states within a single input. While transformer-based models have improved performance, challenges persist particularly in low-resource languages and culturally diverse contexts due to the scarcity of annotated data and the difficulty in generalizing in different languages. This study proposes HybStack, a hybrid stacked ensemble framework that integrates simple stacking and cross-validation stacking, combining predictions from four transformer-base models (BERT, DistilBERT, RoBERTa, and mBERT) using a Random Forest meta-classifier to enhance classification accuracy, adaptability, and cross-lingual generalisation. Hyb-Stack was evaluated on three datasets: a high-resource English corpus (SemEval-2018 Task 1 E-c) and two low-resource corpora, the Bahasa Indonesia hate speech and HaEmoC_V1, a newly constructed Hausa-language emotion corpus developed to address the lack of annotated data for this language. Experimental results demonstrate that mBERT outperforms individual base models, achieving F1-scores of 82.28 (HaEmoC_V1), 85.33 (Bahasa Indonesia), and 88.90 (SemEval-2018 English). Also, the EM-9 ensemble set (BERT+DistilBERT+mBERT) improves performance, yielding F1-scores of 89.48, 88.19, and 90.67 on the respective datasets, which surpasses both individual models and conventional ensemble strategies such as averaging and weighted averaging. These findings highlight the effectiveness of combining multiple transformers with an optimized decision layer to advance multi-label emotion classification on diverse linguistic contexts</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100200805&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21100200805</t>
+  </si>
+  <si>
+    <t>Nature Research</t>
+  </si>
+  <si>
+    <t>Dynamic Sentiment Analysis on the Emergence of Pre-Trained Generative Model-Based Applications in Indonesia</t>
+  </si>
+  <si>
+    <t>Frans Mikael Sinaga; Jefri Junifer Pangaribuan; Kelvin; Ferawaty; Andree Emmanuel Widjaja</t>
+  </si>
+  <si>
+    <t>International Journal of Advanced Computer Science and Applications</t>
+  </si>
+  <si>
+    <t>2156-5570</t>
+  </si>
+  <si>
+    <t>https://thesai.org/Publications/ViewPaper?Volume=16&amp;Issue=12&amp;Code=ijacsa&amp;SerialNo=111</t>
+  </si>
+  <si>
+    <t>Dynamic sentiment; fine-grained; IndoBERT; multi-platform big data; sentiment analysis</t>
+  </si>
+  <si>
+    <t>The emergence of pre-trained generative model–based applications has intensified sentiment dynamics within Indonesia’s multi-platform digital ecosystem, where sentiment intensity and temporal fluctuations occur simultaneously. To overcome these challenges, this study extends IndoBERT by incorporating a time-aware tokenization mechanism within a finegrained dynamic sentiment analysis framework. This mechanism is designed to explicitly capture the evolution of sentiment over time. Instead of relying on external embeddings or implicit timestamps, temporal information is injected directly into the IndoBERT tokenizer through explicit temporal tokens, enabling end-to-end temporal adaptation during fine-tuning. We utilized a large-scale dataset harvested from various platforms—including TikTok, Twitter (X), YouTube, and forums—alongside AIgenerated content from Gemini, ChatGPT, and Copilot. The dataset was annotated into five fine-grained sentiment classes: very positive, positive, neutral, negative, and very negative. The experimental evaluation demonstrates that the proposed timeaware IndoBERT model attains an average accuracy of 96.38%, exceeding the performance of the baseline BERT and RoBERTa models. Furthermore, ablation studies validate that the inclusion of time-aware tokenization yields quantifiable performance gains, proving that explicit temporal encoding refines sentiment sensitivity and offers sharper insights into the shifting public opinion in Indonesia.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100867241&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21100867241?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Science and Information Organization</t>
+  </si>
+  <si>
+    <t>Multilabel classification sentiment analysis on Indonesian mobile app reviews</t>
+  </si>
+  <si>
+    <t>Riccosan Riccosan; Karen Etania Saputra</t>
+  </si>
+  <si>
+    <t>IAES International Journal of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>2252-8938</t>
+  </si>
+  <si>
+    <t>https://ijai.iaescore.com/index.php/IJAI/article/view/27183</t>
+  </si>
+  <si>
+    <t>Indonesia; Mobile application review; Multiclass; Multilabel; Sentiment analysis; Text classification</t>
+  </si>
+  <si>
+    <t>Mobile applications continue to evolve to satisfy the users. For that, the developers need to understand user feedback for improvements. Indonesia, one of the countries with the most mobile app users, has many textual mobile app reviews that may be processed and analyzed. Understanding the value of mobile app reviews requires understanding the value of sentiments and emotions to create more appropriate features to satisfy the users. To acquire a more accurate analysis of user reviews, it is important to detect sentiments that are closely associated with human emotion values due to the nature of multilabeled data. This research classifies the sentiments and emotions in Indonesian textual mobile app reviews, which are multilabel and multiclass in the form of 3 sentiments, namely positive, negative, and neutral, paired with 6 emotions, namely anger, sad, fear, happy, love, and neutral. We employ the Transformers architecture model, which includes two monolingual (a generic English and an Indonesian) and a multilingual pre-trained models with the results: bidirectional encoder representations from transformers (BERT) base uncased (micro avg. F1-score=0.69, precision=0.68, recall=0.70, receiver operating characteristic-area under the curve (ROC-AUC)=0.78), IndoBERT base uncased as best result (micro avg. F1-score=0.77, precision=0.78, recall=0.76, ROC-AUC=0.85), and multilingual BERT (M-BERT) base uncased (micro avg. F1-score=0.72, precision=0.73, recall=0.71, ROC-AUC=0.82).</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100901206&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21100901206?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Institute of Advanced Engineering and Science</t>
+  </si>
+  <si>
+    <t>Public Opinion in Political Dynamics: The Role of Political Parties through Social Media in Indonesia</t>
+  </si>
+  <si>
+    <t>Ardika Nurfurkon; Teguh Ilham; Riyan Jaelani; Fadhli Zul Fauzi</t>
+  </si>
+  <si>
+    <t>Asian Journal for Public Opinion Research</t>
+  </si>
+  <si>
+    <t>22886168</t>
+  </si>
+  <si>
+    <t>https://www.ajpor.org/article/158398-public-opinion-in-political-dynamics-the-role-of-political-parties-through-social-media-in-indonesia</t>
+  </si>
+  <si>
+    <t>political dynamics; political parties; social media; X (Twitter); 2024 Indonesian presidential election; sentiment analysis; content analysis</t>
+  </si>
+  <si>
+    <t>This research aims to explore public opinion formed with the dynamics of political parties on social media. Content and sentiment was conducted on posts on X (Twitter). Potential differences between established and new parties on social media were considered, as well as the influences public opinion had on political dynamics in Indonesia. The findings show a sentiment analysis of generally positive perceptions of political parties, with more positive sentiments towards established parties than new parties. The old party cluster consisting of Demokrat, Gerindra, Golkar, Nasdem, PAN, PDIP, Perindo, PKB, PKS, PPP, and PSI has an average positive sentiment of 67% and negative sentiment of 33%, with PPP having the highest positive sentiment (83%). However, PPP was mentioned the least number of times (551 mentions). Meanwhile, the new party cluster consisting of the Buruh, Gelora, and Ummat Parties has an average positive sentiment of 61% and a negative sentiment of 39%, with Buruh having the highest positive sentiment (72%). Of the old parties, Nasdem was mentioned the most frequently (85,696 times), while the most frequently mentioned new party was Ummat (6,268 mentions). New parties’ mentions accounted for only 2.33% of political party mentions. The contribution of this research is that the dominance of established parties in social media discourse indicates the stability of the party system but also has the potential to limit political innovation and responsiveness to new issues.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100899306&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21100899306?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Center for Asian Public Opinion Research and Collaboration Initiative</t>
+  </si>
+  <si>
+    <t>Emotional discourse and symbolic contestation in Indonesia's digital public sphere: an ethnographic content analysis of online reactions from YouTube comments on LPG subsidy regulatory adjustment news</t>
+  </si>
+  <si>
+    <t>Rulli Nasrullah; Murodi; Suhaimi; Umi Musyarrofah; Nunung Khoiriyah; Muhammad Yahya Saraka</t>
+  </si>
+  <si>
+    <t>Frontiers in Communication</t>
+  </si>
+  <si>
+    <t>2297-900X</t>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/communication/articles/10.3389/fcomm.2025.1737481/full</t>
+  </si>
+  <si>
+    <t>audience participation; digital journalism; digital public sphere; ethnographic content analysis; social media</t>
+  </si>
+  <si>
+    <t>Introduction: The regulatory adjustment to Indonesia's subsidized 3-kilogram LPG distribution in February 2025 triggered widespread public unrest and rapidly became a national controversy. The temporary suspension of retail sales produced acute shortages for households and small businesses, leading to significant media amplification and extensive debate across digital platforms. As YouTube increasingly functions as a participatory space for public expression, understanding emotional discourse and symbolic contestation in its comment sections is essential for analyzing how digital publics articulate grievances and influence policy communication.Methods: This study employed Ethnographic Content Analysis (ECA) to examine 426 YouTube comments posted between February 5 and March 1, 2025, responding to the MetroTV news clip covering the LPG subsidy controversy. Comments—including both primary comments and replies—were treated as independent units of analysis. Sentiments were categorized using a six-type framework adapted from Amarasekara and Grant (2019): appearance, sexual/sexist, hostile, positive, critiques/negative, and general/neutral. Two coders independently applied the coding scheme, achieving near-perfect reliability (Krippendorff's Alpha = 0.993). The ethnographic approach enabled analysis not only of textual meaning but also of communicative markers such as phrasing, capitalization, emojis, and rhetorical style.Results: Findings show that negative and critical comments dominated the discourse (197 comments), followed by hostile sentiment (87 comments). These comments frequently expressed frustration, socio-economic grievances, and delegitimization of authority. Positive sentiment (55 comments) was directed not at government officials but at a citizen who confronted the minister, indicating the emergence of symbolic figures representing collective discontent. Appearance-based (17 comments) and sexual/sexist (1 comment) sentiments, though fewer, illustrated the degradation of discourse into ad hominem attacks. Neutral comments (69 comments) reflected factual observations, rhetorical questioning, or conversational engagement. Overall, the comment section functioned as an arena for emotional release, symbolic contestation, and affective communication.Discussion: The study demonstrates that YouTube comment sections operate as affective extensions of the digital public sphere, where emotional intensity and symbolic representation shape civic engagement. Emotional discourse—including sarcasm, humor, ridicule, and direct criticism—served as a mechanism of civic accountability and revealed public dissatisfaction with governance and policy implementation. The prominence of symbolic figures, such as the protesting citizen, underscores how digital publics mobilize emotional narratives to articulate social frustration. These findings extend theoretical understandings of digital participation, highlighting the role of affect, symbolic activism, and ethnographic insight in interpreting public discourse on social media platforms.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21101061926&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21101061926?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Frontiers Media S.A.</t>
+  </si>
+  <si>
+    <t>The Presence of Digital Volunteer and The Absence of Government in Handling Disaster Management on X</t>
+  </si>
+  <si>
+    <t>Rizky Fauziah; Rehia Karenina Isabella Barus; Evi Yunita Kurniaty; Nina Angelia; Beby Masitho Batubara; Audia Junita</t>
+  </si>
+  <si>
+    <t>Studies in Media and Communication</t>
+  </si>
+  <si>
+    <t>2325808X</t>
+  </si>
+  <si>
+    <t>https://redfame.com/journal/index.php/smc/article/view/7936</t>
+  </si>
+  <si>
+    <t>social network analysis; disaster information; digital volunteer; X; Indonesia</t>
+  </si>
+  <si>
+    <t>Extreme climate change around the world has disrupted the seasonal timeline and made it difficult to predict natural disasters, including in Indonesia. Data from BNPB (Badan Nasional Penanggulangan Bencana or National Board for Disaster Management) recorded that from January 1 to May 26, 2025, there were a total of 1,162 natural disaster events. The need for disaster information has become a hot topic in public discourse, especially on X, because formal government information sources are not disseminated quickly, thereby giving rise to digital volunteers. The evolution of public opinion concerning disaster-related information can be effectively examined through social media platforms. Indonesia ranks among the top five countries globally with the highest number of users on X, making the dissemination of disaster information on this platform a matter of strategic importance. Given the platform’s extensive reach, it is imperative for government agencies to actively engage in shaping and guiding disaster-related narratives on X. Such involvement would help mitigate misinformation and influence public perception regarding disaster management. This study utilizes data from X to track the circulation of disaster-related content across Indonesia, focusing specifically on the period from May 1st to May 31st, 2025, during which a notable surge in disaster events occurred. The primary aim of this research is to explore how digital volunteers disseminate information about natural disasters on X, thereby addressing the informational void left by the absence of timely official communication. Key analytical dimensions include user volume, leading influencers, top-performing tweets, user interaction networks, and sentiment dynamics. The study employs social network analysis as its methodological framework, with X serving as the principal data source. The findings of this study reveal that the dissemination of natural disaster information on the X platform is predominantly driven by digital volunteers, largely due to the limited presence and communication from government agencies. A total of 1,476 users were actively involved, forming 2,157 distinct communication networks. Sentiment analysis indicates that user responses comprised 16% positive, 39% negative, and 45% neutral expressions. Within these networks, the most influential account identified was @tanyakanrl, operated by an individual unaffiliated with formal institutions. Further analysis confirms that the leading source of disaster-related information originates from a member of the digital volunteer community, effectively filling the informational void left by the government’s absence on the platform.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21101062494&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21101062494?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Redfame Publishing Inc.</t>
+  </si>
+  <si>
+    <t>Exploring the Icarus Paradox in Indonesia's Specialist Medical Education System Using the Public Perspective From Online Media: Convergent Mixed Methods Study</t>
+  </si>
+  <si>
+    <t>Faisal Binsar; Mohammad Hamsal</t>
+  </si>
+  <si>
+    <t>JMIR Medical Education</t>
+  </si>
+  <si>
+    <t>2369-3762</t>
+  </si>
+  <si>
+    <t>https://mededu.jmir.org/2026/1/e60452</t>
+  </si>
+  <si>
+    <t>Icarus Paradox; aspirations; realities; medical education; student well-being; community perspective; online reviews</t>
+  </si>
+  <si>
+    <t>Background:
+The Icarus Paradox in health care refers to the tension between the ambition to succeed as a specialist doctor and the limitations of the medical education system. Indonesia aspires to produce quality doctors, yet limited infrastructure and resources hinder the educational journey of prospective specialists.
+Objective:
+This study aimed to identify the Icarus Paradox in Indonesia's specialist medical education by examining prospective specialist medical students and the quality of health services and by analyzing how this paradox is reflected in society’s perspectives.
+Methods:
+Using a convergent mixed methods design, this study integrated quantitative content analysis of 5047 online reviews across multiple platforms with qualitative thematic and cognitive analysis using NVivo 14, combining sentiment classification and topic coding.
+Results:
+Twitter contributed 573 (11.3%) of 5047 reviews, with 218 (38%) negative, 251 (43.8%) neutral, and 104 (18.2%) positive entries. TikTok generated 282 (5.6%) reviews, the majority being neutral (n=225, 79.5%). YouTube produced 96 (1.9%) reviews, with 89 (92.7%) neutral entries. News platforms exhibited the largest volume (n=3040, 60.2%) of reviews, with 2885 (94.9%) neutral, 105 (3.5%) positive, and 50 (1.6%) negative entries. Blogs and websites contributed 353 (7%) and 692 (11.3%) reviews, respectively, with neutral sentiment dominating (n=329, 93.2%, for blogs and n=599, 86.6%, for websites). Three cognitive perspectives demonstrated the Icarus Paradox in the Indonesian medical education system: education system, society’s views of students, and health care services. Although there are aspirations to improve education and health care quality, these ambitions often collide with structural challenges, such as resource shortages, heavy workloads, and limited accessibility, which link directly to cognitive themes of stress, resilience, and ethical dilemmas. We proposed a conceptual model to illustrate these dynamics.
+Conclusions:
+Our findings offer insights into the Icarus Paradox in Indonesia’s medical education system, highlighting its complexity and reinforcing the need for systemic reform. Beyond academic relevance, the findings also emphasize the importance of strengthening student mental health support, ensuring equitable access to health care, and enhancing regulatory oversight of training. This was not a clinical trial. Although limited by reliance on online reviews, the results underscore the urgent need for targeted policy interventions in medical education and health care services.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21101029472&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21101029472?origin=resultslist</t>
+  </si>
+  <si>
+    <t>JMIR Publications Inc.</t>
+  </si>
+  <si>
+    <t>Analisis Sentimen Terhadap Film Sri Asih Dengan CNN, KNN, dan Logistic Regression</t>
+  </si>
+  <si>
+    <t>Ester Caroline Dwi Wijaya; Hendry</t>
+  </si>
+  <si>
+    <t>CSRID (Computer Science Research and Its Development Journal)</t>
+  </si>
+  <si>
+    <t>2460870X</t>
+  </si>
+  <si>
+    <t>https://csridjournal.potensi-utama.org/index.php/CSRIDjournal/article/view/44</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis; Twitter; CNN; KNN; Logistic Regression</t>
+  </si>
+  <si>
+    <t>Sinta 3</t>
+  </si>
+  <si>
+    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/159</t>
+  </si>
+  <si>
+    <t>Technological developments have had a big impact on various sectors, one of which is the film industry. This is of course a challenge for film producers to make works that suit people's tastes. The latest film that has become the public's attention is Sri Asih. With the existence of Twitter social media, the writer can use it as an observation of public opinion to analyze public sentiment towards the Sri Asih film and make emotional observations on this sentiment. In the classification process, this research was carried out using three methods, namely Convolutional Neural Network (CNN) with an accuracy of 78%, K-Nearest Neighbor (KNN) with an accuracy of 61%, and Logistic Regression with an accuracy of 81%. By using three different methods, researchers can find that new algorithms that are complex and require large resources, may not necessarily be able to solve the problems in this study. Therefore it can be concluded that Logistic Regression which is a simple algorithm, is still relevant and able to solve the problems that exist in this study. With the results of the accuracy of the Logistic Regression algorithm, it can be used to fulfill the objectives of this study, which is to provide good information about public opinion about the Sri Asih film, as well as being the basis for evaluation for film producers in developing the quality of the Sri Asih film for the better</t>
+  </si>
+  <si>
+    <t>Article Submission: 0.00 (IDR) Authors are not required to pay any Article Submission Fee as part of the submission process. Fast-Track Review: 0.00 (IDR) With this option, the review, editorial decision, and author notification for the manuscript are guaranteed to be completed within 4 weeks. Article Publication: 0.00 (IDR) If the paper is accepted for publication, no Article Publication Fee is required to cover publication costs. Link: https://csridjournal.potensi-utama.org/index.php/CSRIDjournal/fee</t>
+  </si>
+  <si>
+    <t>Analisis Sentimen Model Distilbert Multilingual Cased Dalam Mengklasifikasikan Ulasan Game Genshin Impact</t>
+  </si>
+  <si>
+    <t>Abdullah Sajada; Nurmalitasarib; Eko Purwanto</t>
+  </si>
+  <si>
+    <t>https://csridjournal.potensi-utama.org/index.php/CSRIDjournal/article/view/125</t>
+  </si>
+  <si>
+    <t>Sentiment analysis; DistilBERT Multilingual Cased; Genshin Impact; Game reviews; Information technology evolution</t>
+  </si>
+  <si>
+    <t>The evolution of information technology has revolutionized the way humans interact with the world, particularly in the gaming sector. Genshin Impact, as one of the most popular games with a large global user base, generates millions of user reviews reflecting a diverse range of sentiments. However, accurately understanding and categorizing sentiments in these reviews is challenging, especially due to language variations and nuances in the review texts. This research explores the use of the DistilBERT Multilingual Cased model to analyze sentiments in Genshin Impact game reviews. The study is driven by the need to overcome the limitations of traditional sentiment analysis, which often fails to capture the complexity of language in multilingual reviews. The research methodology includes data collection from Google PlayStore and Apple AppStore, using 8500 reviews, consisting of 4500 Indonesian-language reviews from Google Play Store and 4000 English-language reviews from Apple App Store, manual data labeling, data preprocessing, and the use of the DistilBERT Multilingual Cased model for analysis. The model’s performance is evaluated using metrics such as accuracy, precision, recall, and f1-score. Findings reveal that the model effectively categorizes sentiments in reviews, achieving an overall accuracy of 82%. Precision, recall, and f1-score metrics consistently exceed 0.77 across all sentiment categories. The study concludes that the DistilBERT Multilingual Cased model shows potential as a valuable tool for multilingual sentiment analysis in the realm of game reviews, particularly in the complex and multilingual case of Genshin Impact.</t>
+  </si>
+  <si>
+    <t>Toward nuanced sentiment analysis through multi-sense emoji embedding</t>
+  </si>
+  <si>
+    <t>Junita Amalia; Agnes Veronika Sihombing; Hanna Dhea Christi Sihombing; Nadya Dioranta Tambunan</t>
+  </si>
+  <si>
+    <t>Indonesian Journal of Electrical Engineering and Computer Science</t>
+  </si>
+  <si>
+    <t>25024760</t>
+  </si>
+  <si>
+    <t>https://ijeecs.iaescore.com/index.php/IJEECS/article/view/42852</t>
+  </si>
+  <si>
+    <t>Bi-LSTM; Emojis; Multi-senses skip-gram; Sentiment analysis; Text</t>
+  </si>
+  <si>
+    <t>Sinta 1</t>
+  </si>
+  <si>
+    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/697</t>
+  </si>
+  <si>
+    <t>This research investigates the role of emojis in sentiment analysis using a more comprehensive multi-sense skip-gram approach. Emojis, which can convey facial expressions, body movements, and intonations often challenging to express in text, enhance digital communication by enriching the meaning of messages. Previous studies have shown that emojis improve sentiment analysis, yet most focused solely on their positive and negative connotations. This study broadens the scope by incorporating positive, negative, and neutral sentiment contexts. In the experiments, emojis were embedded in text and converted into vector representations for further analysis. The classification of sentiment texts was performed using a bidirectional long short-term memory (Bi-LSTM) method enhanced with an attention layer. The experiments resulted in accuracy of 0.83, recall of 0.83, precision of 0.82, and F1-score of 0.82. Statistical tests confirmed the significance of these findings, indicating that the approach improves the accuracy of sentiment analysis involving emojis. Overall, the study demonstrates that the integration of text and emojis leads to a more nuanced and precise understanding of sentiment in sentences, confirming the effectiveness of this method.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100799500&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21100799500</t>
+  </si>
+  <si>
+    <t>Article Publication Fee (APF/APC): 225.00 (USD); Article Registration Fee: 225.00 (USD); To support the cost of wide open access dissemination of research results, to manage the various costs associated with handling and editing the submitted manuscripts, and to manage journal management and publication in general, the authors or the author's institution is requested to pay a publication fee. It is our policy that; Each accepted paper will be charged USD 225 for paper collaboration. We do not appreciate papers with a single (sole) author. Papers with a single author will be charged twice, i.e., USD 450. The above charges are for the first 8 pages, and any published manuscript over 8 pages will incur extra charges of USD 50 per page for the collaboration paper and USD 100 for the sole author. Biographies of authors are exempt from the APC fee. Link: https://ijeecs.iaescore.com/index.php/IJEECS/about/submissions#authorFees</t>
+  </si>
+  <si>
     <t>High Performance of Polynomial Kernel at SVM Algorithm for Sentiment Analysis</t>
   </si>
   <si>
@@ -94,6 +424,9 @@
     <t>JITeCS (Journal of Information Technology and Computer Science)</t>
   </si>
   <si>
+    <t>25409824</t>
+  </si>
+  <si>
     <t>https://jitecs.ub.ac.id/index.php/jitecs/article/view/60</t>
   </si>
   <si>
@@ -238,13 +571,13 @@
     <t>Jurnal Fourier</t>
   </si>
   <si>
+    <t>25415239</t>
+  </si>
+  <si>
     <t>https://www.fourier.or.id/index.php/FOURIER/article/view/70</t>
   </si>
   <si>
     <t>Sentiment Analysis; Text Mining; Machine Learning; R</t>
-  </si>
-  <si>
-    <t>Sinta 3</t>
   </si>
   <si>
     <t>https://sinta.kemdiktisaintek.go.id/journals/profile/2191</t>
@@ -284,6 +617,9 @@
     <t>Journal of Information Technology and Computer Science (JOINTECS)</t>
   </si>
   <si>
+    <t>25416448</t>
+  </si>
+  <si>
     <t>https://publishing-widyagama.ac.id/ejournal-v2/index.php/jointecs/article/view/4737</t>
   </si>
   <si>
@@ -365,6 +701,168 @@
     <t>The use of the internet, especially social media, has become a part of national life. This is partly because many members of the House of Representatives of the Republic of Indonesia (DPR RI) convey ideas, policies and provide comments on government policies through social media. This research was conducted to measure opinions or separate positive and negative sentiments towards the DPR RI. The data used in this study was obtained by crawling on social media twitter. The study was conducted using two algorithms namely Support Vector Machine (SVM) and Naive Bayes (NB).Two algorithms are used in this study, Support Vector Machine (SVM), Naive Bayes (NB), and each is optimized using Particle Swarm Optimization (PSO). The accuracy values of cross-validation test of SVM and NB without PSO are 71.04% and 70.69% with Area Under the Curve (AUC) values of 0.817 and 0.661. The accuracy values of cross-validation test using PSO, for SVM and NB are 75.03% and 73.49%, with AUC values of 0.808 and 0.719. The use of PSO can increase the accuracy of SVM 3.99% and 2.8% for NB. The highest value of accuracy recorded, come from SVM using PSO, measured at 75.03%.</t>
   </si>
   <si>
+    <t>Comparison of Salp Swarm Algorithm and Particle Swarm Optimization as Feature Selection Techniques for Recession Sentiment Analysis in Indonesia</t>
+  </si>
+  <si>
+    <t>Dinar Ajeng Kristiyanti; Samuel Ady Sanjaya; Irmawati; Kristian Ekachandra; Jason Suhali; Akhmad Hairul Umam</t>
+  </si>
+  <si>
+    <t>International Journal on Informatics Visualization</t>
+  </si>
+  <si>
+    <t>2549-9904</t>
+  </si>
+  <si>
+    <t>https://joiv.org/index.php/joiv/article/view/3102</t>
+  </si>
+  <si>
+    <t>Feature selection techniques; machine learning classification; recession sentiment analysis; Salp swarm algorithm</t>
+  </si>
+  <si>
+    <t>Amidst global economic uncertainty, this study focuses on Twitter sentiment during the global recession issue on social media, especially in Indonesia. By utilizing sentiment analysis, this study uses machine learning algorithms such as Naïve Bayes (NB), Support Vector Machine (SVM), K-Nearest Neighbor (KNN) which are still less than optimal on high-dimensional Twitter data. The purpose of this study is to improve the accuracy of conventional machine learning using basic metaheuristic algorithms, namely the Salp Swarm Algorithm (SSA) and Particle Swarm Optimization (PSO) as feature selection. From January to May 2023, this study captures the evolving sentiment in response to economic conditions. Data preprocessing, including labeling through the TextBlob and VADER libraries, sets the stage for the analysis. Performance is compared based on labeling techniques, feature selection, and classification algorithms. Specifically, when applied to VADER labeled data without feature selection, the SVM model achieves an outstanding accuracy of 83% and an F1 score of 67%—notably, the application of SSA and PSO results in a reduction in model accuracy by 1%. However, the application of SSA and PSO slightly reduced the model accuracy performance by 1%. On the TextBlob labeled data, SVM showed an outstanding performance (80% accuracy, 77% F1 score). Interestingly, PSO on TextBlob data with SVM significantly decreased the model's performance. These findings contribute significantly to understanding the intricacies of sentiment dynamics during economic uncertainty on social media platforms, with SVM emerging as a strong choice for practical sentiment analysis.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21101033322&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21101033322?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Politeknik Negeri Padang</t>
+  </si>
+  <si>
+    <t>Assessing Indonesian Islamic schools’ readiness for the independent curriculum using text analytics</t>
+  </si>
+  <si>
+    <t>Dian Sa'adillah Maylawatia; Rohmat Mulyana; Naufal Rizqullah; Ilham Nurjaman; Muhammad Ali Ramdhani</t>
+  </si>
+  <si>
+    <t>Multidisciplinary Reviews</t>
+  </si>
+  <si>
+    <t>2595-3982</t>
+  </si>
+  <si>
+    <t>https://malque.pub/ojs/index.php/mr/article/view/8177</t>
+  </si>
+  <si>
+    <t>education; sentiment; summarization; survey; transformers</t>
+  </si>
+  <si>
+    <t>The Merdeka (Independent) Curriculum is an initiative program from Indonesia’s government that aims to enhance education by focusing on student needs and supporting personalized learning. However, this program has received different acceptance from academic communities at elementary to secondary school levels, especially in Islamic schools. Therefore, this study aims to assess the readiness of Islamic schools in Indonesia to implement this curriculum using text analytics techniques, specifically sentiment analysis, text networks, and automatic text summarization. The study analyzed 13,344 survey responses from Islamic school academic communities to evaluate sentiment and understanding regarding the curriculum. A pre-trained Bidirectional Encoder Representations from Transformers (BERT) model was used for sentiment analysis to classify opinions into positive, negative, and neutral categories. The findings revealed that 52.14% of respondents expressed positive sentiments, indicating a strong understanding and favorable outlook toward the Independent Curriculum. However, 36.28% showed negative sentiments, citing challenges such as inadequate resources and infrastructure limitations, while 11.58% remained neutral. These results suggest that while the majority support the curriculum, there are significant areas that require improvement for successful implementation. The report suggests targeted teacher training, improved infrastructure, and continuing evaluations to help the Independent Curriculum be adopted effectively. These findings have important policy implications for educational stakeholders, ensuring a smoother transition and higher effectiveness in curriculum reform efforts.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21101163455&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21101163455?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Malque Publishing</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis of BNI Mobile Application Using The K-Nearest Neighbor Algorithm (KNN) With Particle Swarm Optimization (PSO) Feature Selection</t>
+  </si>
+  <si>
+    <t>Dewi Yustika Lakoro; Ema Utami; Dhani Ariatmanto</t>
+  </si>
+  <si>
+    <t>INTECOMS: Journal of Information Technology and Computer Science</t>
+  </si>
+  <si>
+    <t>26141574</t>
+  </si>
+  <si>
+    <t>https://journal.ipm2kpe.or.id/index.php/INTECOM/article/view/7912</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis; BNI Mobile; TF-IDF; KNN; PSO</t>
+  </si>
+  <si>
+    <t>Sinta 4</t>
+  </si>
+  <si>
+    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/6532</t>
+  </si>
+  <si>
+    <t>Analysis sentiment is field studies analyze opinions, sentiments, evaluations, attitudes and emotions to entity like products, services, organizations, individuals, issues, events, films and topics. Sentiment analysis first succeed used previously in various fields, such as movie ratings, service ratings, product ratings, etc. and recently This get popularity in the field economy especially on e- commerce applications. Moment This industry banking do various innovation finance that is shift their focus from banking traditional to banking based technology for fulfil need customers as well as For increase Power competitive. Mobile banking is one of them from innovation that. Response in use of this mobile banking application enter every the day with amount response as much hundreds so that response the difficult For sorted become responses included positive or including negative response. Study This using private data which is comment BNI Mobile banking application in the application laystore. Existing data Then will be done preprocessing with do a number of stages, ie started from tokenization, stemming, stopword removal and Term Frequency Inverse Document Frequency (TF-IDF) was carried out. Initial process carried out in classification is accept input comment data then the preprocessing process is carried out, then included in the classification model, method classification used is K-Nearest Neighbor with particle swarm optimization Optimization and finally is the results issued is accuracy from method used. After That researcher do optimization use one algorithm optimization namely PSO with combine with KNN or called KNN-PSO gain accuracy of 92.33% or only has an error of 7.67%. If seen from the amount of data is successful do classification as many as 277 data, in meaning only has 23 errors or missing data succeed classified with good.</t>
+  </si>
+  <si>
+    <t>This journal charges the following author fees. Article Submission Charge (ASC): 0.00 (IDR) Article Publication Charge (APC): 800.000 (IDR), If this paper is accepted for publication, you will be asked to pay an Article Publication Fee to cover publications costs. Link: https://journal.ipm2kpe.or.id/index.php/INTECOM/ComitmenFee</t>
+  </si>
+  <si>
+    <t>Analisis Sentimen Ulasan Aplikasi Mola Pada Google Play Store Menggunakan Algoritma Support Vector Machine</t>
+  </si>
+  <si>
+    <t>Muhammad Diki Hendriyanto; Azhari Ali Ridha; Ultach Enri</t>
+  </si>
+  <si>
+    <t>https://journal.ipm2kpe.or.id/index.php/INTECOM/article/view/3708</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis; Support Vector Machine; MOLA</t>
+  </si>
+  <si>
+    <t>MOLA is one of the video streaming platform applications on the google play store. The mola application has been downloaded 5 million times but only has a 3.2 rating. On the Google Play Store app rating is followed by user reviews of the app. There are quite a lot of reviews that are unstructured and contain opinions from users about their satisfaction with the application so that it is often taken into consideration by potential users to choose the application used. Based on this, sentiment analysis was carried out using the Support Vector Machine algorithm to find out how the sentiments of users towards the MOLA application on the google play store were carried out. This study uses the Knowledge Discovery in Database (KDD) method. The data used is a review of the MOLA application with as many 520 data consisting of 312 positive reviews and 208 negative reviews. The best results are obtained in scenario 1 (90:10) using the RBF (Radial Basis Function) kernel which produces 92.31% accuracy, 96.3% precision, 89.66% recall, and 92.86% f1-score.</t>
+  </si>
+  <si>
+    <t>Analyzing Public Sentiment on Digital Banks in Indonesia via Social Media X</t>
+  </si>
+  <si>
+    <t>Erman Arif; Suherman Suherman; Aris Puji Widodo</t>
+  </si>
+  <si>
+    <t>APTISI Transactions on Technopreneurship</t>
+  </si>
+  <si>
+    <t>26568888</t>
+  </si>
+  <si>
+    <t>https://att.aptisi.or.id/index.php/att/article/view/530</t>
+  </si>
+  <si>
+    <t>Public Sentiment; Digital Banks; Social Media X; Sentiment Analysis; Financial Technology</t>
+  </si>
+  <si>
+    <t>This study aims to analyze public sentiment towards digital banks in Indonesia, specifically Bank Jago, using data from social media Twitter. Sentiment analysis methods were used to classify tweets into positive, negative and neutral categories. The findings show that public perceptions are generally positive, with a focus on technological innovation and ease of service. However, key complaints related to technical issues and customer service remain noteworthy. Most tweets had neutral to positive sentiments, reflecting a favorable public view of digital banks. These results highlight the importance for digital banks to continuously improve the customer service and technical stability of their apps to maintain a good reputation in the eyes of the public. In addition, the positive sentiments that arise regarding technological innovation can be leveraged to reinforce the bank’s image as a modern and efficient institution. Recommendations from this study include developing a more responsive customer support system and improving app stability. With these measures, digital banks can maintain public trust and compete in an increasingly competitive market, as well as increase customer satisfaction and loyalty. This research provides valuable insights for digital bank business strategy in Indonesia.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21101196736&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21101196736?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Pandawan Sejahtera</t>
+  </si>
+  <si>
+    <t>Twitter Sentiment Analysis on the Iran-Israel Conflict Using the Naïve Bayes Classification Algorithm</t>
+  </si>
+  <si>
+    <t>Annisa Karima; Athiyatul Ulya; T. Sukma Achriadi Sukiman; Anni Zufia</t>
+  </si>
+  <si>
+    <t>Journal of Computer Science, Information Technology and Telecommunication Engineering (JCoSITTE)</t>
+  </si>
+  <si>
+    <t>27213838</t>
+  </si>
+  <si>
+    <t>https://jurnal.umsu.ac.id/index.php/jcositte/article/view/26093</t>
+  </si>
+  <si>
+    <t>Naive Bayes; Gaussian; Multinomial; Bernoulli</t>
+  </si>
+  <si>
+    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/9768</t>
+  </si>
+  <si>
+    <t>The armed conflict between Iran and Israel, which has attracted global attention, has sparked various public reactions, including from the Indonesian community. Given its potential impact on global social and economic stability, it is important to systematically analyze public perceptions using a sentiment analysis approach. A total of 310 tweets were collected through a crawling process and processed using several preprocessing stages, such as text cleaning, normalization, stopword removal, tokenization, stemming, and translation. Labeling was performed directly using the Naive Bayes algorithm, by comparing three algorithms: Gaussian Naive Bayes, Multinomial Naive Bayes, and Bernoulli Naive Bayes. Performance evaluation was conducted using metrics such as accuracy, precision, recall, and F1-score. The classification results showed that Multinomial Naive Bayes achieved an accuracy of 75.81%, Gaussian Naive Bayes achieved 77.42%, while Bernoulli Naive Bayes achieved 87.1%. Bernoulli Naive Bayes demonstrated superior performance in handling textual data with word frequency representation. This study contributes to strengthening the use of machine learning methods for public opinion analysis on social media, particularly in the context of geopolitical issues. The findings indicate that Bernoulli Naive Bayes is more suitable for classifying public opinion texts compared to the Gaussian and Multinomial variants.</t>
+  </si>
+  <si>
+    <t>As of 2023, authors are enabled to pay page charges with Rp. 350.000,-; which cover the cost of the publishing process and will be invoiced upon paper acceptance.; The cost paid by Author with non-Indonesian citizenship or a collaboration with Indonesian citizenship is USD 0 (Free of charge). Link: https://jurnal.umsu.ac.id/index.php/jcositte/pages/view/fees</t>
+  </si>
+  <si>
     <t>Design of Sentiment Analysis on Indodax Instagram Social Media Comments About Cryptocurrency Using Naïve Bayes Classifier</t>
   </si>
   <si>
@@ -374,6 +872,9 @@
     <t>Al'Adzkiya International of Computer Science and Information Technology Journal</t>
   </si>
   <si>
+    <t>27220001</t>
+  </si>
+  <si>
     <t>https://aladzkiyajournal.com/index.php/AIoCSIT/article/view/325</t>
   </si>
   <si>
@@ -386,34 +887,658 @@
     <t>In today's digital era, social media such as Instagram has become the main platform for many individuals to interact and express opinions online. One application that is often the subject of conversation is Indodax, a well-known digital asset trading platform in Indonesia. This research aims to evaluate the sentiment of Instagram users towards Indodax services through a sentiment analysis approach using Naive Bayes Classifier. The data collected consists of Instagram users' comments, which are analyzed to assess the tendency of their sentiments, whether positive or negative towards Indodax services. This method applies probability and statistical concepts to classify sentiments based on the words present in the comments. It is hoped that the results of this study can provide insights for Indodax to improve the quality of their services based on the perceptions of users. Based on the experiments conducted, the Naive Bayes Classifier method shows fairly accurate classification results, so it can support sentiment analysis related to the Indodax application.</t>
   </si>
   <si>
+    <t>A Framework for Arabic Concept-Level Sentiment Analysis using SenticNet</t>
+  </si>
+  <si>
+    <t>Hend G. Hassan; Hitham M. Abo Bakr; Ibrahim E. Ziedan</t>
+  </si>
+  <si>
+    <t>International Journal of Electrical and Computer Engineering</t>
+  </si>
+  <si>
+    <t>27222578</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/7965</t>
+  </si>
+  <si>
+    <t>Arabic reviews; Opinion mining; Sentiment analysis; Sentiment lexicons</t>
+  </si>
+  <si>
+    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/693</t>
+  </si>
+  <si>
+    <t>Arabic Sentiment analysis research field has been progressing in a slow pace compared to English and other languages. In addition to that most of the contributions are based on using supervised machine learning algorithms while comparing the performance of different classifiers with different selected stylistic and syntactic features. In this paper, we presented a novel framework for using the Concept-level sentiment analysis approach which classifies text based on their semantics rather than syntactic features. Moreover, we provided a lexicon dataset of around 69 k unique concepts that covers multi-domain reviews collected from the internet. We also tested the lexicon on a test sample from the dataset it was collected from and obtained an accuracy of 70%. The lexicon has been made publicly available for scientific purposes.</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21100373959</t>
+  </si>
+  <si>
+    <t>Article Submission: 0.00 (USD); Authors are not required to pay an Article Submission Fee as part of the submission process to contribute to review costs.; Article Publication: 215.00 (USD). Link: https://ijece.iaescore.com/index.php/IJECE/about/submissions#authorFees</t>
+  </si>
+  <si>
+    <t>A Novel Hybrid Classification Approach for Sentiment Analysis of Text Document</t>
+  </si>
+  <si>
+    <t>Yassine Al Amrani; Mohamed Lazaar; Kamal Eddine El Kadiri</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/12393</t>
+  </si>
+  <si>
+    <t>Amazon; Classifiers; Random Forest; Sentiment Analysis; Support Vector Machine</t>
+  </si>
+  <si>
+    <t>Sentiment analysis is a more popular area of highly active research in Automatic Language Processing. She assigns a negative or positive polarity to one or more entities using different natural language processing tools and also predicted high and low performance of various sentiment classifiers. Our approach focuses on the analysis of feelings resulting from reviews of products using original text search techniques. These reviews can be classified as having a positive or negative feeling based on certain aspects in relation to a query based on terms. In this paper, we chose to use two automatic learning methods for classification: Support Vector Machines (SVM) and Random Forest, and we introduce a novel hybrid approach to identify product reviews offered by Amazon. This is useful for consumers who want to research the sentiment of products before purchase, or companies that want to monitor the public sentiment of their brands. The results summarize that the proposed method outperforms these individual classifiers in this amazon dataset.</t>
+  </si>
+  <si>
+    <t>Business intelligence analytics using sentiment analysis-a survey</t>
+  </si>
+  <si>
+    <t>Prakash P. Rokade; Aruna Kumari D.</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/10540</t>
+  </si>
+  <si>
+    <t>Feature extraction; Machine learning; Sentiment analysis</t>
+  </si>
+  <si>
+    <t>Sentiment analysis (SA) is the study and analysis of sentiments, appraisals and impressions by people about entities, person, happening, topics and services. SA uses text analysis techniques and natural language processing methods to locate and extract information from big data. As most of the people are networked themselves through social websites, they use to express their sentiments through these websites.These sentiments are proved fruitful to an individual, business, government for making decisions. The impressions posted on different available sources are being used by organization to know the market mood about the services they are providing. Analyzing huge moods expressed with different features, style have raised challenge for users. This paper focuses on understanding the fundamentals of sentiment analysis, the techniques used for sentiment extraction and analysis. These techniques are then compared for accuracy, advantages and limitations. Based on the accuracy for expexted approach, we may use the suitable technique.</t>
+  </si>
+  <si>
+    <t>Detecting the magnitude of depression in Twitter users using sentiment analysis</t>
+  </si>
+  <si>
+    <t>Jini Jojo Stephen; Prabu P</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/16306</t>
+  </si>
+  <si>
+    <t>Depression; Emotional integrity; Sentiment analysis; Twitter data; Weighted average scoring</t>
+  </si>
+  <si>
+    <t>Today the different social networking sites have enabled everyone to easily express and share their feelings with people around the world. A lot of people use text for communicating, which can be done through different social media messaging platforms available today such as Twitter, Facebook etc, as they find it easier to express their feelings through text instead of speaking them out. Many people who also suffer from stress find it easier to express their feelings on online platform, as over there they can express themselves very easily. So if they are alerted beforehand, there are ways to overcome the mental problems and stress they are suffering from. Depression stands out to be one of the most well known mental health disorders and a major issue for medical and mental health practitioners. Legitimate checking can help in its discovery, which could be useful to anticipate and prevent depression all-together. Hence there is a need for a system, which can cater to such issues and help the user. The purpose of this paper is to propose an efficient method that can detect the level of depression in Twitter users. Sentiment scores calculated can be combined with different emotions to provide a better method to calculate depression scores. This process will help underscore various aspects of depression that have not been understood previously. The main aim is to provide a sense of understanding regarding depression levels in different users and how the scores can be correlated to the main data.</t>
+  </si>
+  <si>
+    <t>Business recommendation based on collaborative filtering and feature engineering – aproposed approach</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/10909</t>
+  </si>
+  <si>
+    <t>Collaborative filtering; Feature extraction; Machine learning; Sentiment analysis</t>
+  </si>
+  <si>
+    <t>Business decisions for any service or product depend on sentiments by people. We get these sentiments or rating on social websites like twitter, kaggle. The mood of people towards any event, service and product are expressed in these sentiments or rating. The text of sentiment contains different linguistic features of sentence. A sentiment sentence also contains other features which are playing a vital role in deciding the polarity of sentiments. If features selection is proper one can extract better sentiments for decision making. A directed preprocessing will feed filtered input to any machine learning approach. Feature based collaborative filtering can be used for better sentiment analysis. Better use of parts of speech (POS) followed by guided preprocessing and evaluation will minimize error for sentiment polarity and hence the better recommendation to the user for business analytics can be attained.</t>
+  </si>
+  <si>
+    <t>Heart rate encapsulation and response tool using sentiment analysis</t>
+  </si>
+  <si>
+    <t>Nandyala Srujana Reddy; Prabadevi B; Deepa B</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/7824</t>
+  </si>
+  <si>
+    <t>Comments; Feedback; Healthcare data; NLP; NLTK; Sentiment analysis</t>
+  </si>
+  <si>
+    <t>Users of every system expect it to get better. Providing feedback to the owners of the system was difficult but with the advent of technology, it has become handy. Users can now post their comments through online blogs, android apps and websites. Due to the enormous data piling up every second, it has become a problem in analyzing it. In this paper, sentiment analysis is used for analyzing comments and reviews posted by users. The experiments are done with dynamic and real data. The tools, algorithms and methodology that could fetch accurate results are described. Experimental results indicate 90% of accuracy in proposed system. The review report generated would help the hospital management to identify the positive and negative feedback which further assists them in improving their facilities that could not only create customer satisfaction but also enhanced business processes.</t>
+  </si>
+  <si>
+    <t>Sentimental classification analysis of polarity multi-view textual data using data mining techniques</t>
+  </si>
+  <si>
+    <t>Ali Hameed Yassir; Ali A. Mohammed; Adel Abdul-Jabbar Alkhazraji; Mustafa Emad Hameed; Mohammed Saad Talib; Mohanad Faeq Ali</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/21583</t>
+  </si>
+  <si>
+    <t>Data mining; Data science; Polarity text data; Sentiment analysis; Text data mining</t>
+  </si>
+  <si>
+    <t>The data and information available in most community environments is complex in nature. Sentimental data resources may possibly consist of textual data collected from multiple information sources with different representations and usually handled by different analytical models. These types of data resource characteristics can form multi-view polarity textual data. However, knowledge creation from this type of sentimental textual data requires considerable analytical efforts and capabilities. In particular, data mining practices can provide exceptional results in handling textual data formats. Besides, in the case of the textual data exists as multi-view or unstructured data formats, the hybrid and integrated analysis efforts of text data mining algorithms are vital to get helpful results. The objective of this research is to enhance the knowledge discovery from sentimental multi-view textual data which can be considered as unstructured data format to classify the polarity information documents in the form of two different categories or types of useful information. A proposed framework with integrated data mining algorithms has been discussed in this paper, which is achieved through the application of X-means algorithm for clustering and HotSpot algorithm of association rules. The analysis results have shown improved accuracies of classifying the sentimental multi-view textual data into two categories through the application of the proposed framework on online polarity user-reviews dataset upon a given topics.</t>
+  </si>
+  <si>
+    <t>Multi-lingual Twitter sentiment analysis using machine learning</t>
+  </si>
+  <si>
+    <t>K. Arun; A. Srinagesh</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/20770</t>
+  </si>
+  <si>
+    <t>Machine learning algorithms; Multilingual; NLP; Twitter sentiment analysis</t>
+  </si>
+  <si>
+    <t>Twitter Sentiment Analysis is one of the leading research fields nowadays. Most of the researchers have contributed to the research in twitter sentiment analysis in English tweets, but few researchers have focused on the multilingual twitter sentiment analysis. Still, some more challenges are present and not yet addressed in the domain of multilingual twitter sentiment analysis (MLTSA). Research is highly warranted in these unexplored areas. This study presents the implementation of sentiment analysis in multilingual twitter data and improves the data classification up to the adequate level of accuracy. Twitter is the sixth leading social networking site in the world. Active users for twitter in a month are 330 million. People can tweet or retweet in their languages and allow users to use emoji’s, abbreviations, contraction words, misspellings, and shortcut words. The best platform for sentiment analysis is twitter. Multilingual tweets and data sparsity are the two main challenges. In this paper, the MLTSA algorithm gives the solution for these two challenges. MLTSA algorithm is divided into two parts. One for detecting and translating non-English tweets into English using natural language processing (NLP) and the second one is an appropriate pre-processing method with NLP support that can reduce the data sparsity. The result of the MLTSA with SVM achieves good accuracy by up to 95%.</t>
+  </si>
+  <si>
+    <t>Sentiment analysis of comments in social media</t>
+  </si>
+  <si>
+    <t>Abdulrahman Alrumaih; Ali Al-Sabbagh; Ruaa Alsabah; Harith Kharrufa; James Baldwin</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/22285</t>
+  </si>
+  <si>
+    <t>Complex networks; Sentimental analysis; Social media platform; Tweets</t>
+  </si>
+  <si>
+    <t>Social media platforms are witnessing a significant growth in both size and purpose. One specific aspect of social media platforms is sentiment analysis, by which insights into the emotions and feelings of a person can be inferred from their posted text. Research related to sentiment analysis is acquiring substantial interest as it is a promising filed that can improve user experience and provide countless personalized services. Twitter is one of the most popular social media platforms, it has users from different regions with a variety of cultures and languages. It can thus provide valuable information for a diverse and large amount of data to be used to improve decision making. In this paper, the sentiment orientation of the textual features and emoji-based components is studied targeting “Tweets” and comments posted in Arabic on Twitter, during the 2018 world cup event. This study also measures the significance of analyzing texts including or excluding emojis. The data is obtained from thousands of extracted tweets, to find the results of sentiment analysis for texts and emojis separately. Results show that emojis support the sentiment orientation of the texts and those texts or emojis cannot separately provide reliable information as they complement each other to give the intended meaning.</t>
+  </si>
+  <si>
+    <t>A powerful comparison of deep learning frameworks for Arabic sentiment analysis</t>
+  </si>
+  <si>
+    <t>Youssra Zahidi; Yacine El Younoussi; Yassine Al-Amrani</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/21154</t>
+  </si>
+  <si>
+    <t>ANLP; ASA; DL; Java libraries; Python libraries</t>
+  </si>
+  <si>
+    <t>Deep learning (DL) is a machine learning (ML) subdomain that involves algorithms taken from the brain function named artificial neural networks (ANNs). Recently, DL approaches have gained major accomplishments across various Arabic natural language processing (ANLP) tasks, especially in the domain of Arabic sentiment analysis (ASA). For working on Arabic SA, researchers can use various DL libraries in their projects, but without justifying their choice or they choose a group of libraries relying on their particular programming language familiarity. We are basing in this work on Java and Python programming languages because they have a large set of deep learning libraries that are very useful in the ASA domain. This paper focuses on a comparative analysis of different valuable Python and Java libraries to conclude the most relevant and robust DL libraries for ASA. Throw this comparative analysis, and we find that: TensorFlow, Theano, and Keras Python frameworks are very popular and very used in this research domain</t>
+  </si>
+  <si>
+    <t>Different valuable tools for Arabic sentiment analysis: a comparative evaluation</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/21153</t>
+  </si>
+  <si>
+    <t>ANLP; ASA; ASA programming languages; Java libraries; Python libraries</t>
+  </si>
+  <si>
+    <t>Arabic Natural language processing (ANLP) is a subfield of artificial intelligence (AI) that tries to build various applications in the Arabic language like Arabic sentiment analysis (ASA) that is the operation of classifying the feelings and emotions expressed for defining the attitude of the writer (neutral, negative or positive). In order to work on ASA, researchers can use various tools in their research projects without explaining the cause behind this use, or they choose a set of libraries according to their knowledge about a specific programming language. Because of their libraries' abundance in the ANLP field, especially in ASA, we are relying on JAVA and Python programming languages in our research work. This paper relies on making an in-depth comparative evaluation of different valuable Python and Java libraries to deduce the most useful ones in Arabic sentiment analysis (ASA). According to a large variety of great and influential works in the domain of ASA, we deduce that the NLTK, Gensim and TextBlob libraries are the most useful for Python ASA task. In connection with Java ASA libraries, we conclude that Weka and CoreNLP tools are the most used, and they have great results in this research domain</t>
+  </si>
+  <si>
+    <t>MTVRep: A movie and TV show reputation system based on fine-grained sentiment and semantic analysis</t>
+  </si>
+  <si>
+    <t>Abdessamad Benlahbib; El Habib Nfaoui</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/23876</t>
+  </si>
+  <si>
+    <t>Decision making; Fine-grained sentiment analysis; Natural language processing; Reputation generation; Text mining</t>
+  </si>
+  <si>
+    <t>Customer reviews are a valuable source of information from which we can extract very useful data about different online shopping experiences. For trendy items (products, movies, TV shows, hotels, services . . . ), the number of available users and customers’ opinions could easily surpass thousands. Therefore, online reputation systems could aid potential customers in making the right decision (buying, renting, booking . . . ) by automatically mining textual reviews and their ratings. This paper presents MTVRep, a movie and TV show reputation system that incorporates fine-grained opinion mining and semantic analysis to generate and visualize reputation toward movies and TV shows. Differently from previous studies on reputation generation that treat the task of sentiment analysis as a binary classification problem (positive, negative), the proposed system identifies the sentiment strength during the phase of sentiment classification by using fine-grained sentiment analysis to separate movie and TV show reviews into five discrete classes: strongly negative, weakly negative, neutral, weakly positive and strongly positive. Besides, it employs embeddings from language models (ELMo) representations to extract semantic relations between reviews. The contribution of this paper is threefold. First, movie and TV show reviews are separated into five groups based on their sentiment orientation. Second, a custom score is computed for each opinion group. Finally, a numerical reputation value is produced toward the target movie or TV show. The efficacy of the proposed system is illustrated by conducting several experiments on a real-world movie and TV show dataset.</t>
+  </si>
+  <si>
+    <t>Performance analysis of sentiments in Twitter dataset using SVM models</t>
+  </si>
+  <si>
+    <t>Lakshmana Kumar Ramasamy; Seifedine Kadry; Yunyoung Nam; Maytham N. Meqdad</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/21825</t>
+  </si>
+  <si>
+    <t>Machine learning; Sentiment analysis; SVM model; Twitter dataset</t>
+  </si>
+  <si>
+    <t>Sentiment analysis is a current research topic by many researches using supervised and machine learning algorithms. The analysis can be done on movie reviews, twitter reviews, online product reviews, blogs, discussion forums, Myspace comments and social networks. The Twitter data set is analyzed using support vector machines (SVM) classifier with various parameters. The content of tweet is classified to find whether it contains fact data or opinion data. The deep analysis is required to find the opinion of the tweets posted by the individual. The sentiment is classified in to positive, negative and neutral. From this classification and analysis, an important decision can be made to improve the productivity. The performance of SVM radial kernel, SVM linear grid and SVM radial grid was compared and found that SVM linear grid performs better than other SVM models</t>
+  </si>
+  <si>
+    <t>Personal customized recommendation system reflecting purchase criteria and product reviews sentiment analysis</t>
+  </si>
+  <si>
+    <t>Wu Guanchen; Minkyu Kim; Hoekyung Jung</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/23916</t>
+  </si>
+  <si>
+    <t>Product attribute; Purchase priority; Recommend system; Sentiment analysis</t>
+  </si>
+  <si>
+    <t>As the size of the e-commerce market grows, the consequences of it are appearing throughout society. The business environment of a company changes from a product center to a user center and introduces a recommendation system. However, the existing research has shown a limitation in deriving customized recommendation information to reflect the detailed information that users consider when purchasing a product. Therefore, the proposed system reflects the user's subjective purchasing criteria in the recommendation algorithm. And conduct sentiment analysis of product review data. Finally, the final sentiment score is weighted according to the purchase criteria priority, recommends the results to the user.</t>
+  </si>
+  <si>
+    <t>The impact of sentiment analysis from user on Facebook to enhanced the service quality</t>
+  </si>
+  <si>
+    <t>Daniel D. Albesta; Michael L. Jonathan; Muhammad Jawad; Oktovianus Hardiawan; Derwin Suhartono</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/24576</t>
+  </si>
+  <si>
+    <t>Data mining; Facebook; Sentiment analysis; Service quality</t>
+  </si>
+  <si>
+    <t>Facebook's influence on the modern social media platform is undoubtedly enormous. While it has gotten a backlash for its inability to control its influence over important affairs, there are still many questions regarding people's perception of Facebook and their sentiment over Facebook. This paper's role in this ongoing debate is to give a glimpse of people's sentiment and perception of Facebook in recent times. By collecting samples data from Facebook's Top Page, this paper hopes to represent a significant amount of people's aspirations towards this company. By processing the data with a processing tool to construct and model out the data and a sentiment analyzer tool helps determine the sentiment, this paper can deduce a 600-comment worth of processed data. The results from the 600 sampled comments concluded that the sentiments towards Facebook are 41.50% negative comments, 22.83% neutral comments, and 35.67% positive comments.</t>
+  </si>
+  <si>
+    <t>Sentiment analysis on film review in Gujarati language using machine learning</t>
+  </si>
+  <si>
+    <t>Parita Shah; Priya Swaminarayan; Maitri Patel</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/24642</t>
+  </si>
+  <si>
+    <t>Classifier; Features selection; Film; Gujarati; Precision; Sentimentality</t>
+  </si>
+  <si>
+    <t>Opinion analysis is by a long shot most basic zone of characteristic language handling. It manages the portrayal of information to choose the motivation behind the wellspring of the content. The reason might be of a type of gratefulness (positive) or study (negative). This paper offers a correlation between the outcomes accomplished by applying the calculation arrangement using various classifiers for instance K-nearest neighbor and multinomial naive Bayes. These techniques are utilized to assess a significant assessment with either a positive remark or negative remark. The gathered information considered on the grounds of the extremity film datasets and an association with the results accessible proof has been created for a careful assessment. This paper investigates the word level count vectorizer and term frequency inverse document frequency (TF-IDF) influence on film sentiment analysis. We concluded that multinomial naive Bayes (MNB) classier generate more accurate result using TF-IDF vectorizer compared to CountVectorizer, K-nearest-neighbors (KNN) classifier has the same accuracy result in case of TF-IDF and CountVectorizer.</t>
+  </si>
+  <si>
+    <t>Text pre-processing of multilingual for sentiment analysis based on social network data</t>
+  </si>
+  <si>
+    <t>Neha Garg; Kamlesh Sharma</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/25456</t>
+  </si>
+  <si>
+    <t>Code-switch; Linguistic-switching; Machine learning; Multilingual; Pre-processing; Sentiment analysis</t>
+  </si>
+  <si>
+    <t>Sentiment analysis (SA) is an enduring area for research especially in the field of text analysis. Text pre-processing is an important aspect to perform SA accurately. This paper presents a text processing model for SA, using natural language processing techniques for twitter data. The basic phases for machine learning are text collection, text cleaning, pre-processing, feature extractions in a text and then categorize the data according to the SA techniques. Keeping the focus on twitter data, the data is extracted in domain specific manner. In data cleaning phase, noisy data, missing data, punctuation, tags and emoticons have been considered. For pre-processing, tokenization is performed which is followed by stop word removal (SWR). The proposed article provides an insight of the techniques, that are used for text pre-processing, the impact of their presence on the dataset. The accuracy of classification techniques has been improved after applying text preprocessing and dimensionality has been reduced. The proposed corpus can be utilized in the area of market analysis, customer behaviour, polling analysis, and brand monitoring. The text pre-processing process can serve as the baseline to apply predictive analysis, machine learning and deep learning algorithms which can be extended according to problem definition.</t>
+  </si>
+  <si>
+    <t>Improving collaborative filtering using lexicon-based sentiment analysis</t>
+  </si>
+  <si>
+    <t>Rouhia Mohammed Sallam; Mahmoud Hussein; Hamdy M. Mousa</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/24346</t>
+  </si>
+  <si>
+    <t>A large-scale Arabic book; reviews dataset; Collaborative filtering; LABR lexicon; Sentiment analysis</t>
+  </si>
+  <si>
+    <t>Since data is available increasingly on the Internet, efforts are needed to develop and improve recommender systems to produce a list of possible favorite items. In this paper, we expand our work to enhance the accuracy of Arabic collaborative filtering by applying sentiment analysis to user reviews, we also addressed major problems of the current work by applying effective techniques to handle the scalability and sparsity problems. The proposed approach consists of two phases: the sentiment analysis and the recommendation phase. The sentiment analysis phase estimates sentiment scores using a special lexicon for the Arabic dataset. The item-based and singular value decomposition-based collaborative filtering are used in the second phase. Overall, our proposed approach improves the experiments’ results by reducing average of mean absolute and root mean squared errors using a large Arabic dataset consisting of 63,000 book reviews.</t>
+  </si>
+  <si>
+    <t>A sentiment analysis model of agritech startup on Facebook comments using naive Bayes classifier</t>
+  </si>
+  <si>
+    <t>Nawapon Kewsuwun; Siriwan Kajornkasirat</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/25674</t>
+  </si>
+  <si>
+    <t>Agritech startup; Facebook; Naive Bayes; Python; Sentiment analysis</t>
+  </si>
+  <si>
+    <t>Facebook page is a tool able to generate perceptions and acceptance, and support people and investors in making business decisions. Moreover, Facebook page plays a part in engaging people in the form of a community. People share experiences and opinions toward products, services, and trends in particular periods on the Facebook page community. Regarding sentiment analysis on Facebook pages, most education and other general topics in English have only been analyzed in English. However, sentiment analysis regarding agritech startups topics in Thai language has not been done yet. This study analyzes opinions and categorizes positive and negative comments by using naive Bayes classifier to examine the sentiments and attitudes of people and investors. The results could possibly reflect the perception rate of agritech startups in Thailand and could be applied to explain attentiveness and assess people’s engagement opinions. Furthermore, it could be applied in studying consumer behavior, marketing analysis, spread of information, and attitudes. The study's model is generic and could be applied in other contexts to provide insightful suggestions.</t>
+  </si>
+  <si>
+    <t>Ensemble-based face expression recognition approach for image sentiment analysis</t>
+  </si>
+  <si>
+    <t>Ervin Gubin Moung; Chai Chuan Wooi; Maisarah Mohd Sufian; Chin Kim On; Jamal Ahmad Dargham</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/26411</t>
+  </si>
+  <si>
+    <t>Classification; Convolutional neural network; Ensemble; Facial expression recognition; Image sentiment analysis; InceptionV3; ResNet50</t>
+  </si>
+  <si>
+    <t>Sentiment analysis based on images is an evolving area of study. Developing a reliable facial expression recognition (FER) device remains a difficult challenge as recognizing emotional feelings reflected in an image is dependent on a diverse set of factors. This paper presented an ensemblebased model for FER that incorporates multiple classification models: i) customized convolutional neural network (CNN), ii) ResNet50, and iii) InceptionV3. The model averaging ensemble classifier method is used to ensemble the predictions from the three models. Subsequently, the proposed FER model is trained and tested on a dataset with an uncontrolled environment (FER-2013 dataset). The experiment demonstrated that ensembling multiple classifiers outperformed all single classifiers in classifying positive and neutral expressions (91.7%, 81.7% and 76.5% accuracy rate for happy, surprise, and neutral, respectively). However, when classifying disgust, anger, and sadness, the ResNet50 model alone is the better choice. Although the Custom CNN performs the best in classifying fear expression (55.7% accuracy), the proposed FER model can still classify fear expression with comparable performance (52.8% accuracy). This paper demonstrated the potential of using the ensemble-based method to enhance the performance of FER. As a result, the proposed FER model has shown a 72.3% accuracy rate.</t>
+  </si>
+  <si>
+    <t>Analyzing sentiment dynamics from sparse text coronavirus disease-19 vaccination using natural language processing model</t>
+  </si>
+  <si>
+    <t>Jalaja Govindappa; Kavitha Channegowda</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/26390</t>
+  </si>
+  <si>
+    <t>Coronavirus disease-19; Machine learning; Natural language processing; Sentiment analysis; Tweeter; Vaccination</t>
+  </si>
+  <si>
+    <t>Social media platforms enable people exchange their thoughts, reactions, emotions regarding all aspects of their lives. Therefore, sentiment analysis using textual data is widely practiced field. Due to large textual content available on social media, sentiment analysis is usually considered a text classification task. The high feature dimension is an important issue that needs to be resolved by examining text meaningfully. The proposed study considers a case study of coronavirus (COVID) vaccination to conclude public opinions about prospects for vaccination. Text corpus of tweets is collected, published between December 12, 2020, and July 13, 2021 is considered. The proposed model is developed considering phase-by-phase data analysis process, followed by an assessment of important information about the collected tweets on coronavirus disease (COVID-19) vaccine using two sentiment analyzer methods and probabilistic models for validation and knowledge analysis. The result indicated that public sentiment is more positive than negative. The study also presented statistics of trends in vaccination progress in the top countries from early 2021 to July 2021. The scope of study is enormous regarding sentiment analysis based on keywordand document modeling. The proposed work offers an effective mechanism for a decision-making system to understand public opinion and accordingly assists policymakers in health measures and vaccination campaigns.</t>
+  </si>
+  <si>
+    <t>Analysis of student sentiment during video class with multilayer deep learning approach</t>
+  </si>
+  <si>
+    <t>Imrus Salehin; Nazmun Nessa Moon; Iftakhar Mohammad Talha; Md. Mehedi Hasan; Farnaz Narin Nur; Md. Azizul Hakim; Farhan Al Haque</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/26434</t>
+  </si>
+  <si>
+    <t>Convolutional neural network; Deep learning; Electronic-learning; Image data; Sentiment analysis</t>
+  </si>
+  <si>
+    <t>The modern education system is an essential part of the rise of technology. The E-learning education system is not just an experimental system; it is a vital learning system for the whole world over the last few months. In our research, we have developed our learning method in a more effective and modern way for students and teachers. For significant implementation, we are implementing convolutions neural networks and advanced data classifiers. The expression and mood analysis of a student during the online class is the main focus of our study. For output measure, we divide the final output result as attentive, inattentive, understand, and neutral. Showing the output in real-time online class and for sensory analysis, we have used support vector machine (SVM) and OpenCV. The level of 5*4 neural network is created for this work. An advanced learning medium is proposed through our study. Teachers can monitor the live class and different feelings of a student during the class period through this system.</t>
+  </si>
+  <si>
+    <t>Dialectal Arabic sentiment analysis based on tree-based pipeline optimization tool</t>
+  </si>
+  <si>
+    <t>Soukaina Mihi; Brahim Ait Ben Ali; Ismail El Bazi; Sara Arezki; Nabil Laachfoubi</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/24935</t>
+  </si>
+  <si>
+    <t>AutoML; Informal Arabic; Polarity detection; Sentiment analysis; Tree-based optimization tool</t>
+  </si>
+  <si>
+    <t>The heavy involvement of the Arabic internet users resulted in spreading data written in the Arabic language and creating a vast research area regarding natural language processing (NLP). Sentiment analysis is a growing field of research that is of great importance to everyone considering the high added potential for decision-making and predicting upcoming actions using the texts produced in social networks. Arabic used in microblogging websites, especially Twitter, is highly informal. It is not compliant with neither standards nor spelling regulations making it quite challenging for automatic machine-learning techniques. In this paper’s scope, we propose a new approach based on AutoML methods to improve the efficiency of the sentiment classification process for dialectal Arabic. This approach was validated through benchmarks testing on three different datasets that represent three vernacular forms of Arabic. The obtained results show that the presented framework has significantly increased accuracy than similar works in the literature.</t>
+  </si>
+  <si>
+    <t>Sentiment analysis on Bangla conversation using machine learning approach</t>
+  </si>
+  <si>
+    <t>Mahmudul Hassan; Shahriar Shakil; Nazmun Nessa Moon; Mohammad Monirul Islam; Refath Ara Hossain; Asma Mariam; Fernaz Narin Nur</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/27095</t>
+  </si>
+  <si>
+    <t>Accuracy rate; Detection approach; Natural language processing; Sentiment analysis; Support vector machine; Tokenizer</t>
+  </si>
+  <si>
+    <t>Nowadays, online communication is more convenient and popular than faceto-face conversation. Therefore, people prefer online communication over face-to-face meetings. Enormous people use online chatting systems to speak with their loved ones at any given time throughout the world. People create massive quantities of conversation every second because of their online engagement. People's feelings during the conversation period can be gleaned as useful information from these conversations. Text analysis and conclusion of any material as summarization can be done using sentiment analysis by natural language processing. The use of communication for customer service portals in various e-commerce platforms and crime investigations based on digital evidence is increasing the need for sentiment analysis of a conversation. Other languages, such as English, have welldeveloped libraries and resources for natural language processing, yet there are few studies conducted on Bangla. It is more challenging to extract sentiments from Bangla conversational data due to the language's grammatical complexity. As a result, it opens vast study opportunities. So, support vector machine, multinomial naïve Bayes, k-nearest neighbors, logistic regression, decision tree, and random forest was used. From the dataset, extracted information was labeled as positive and negative.</t>
+  </si>
+  <si>
+    <t>An automated essay evaluation system using natural language processing and sentiment analysis</t>
+  </si>
+  <si>
+    <t>Vijaya Shetty Sadanand; Kadagathur Raghavendra Rao Guruvyas; Pranav Prashantha Patil; Jeevan Janardhan Acharya; Sharvani Gunakimath Suryakanth</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/28738</t>
+  </si>
+  <si>
+    <t>Essay scoring; Long short-term memory; Natural language processing; Plagiarism check; Sentiment analyzer</t>
+  </si>
+  <si>
+    <t>An automated essay evaluation system is a machine-based approach leveraging long short-term memory (LSTM) model to award grades to essays written in English language. natural language processing (NLP) is used to extract feature representations from the essays. The LSTM network learns from the extracted features and generates parameters for testing and validation. The main objectives of the research include proposing and training an LSTM model using a dataset of manually graded essays with scores. Sentiment analysis is performed to determine the sentiment of the essay as either positive, negative or neutral. The twitter sample dataset is used to build sentiment classifier that analyzes the sentiment based on the student’s approach towards a topic. Additionally, each essay is subjected to detection of syntactical errors as well as plagiarism check to detect the novelty of the essay. The overall grade is calculated based on the quality of the essay, the number of syntactic errors, the percentage of plagiarism found and sentiment of the essay. The corrected essay is provided as feedback to the students. This essay grading model has gained an average quadratic weighted kappa (QWK) score of 0.911 with 99.4% accuracy for the sentiment analysis classifier.</t>
+  </si>
+  <si>
+    <t>Enhanced sentiment analysis based on improved word embeddings and Xgboost</t>
+  </si>
+  <si>
+    <t>Amina Samih; Abderrahim Ghadi; Abdelhadi Fennan</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/28408</t>
+  </si>
+  <si>
+    <t>Machine learning; Sentiment analysis; Sentiment2Vec; Word2Vec; Xgboost</t>
+  </si>
+  <si>
+    <t>Sentiment analysis is a well-known and rapidly expanding study topic in natural language processing (NLP) and text classification. This approach has evolved into a critical component of many applications, including politics, business, advertising, and marketing. Most current research focuses on obtaining sentiment features through lexical and syntactic analysis. Word embeddings explicitly express these characteristics. This article proposes a novel method, improved words vector for sentiments analysis (IWVS), using XGboost to improve the F1-score of sentiment classification. The proposed method constructed sentiment vectors by averaging the word embeddings (Sentiment2Vec). We also investigated the Polarized lexicon for classifying positive and negative sentiments. The sentiment vectors formed a feature space to which the examined sentiment text was mapped to. Those features were input into the chosen classifier (XGboost). We compared the F1-score of sentiment classification using our method via different machine learning models and sentiment datasets. We compare the quality of our proposition to that of baseline models, term frequency-inverse document frequency (TF-IDF) and Doc2vec, and the results show that IWVS performs better on the F1-measure for sentiment classification. At the same time, XGBoost with IWVS features was the best model in our evaluation.</t>
+  </si>
+  <si>
+    <t>Sentiment analysis in SemEval: a review of sentiment identification approaches</t>
+  </si>
+  <si>
+    <t>Bousselham El Haddaoui; Raddouane Chiheb; Rdouan Faizi; Abdellatif El Afia</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/28825</t>
+  </si>
+  <si>
+    <t>Deep learning; Machine learning; Sentiment analysis; Social media; Transformers</t>
+  </si>
+  <si>
+    <t>Social media platforms are becoming the foundations of social interactions including messaging and opinion expression. In this regard, sentiment analysis techniques focus on providing solutions to ensure the retrieval and analysis of generated data including sentiments, emotions, and discussed topics. International competitions such as the International Workshop on Semantic Evaluation (SemEval) have attracted many researchers and practitioners with a special research interest in building sentiment analysis systems. In our work, we study top-ranking systems for each SemEval edition during the 2013-2021 period, a total of 658 teams participated in these editions with increasing interest over years. We analyze the proposed systems marking the evolution of research trends with a focus on the main components of sentiment analysis systems including data acquisition, preprocessing, and classification. Our study shows an active use of preprocessing techniques, an evolution of features engineering and word representation from lexicon-based approaches to word embeddings, and the dominance of neural networks and transformers over the classification phase fostering the use of ready-to-use models. Moreover, we provide researchers with insights based on experimented systems which will allow rapid prototyping of new systems and help practitioners build for future SemEval editions.</t>
+  </si>
+  <si>
+    <t>Customer sentiment analysis for Arabic social media using a novel ensemble machine learning approach</t>
+  </si>
+  <si>
+    <t>Nouri Hicham; Sabri Karim; Nassera Habbat</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/30603</t>
+  </si>
+  <si>
+    <t>Arabic language; Ensemble classifier; Machine learning; Novel approach; Sentiment analysis</t>
+  </si>
+  <si>
+    <t>Arabic’s complex morphology, orthography, and dialects make sentiment analysis difficult. This activity makes it harder to extract text attributes from short conversations to evaluate tone. Analyzing and judging a person’s emotional state is complex. Due to these issues, interpreting sentiments accurately and identifying polarity may take much work. Sentiment analysis extracts subjective information from text. This research evaluates machine learning (ML) techniques for understanding Arabic emotions. Sentiment analysis (SA) uses a support vector machine (SVM), AdaBoost classifier (AC), maximum entropy (ME), k-nearest neighbors (KNN), decision tree (DT), random forest (RF), logistic regression (LR), and naive Bayes (NB). A model for the ensemble-based sentiment was developed. Ensemble classifiers (ECs) with 10-fold cross-validation out-performed other machine learning classifiers in accuracy (A), specificity (S), precision (P), F1 score (FS), and sensitivity (S).</t>
+  </si>
+  <si>
+    <t>A large-scale sentiment analysis using political tweets</t>
+  </si>
+  <si>
+    <t>Yin Min Tun; Myo Khaing</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/29712</t>
+  </si>
+  <si>
+    <t>Apache flume; Big data analytic; Machine learning; Sentiment analysis Apache; Social media data; Spark</t>
+  </si>
+  <si>
+    <t>Twitter has become a key element of political discourse in candidates’ campaigns. The political polarization on Twitter is vital to politicians as it is a popular public medium to analyze and predict public opinion concerning political events. The analysis of the sentiment of political tweet contents mainly depends on the quality of sentiment lexicons. Therefore, it is crucial to create sentiment lexicons of the highest quality. In the proposed system, the domain-specific of the political lexicon is constructed by using the supervised approach to extract extreme political opinions words, and features in tweets. Political multi-class sentiment analysis (PMSA) system on the big data platform is developed to predict the inclination of tweets to infer the results of the elections by conducting the analysis on different political datasets: including the Trump election dataset and the BBC News politics. The comparative analysis is the experimental results which are better political text classification by using the three different models (multinomial naïve Bayes (MNB), decision tree (DT), linear support vector classification (SVC)). In the comparison of three different models, linear SVC has the better performance than the other two techniques. The analytical evaluation results show that the proposed system can be performed with 98% accuracy in linear SVC.</t>
+  </si>
+  <si>
+    <t>Graph embedding approach to analyze sentiments on cryptocurrency</t>
+  </si>
+  <si>
+    <t>Ihab Moudhich; Abdelhadi Fennan</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/32713</t>
+  </si>
+  <si>
+    <t>Graph embedding; Machine learning; Natural language processing; Sentiment analysis; Word embedding; Word2vec</t>
+  </si>
+  <si>
+    <t>This paper presents a comprehensive exploration of graph embedding techniques for sentiment analysis. The objective of this study is to enhance the accuracy of sentiment analysis models by leveraging the rich contextual relationships between words in text data. We investigate the application of graph embedding in the context of sentiment analysis, focusing on it is effectiveness in capturing the semantic and syntactic information of text. By representing text as a graph and employing graph embedding techniques, we aim to extract meaningful insights and improve the performance of sentiment analysis models. To achieve our goal, we conduct a thorough comparison of graph embedding with traditional word embedding and simple embedding layers. Our experiments demonstrate that the graph embedding model outperforms these conventional models in terms of accuracy, highlighting it is potential for sentiment analysis tasks. Furthermore, we address two limitations of graph embedding techniques: handling out-of-vocabulary words and incorporating sentiment shift over time. The findings of this study emphasize the significance of graph embedding techniques in sentiment analysis, offering valuable insights into sentiment analysis within various domains. The results suggest that graph embedding can capture intricate relationships between words, enabling a more nuanced understanding of the sentiment expressed in text data.</t>
+  </si>
+  <si>
+    <t>Emoji’s sentiment score estimation using convolutional neural network with multi-scale emoji images</t>
+  </si>
+  <si>
+    <t>Theerawee Kulkongkoon; Nagul Cooharojananone; Rajalida Lipikorn</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/33163</t>
+  </si>
+  <si>
+    <t>Convolutional neural network; Emoji classification; Majority voting with; probability; Multi-scale images; Sentiment analysis</t>
+  </si>
+  <si>
+    <t>Emojis are any small images, symbols, or icons that are used in social media. Several well-known emojis have been ranked and sentiment scores have been assigned to them. These ranked emojis can be used for sentiment analysis; however, many new released emojis have not been ranked and have no sentiment score yet. This paper proposes a new method to estimate the sentiment score of any unranked emotion emoji from its image by classifying it into the class of the most similar ranked emoji and then estimating the sentiment score using the score of the most similar emoji. The accuracy of sentiment score estimation is improved by using multi-scale images. The ranked emoji image data set consisted of 613 classes with 161 emoji images from three different platforms in each class. The images were cropped to produce multi-scale images. The classification and estimation were performed by using convolutional neural network (CNN) with multiscale emoji images and the proposed voting algorithm called the majority voting with probability (MVP). The proposed method was evaluated on two datasets: ranked emoji images and unranked emoji images. The accuracies of sentiment score estimation for the ranked and unranked emoji test images are 98% and 51%, respectively.</t>
+  </si>
+  <si>
+    <t>Smart city: an advanced framework for analyzing public sentiment orientation toward recycled water</t>
+  </si>
+  <si>
+    <t>Mohamed Bahra; Abdelhadi Fennan</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/30789/17157</t>
+  </si>
+  <si>
+    <t>Fuzzy logic; Neural network; Ontology; Recycled water; Sentiment analysis; Sentiment orientation; Smart city</t>
+  </si>
+  <si>
+    <t>The coronavirus pandemic of the past several years has had a profound impact on all aspects of life, including resource utilization. One notable example is the increased demand for freshwater, a lifeblood of our planet, on the other hand, the smart city vision aims to attain a smart water management goal by investing in innovative solutions such as recycled water systems. However, the problem lies in the public’s sentiment and willingness to use this new resource which discourages investors and hinders the development of this field. Therefore, in our work, we applied sentiment analysis using an extended version of the fuzzy logic and neural network model from our previous work, to find out the general public opinion regarding recycled water and to assess the effects of sentiments on the public’s readiness to use this resource. Our analysis was based on a dataset of over 1 million text content from 2013 to 2022. The results show, from spatio-temporal perspectives, that sentiment orientation and acceptance behavior towards using recycled water have increased positively. Additionally, the public is more concerned in areas driven by the smart city vision than in areas of medium and low economic development, where investment in sensibilization campaigns is needed.</t>
+  </si>
+  <si>
+    <t>Sentimental analysis of audio based customer reviews without textual conversion</t>
+  </si>
+  <si>
+    <t>Sumana Maradithaya; Anantshesh Katti</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/33116</t>
+  </si>
+  <si>
+    <t>Deep neural network; Feature extraction; Mel frequency cepstral; coefficients; Natural language processing; Sentiment analysis; Speech emotion</t>
+  </si>
+  <si>
+    <t>The current trends or procedures followed in the customer relation management system (CRM) are based on reviews, mails, and other textual data, gathered in the form of feedback from the customers. Sentiment analysis algorithms are deployed in order to gain polarity results, which can be used to improve customer services. But with evolving technologies, lately reviews or feedbacks are being dominated by audio data. As per literature, the audio contents are being translated to text and sentiments are analyzed using natural processing language techniques. However, these approaches can be time consuming. The proposed work focuses on analyzing the sentiments on the audio data itself without any textual conversion. The basic sentiment analysis polarities are mostly termed as positive, negative, and natural. But the focus is to make use of basic emotions as the base of deciding the polarity. The proposed model uses deep neural network and features such as Mel frequency cepstral coefficients (MFCC), Chroma and Mel Spectrogram on audio-based reviews</t>
+  </si>
+  <si>
+    <t>Automatic customer review summarization using deep learning based hybrid sentiment analysis</t>
+  </si>
+  <si>
+    <t>Gagandeep Kaur; Amit Sharma</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/32036</t>
+  </si>
+  <si>
+    <t>Aspect features; Customer review summarization; Deep learning; Hybrid features; Review features; Sentiment analysis</t>
+  </si>
+  <si>
+    <t>Customer review summarization (CRS) offers business owners summarized customer feedback. The functionality of CRS mainly depends on the sentiment analysis (SA) model; hence it needs an efficient SA technique. The aim of this study is to construct an SA model employing deep learning for CRS (SADL-CRS) to present summarized data and assist businesses in understanding the behavior of their customers. The SA model employing deep learning (SADL) and CRS phases make up the proposed automatic SADL-CRS model. The SADL consists of review preprocessing, feature extraction, and sentiment classification. The preprocessing stage removes irrelevant text from the reviews using natural language processing (NLP) methods. The proposed hybrid approach combines review-related features and aspect-related features to efficiently extract the features and create a unique hybrid feature vector (HF) for each review. The classification of input reviews is performed using a deep learning (DL) classifier long shortterm memory (LSTM). The CRS phase performs the automatic summarization employing the outcome of SADL. The experimental evaluation of the proposed model is done using diverse research data sets. The SADL-CRS model attains the average recall, precision, and F1-score of 95.53%, 95.76%, and 95.06%, respectively. The review summarization efficiency of the suggested model is improved by 6.12% compared to underlying CRS methods.</t>
+  </si>
+  <si>
+    <t>The social media sentiment analysis framework: deep learning for sentiment analysis on social media</t>
+  </si>
+  <si>
+    <t>Prasanna Kumar Rangarjan; Bharathi Mohan Gurusamy; Gayathri Muthurasu; Rithani Mohan; Gundala Pallavi; Sulochana Vijayakumar Ali Altalbe</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/35391</t>
+  </si>
+  <si>
+    <t>Convolutional neural networks; Deep neural networks; Emotion; Recurrent neural networks; Sentiment analysis; Social media</t>
+  </si>
+  <si>
+    <t>Researching public opinion can help us learn important facts. People may quickly and easily express their thoughts and feelings on any subject using social media, which creates a deluge of unorganized data. Sentiment analysis on social media platforms like Twitter and Facebook has developed into a potent tool for gathering insights into users' perspectives. However, difficulties in interpreting natural language limit the effectiveness and precision of sentiment analysis. This research focuses on developing a social media sentiment analysis (SMSA) framework, incorporating a custom-built emotion thesaurus to enhance the precision of sentiment analysis. It delves into the efficacy of various deep learning algorithms, under different parameter calibrations, for sentiment extraction from social media. The study distinguishes itself by its unique approach towards sentiment dictionary creation and its application to deep learning models. It contributes new insights into sentiment analysis, particularly in social media contexts, showcasing notable advancements over previous methodologies. The results demonstrate improved accuracy and deeper understanding of social media sentiment, opening avenues for future research and applications in diverse fields.</t>
+  </si>
+  <si>
+    <t>Negation handling for sentiment analysis task: approaches and performance analysis</t>
+  </si>
+  <si>
+    <t>Lutfi Budi Ilmawan; Muladi; Didik Dwi Prasetya</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/35021</t>
+  </si>
+  <si>
+    <t>Hybrid approach; Machine learning; Multi-task learning; Negation handling; Negation scope detection; Rule-based</t>
+  </si>
+  <si>
+    <t>Negation plays an essential role in sentiment analysis within natural language processing (NLP). Its integration involves two key aspects: identifying the scope of negation and incorporating this information into the sentiment model. Before delving into scope detection, the specific negation cue must be identified, with explicit and implicit negation cues being the two main types. Various methodologies, such as rule-based, machine learning, and hybrid approaches, address the negation scope detection challenge. Strategies for leveraging negation information in sentiment models encompass heuristic polarity modification, feature space augmentation, endto-end approach, and hierarchical multi-task learning. Notably, there is a need for more studies addressing implicit negation cue detection, even within the state-of-the-art bidirectional encoder representation for transformers (BERT) approach. Some studies have employed reinforcement learning and hybrid techniques to address the implicit negation problem. Further exploration, particularly through a hybrid and multi-task learning approach, is warranted to make potential contributions to the nuanced challenges of handling negation in sentiment analysis, especially in complex sentence structures</t>
+  </si>
+  <si>
+    <t>Enhancing online learning: sentiment analysis and collaborative filtering from Twitter social network for personalized recommendations</t>
+  </si>
+  <si>
+    <t>Qamar El Maazouzi; Asmaâ Retbi; Samir Bennani</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/34747</t>
+  </si>
+  <si>
+    <t>Deep learning; E-learning; Natural language processing; Recommender system; Sentiment analysis; Social media</t>
+  </si>
+  <si>
+    <t>Online learning presents a major challenge for learners, namely the diversification of courses and information overload. In response to this issue, recommender systems are widely used. Nowadays, social networks have become a global platform where individuals share a multitude of information. For instance, Twitter is a social network where users exchange messages and interact with various communities. These interactions on social networks have created a new dimension in the field of online learning. In this article, we propose a novel approach that combines sentiment analysis of learners’ reviews on social networks with collaborative filtering methods to provide more personalized and relevant course recommendations. To achieve this, we explored different models to analyze the sentiments of tweets related to online courses. Additionally, we used collaborative filtering based on k-nearest neighbors (KNN). Our results demonstrate that integrating sentiment analysis provides more relevant recommendations. This has also been shown based on the calculation of root mean square error (RMSE) compared to a traditional approach. In this study, we demonstrated that by leveraging this information from social networks like Twitter, online learning platforms can enhance the effectiveness of their course recommendations, tailoring them to each individual learner’s needs.</t>
+  </si>
+  <si>
     <t>AlgoDM: algorithm to perform aspect-based sentiment analysis using IDistance matrix</t>
   </si>
   <si>
     <t>Sandhya Raghavendra Savanur; Sumathi Ranganathaiah; Shreedhara Kondajji Srinivasamurthy</t>
   </si>
   <si>
-    <t>International Journal of Electrical and Computer Engineering</t>
-  </si>
-  <si>
     <t>https://ijece.iaescore.com/index.php/IJECE/article/view/34461</t>
   </si>
   <si>
     <t>Aspect-based; Distance matrix; Sentence level; Sentiment analysis; Text analysis</t>
   </si>
   <si>
-    <t>Sinta 1</t>
-  </si>
-  <si>
-    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/693</t>
-  </si>
-  <si>
     <t>Sentiment analysis is a method of analyzing data to identify its intent. It identifies the emotional tone of a text body. Aspect-based sentiment analysis is a text analysis technique that identifies the aspect and the sentiment associated with each aspect. Different organizations use aspect-based sentiment analysis to analyze opinions about a product, service, or idea. Traditional sentiment analysis methods analyze the complete text and assign a single sentiment label to it. They do not handle the tasks of aspect association, dealing with multiple aspects and inclusion of linguistic concepts together as a system. In this article, AlgoDM, an algorithm to perform aspect-based sentiment analysis is proposed. AlgoDM uses a novel concept of IDistance matrix to extract aspects, associate aspects with sentiment words, and determine the sentiment associated with each aspect. The IDistance matrix is constructed to calculate the distance between aspects and the words expressing the sentiment related to the aspect. It works at the sentence level and identifies the opinion expressed on each aspect appearing in the sentence. It also evaluates the overall sentiment expressed in the sentence. The proposed algorithm can perform sentiment analysis of any opinionated text.</t>
   </si>
   <si>
-    <t>https://www.scopus.com/sourceid/21100373959</t>
-  </si>
-  <si>
-    <t>Article Submission: 0.00 (USD); Authors are not required to pay an Article Submission Fee as part of the submission process to contribute to review costs.; Article Publication: 215.00 (USD). Link: https://ijece.iaescore.com/index.php/IJECE/about/submissions#authorFees</t>
+    <t>Optimized automated testing: test case generation and maintenance using latent semantic analysis-based TextRank and particle swarm optimization algorithms</t>
+  </si>
+  <si>
+    <t>Baswaraju Swathi; Soma Sekhar Kolisetty</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/34859</t>
+  </si>
+  <si>
+    <t>Automated testing; Latent semantic analysis-based; TextRank; Natural language processing; Particle swarm optimization; Test case generation; Test case maintenance</t>
+  </si>
+  <si>
+    <t>Software development would have to include automated testing to ensure the finished product and performs as intended. However, the process of test case generation and maintenance can be time-consuming and error-prone, especially when manual methods are used. This research proposes a new approach to improve the efficiency and accuracy of automated testing using latent semantic analysis (LSA)-based TextRank (TR) and particle swarm optimization (PSO) algorithms. The study aims to evaluate the effectiveness of these algorithms in generating and optimizing test cases based on requirements analysis. To retrieve key information from the criteria, methods including text classification (TC), named entity recognition (NER), and sentiment analysis (SA) are used to evaluate the text. Test cases are then generated using LSA-based TR for text summarization and PSO for optimization. The aim of this work is to identify any limitations that need to be addressed and to evaluate the overall efficiency and accuracy of automated testing (AT) using proposed algorithms. The results of this research are expected to have important implications for the software industry, helps to improve the overall efficiency and accuracy of AT. The findings could guide future research that led to the creation of more advanced and effective tools for AT.</t>
+  </si>
+  <si>
+    <t>Aspect-based sentiment analysis: natural language understanding for implicit review</t>
+  </si>
+  <si>
+    <t>Suhariyanto; Riyanarto Sarno; Chastine Fatichah; Rachmad Abdullah</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/36262</t>
+  </si>
+  <si>
+    <t>Aspect-based sentiment analysis; Bidirectional encoder; representations from; transformers; Machine learning; Natural language understanding; Semantic similarity</t>
+  </si>
+  <si>
+    <t>The different types of implicit reviews should be well understood so that the developed extraction technique can solve all problems in implicit reviews and produce precise terms of aspects and opinions. We propose an aspect based sentiment analysis (ABSA) method with natural language understanding for implicit reviews based on sentence and word structure. We built a text extraction method using a machine learning algorithm rule with a deep understanding of different types of sentences and words. Furthermore, the aspect category of each review is determined by measuring the word similarity between the aspect terms contained in each review and aspect keywords extracted from Wikipedia. Bidirectional encoder representations from transformers (BERT) embedding and semantic similarity are used to measure the word similarity value. Moreover, the proposed ABSA method uses BERT, a hybrid lexicon, and manual weighting of opinion terms. The purpose of the hybrid lexicon and the manual weighting of opinion terms is to update the existing lexicon and solve the problem of weighting words and phrases of opinion terms. The evaluation results were very good, with average F1-scores of 93.84% for aspect categorization and 92.42% for ABSA.</t>
+  </si>
+  <si>
+    <t>Enhancing sentiment analysis in Kannada texts by feature selection</t>
+  </si>
+  <si>
+    <t>Sunil Mugalihalli Eshwarappa; Vinay Shivasubramanyan</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/36130</t>
+  </si>
+  <si>
+    <t>BERT; Kannada; Probability clustering; SemEval 2014; Sentiment analysis</t>
+  </si>
+  <si>
+    <t>In recent years, there has been a noticeable surge in research activities focused on sentiment analysis within the Kannada language domain. The existing research highlights a lack of labelled datasets and limited exploration in feature selection for Kannada sentiment analysis, hindering accurate sentiment classification. To address this gap, the study aims to introduce a novel Kannada dataset and develop an effective classifier for improved sentiment analysis in Kannada texts. The study presents a new Kannada dataset from SemEval 2014 Task4 using Google Translate. It then introduces a modified bidirectional encoder representation from transformers BERT for Kannada dataset called as Kannada-BERT (K-BERT). Further, a probability-clustering (PC) approach is presented to extract the topics and its related aspects. Both the K-BERT classifier and PC approach were merged to attain a K-BERT-PC classifier, integrating a modified BERT model and probability clustering approach for achieving better results. Experimental results demonstrate that K-BERT-PC achieves superior performance in polarity and sentiment analysis accuracy, with an impressive accuracy rate of 91%, surpassing existing classifiers. This work contributes by providing a solution to the scarcity of labelled datasets for Kannada sentiment analysis and introduces an effective classifier, K-BERT-PC, for enhanced sentiment analysis outcomes in Kannada texts.</t>
+  </si>
+  <si>
+    <t>Enhancing sentiment analysis through deep layer integration with long short-term memory networks</t>
+  </si>
+  <si>
+    <t>Parul Dubey; Pushkar Dubey; Hitesh Gehani</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/37040</t>
+  </si>
+  <si>
+    <t>Deep learning; Long short-term memory; Natural language processing; Sentiment analysis; Text classification</t>
+  </si>
+  <si>
+    <t>This involves studying one of the most important parts of natural language processing (NLP): sentiment, or whether a thing that makes a sentence is neutral, positive, or negative. This paper presents an enhanced long short-term memory (LSTM) network for the sentiment analysis task using an additional deep layer to capture sublevel patterns from the word input. So, the process that we followed in our approach is that we cleaned the data, preprocessed it, built the model, trained the model, and finally tested it. The novelty here lies in the additional layer in the architecture of LSTM model, which improves the model performance. We added a deep layer with the intention of improving accuracy and generalizing the model. The results of the experiment are analyzed using recall, F1-score, and accuracy, which in turn show that the deep-layered LSTM model gives us a better prediction. The LSTM model outperformed the baseline in terms of accuracy, recall, and f1-score. The deep layer's forecast accuracy increased dramatically once it was trained to capture intricate sequences. However, the improved model overfitted, necessitating additional regularization and hyperparameter adjustment. In this paper, we have discussed the advantages and disadvantages of using deep layers in LSTM networks and their application to developing models for deep learning with better-performing sentiment analysis.</t>
+  </si>
+  <si>
+    <t>An improved reptile search algorithm-based machine learning for sentiment analysis</t>
+  </si>
+  <si>
+    <t>Nitesh Sureja; Nandini M. Chaudhari; Jalpa Bhatt; Tushar Desai; Vruti Parikh; Sonia Panesar; Heli Sureja; Jahnavi Kharva</t>
+  </si>
+  <si>
+    <t>https://ijece.iaescore.com/index.php/IJECE/article/view/36230</t>
+  </si>
+  <si>
+    <t>Deep learning; Machine learning; Reinforcement learning; Reptile search algorithm; Sentiment analysis; Social media; Swarm intelligence</t>
+  </si>
+  <si>
+    <t>The rapid growth of mobile technologies has transformed social media, making it crucial for expressing emotions and thoughts. When making significant decisions, businesses and governments can benefit from understanding public opinion. This information makes sentiment analysis vital for understanding public sentiment polarity. This study develops a hyper tuned deep learning model with swarm intelligence and many approaches for sentiment analysis. convolutional neural network (CNN), bidirectional encoder representations from transformers (BERT), long shortterm memory (LSTM), CNN-LSTM, BERT-LSTM, and BERT-CNN are the six deep learning models of the sentiment analysis using deep learning with reinforced learning based on reptile search algorithm (SA-DLRLRSA) model. The reptile search algorithm, an enhanced swarm intelligence algorithm (SIA), optimizes deep learning model hyper parameters. Word2Vec word embedding is used to convert textual input sequences to representative embedding spaces. Pre-trained Word2Vec embedding is also used to address issue of unbalanced datasets. Experimental results demonstrate that the SA-DLRLRSA model works best with accuracies of 93.1%, 94.7%, 96.8%, 96.3%, 97.2%, and 98.3% utilizing CNN, LSTM, BERT, CNN-LSTM, BERT-CNN, and BERT-LSTM</t>
   </si>
   <si>
     <t>Systematic Literature Review: Analisa Sentimen Masyarakat terhadap Penerapan Peraturan ETLE</t>
@@ -425,6 +1550,9 @@
     <t>Journal of Applied Computer Science and Technology (JACOST)</t>
   </si>
   <si>
+    <t>27231453</t>
+  </si>
+  <si>
     <t>https://journal.isas.or.id/index.php/JACOST/article/view/493</t>
   </si>
   <si>
@@ -470,6 +1598,31 @@
     <t>Mental health is a significant concern in society today, particularly for Generation Z, who are vulnerable to experiencing mental health problems that can disrupt daily productivity. The influence of working hours also contributes to the mental health of this generation. To assess public opinion on this issue, sentiment analysis is needed on social media, especially twitter. This research uses the Gaussian Naïve Bayes algorithm and Support Vector Machine with various stemming algorithms such as Nazief-Adriani, Arifin Setiono, and Sastrawi. The sentiment analysis method is used to assess positive, negative, and neutral sentiment in related tweets. The research results show that the Sastrawi stemming algorithm on the Gaussian Naïve Bayes model achieves 84% precision, 84% recall, and 84% f1-score, with 84% accuracy. Meanwhile, Support Vector Machine achieved 91% precision, 90% recall, 90% f1-score, and 91% accuracy. The Nazief-Adriani stemming algorithm on the Gaussian Naïve Bayes model has 80% precision, 80% recall, and 80% f1-score, with 80% accuracy. Meanwhile, on the Support Vector Machine, precision is 87%, recall is 85%, f1-score is 86%, and accuracy is 85%. Arifin Setiono's stemming algorithm on the Gaussian Naïve Bayes model achieved 81% precision, 81% recall, 81% f1-score, with 82% accuracy, while on Support Vector Machine, 88% precision, 86% recall, 86% f1-score, with 86% accuracy. Public opinion was recorded as 33% positive, 9% neutral, and 58% negative. This research aims to increase public awareness of the importance of mental health, especially regarding the influence of working hours, to create a healthy work environment for Generation Z and society in general, as well as improving the quality of mental health.</t>
   </si>
   <si>
+    <t>Application Of TF-IDF And Word2vec For Feature Extraction In Sentiment Analysis Of Free Nutritious Food Policies</t>
+  </si>
+  <si>
+    <t>Qisthi Annisa Haq; Alam Rahmatulloh</t>
+  </si>
+  <si>
+    <t>Journal of Computer, Electronic, and Telecommunication (COMPLETE)</t>
+  </si>
+  <si>
+    <t>27235912</t>
+  </si>
+  <si>
+    <t>https://journal.ittelkom-sby.ac.id/complete/article/view/741</t>
+  </si>
+  <si>
+    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/11039</t>
+  </si>
+  <si>
+    <t>Abstract: The free nutritious meal policy has become a hot topic of discussion among the public because it is related to improving health and education quality. However, its implementation has given rise to a variety of pros and cons that need to be analyzed systematically. This study aims to analyze sentiment toward the policy by utilizing Term Frequency–Inverse Document Frequency (TF-IDF) and Word2Vec as feature extraction methods on public review data obtained from social media X. After undergoing preprocessing and automatic labeling, the data was classified into positive and negative sentiments using the Support Vector Machine (SVM) algorithm. The analysis results show that the sentiment data is unbalanced, with the positive class dominating at 75% and the negative class at 25%. In model testing, TF-IDF achieved an accuracy of 81%, while Word2Vec achieved an accuracy of 80%. This difference shows that TF-IDF is more stable in handling short and informal texts, while Word2Vec still has the potential to capture the semantic context between words. This research opens up opportunities for further research, it is recommended to balance the data between classes and combine the TF-IDF and Word2Vec methods, or use a deep learning approach such as BERT to obtain more accurate results and capture deeper semantic context.</t>
+  </si>
+  <si>
+    <t>Free for submissions that include at least one author from outside Indonesia. This includes mixed author groups with both Indonesian and international authors.
+A fee of IDR 500,000 applies if all authors of the submission are from Indonesia. Link: https://journal.ittelkom-sby.ac.id/complete/PublicationCharge</t>
+  </si>
+  <si>
     <t>Analyzing Public Sentiment Toward Makanan Bergizi Gratis Program Using Machine Learning</t>
   </si>
   <si>
@@ -479,6 +1632,9 @@
     <t>Computer Science (CO-SCIENCE)</t>
   </si>
   <si>
+    <t>27749711</t>
+  </si>
+  <si>
     <t>https://jurnal.bsi.ac.id/index.php/co-science/article/view/10445</t>
   </si>
   <si>
@@ -554,6 +1710,36 @@
     <t>Transportation is a means that a person uses to move from one place to another. One mode of transportation that is popular among the public is online motorcycle taxis, such as Gojek. Gojek continues to innovate to meet customer needs more effectively, as well as expand the scope of its services. This research aims to identify the number of positive and negative sentiments in the user review dataset, evaluate the performance of the algorithm used, and measure the level of customer satisfaction with Gojek services. Analysis was carried out on 6,485 customer reviews, which resulted in 4,387 positive sentiments and 2,098 negative sentiments. The classification model used, namely Naive Bayes, shows an accuracy of 88.5%, precision of 88.1%, and recall of 89.0%. The results of this research indicate that the Naive Bayes method provides good performance in analyzing the sentiment of user reviews of Gojek services</t>
   </si>
   <si>
+    <t>Public Reactions to Indonesia's KRIS Policy: A Textual Network Analysis of Digital Legitimacy</t>
+  </si>
+  <si>
+    <t>Pradono Handojo; Sudarsono Hardjosoekarto; Lydia Freyani Hayadi; Lora Luayya; Haifa Mayang Lestari; Rianca Amalia</t>
+  </si>
+  <si>
+    <t>Journal of Public Health and Pharmacy</t>
+  </si>
+  <si>
+    <t>27754952</t>
+  </si>
+  <si>
+    <t>https://jurnal.unismuhpalu.ac.id/index.php/jphp/article/view/7401</t>
+  </si>
+  <si>
+    <t>Text Network Analysis; Public Policy; Public Health; Inpatient Class; Nursing Policy; Health Insurance; YouTube Comments; Digital Legitimacy</t>
+  </si>
+  <si>
+    <t>Introduction: Through the Presidential Regulation No. 59 of 2024 issued on May 8, 2024, the Government of Indonesia announced the elimination of the three-class inpatient service (Class 1, Class 2, and Class 3) in Indonesia. The regulation introduces a single standard inpatient service class (KRIS), effective July 1, 2025. This study analyzes the KRIS nursing policy by exploring comments on YouTube news reports during two distinct periods: before and after the policy announcement. It also evaluates the impact of public communication efforts by relevant institutions on public support for the policy. Methodologically, this study introduces a novel approach by integrating Textual Network Analysis (TNA) with digital legitimacy theory, offering a fresh lens to examine the construction of policy legitimacy in digital environments (YouTube). Methods: To address the first research question, TNA was conducted on comments on YouTube, capturing and analyzing public responses to KRIS policy-related news during both pre- and post-policy announcement periods. Data were collected using Communalityc and APIFY and analyzed using Gephi to visualize and generate word networks. To address the second research question, the authors quantified KRIS policy socialization videos and compared them with COVID-19 vaccination campaign videos, followed by a qualitative analysis. Results: The authors discover that public discourse and sentiment remained consistently negative both pre- and post-announcement. However, the focus of the discussion shifted from complaints about service quality and contribution burdens to more direct concerns over increased contributions and reduced benefits. Regarding the second research question, the authors conclude that compared to the COVID-19 vaccination campaign, efforts to promote the benefits of the KRIS policy have been relatively limited, with minimal engagement from the four government institutions involved. Conclusion: This study provides valuable insights into public discourse and sentiment regarding the Standard Inpatient Class (KRIS) policy, which is scheduled to take effect on July 1, 2025. The findings suggest that the government should strengthen its public engagement by adopting a more intensive, structured, and coordinated communication strategy—similar to that employed during the COVID-19 vaccination campaign—to boost public acceptance and enhance policy legitimacy</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21101197193&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21101197193?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Muhammadiyah Palu University</t>
+  </si>
+  <si>
     <t>Analysis of Public Opinion Sentiment About Covid-19 Vaccination in Indonesia Using Naïve Bayes and Decission Tree</t>
   </si>
   <si>
@@ -563,6 +1749,9 @@
     <t>Malcom: Indonesian Journal of Machine Learning and Computer Science</t>
   </si>
   <si>
+    <t>27758575</t>
+  </si>
+  <si>
     <t>https://journal.irpi.or.id/index.php/malcom/article/view/63</t>
   </si>
   <si>
@@ -878,6 +2067,51 @@
     <t>Starlink, a satellite internet service from SpaceX, will begin operations in Indonesia in 2024 to address the digital divide in remote areas. However, its presence poses challenges such as high prices, potential impact on local providers, and regulatory issues. This research analyzes public sentiment towards Starlink using Naïve Bayes algorithm combined with TF-IDF and Cross Validation techniques which are still rarely applied in similar studies in Indonesia. The data used are Indonesian tweets from users of platform X during May-November 2024. The analysis results show that the Naïve Bayes model has optimal performance in detecting positive sentiment compared to negative or neutral, as measured using confusion matrix. The main findings showed that Naïve Bayes 49.38% of tweets had positive sentiment, 32.94% were neutral, and 17.68% were negative. The positive sentiment was dominated by appreciation of the speed and stability of the service, while the negative sentiment criticized the high price and its impact on local providers. While the model performed well on positive sentiments, the classification accuracy of negative and neutral sentiments still needs to be improved. The results of this study provide strategic insights for Starlink's business development as well as a basis for consideration for the government regarding satellite-based internet services in Indonesia</t>
   </si>
   <si>
+    <t>Comparison of Naïve Bayes and Support Vector Machine in Sentiment Analysis of Confiscation of Corrupt Assets on Twitter</t>
+  </si>
+  <si>
+    <t>Ananda sholekhah; Muntahanah Muntahanah</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2068</t>
+  </si>
+  <si>
+    <t>Asset Forfeiture; Corruptors; Naive Bayes; Sentiment Analysis; Support Vector Machine</t>
+  </si>
+  <si>
+    <t>Sentiment analysis is one approach used to understand public perception of social issues and government policies through textual data. This study examines Indonesian public opinion toward President Prabowo Subianto’s statement regarding the confiscation of corruptors’ assets, which questioned, "Is it fair for the children to suffer?”. The dataset was collected from Twitter, comprising 1,561 tweets gathered between April 9 and April 25, 2025, using relevant keywords. The analysis involved preprocessing, TF-IDF vectorization, and classification using Naïve Bayes and Support Vector Machine (SVM) algorithms. Model performance was evaluated using a confusion matrix and four evaluation metrics: accuracy, precision, recall, and F1-score. The results indicate that SVM outperformed Naïve Bayes, achieving an accuracy of 70.51% and an F1-score of 0.69, while Naïve Bayes recorded 66.34% accuracy and 0.66 F1-score. Most of the sentiments were classified as positive, reflecting majority public support for the asset confiscation policy despite its impact on the perpetrators’ families. This research demonstrates the effectiveness of machine learning-based classification in mapping public opinion on controversial policy issues through social media platforms.</t>
+  </si>
+  <si>
+    <t>Comparison of Deep Learning Algorithm in Sentiment Analysis Ecotourism in Bogor</t>
+  </si>
+  <si>
+    <t>Peni Agustini; Muhammad Iqbal; Vicha Amalia Akbar; Robert Kurniawan</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2191</t>
+  </si>
+  <si>
+    <t>Bogor; Deep Learning; Ecotourism; Scraping; Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>Bogor has a leading ecotourism destination in Indonesia, offering pristine nature and easy access from Jakarta. However, the increasing number of tourists poses challenges to environmental management, such as waste management and pressure on natural resources. Social media, particularly Google Maps, plays a crucial role in promoting tourism and understanding tourist behavior through its review features. This study aims to conduct sentiment analysis on ecotourism reviews in Bogor collected from Google Maps using neural network-based deep learning methods, namely Convolutional Neural Network (CNN), Recurrent Neural Network (RNN), and Long Short-Term Memory (LSTM). The performance of these three models is compared to determine the best method for classifying visitor sentiment. The results of this study indicate that the CNN model has the highest accuracy of 72 percent, outperforming the RNN and LSTM models. The CNN model can be used as a primary reference in applying sentiment analysis to similar topics.</t>
+  </si>
+  <si>
+    <t>Sentiment Classification Using Multilayer Perceptron Algorithm with TF-IDF Features</t>
+  </si>
+  <si>
+    <t>Abdurrahman Arasy; Surya Agustian; Lestari Handayani; Iwan Iskandar</t>
+  </si>
+  <si>
+    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2052</t>
+  </si>
+  <si>
+    <t>Classification; Multi-Layer Perceptron; Sentiment Analysis; Term Frequency-Inverse Document Frequency</t>
+  </si>
+  <si>
+    <t>Social media, particularly Twitter (X), has become the main platform for discussions on politics and government policy. The term used for messages sent on Twitter is a "tweet", which consists of a message with a maximum of 280 characters. Although Tweets are often just text, they can also include hyperlinks, videos, and other types of media that can be used to gauge public opinion. This study aims to classify public sentiment regarding the appointment of Kaesang Pangarep as Chairman of the Indonesian Solidarity Party (PSI) using the Multi-Layer Perceptron (MLP) Classifier method with the Term Frequency-Inverse Document Frequency (TF-IDF) approach, utilizing the Python programming language. The data used consists of 300 Tweets, with 100 Tweets per class or option for optimal results. The three categories are positive, neutral, and negative. Based on the research conducted, the best method achieved an F1-score of 0.6767 and an accuracy of 0.6667. These results indicate that the combination of the MLP Classifier and TF-IDF can overcome the limitations of the dataset to a certain extent compared to the baseline method. This study also provides insights into sentiment classification optimization under limited data conditions, which can be applied to other topics with similar issues.</t>
+  </si>
+  <si>
     <t>Sentiment Analysis of Coretax: A Comparison of Manual, Transformers-Based, and Lexicon-Based Data Labeling on IndoBERT Performance</t>
   </si>
   <si>
@@ -893,51 +2127,6 @@
     <t>Sentiment analysis of public opinion on social media presents significant challenges due to informal language and large data volume. This study aims to evaluate the impact of five labeling approaches manual, IndoBERT , IndoBERT weet, RoBERTa , and InSet Lexicon on the performance of the Indonesian Bidirectional Encoder Representations from Transformers (IndoBERT) model in classifying sentiments related to the Coretax issue. A total of 8.035 tweets were collected, processed, and labeled using each method. The labeled datasets were then used to retrain the IndoBERT model and evaluated using accuracy, F1-Score, confusion matrix, and Receiver Operating Characteristic-Area Under the Curve (ROC-AUC) curve. Results show that Indonesian Bidirectional Encoder Representations from Transformers for Tweet (IndoBERTweet) achieved the highest metric performance F1-Score (0.9802) but suffered from a strong dominance of the neutral class, indicating a potential model bias towards that class or significant data imbalance. Manual labeling produced a more balanced class distribution despite lower performance F1-Score (0.8684), while Robustly Optimized BERT Pretraining Approach (RoBERTa) demonstrated the best balance between metric performance and label distribution. In contrast, InSet Lexicon and IndoBERT tended to overpredict specific sentiment classes. The study concludes that labeling effectiveness should not be assessed solely by metric scores, but also by the fairness and balance of class distribution to produce reliable and generalizable models.</t>
   </si>
   <si>
-    <t>Comparison of Naïve Bayes and Support Vector Machine in Sentiment Analysis of Confiscation of Corrupt Assets on Twitter</t>
-  </si>
-  <si>
-    <t>Ananda sholekhah; Muntahanah Muntahanah</t>
-  </si>
-  <si>
-    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2068</t>
-  </si>
-  <si>
-    <t>Asset Forfeiture; Corruptors; Naive Bayes; Sentiment Analysis; Support Vector Machine</t>
-  </si>
-  <si>
-    <t>Sentiment analysis is one approach used to understand public perception of social issues and government policies through textual data. This study examines Indonesian public opinion toward President Prabowo Subianto’s statement regarding the confiscation of corruptors’ assets, which questioned, "Is it fair for the children to suffer?”. The dataset was collected from Twitter, comprising 1,561 tweets gathered between April 9 and April 25, 2025, using relevant keywords. The analysis involved preprocessing, TF-IDF vectorization, and classification using Naïve Bayes and Support Vector Machine (SVM) algorithms. Model performance was evaluated using a confusion matrix and four evaluation metrics: accuracy, precision, recall, and F1-score. The results indicate that SVM outperformed Naïve Bayes, achieving an accuracy of 70.51% and an F1-score of 0.69, while Naïve Bayes recorded 66.34% accuracy and 0.66 F1-score. Most of the sentiments were classified as positive, reflecting majority public support for the asset confiscation policy despite its impact on the perpetrators’ families. This research demonstrates the effectiveness of machine learning-based classification in mapping public opinion on controversial policy issues through social media platforms.</t>
-  </si>
-  <si>
-    <t>Comparison of Deep Learning Algorithm in Sentiment Analysis Ecotourism in Bogor</t>
-  </si>
-  <si>
-    <t>Peni Agustini; Muhammad Iqbal; Vicha Amalia Akbar; Robert Kurniawan</t>
-  </si>
-  <si>
-    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2191</t>
-  </si>
-  <si>
-    <t>Bogor; Deep Learning; Ecotourism; Scraping; Sentiment Analysis</t>
-  </si>
-  <si>
-    <t>Bogor has a leading ecotourism destination in Indonesia, offering pristine nature and easy access from Jakarta. However, the increasing number of tourists poses challenges to environmental management, such as waste management and pressure on natural resources. Social media, particularly Google Maps, plays a crucial role in promoting tourism and understanding tourist behavior through its review features. This study aims to conduct sentiment analysis on ecotourism reviews in Bogor collected from Google Maps using neural network-based deep learning methods, namely Convolutional Neural Network (CNN), Recurrent Neural Network (RNN), and Long Short-Term Memory (LSTM). The performance of these three models is compared to determine the best method for classifying visitor sentiment. The results of this study indicate that the CNN model has the highest accuracy of 72 percent, outperforming the RNN and LSTM models. The CNN model can be used as a primary reference in applying sentiment analysis to similar topics.</t>
-  </si>
-  <si>
-    <t>Sentiment Classification Using Multilayer Perceptron Algorithm with TF-IDF Features</t>
-  </si>
-  <si>
-    <t>Abdurrahman Arasy; Surya Agustian; Lestari Handayani; Iwan Iskandar</t>
-  </si>
-  <si>
-    <t>https://journal.irpi.or.id/index.php/malcom/article/view/2052</t>
-  </si>
-  <si>
-    <t>Classification; Multi-Layer Perceptron; Sentiment Analysis; Term Frequency-Inverse Document Frequency</t>
-  </si>
-  <si>
-    <t>Social media, particularly Twitter (X), has become the main platform for discussions on politics and government policy. The term used for messages sent on Twitter is a "tweet", which consists of a message with a maximum of 280 characters. Although Tweets are often just text, they can also include hyperlinks, videos, and other types of media that can be used to gauge public opinion. This study aims to classify public sentiment regarding the appointment of Kaesang Pangarep as Chairman of the Indonesian Solidarity Party (PSI) using the Multi-Layer Perceptron (MLP) Classifier method with the Term Frequency-Inverse Document Frequency (TF-IDF) approach, utilizing the Python programming language. The data used consists of 300 Tweets, with 100 Tweets per class or option for optimal results. The three categories are positive, neutral, and negative. Based on the research conducted, the best method achieved an F1-score of 0.6767 and an accuracy of 0.6667. These results indicate that the combination of the MLP Classifier and TF-IDF can overcome the limitations of the dataset to a certain extent compared to the baseline method. This study also provides insights into sentiment classification optimization under limited data conditions, which can be applied to other topics with similar issues.</t>
-  </si>
-  <si>
     <t>Machine Learning-Based Sentiment Analysis of Public Opinion on Palm Oil Plantation Expansion in Papua</t>
   </si>
   <si>
@@ -1037,6 +2226,9 @@
     <t>International Journal Software Engineering and Computer Science (IJSECS)</t>
   </si>
   <si>
+    <t>27763242</t>
+  </si>
+  <si>
     <t>https://journal.lembagakita.org/ijsecs/article/view/1699</t>
   </si>
   <si>
@@ -1200,6 +2392,102 @@
   </si>
   <si>
     <t>Student aspirations play an important role as a means of two-way communication to improve the quality of academic and non-academic services in higher education. However, manual aspiration submission systems often result in delays in follow-up and a lack of documentation. This study aims to design and implement a web-based student aspiration processing information system integrated with sentiment analysis. The development method used is Waterfall, with stages of requirements analysis, design, implementation, testing, and maintenance. The implementation was carried out using the PHP programming language and MySQL database. The main features of the system include registration, login, feedback form, feedback list, admin replies, and lexicon-based sentiment analysis. Testing using Black Box Testing showed that all functions ran according to user requirements (100% success rate), with an average system response time of 2.7 seconds and a user satisfaction rate of 92%. This system is capable of classifying aspirations into positive (46%), negative (38%), and neutral (16%) categories, thereby facilitating the evaluation of campus services. This research proves that the system is capable of accelerating the handling of aspirations by up to 40% compared to manual mechanisms and supports decision-making based on sentiment data.</t>
+  </si>
+  <si>
+    <t>Bidirectional Encoder Representations from Transformers Fine-Tuning for Sentiment Classification of Cek Bansos Reviews</t>
+  </si>
+  <si>
+    <t>Erna Haerani; Alam Rahmatulloh; Souhayla Elmeftahi</t>
+  </si>
+  <si>
+    <t>International Journal of Engineering and Computer Science Applications (IJECSA)</t>
+  </si>
+  <si>
+    <t>28285611</t>
+  </si>
+  <si>
+    <t>https://journal.universitasbumigora.ac.id/IJECSA/article/view/4981</t>
+  </si>
+  <si>
+    <t>https://sinta.kemdiktisaintek.go.id/journals/profile/13066</t>
+  </si>
+  <si>
+    <t>Social assistance programs are essential government initiatives aimed at supporting underprivileged communities. One such program is facilitated through the Cek Bansos application, which enables users to check their eligibility for social aid. However, user experiences with the application vary, leading to various sentiments in their reviews. Understanding these sentiments is crucial for improving the application’s functionality and user satisfaction. This study focuses on sentiment analysis of user reviews of the Cek Bansos application by leveraging a fine-tuned Indonesian-language Bidirectional Encoder Representations from Transformers (BERT) model. This research aims to evaluate the BERT model’s effectiveness in classifying sentiments in user reviews and provide insights that could improve the Cek Bansos application. This research method is the BERT model was fine-tuned using hyperparameters such as a learning rate of 3e-6, batch size of 16, and 9 epochs. The dataset consisted of 8,000 reviews, divided into training (70%), validation (20.1%), and test (9.9%) sets. Review scores were manually categorized, where ratings of 1 to 2 were classified as negative sentiment, 3 as neutral, and 4 to 5 as positive. The results of this research are as follows: the fine-tuned model achieved an accuracy of 77%, with additional evaluation metrics such as precision, recall, and F1 score, demonstrating the model’s effectiveness in identifying positive, negative, and neutral sentiments separately. This study concludes that the BERT model provides a reliable method for sentiment classification of user reviews, which could support developers and policymakers in refining the Cek Bansos application to enhance user experience. Additionally, a web-based application developed using Streamlit allows government officials to visualize sentiment trends in real time, improving their understanding of user feedback. Future research could further explore alternative machine learning models and additional linguistic features to improve sentiment classification accuracy and the overall user experience.</t>
+  </si>
+  <si>
+    <t>IJECSA is committed to keeping open access publishing affordable and sustainable. IJECSA does not charge authors for submitting their manuscripts nor for publication of the articles. Universitas Bumigora provides IJECSA with technical and financial support, hence zero APCs. Based on that, IJECSA is dedicated to providing free services for authors from low-income countries or those facing financial constraints, ensuring inclusivity and equitable access to open knowledge. Link: https://journal.universitasbumigora.ac.id/index.php/IJECSA/PublicationCharge</t>
+  </si>
+  <si>
+    <t>Comparison of Lexicon-based Methods and Bidirectional Encoder Representations for Transformers Models in Sentiment Analysis of Government Debt Market Movements</t>
+  </si>
+  <si>
+    <t>Firda Rachmawati; Ulil Azmi; Rahmania Azwarini</t>
+  </si>
+  <si>
+    <t>https://journal.universitasbumigora.ac.id/IJECSA/article/view/4832</t>
+  </si>
+  <si>
+    <t>The State Budget of Indonesia (APBN) is the main tool for implementing fiscal policies and serves as a budgeting guideline for development execution in Indonesia. One of the funding sources in budget financing is Debt Financing, which consists of Government Securities (SBN) issuance and Loans. Overall, Government Securities (SUN) contributes IDR 5,824.34 trillion, highlighting its significant proportion in debt financing. Understanding public sentiment toward SUN is essential in developing effective government policies. This research conducts sentiment analysis on tweets from the social media X over the past 7.75 years to assess public perception and propose strategic recommendations. This research aims to compare the BERT model and the Lexicon-based method to determine which achieves the highest accuracy in sentiment analysis. The findings can help the government develop strategies for issuing SUN, especially in improving public involvement and investor trust. This research method is based on deep learning pre-trained Bidirectional Encoder Representations from Transformers (BERT) model, specifically IndoBERT, with fine-tuning and a Lexicon-based approach utilizing the InSet lexicon. The results of this research are as follows: on the overall tweet dataset, the BERT model with optimal hyperparameters outperformed the Lexicon-based method, achieving an accuracy of 70.28% compared to 55.77%. Similarly, on an annual basis, BERT exhibited higher accuracy than the Lexicon-based method, except in 2021. Public sentiment on SUN in social media X is categorized as 49% positive, 30% neutral, and 21% negative. These findings indicate a generally favorable perception of SUN but highlight areas for improvement in public communication. Overall, the BERT model demonstrates superior performance over the Lexicon-based method. Considering the opportunities available, the government could leverage social media through Key Opinion Leaders and enhance transparency in explaining policies such as Tapera. This approach could maximize public participation in investing in SUN in Indonesia.</t>
+  </si>
+  <si>
+    <t>Classification of Customer Opinions on the Quality of Cooperative Minimarket Services Using the Lexicon Approach</t>
+  </si>
+  <si>
+    <t>Muhammad Sholeh; Uning Lestari; Dina Andayati</t>
+  </si>
+  <si>
+    <t>https://journal.universitasbumigora.ac.id/IJECSA/article/view/6172</t>
+  </si>
+  <si>
+    <t>Comments; Lexicon; Logistic Regression; Minimarket; Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>Almost every strategic location today has a store that sells daily necessities. These stores compete with each other by offering prices and services that they hope will satisfy their customers. This competition must be anticipated in the management of cooperatives’ minimarkets. Minimarkets run by cooperatives need to maintain the loyalty of their members and general customers by improving service quality. Customer reviews, suggestions, and criticisms from members or customers are valuable sources of data for evaluating service performance. These customer reviews are unstructured data that is difficult to process manually. This study aims to classify customer opinions on the service quality of cooperative minimarkets into positive, negative, and neutral sentiments using a Lexicon-Based approach. The research methods used are text data preprocessing, sentiment weighting using a lexicon dictionary, classification into positive, negative, or neutral classes, and system performance testing using a confusion matrix. The data labeling stage is automated using the Lexicon InSet dictionary to determine the sentiment class (positive or negative). The labeled data was then processed using TF-IDF feature extraction and used to train the logistic regression model. Model performance evaluation was carried out using a Confusion Matrix with a training data and test data ratio of 80:20. The results of this study show that the logistic regression algorithm is capable of classifying cooperative service sentiment with an accuracy rate of 81%, precision of 83%, recall of 81%, and an F1 score of 79%. These results indicate that the method is quite effective at identifying customer opinions and can serve as a decision-support system for cooperative managers to continuously improve service quality by analyzing customer sentiment data.</t>
+  </si>
+  <si>
+    <t>Assessing Twitter User Sentiment Regarding Divorce Issues Using the Random Forest Method</t>
+  </si>
+  <si>
+    <t>Muhamad Azwar; I Putu Hariyadi; Raisul Azhar</t>
+  </si>
+  <si>
+    <t>https://journal.universitasbumigora.ac.id/IJECSA/article/view/4980</t>
+  </si>
+  <si>
+    <t>Confusion Matrix; Divorce; Random Forest; Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>The issue of divorce remains a complex and sensitive topic within Indonesian society, influenced by various factors such as repeated disputes, domestic violence, lack of harmony, financial difficulties, and other socio-cultural aspects. With the rise of social media, particularly Twitter, public discussions regarding divorce have become more widespread, allowing individuals to express their opinions and sentiments on the subject. These diverse perspectives create a wealth of sentiment data that can be analyzed to understand public perception and societal trends related to divorce. This study aims to classify public sentiment on divorce-related discussions using the Random Forest algorithm, providing insight into how people perceive and react to divorce issues. The research adopts a quantitative approach with a case study framework. The methodology involves data collection through web scraping techniques to gather approximately 1500 tweets containing discussions on divorce. The collected data is then preprocessed, including text cleaning, tokenization, and feature extraction, before being used to train and evaluate the Random Forest model. Sentiments are classified into three categories: negative, neutral, and positive. The classification model’s performance is assessed using accuracy and F1-score metrics derived from the confusion matrix to determine its effectiveness in categorizing sentiments. Experimental results indicate that the Random Forest algorithm achieves an accuracy of 70%. The relatively low accuracy is attributed to the imbalance in sentiment class distribution, where negative sentiments dominate while positive sentiments are underrepresented. This imbalance affects the model’s ability to predict positive sentiments effectively. The implications of this research contribute to a better understanding of public sentiment dynamics regarding divorce, which can be beneficial for policymakers, psychologists, and social researchers in analyzing societal attitudes towards marital dissolution.</t>
+  </si>
+  <si>
+    <t>Sentiment Classification of Football Supporters Using NusaBERT Embeddings, BiLSTM, and BiGRU Methods</t>
+  </si>
+  <si>
+    <t>Muhammad Guntara; I Gusti Ayu Diah Gita Kartika Santi; Hairani Hairani; Lalu Zazuli Azhar Mardedi</t>
+  </si>
+  <si>
+    <t>https://journal.universitasbumigora.ac.id/IJECSA/article/view/6151</t>
+  </si>
+  <si>
+    <t>BiLSTM; BiGRU; NusaBERT; Sentiment Analysis; SMOTE</t>
+  </si>
+  <si>
+    <t>Class imbalance and the use of non-standard language in football supporters’ opinions on social media constitute major obstacles to producing accurate sentiment classification for evaluating federation performance. This study aims to identify the most effective bidirectional recurrent architecture for capturing public opinion after applying data balancing techniques. Using a primary dataset of 1,039 instances (604 positive and 435 negative samples), the proposed method integrates a pre-trained NusaBERT model with hybrid Bidirectional Long Short-Term Memory (BiLSTM) and Bidirectional Gated Recurrent Unit (BiGRU) layers. To address data imbalance, the Synthetic Minority Over-sampling Technique (SMOTE) is applied to the training data, with dataset partitioning using a stratified split ratio of 70:30. The results indicate that the NusaBERT-BiLSTM model achieves the best performance, with a testing accuracy of 70.83% and an F1-score of 0.6990, outperforming the BiGRU variant, which attains an accuracy of only 64.74%. Furthermore, NusaBERT-BiLSTM demonstrates greater reliability in detecting negative sentiment, achieving a recall value of 0.6336 compared to 0.4504 for BiGRU. In conclusion, combining NusaBERT’s semantic strength with SMOTE-based balancing and BiLSTM layers significantly enhances the model’s sensitivity to minority opinions without causing data leakage. This study contributes a more objective classification model for national team management to accurately map public criticism and aspirations on social media.</t>
+  </si>
+  <si>
+    <t>Sentiment Analysis and Topic Modeling of Kitabisa Applications using Support Vector Machine (SVM) and Smote-Tomek Links Methods</t>
+  </si>
+  <si>
+    <t>I Nyoman Switrayana;Diki Ashadi; Hairani Hairani; Afrig Aminuddin</t>
+  </si>
+  <si>
+    <t>https://journal.universitasbumigora.ac.id/IJECSA/article/view/3406</t>
+  </si>
+  <si>
+    <t>Latent Dirichlet Allocation; Sentiment Analysis; SMOTE-Tomek Links; Support Vector Machine</t>
+  </si>
+  <si>
+    <t>Kitabisa is an Indonesian application that functions to raise funds online. Users can easily support various types of campaigns and donate funds to various social causes through the app. User reviews of the application are very diverse, and it is not sure whether user reviews of the application tend to be positive, neutral, or negative. This research aimed to analyze the sentiment of the Kitabisa application by modeling topics using Latent Dirichlet Allocation (LDA) and classifying user reviews using a Support Vector Machine (SVM). The scrapped dataset showed imbalanced dataset problems, so the SMOTE-Tomek Links oversampling technique was proposed. The results of this study show that using LDA produces five topics often discussed in 750 reviews. Then, the performance of SVM without using SMOTE-Tomek Links was 72% accuracy, 76% precision, 72% recall, and 64% f1 score. Meanwhile, using SMOTE-Tomek Links could significantly improve the performance, namely 98% accuracy, 98% precision, 98% recall, and 98% f1 score. Based on this research, the application of SVM achieved high performance for user sentiment classification, especially when the dataset was in a balanced state. Therefore, the SMOTE-Tomek Links oversampling technique is recommended for dealing with unbalanced sentiment datasets</t>
   </si>
 </sst>
 </file>
@@ -1255,8 +2543,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:U70" totalsRowShown="0">
-  <autoFilter ref="A1:U70" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:U136" totalsRowShown="0">
+  <autoFilter ref="A1:U136" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U136">
+    <sortCondition ref="R2:R136"/>
+  </sortState>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Title of Article"/>
@@ -1563,7 +2854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U70"/>
+  <dimension ref="A1:U136"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
@@ -1636,40 +2927,43 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2">
-        <v>25409824</v>
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="P2" t="s">
-        <v>28</v>
+        <v>37</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -1677,40 +2971,46 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>285</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>286</v>
       </c>
       <c r="D3">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3">
-        <v>25409824</v>
+        <v>287</v>
+      </c>
+      <c r="H3" t="s">
+        <v>288</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>289</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>290</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>291</v>
       </c>
       <c r="P3" t="s">
-        <v>33</v>
+        <v>292</v>
+      </c>
+      <c r="R3" t="s">
+        <v>293</v>
+      </c>
+      <c r="U3" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -1718,40 +3018,46 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>295</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>296</v>
       </c>
       <c r="D4">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4">
-        <v>25409824</v>
+        <v>287</v>
+      </c>
+      <c r="H4" t="s">
+        <v>288</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>297</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>298</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>291</v>
       </c>
       <c r="P4" t="s">
-        <v>38</v>
+        <v>299</v>
+      </c>
+      <c r="R4" t="s">
+        <v>293</v>
+      </c>
+      <c r="U4" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -1759,40 +3065,46 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>301</v>
       </c>
       <c r="D5">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5">
-        <v>25409824</v>
+        <v>287</v>
+      </c>
+      <c r="H5" t="s">
+        <v>288</v>
       </c>
       <c r="I5" t="s">
-        <v>41</v>
+        <v>302</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>303</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>291</v>
       </c>
       <c r="P5" t="s">
-        <v>43</v>
+        <v>304</v>
+      </c>
+      <c r="R5" t="s">
+        <v>293</v>
+      </c>
+      <c r="U5" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -1800,40 +3112,46 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>305</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>306</v>
       </c>
       <c r="D6">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6">
-        <v>25409824</v>
+        <v>287</v>
+      </c>
+      <c r="H6" t="s">
+        <v>288</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
+        <v>307</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
+        <v>308</v>
       </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="L6" t="s">
-        <v>27</v>
+        <v>291</v>
       </c>
       <c r="P6" t="s">
-        <v>48</v>
+        <v>309</v>
+      </c>
+      <c r="R6" t="s">
+        <v>293</v>
+      </c>
+      <c r="U6" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -1841,40 +3159,46 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>310</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>301</v>
       </c>
       <c r="D7">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7">
-        <v>25409824</v>
+        <v>287</v>
+      </c>
+      <c r="H7" t="s">
+        <v>288</v>
       </c>
       <c r="I7" t="s">
-        <v>51</v>
+        <v>311</v>
       </c>
       <c r="J7" t="s">
-        <v>52</v>
+        <v>312</v>
       </c>
       <c r="K7" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="L7" t="s">
-        <v>27</v>
+        <v>291</v>
       </c>
       <c r="P7" t="s">
-        <v>53</v>
+        <v>313</v>
+      </c>
+      <c r="R7" t="s">
+        <v>293</v>
+      </c>
+      <c r="U7" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -1882,40 +3206,46 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>314</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>315</v>
       </c>
       <c r="D8">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8">
-        <v>25409824</v>
+        <v>287</v>
+      </c>
+      <c r="H8" t="s">
+        <v>288</v>
       </c>
       <c r="I8" t="s">
-        <v>56</v>
+        <v>316</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>317</v>
       </c>
       <c r="K8" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>291</v>
       </c>
       <c r="P8" t="s">
-        <v>58</v>
+        <v>318</v>
+      </c>
+      <c r="R8" t="s">
+        <v>293</v>
+      </c>
+      <c r="U8" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -1923,40 +3253,46 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>319</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>320</v>
       </c>
       <c r="D9">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9">
-        <v>25409824</v>
+        <v>287</v>
+      </c>
+      <c r="H9" t="s">
+        <v>288</v>
       </c>
       <c r="I9" t="s">
-        <v>61</v>
+        <v>321</v>
       </c>
       <c r="J9" t="s">
-        <v>62</v>
+        <v>322</v>
       </c>
       <c r="K9" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>291</v>
       </c>
       <c r="P9" t="s">
-        <v>63</v>
+        <v>323</v>
+      </c>
+      <c r="R9" t="s">
+        <v>293</v>
+      </c>
+      <c r="U9" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -1964,2686 +3300,5677 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>324</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>325</v>
       </c>
       <c r="D10">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
         <v>6</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
       <c r="G10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10">
-        <v>25409824</v>
+        <v>287</v>
+      </c>
+      <c r="H10" t="s">
+        <v>288</v>
       </c>
       <c r="I10" t="s">
-        <v>66</v>
+        <v>326</v>
       </c>
       <c r="J10" t="s">
-        <v>67</v>
+        <v>327</v>
       </c>
       <c r="K10" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="L10" t="s">
-        <v>27</v>
+        <v>291</v>
       </c>
       <c r="P10" t="s">
-        <v>68</v>
+        <v>328</v>
+      </c>
+      <c r="R10" t="s">
+        <v>293</v>
+      </c>
+      <c r="U10" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="D11">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
         <v>6</v>
       </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
       <c r="G11" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11">
-        <v>25415239</v>
+        <v>287</v>
+      </c>
+      <c r="H11" t="s">
+        <v>288</v>
       </c>
       <c r="I11" t="s">
-        <v>72</v>
+        <v>331</v>
       </c>
       <c r="J11" t="s">
-        <v>73</v>
+        <v>332</v>
       </c>
       <c r="K11" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L11" t="s">
-        <v>75</v>
-      </c>
-      <c r="M11" t="s">
-        <v>76</v>
+        <v>291</v>
       </c>
       <c r="P11" t="s">
-        <v>77</v>
+        <v>333</v>
+      </c>
+      <c r="R11" t="s">
+        <v>293</v>
       </c>
       <c r="U11" t="s">
-        <v>78</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>334</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>335</v>
       </c>
       <c r="D12">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E12">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
-      </c>
-      <c r="H12">
-        <v>25415239</v>
+        <v>287</v>
+      </c>
+      <c r="H12" t="s">
+        <v>288</v>
       </c>
       <c r="I12" t="s">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="J12" t="s">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="K12" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L12" t="s">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="P12" t="s">
-        <v>83</v>
+        <v>338</v>
+      </c>
+      <c r="R12" t="s">
+        <v>293</v>
       </c>
       <c r="U12" t="s">
-        <v>78</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>339</v>
+      </c>
+      <c r="C13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D13">
+        <v>2021</v>
+      </c>
+      <c r="E13">
+        <v>11</v>
+      </c>
+      <c r="F13">
         <v>1</v>
       </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13">
-        <v>2023</v>
-      </c>
-      <c r="E13">
-        <v>8</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
       <c r="G13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13">
-        <v>25416448</v>
+        <v>287</v>
+      </c>
+      <c r="H13" t="s">
+        <v>288</v>
       </c>
       <c r="I13" t="s">
-        <v>87</v>
+        <v>340</v>
       </c>
       <c r="J13" t="s">
-        <v>88</v>
+        <v>341</v>
       </c>
       <c r="K13" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L13" t="s">
-        <v>89</v>
-      </c>
-      <c r="M13" t="s">
-        <v>90</v>
+        <v>291</v>
       </c>
       <c r="P13" t="s">
-        <v>91</v>
+        <v>342</v>
+      </c>
+      <c r="R13" t="s">
+        <v>293</v>
       </c>
       <c r="U13" t="s">
-        <v>92</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>343</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>344</v>
       </c>
       <c r="D14">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14">
-        <v>25416448</v>
+        <v>287</v>
+      </c>
+      <c r="H14" t="s">
+        <v>288</v>
       </c>
       <c r="I14" t="s">
-        <v>95</v>
+        <v>345</v>
       </c>
       <c r="J14" t="s">
-        <v>96</v>
+        <v>346</v>
       </c>
       <c r="K14" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s">
-        <v>89</v>
-      </c>
-      <c r="M14" t="s">
-        <v>76</v>
+        <v>291</v>
       </c>
       <c r="P14" t="s">
-        <v>97</v>
+        <v>347</v>
+      </c>
+      <c r="R14" t="s">
+        <v>293</v>
       </c>
       <c r="U14" t="s">
-        <v>92</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>348</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>349</v>
       </c>
       <c r="D15">
         <v>2021</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15">
-        <v>25416448</v>
+        <v>287</v>
+      </c>
+      <c r="H15" t="s">
+        <v>288</v>
       </c>
       <c r="I15" t="s">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="J15" t="s">
-        <v>101</v>
+        <v>351</v>
       </c>
       <c r="K15" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s">
-        <v>89</v>
-      </c>
-      <c r="M15" t="s">
-        <v>102</v>
+        <v>291</v>
       </c>
       <c r="P15" t="s">
-        <v>103</v>
+        <v>352</v>
+      </c>
+      <c r="R15" t="s">
+        <v>293</v>
       </c>
       <c r="U15" t="s">
-        <v>92</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>353</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="D16">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" t="s">
-        <v>86</v>
-      </c>
-      <c r="H16">
-        <v>25416448</v>
+        <v>287</v>
+      </c>
+      <c r="H16" t="s">
+        <v>288</v>
       </c>
       <c r="I16" t="s">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="J16" t="s">
-        <v>107</v>
+        <v>356</v>
       </c>
       <c r="K16" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s">
-        <v>89</v>
+        <v>291</v>
       </c>
       <c r="P16" t="s">
-        <v>108</v>
+        <v>357</v>
+      </c>
+      <c r="R16" t="s">
+        <v>293</v>
       </c>
       <c r="U16" t="s">
-        <v>92</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>109</v>
+        <v>358</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>359</v>
       </c>
       <c r="D17">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17">
-        <v>25416448</v>
+        <v>287</v>
+      </c>
+      <c r="H17" t="s">
+        <v>288</v>
       </c>
       <c r="I17" t="s">
-        <v>111</v>
+        <v>360</v>
       </c>
       <c r="J17" t="s">
-        <v>112</v>
+        <v>361</v>
       </c>
       <c r="K17" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L17" t="s">
-        <v>89</v>
+        <v>291</v>
       </c>
       <c r="P17" t="s">
-        <v>113</v>
+        <v>362</v>
+      </c>
+      <c r="R17" t="s">
+        <v>293</v>
       </c>
       <c r="U17" t="s">
-        <v>92</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>363</v>
+      </c>
+      <c r="C18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D18">
+        <v>2022</v>
+      </c>
+      <c r="E18">
+        <v>12</v>
+      </c>
+      <c r="F18">
         <v>1</v>
       </c>
-      <c r="B18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C18" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18">
-        <v>2024</v>
-      </c>
-      <c r="E18">
-        <v>5</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
       <c r="G18" t="s">
-        <v>116</v>
-      </c>
-      <c r="H18">
-        <v>27220001</v>
+        <v>287</v>
+      </c>
+      <c r="H18" t="s">
+        <v>288</v>
       </c>
       <c r="I18" t="s">
-        <v>117</v>
+        <v>365</v>
       </c>
       <c r="J18" t="s">
-        <v>118</v>
+        <v>366</v>
       </c>
       <c r="K18" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="L18" t="s">
-        <v>119</v>
+        <v>291</v>
       </c>
       <c r="P18" t="s">
-        <v>120</v>
+        <v>367</v>
+      </c>
+      <c r="R18" t="s">
+        <v>293</v>
+      </c>
+      <c r="U18" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>368</v>
+      </c>
+      <c r="C19" t="s">
+        <v>369</v>
+      </c>
+      <c r="D19">
+        <v>2022</v>
+      </c>
+      <c r="E19">
+        <v>12</v>
+      </c>
+      <c r="F19">
         <v>1</v>
       </c>
-      <c r="B19" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="G19" t="s">
+        <v>287</v>
+      </c>
+      <c r="H19" t="s">
+        <v>288</v>
+      </c>
+      <c r="I19" t="s">
+        <v>370</v>
+      </c>
+      <c r="J19" t="s">
+        <v>371</v>
+      </c>
+      <c r="K19" t="s">
         <v>122</v>
       </c>
-      <c r="D19">
-        <v>2024</v>
-      </c>
-      <c r="E19">
-        <v>14</v>
-      </c>
-      <c r="F19">
-        <v>4</v>
-      </c>
-      <c r="G19" t="s">
-        <v>123</v>
-      </c>
-      <c r="H19">
-        <v>27222578</v>
-      </c>
-      <c r="I19" t="s">
-        <v>124</v>
-      </c>
-      <c r="J19" t="s">
-        <v>125</v>
-      </c>
-      <c r="K19" t="s">
-        <v>126</v>
-      </c>
       <c r="L19" t="s">
-        <v>127</v>
+        <v>291</v>
       </c>
       <c r="P19" t="s">
-        <v>128</v>
+        <v>372</v>
       </c>
       <c r="R19" t="s">
-        <v>129</v>
+        <v>293</v>
       </c>
       <c r="U19" t="s">
-        <v>130</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>373</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>374</v>
       </c>
       <c r="D20">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>133</v>
-      </c>
-      <c r="H20">
-        <v>27231453</v>
+        <v>287</v>
+      </c>
+      <c r="H20" t="s">
+        <v>288</v>
       </c>
       <c r="I20" t="s">
-        <v>134</v>
+        <v>375</v>
       </c>
       <c r="J20" t="s">
-        <v>135</v>
+        <v>376</v>
       </c>
       <c r="K20" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L20" t="s">
-        <v>136</v>
+        <v>291</v>
       </c>
       <c r="P20" t="s">
-        <v>137</v>
+        <v>377</v>
+      </c>
+      <c r="R20" t="s">
+        <v>293</v>
       </c>
       <c r="U20" t="s">
-        <v>138</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>139</v>
+        <v>378</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>379</v>
       </c>
       <c r="D21">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" t="s">
-        <v>133</v>
-      </c>
-      <c r="H21">
-        <v>27231453</v>
+        <v>287</v>
+      </c>
+      <c r="H21" t="s">
+        <v>288</v>
       </c>
       <c r="I21" t="s">
-        <v>141</v>
+        <v>380</v>
       </c>
       <c r="J21" t="s">
-        <v>142</v>
+        <v>381</v>
       </c>
       <c r="K21" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L21" t="s">
-        <v>136</v>
+        <v>291</v>
       </c>
       <c r="P21" t="s">
-        <v>143</v>
+        <v>382</v>
+      </c>
+      <c r="R21" t="s">
+        <v>293</v>
       </c>
       <c r="U21" t="s">
-        <v>138</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>383</v>
+      </c>
+      <c r="C22" t="s">
+        <v>384</v>
+      </c>
+      <c r="D22">
+        <v>2022</v>
+      </c>
+      <c r="E22">
+        <v>12</v>
+      </c>
+      <c r="F22">
         <v>3</v>
       </c>
-      <c r="B22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" t="s">
-        <v>145</v>
-      </c>
-      <c r="D22">
-        <v>2024</v>
-      </c>
-      <c r="E22">
-        <v>5</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
       <c r="G22" t="s">
-        <v>133</v>
-      </c>
-      <c r="H22">
-        <v>27231453</v>
+        <v>287</v>
+      </c>
+      <c r="H22" t="s">
+        <v>288</v>
       </c>
       <c r="I22" t="s">
-        <v>146</v>
+        <v>385</v>
       </c>
       <c r="J22" t="s">
-        <v>147</v>
+        <v>386</v>
       </c>
       <c r="K22" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L22" t="s">
-        <v>136</v>
+        <v>291</v>
       </c>
       <c r="P22" t="s">
-        <v>148</v>
+        <v>387</v>
+      </c>
+      <c r="R22" t="s">
+        <v>293</v>
       </c>
       <c r="U22" t="s">
-        <v>138</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>149</v>
+        <v>388</v>
       </c>
       <c r="C23" t="s">
-        <v>150</v>
+        <v>389</v>
       </c>
       <c r="D23">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G23" t="s">
-        <v>151</v>
-      </c>
-      <c r="H23">
-        <v>27749711</v>
+        <v>287</v>
+      </c>
+      <c r="H23" t="s">
+        <v>288</v>
       </c>
       <c r="I23" t="s">
-        <v>152</v>
+        <v>390</v>
       </c>
       <c r="J23" t="s">
-        <v>153</v>
+        <v>391</v>
       </c>
       <c r="K23" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L23" t="s">
-        <v>154</v>
+        <v>291</v>
       </c>
       <c r="P23" t="s">
-        <v>155</v>
+        <v>392</v>
+      </c>
+      <c r="R23" t="s">
+        <v>293</v>
       </c>
       <c r="U23" t="s">
-        <v>156</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>157</v>
+        <v>393</v>
       </c>
       <c r="C24" t="s">
-        <v>158</v>
+        <v>394</v>
       </c>
       <c r="D24">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G24" t="s">
-        <v>151</v>
-      </c>
-      <c r="H24">
-        <v>27749711</v>
+        <v>287</v>
+      </c>
+      <c r="H24" t="s">
+        <v>288</v>
       </c>
       <c r="I24" t="s">
-        <v>159</v>
+        <v>395</v>
       </c>
       <c r="J24" t="s">
-        <v>160</v>
+        <v>396</v>
       </c>
       <c r="K24" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L24" t="s">
-        <v>154</v>
+        <v>291</v>
       </c>
       <c r="P24" t="s">
-        <v>161</v>
+        <v>397</v>
+      </c>
+      <c r="R24" t="s">
+        <v>293</v>
       </c>
       <c r="U24" t="s">
-        <v>156</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>162</v>
+        <v>398</v>
       </c>
       <c r="C25" t="s">
-        <v>163</v>
+        <v>399</v>
       </c>
       <c r="D25">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E25">
+        <v>12</v>
+      </c>
+      <c r="F25">
         <v>4</v>
       </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
       <c r="G25" t="s">
-        <v>151</v>
-      </c>
-      <c r="H25">
-        <v>27749711</v>
+        <v>287</v>
+      </c>
+      <c r="H25" t="s">
+        <v>288</v>
       </c>
       <c r="I25" t="s">
-        <v>164</v>
+        <v>400</v>
       </c>
       <c r="J25" t="s">
-        <v>165</v>
+        <v>401</v>
       </c>
       <c r="K25" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L25" t="s">
-        <v>154</v>
+        <v>291</v>
       </c>
       <c r="P25" t="s">
-        <v>166</v>
+        <v>402</v>
+      </c>
+      <c r="R25" t="s">
+        <v>293</v>
       </c>
       <c r="U25" t="s">
-        <v>156</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>167</v>
+        <v>403</v>
       </c>
       <c r="C26" t="s">
-        <v>168</v>
+        <v>404</v>
       </c>
       <c r="D26">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>151</v>
-      </c>
-      <c r="H26">
-        <v>27749711</v>
+        <v>287</v>
+      </c>
+      <c r="H26" t="s">
+        <v>288</v>
       </c>
       <c r="I26" t="s">
-        <v>169</v>
+        <v>405</v>
       </c>
       <c r="J26" t="s">
-        <v>170</v>
+        <v>406</v>
       </c>
       <c r="K26" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L26" t="s">
-        <v>154</v>
+        <v>291</v>
       </c>
       <c r="P26" t="s">
-        <v>171</v>
+        <v>407</v>
+      </c>
+      <c r="R26" t="s">
+        <v>293</v>
+      </c>
+      <c r="U26" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
+        <v>408</v>
       </c>
       <c r="C27" t="s">
-        <v>173</v>
+        <v>409</v>
       </c>
       <c r="D27">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G27" t="s">
-        <v>151</v>
-      </c>
-      <c r="H27">
-        <v>27749711</v>
+        <v>287</v>
+      </c>
+      <c r="H27" t="s">
+        <v>288</v>
       </c>
       <c r="I27" t="s">
-        <v>174</v>
+        <v>410</v>
       </c>
       <c r="J27" t="s">
-        <v>175</v>
+        <v>411</v>
       </c>
       <c r="K27" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L27" t="s">
-        <v>154</v>
+        <v>291</v>
       </c>
       <c r="P27" t="s">
-        <v>176</v>
+        <v>412</v>
+      </c>
+      <c r="R27" t="s">
+        <v>293</v>
+      </c>
+      <c r="U27" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>177</v>
+        <v>413</v>
       </c>
       <c r="C28" t="s">
-        <v>178</v>
+        <v>414</v>
       </c>
       <c r="D28">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H28" t="s">
+        <v>288</v>
       </c>
       <c r="I28" t="s">
-        <v>180</v>
+        <v>415</v>
       </c>
       <c r="J28" t="s">
-        <v>181</v>
+        <v>416</v>
       </c>
       <c r="K28" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L28" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P28" t="s">
-        <v>183</v>
+        <v>417</v>
+      </c>
+      <c r="R28" t="s">
+        <v>293</v>
       </c>
       <c r="U28" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>185</v>
+        <v>418</v>
       </c>
       <c r="C29" t="s">
-        <v>186</v>
+        <v>419</v>
       </c>
       <c r="D29">
         <v>2023</v>
       </c>
       <c r="E29">
+        <v>13</v>
+      </c>
+      <c r="F29">
         <v>3</v>
       </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
       <c r="G29" t="s">
-        <v>179</v>
-      </c>
-      <c r="H29">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H29" t="s">
+        <v>288</v>
       </c>
       <c r="I29" t="s">
-        <v>187</v>
+        <v>420</v>
       </c>
       <c r="J29" t="s">
-        <v>188</v>
+        <v>421</v>
       </c>
       <c r="K29" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L29" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P29" t="s">
-        <v>189</v>
+        <v>422</v>
+      </c>
+      <c r="R29" t="s">
+        <v>293</v>
       </c>
       <c r="U29" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>190</v>
+        <v>423</v>
       </c>
       <c r="C30" t="s">
-        <v>191</v>
+        <v>424</v>
       </c>
       <c r="D30">
         <v>2023</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30" t="s">
-        <v>179</v>
-      </c>
-      <c r="H30">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H30" t="s">
+        <v>288</v>
       </c>
       <c r="I30" t="s">
-        <v>192</v>
+        <v>425</v>
       </c>
       <c r="J30" t="s">
-        <v>193</v>
+        <v>426</v>
       </c>
       <c r="K30" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L30" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P30" t="s">
-        <v>194</v>
+        <v>427</v>
+      </c>
+      <c r="R30" t="s">
+        <v>293</v>
       </c>
       <c r="U30" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>195</v>
+        <v>428</v>
       </c>
       <c r="C31" t="s">
-        <v>196</v>
+        <v>429</v>
       </c>
       <c r="D31">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G31" t="s">
-        <v>179</v>
-      </c>
-      <c r="H31">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H31" t="s">
+        <v>288</v>
       </c>
       <c r="I31" t="s">
-        <v>197</v>
+        <v>430</v>
       </c>
       <c r="J31" t="s">
-        <v>198</v>
+        <v>431</v>
       </c>
       <c r="K31" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L31" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P31" t="s">
-        <v>199</v>
+        <v>432</v>
+      </c>
+      <c r="R31" t="s">
+        <v>293</v>
       </c>
       <c r="U31" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>200</v>
+        <v>433</v>
       </c>
       <c r="C32" t="s">
-        <v>201</v>
+        <v>434</v>
       </c>
       <c r="D32">
         <v>2024</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>179</v>
-      </c>
-      <c r="H32">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H32" t="s">
+        <v>288</v>
       </c>
       <c r="I32" t="s">
-        <v>202</v>
+        <v>435</v>
       </c>
       <c r="J32" t="s">
-        <v>203</v>
+        <v>436</v>
       </c>
       <c r="K32" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L32" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P32" t="s">
-        <v>204</v>
+        <v>437</v>
+      </c>
+      <c r="R32" t="s">
+        <v>293</v>
       </c>
       <c r="U32" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>205</v>
+        <v>438</v>
       </c>
       <c r="C33" t="s">
-        <v>206</v>
+        <v>439</v>
       </c>
       <c r="D33">
         <v>2024</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>179</v>
-      </c>
-      <c r="H33">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H33" t="s">
+        <v>288</v>
       </c>
       <c r="I33" t="s">
-        <v>207</v>
+        <v>440</v>
       </c>
       <c r="J33" t="s">
-        <v>208</v>
+        <v>441</v>
       </c>
       <c r="K33" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L33" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P33" t="s">
-        <v>209</v>
+        <v>442</v>
+      </c>
+      <c r="R33" t="s">
+        <v>293</v>
       </c>
       <c r="U33" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>210</v>
+        <v>443</v>
       </c>
       <c r="C34" t="s">
-        <v>211</v>
+        <v>444</v>
       </c>
       <c r="D34">
         <v>2024</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>179</v>
-      </c>
-      <c r="H34">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H34" t="s">
+        <v>288</v>
       </c>
       <c r="I34" t="s">
-        <v>212</v>
+        <v>445</v>
       </c>
       <c r="J34" t="s">
-        <v>213</v>
+        <v>446</v>
       </c>
       <c r="K34" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L34" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P34" t="s">
-        <v>214</v>
+        <v>447</v>
+      </c>
+      <c r="R34" t="s">
+        <v>293</v>
       </c>
       <c r="U34" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>215</v>
+        <v>448</v>
       </c>
       <c r="C35" t="s">
-        <v>216</v>
+        <v>449</v>
       </c>
       <c r="D35">
         <v>2024</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>179</v>
-      </c>
-      <c r="H35">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H35" t="s">
+        <v>288</v>
       </c>
       <c r="I35" t="s">
-        <v>217</v>
+        <v>450</v>
       </c>
       <c r="J35" t="s">
-        <v>218</v>
+        <v>451</v>
       </c>
       <c r="K35" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L35" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P35" t="s">
-        <v>219</v>
+        <v>452</v>
+      </c>
+      <c r="R35" t="s">
+        <v>293</v>
       </c>
       <c r="U35" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>220</v>
+        <v>453</v>
       </c>
       <c r="C36" t="s">
-        <v>221</v>
+        <v>454</v>
       </c>
       <c r="D36">
         <v>2024</v>
       </c>
       <c r="E36">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" t="s">
-        <v>179</v>
-      </c>
-      <c r="H36">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H36" t="s">
+        <v>288</v>
       </c>
       <c r="I36" t="s">
-        <v>222</v>
+        <v>455</v>
       </c>
       <c r="J36" t="s">
-        <v>223</v>
+        <v>456</v>
       </c>
       <c r="K36" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L36" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P36" t="s">
-        <v>224</v>
+        <v>457</v>
+      </c>
+      <c r="R36" t="s">
+        <v>293</v>
       </c>
       <c r="U36" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>225</v>
+        <v>458</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>459</v>
       </c>
       <c r="D37">
         <v>2024</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F37">
         <v>3</v>
       </c>
       <c r="G37" t="s">
-        <v>179</v>
-      </c>
-      <c r="H37">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H37" t="s">
+        <v>288</v>
       </c>
       <c r="I37" t="s">
-        <v>227</v>
+        <v>460</v>
       </c>
       <c r="J37" t="s">
-        <v>228</v>
+        <v>461</v>
       </c>
       <c r="K37" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L37" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P37" t="s">
-        <v>229</v>
+        <v>462</v>
+      </c>
+      <c r="R37" t="s">
+        <v>293</v>
       </c>
       <c r="U37" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>230</v>
+        <v>463</v>
       </c>
       <c r="C38" t="s">
-        <v>231</v>
+        <v>464</v>
       </c>
       <c r="D38">
         <v>2024</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38" t="s">
-        <v>179</v>
-      </c>
-      <c r="H38">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H38" t="s">
+        <v>288</v>
       </c>
       <c r="I38" t="s">
-        <v>232</v>
+        <v>465</v>
       </c>
       <c r="J38" t="s">
-        <v>233</v>
+        <v>466</v>
       </c>
       <c r="K38" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L38" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P38" t="s">
-        <v>234</v>
+        <v>467</v>
+      </c>
+      <c r="R38" t="s">
+        <v>293</v>
       </c>
       <c r="U38" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>235</v>
+        <v>468</v>
       </c>
       <c r="C39" t="s">
-        <v>236</v>
+        <v>469</v>
       </c>
       <c r="D39">
         <v>2024</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>179</v>
-      </c>
-      <c r="H39">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H39" t="s">
+        <v>288</v>
       </c>
       <c r="I39" t="s">
-        <v>237</v>
+        <v>470</v>
       </c>
       <c r="J39" t="s">
-        <v>238</v>
+        <v>471</v>
       </c>
       <c r="K39" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L39" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P39" t="s">
-        <v>239</v>
+        <v>472</v>
+      </c>
+      <c r="R39" t="s">
+        <v>293</v>
       </c>
       <c r="U39" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>240</v>
+        <v>473</v>
       </c>
       <c r="C40" t="s">
-        <v>241</v>
+        <v>474</v>
       </c>
       <c r="D40">
         <v>2024</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F40">
         <v>4</v>
       </c>
       <c r="G40" t="s">
-        <v>179</v>
-      </c>
-      <c r="H40">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H40" t="s">
+        <v>288</v>
       </c>
       <c r="I40" t="s">
-        <v>242</v>
+        <v>475</v>
       </c>
       <c r="J40" t="s">
-        <v>243</v>
+        <v>476</v>
       </c>
       <c r="K40" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L40" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P40" t="s">
-        <v>244</v>
+        <v>477</v>
+      </c>
+      <c r="R40" t="s">
+        <v>293</v>
       </c>
       <c r="U40" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>245</v>
+        <v>478</v>
       </c>
       <c r="C41" t="s">
-        <v>246</v>
+        <v>479</v>
       </c>
       <c r="D41">
         <v>2024</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F41">
         <v>4</v>
       </c>
       <c r="G41" t="s">
-        <v>179</v>
-      </c>
-      <c r="H41">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H41" t="s">
+        <v>288</v>
       </c>
       <c r="I41" t="s">
-        <v>247</v>
+        <v>480</v>
       </c>
       <c r="J41" t="s">
-        <v>248</v>
+        <v>481</v>
       </c>
       <c r="K41" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L41" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P41" t="s">
-        <v>249</v>
+        <v>482</v>
+      </c>
+      <c r="R41" t="s">
+        <v>293</v>
       </c>
       <c r="U41" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>250</v>
+        <v>483</v>
       </c>
       <c r="C42" t="s">
-        <v>251</v>
+        <v>484</v>
       </c>
       <c r="D42">
         <v>2024</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F42">
         <v>4</v>
       </c>
       <c r="G42" t="s">
-        <v>179</v>
-      </c>
-      <c r="H42">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H42" t="s">
+        <v>288</v>
       </c>
       <c r="I42" t="s">
-        <v>252</v>
+        <v>485</v>
       </c>
       <c r="J42" t="s">
-        <v>253</v>
+        <v>486</v>
       </c>
       <c r="K42" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L42" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P42" t="s">
-        <v>254</v>
+        <v>487</v>
+      </c>
+      <c r="R42" t="s">
+        <v>293</v>
       </c>
       <c r="U42" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>255</v>
+        <v>488</v>
       </c>
       <c r="C43" t="s">
-        <v>256</v>
+        <v>489</v>
       </c>
       <c r="D43">
         <v>2024</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G43" t="s">
-        <v>179</v>
-      </c>
-      <c r="H43">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H43" t="s">
+        <v>288</v>
       </c>
       <c r="I43" t="s">
-        <v>257</v>
+        <v>490</v>
       </c>
       <c r="J43" t="s">
-        <v>258</v>
+        <v>491</v>
       </c>
       <c r="K43" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L43" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P43" t="s">
-        <v>259</v>
+        <v>492</v>
+      </c>
+      <c r="R43" t="s">
+        <v>293</v>
       </c>
       <c r="U43" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>260</v>
+        <v>493</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>494</v>
       </c>
       <c r="D44">
         <v>2025</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>179</v>
-      </c>
-      <c r="H44">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H44" t="s">
+        <v>288</v>
       </c>
       <c r="I44" t="s">
-        <v>262</v>
+        <v>495</v>
       </c>
       <c r="J44" t="s">
-        <v>263</v>
+        <v>496</v>
       </c>
       <c r="K44" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L44" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P44" t="s">
-        <v>264</v>
+        <v>497</v>
+      </c>
+      <c r="R44" t="s">
+        <v>293</v>
       </c>
       <c r="U44" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>265</v>
+        <v>498</v>
       </c>
       <c r="C45" t="s">
-        <v>266</v>
+        <v>499</v>
       </c>
       <c r="D45">
         <v>2025</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>179</v>
-      </c>
-      <c r="H45">
-        <v>27758575</v>
+        <v>287</v>
+      </c>
+      <c r="H45" t="s">
+        <v>288</v>
       </c>
       <c r="I45" t="s">
-        <v>267</v>
+        <v>500</v>
       </c>
       <c r="J45" t="s">
-        <v>268</v>
+        <v>501</v>
       </c>
       <c r="K45" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L45" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="P45" t="s">
-        <v>269</v>
+        <v>502</v>
+      </c>
+      <c r="R45" t="s">
+        <v>293</v>
       </c>
       <c r="U45" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>270</v>
+        <v>116</v>
       </c>
       <c r="C46" t="s">
-        <v>271</v>
+        <v>117</v>
       </c>
       <c r="D46">
         <v>2025</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" t="s">
-        <v>179</v>
-      </c>
-      <c r="H46">
-        <v>27758575</v>
+        <v>118</v>
+      </c>
+      <c r="H46" t="s">
+        <v>119</v>
       </c>
       <c r="I46" t="s">
-        <v>272</v>
+        <v>120</v>
       </c>
       <c r="J46" t="s">
-        <v>273</v>
+        <v>121</v>
       </c>
       <c r="K46" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="L46" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>274</v>
+        <v>124</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>125</v>
+      </c>
+      <c r="R46" t="s">
+        <v>126</v>
       </c>
       <c r="U46" t="s">
-        <v>184</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>275</v>
+        <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>276</v>
+        <v>42</v>
       </c>
       <c r="D47">
         <v>2025</v>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G47" t="s">
-        <v>179</v>
-      </c>
-      <c r="H47">
-        <v>27758575</v>
+        <v>43</v>
+      </c>
+      <c r="H47" t="s">
+        <v>44</v>
       </c>
       <c r="I47" t="s">
-        <v>277</v>
+        <v>45</v>
       </c>
       <c r="J47" t="s">
-        <v>278</v>
-      </c>
-      <c r="K47" t="s">
-        <v>74</v>
-      </c>
-      <c r="L47" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="P47" t="s">
-        <v>279</v>
-      </c>
-      <c r="U47" t="s">
-        <v>184</v>
+        <v>47</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>48</v>
+      </c>
+      <c r="R47" t="s">
+        <v>49</v>
+      </c>
+      <c r="S47" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>280</v>
+        <v>61</v>
       </c>
       <c r="C48" t="s">
-        <v>281</v>
+        <v>62</v>
       </c>
       <c r="D48">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E48">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>179</v>
-      </c>
-      <c r="H48">
-        <v>27758575</v>
+        <v>63</v>
+      </c>
+      <c r="H48" t="s">
+        <v>64</v>
       </c>
       <c r="I48" t="s">
-        <v>282</v>
+        <v>65</v>
       </c>
       <c r="J48" t="s">
-        <v>283</v>
-      </c>
-      <c r="K48" t="s">
-        <v>74</v>
-      </c>
-      <c r="L48" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="P48" t="s">
-        <v>284</v>
-      </c>
-      <c r="U48" t="s">
-        <v>184</v>
+        <v>67</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>68</v>
+      </c>
+      <c r="R48" t="s">
+        <v>69</v>
+      </c>
+      <c r="S48" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>285</v>
+        <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>286</v>
+        <v>52</v>
       </c>
       <c r="D49">
         <v>2025</v>
       </c>
       <c r="E49">
+        <v>14</v>
+      </c>
+      <c r="F49">
         <v>5</v>
       </c>
-      <c r="F49">
-        <v>3</v>
-      </c>
       <c r="G49" t="s">
-        <v>179</v>
-      </c>
-      <c r="H49">
-        <v>27758575</v>
+        <v>53</v>
+      </c>
+      <c r="H49" t="s">
+        <v>54</v>
       </c>
       <c r="I49" t="s">
-        <v>287</v>
+        <v>55</v>
       </c>
       <c r="J49" t="s">
-        <v>288</v>
-      </c>
-      <c r="K49" t="s">
-        <v>74</v>
-      </c>
-      <c r="L49" t="s">
-        <v>182</v>
+        <v>56</v>
       </c>
       <c r="P49" t="s">
-        <v>289</v>
-      </c>
-      <c r="U49" t="s">
-        <v>184</v>
+        <v>57</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>58</v>
+      </c>
+      <c r="R49" t="s">
+        <v>59</v>
+      </c>
+      <c r="S49" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>290</v>
+        <v>91</v>
       </c>
       <c r="C50" t="s">
-        <v>291</v>
+        <v>92</v>
       </c>
       <c r="D50">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E50">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>179</v>
-      </c>
-      <c r="H50">
-        <v>27758575</v>
+        <v>93</v>
+      </c>
+      <c r="H50" t="s">
+        <v>94</v>
       </c>
       <c r="I50" t="s">
-        <v>292</v>
+        <v>95</v>
       </c>
       <c r="J50" t="s">
-        <v>293</v>
-      </c>
-      <c r="K50" t="s">
-        <v>74</v>
-      </c>
-      <c r="L50" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="P50" t="s">
-        <v>294</v>
-      </c>
-      <c r="U50" t="s">
-        <v>184</v>
+        <v>97</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>98</v>
+      </c>
+      <c r="R50" t="s">
+        <v>99</v>
+      </c>
+      <c r="S50" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>295</v>
+        <v>223</v>
       </c>
       <c r="C51" t="s">
-        <v>296</v>
+        <v>224</v>
       </c>
       <c r="D51">
         <v>2025</v>
       </c>
       <c r="E51">
+        <v>9</v>
+      </c>
+      <c r="F51">
         <v>5</v>
       </c>
-      <c r="F51">
-        <v>3</v>
-      </c>
       <c r="G51" t="s">
-        <v>179</v>
-      </c>
-      <c r="H51">
-        <v>27758575</v>
+        <v>225</v>
+      </c>
+      <c r="H51" t="s">
+        <v>226</v>
       </c>
       <c r="I51" t="s">
-        <v>297</v>
+        <v>227</v>
       </c>
       <c r="J51" t="s">
-        <v>298</v>
-      </c>
-      <c r="K51" t="s">
-        <v>74</v>
-      </c>
-      <c r="L51" t="s">
-        <v>182</v>
+        <v>228</v>
       </c>
       <c r="P51" t="s">
-        <v>299</v>
-      </c>
-      <c r="U51" t="s">
-        <v>184</v>
+        <v>229</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>230</v>
+      </c>
+      <c r="R51" t="s">
+        <v>231</v>
+      </c>
+      <c r="S51" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>300</v>
+        <v>71</v>
       </c>
       <c r="C52" t="s">
-        <v>301</v>
+        <v>72</v>
       </c>
       <c r="D52">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E52">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>179</v>
-      </c>
-      <c r="H52">
-        <v>27758575</v>
+        <v>73</v>
+      </c>
+      <c r="H52" t="s">
+        <v>74</v>
       </c>
       <c r="I52" t="s">
-        <v>302</v>
+        <v>75</v>
       </c>
       <c r="J52" t="s">
-        <v>303</v>
-      </c>
-      <c r="K52" t="s">
-        <v>74</v>
-      </c>
-      <c r="L52" t="s">
-        <v>182</v>
+        <v>76</v>
       </c>
       <c r="P52" t="s">
-        <v>304</v>
-      </c>
-      <c r="U52" t="s">
-        <v>184</v>
+        <v>77</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>78</v>
+      </c>
+      <c r="R52" t="s">
+        <v>79</v>
+      </c>
+      <c r="S52" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="C53" t="s">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="D53">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E53">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>179</v>
-      </c>
-      <c r="H53">
-        <v>27758575</v>
+        <v>83</v>
+      </c>
+      <c r="H53" t="s">
+        <v>84</v>
       </c>
       <c r="I53" t="s">
-        <v>287</v>
+        <v>85</v>
       </c>
       <c r="J53" t="s">
-        <v>288</v>
-      </c>
-      <c r="K53" t="s">
-        <v>74</v>
-      </c>
-      <c r="L53" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="P53" t="s">
-        <v>289</v>
-      </c>
-      <c r="U53" t="s">
-        <v>184</v>
+        <v>87</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>88</v>
+      </c>
+      <c r="R53" t="s">
+        <v>89</v>
+      </c>
+      <c r="S53" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>305</v>
+        <v>233</v>
       </c>
       <c r="C54" t="s">
-        <v>306</v>
+        <v>234</v>
       </c>
       <c r="D54">
         <v>2025</v>
       </c>
       <c r="E54">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F54">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G54" t="s">
-        <v>179</v>
-      </c>
-      <c r="H54">
-        <v>27758575</v>
+        <v>235</v>
+      </c>
+      <c r="H54" t="s">
+        <v>236</v>
       </c>
       <c r="I54" t="s">
-        <v>307</v>
+        <v>237</v>
       </c>
       <c r="J54" t="s">
-        <v>308</v>
-      </c>
-      <c r="K54" t="s">
-        <v>74</v>
-      </c>
-      <c r="L54" t="s">
-        <v>182</v>
+        <v>238</v>
       </c>
       <c r="P54" t="s">
-        <v>309</v>
-      </c>
-      <c r="U54" t="s">
-        <v>184</v>
+        <v>239</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>240</v>
+      </c>
+      <c r="R54" t="s">
+        <v>241</v>
+      </c>
+      <c r="S54" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>310</v>
+        <v>258</v>
       </c>
       <c r="C55" t="s">
-        <v>311</v>
+        <v>259</v>
       </c>
       <c r="D55">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E55">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>179</v>
-      </c>
-      <c r="H55">
-        <v>27758575</v>
+        <v>260</v>
+      </c>
+      <c r="H55" t="s">
+        <v>261</v>
       </c>
       <c r="I55" t="s">
-        <v>312</v>
+        <v>262</v>
       </c>
       <c r="J55" t="s">
-        <v>313</v>
-      </c>
-      <c r="K55" t="s">
-        <v>74</v>
-      </c>
-      <c r="L55" t="s">
-        <v>182</v>
+        <v>263</v>
       </c>
       <c r="P55" t="s">
-        <v>314</v>
-      </c>
-      <c r="U55" t="s">
-        <v>184</v>
+        <v>264</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>265</v>
+      </c>
+      <c r="R55" t="s">
+        <v>266</v>
+      </c>
+      <c r="S55" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>315</v>
+        <v>559</v>
       </c>
       <c r="C56" t="s">
-        <v>316</v>
+        <v>560</v>
       </c>
       <c r="D56">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>179</v>
-      </c>
-      <c r="H56">
-        <v>27758575</v>
+        <v>561</v>
+      </c>
+      <c r="H56" t="s">
+        <v>562</v>
       </c>
       <c r="I56" t="s">
-        <v>317</v>
+        <v>563</v>
       </c>
       <c r="J56" t="s">
-        <v>318</v>
-      </c>
-      <c r="K56" t="s">
-        <v>74</v>
-      </c>
-      <c r="L56" t="s">
-        <v>182</v>
+        <v>564</v>
       </c>
       <c r="P56" t="s">
-        <v>319</v>
-      </c>
-      <c r="U56" t="s">
-        <v>184</v>
+        <v>565</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>566</v>
+      </c>
+      <c r="R56" t="s">
+        <v>567</v>
+      </c>
+      <c r="S56" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="C57" t="s">
-        <v>321</v>
+        <v>22</v>
       </c>
       <c r="D57">
         <v>2025</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F57">
         <v>4</v>
       </c>
       <c r="G57" t="s">
-        <v>179</v>
-      </c>
-      <c r="H57">
-        <v>27758575</v>
+        <v>23</v>
+      </c>
+      <c r="H57" t="s">
+        <v>24</v>
       </c>
       <c r="I57" t="s">
-        <v>322</v>
+        <v>25</v>
       </c>
       <c r="J57" t="s">
-        <v>323</v>
-      </c>
-      <c r="K57" t="s">
-        <v>74</v>
-      </c>
-      <c r="L57" t="s">
-        <v>182</v>
+        <v>26</v>
       </c>
       <c r="P57" t="s">
-        <v>324</v>
-      </c>
-      <c r="U57" t="s">
-        <v>184</v>
+        <v>27</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>28</v>
+      </c>
+      <c r="R57" t="s">
+        <v>29</v>
+      </c>
+      <c r="S57" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>325</v>
+        <v>101</v>
       </c>
       <c r="C58" t="s">
-        <v>326</v>
+        <v>102</v>
       </c>
       <c r="D58">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="E58">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58" t="s">
-        <v>179</v>
-      </c>
-      <c r="H58">
-        <v>27758575</v>
+        <v>103</v>
+      </c>
+      <c r="H58" t="s">
+        <v>104</v>
       </c>
       <c r="I58" t="s">
-        <v>327</v>
+        <v>105</v>
       </c>
       <c r="J58" t="s">
-        <v>328</v>
+        <v>106</v>
       </c>
       <c r="K58" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="L58" t="s">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="P58" t="s">
-        <v>329</v>
+        <v>109</v>
       </c>
       <c r="U58" t="s">
-        <v>184</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>330</v>
+        <v>111</v>
       </c>
       <c r="C59" t="s">
-        <v>331</v>
+        <v>112</v>
       </c>
       <c r="D59">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="E59">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" t="s">
-        <v>179</v>
-      </c>
-      <c r="H59">
-        <v>27758575</v>
+        <v>103</v>
+      </c>
+      <c r="H59" t="s">
+        <v>104</v>
       </c>
       <c r="I59" t="s">
-        <v>332</v>
+        <v>113</v>
       </c>
       <c r="J59" t="s">
-        <v>333</v>
+        <v>114</v>
       </c>
       <c r="K59" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="L59" t="s">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="P59" t="s">
-        <v>334</v>
+        <v>115</v>
       </c>
       <c r="U59" t="s">
-        <v>184</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>335</v>
+        <v>128</v>
       </c>
       <c r="C60" t="s">
-        <v>336</v>
+        <v>129</v>
       </c>
       <c r="D60">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="E60">
         <v>3</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60" t="s">
-        <v>337</v>
-      </c>
-      <c r="H60">
-        <v>27763242</v>
+        <v>130</v>
+      </c>
+      <c r="H60" t="s">
+        <v>131</v>
       </c>
       <c r="I60" t="s">
-        <v>338</v>
+        <v>132</v>
       </c>
       <c r="J60" t="s">
-        <v>339</v>
+        <v>133</v>
       </c>
       <c r="K60" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="L60" t="s">
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>341</v>
-      </c>
-      <c r="U60" t="s">
-        <v>342</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>343</v>
+        <v>137</v>
       </c>
       <c r="C61" t="s">
-        <v>344</v>
+        <v>138</v>
       </c>
       <c r="D61">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>337</v>
-      </c>
-      <c r="H61">
-        <v>27763242</v>
+        <v>130</v>
+      </c>
+      <c r="H61" t="s">
+        <v>131</v>
       </c>
       <c r="I61" t="s">
-        <v>345</v>
+        <v>139</v>
       </c>
       <c r="J61" t="s">
-        <v>346</v>
+        <v>140</v>
       </c>
       <c r="K61" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="L61" t="s">
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="P61" t="s">
-        <v>347</v>
-      </c>
-      <c r="U61" t="s">
-        <v>342</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>142</v>
+      </c>
+      <c r="C62" t="s">
+        <v>143</v>
+      </c>
+      <c r="D62">
+        <v>2025</v>
+      </c>
+      <c r="E62">
+        <v>10</v>
+      </c>
+      <c r="F62">
         <v>3</v>
       </c>
-      <c r="B62" t="s">
-        <v>348</v>
-      </c>
-      <c r="C62" t="s">
-        <v>349</v>
-      </c>
-      <c r="D62">
-        <v>2024</v>
-      </c>
-      <c r="E62">
-        <v>4</v>
-      </c>
-      <c r="F62">
-        <v>2</v>
-      </c>
       <c r="G62" t="s">
-        <v>337</v>
-      </c>
-      <c r="H62">
-        <v>27763242</v>
+        <v>130</v>
+      </c>
+      <c r="H62" t="s">
+        <v>131</v>
       </c>
       <c r="I62" t="s">
-        <v>350</v>
+        <v>144</v>
       </c>
       <c r="J62" t="s">
-        <v>351</v>
+        <v>145</v>
       </c>
       <c r="K62" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="L62" t="s">
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="P62" t="s">
-        <v>352</v>
-      </c>
-      <c r="U62" t="s">
-        <v>342</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>353</v>
+        <v>147</v>
       </c>
       <c r="C63" t="s">
-        <v>354</v>
+        <v>148</v>
       </c>
       <c r="D63">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F63">
         <v>3</v>
       </c>
       <c r="G63" t="s">
-        <v>337</v>
-      </c>
-      <c r="H63">
-        <v>27763242</v>
+        <v>130</v>
+      </c>
+      <c r="H63" t="s">
+        <v>131</v>
       </c>
       <c r="I63" t="s">
-        <v>355</v>
+        <v>149</v>
       </c>
       <c r="J63" t="s">
-        <v>356</v>
+        <v>150</v>
       </c>
       <c r="K63" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="L63" t="s">
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>357</v>
-      </c>
-      <c r="U63" t="s">
-        <v>342</v>
+        <v>151</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>358</v>
+        <v>152</v>
       </c>
       <c r="C64" t="s">
-        <v>359</v>
+        <v>153</v>
       </c>
       <c r="D64">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E64">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>337</v>
-      </c>
-      <c r="H64">
-        <v>27763242</v>
+        <v>130</v>
+      </c>
+      <c r="H64" t="s">
+        <v>131</v>
       </c>
       <c r="I64" t="s">
-        <v>360</v>
+        <v>154</v>
       </c>
       <c r="J64" t="s">
-        <v>361</v>
+        <v>155</v>
       </c>
       <c r="K64" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="L64" t="s">
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>362</v>
-      </c>
-      <c r="U64" t="s">
-        <v>342</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>157</v>
+      </c>
+      <c r="C65" t="s">
+        <v>158</v>
+      </c>
+      <c r="D65">
+        <v>2021</v>
+      </c>
+      <c r="E65">
         <v>6</v>
       </c>
-      <c r="B65" t="s">
-        <v>363</v>
-      </c>
-      <c r="C65" t="s">
-        <v>364</v>
-      </c>
-      <c r="D65">
-        <v>2024</v>
-      </c>
-      <c r="E65">
-        <v>4</v>
-      </c>
       <c r="F65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G65" t="s">
-        <v>337</v>
-      </c>
-      <c r="H65">
-        <v>27763242</v>
+        <v>130</v>
+      </c>
+      <c r="H65" t="s">
+        <v>131</v>
       </c>
       <c r="I65" t="s">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="J65" t="s">
-        <v>366</v>
+        <v>160</v>
       </c>
       <c r="K65" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="L65" t="s">
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>367</v>
-      </c>
-      <c r="U65" t="s">
-        <v>342</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>368</v>
+        <v>162</v>
       </c>
       <c r="C66" t="s">
-        <v>369</v>
+        <v>163</v>
       </c>
       <c r="D66">
         <v>2025</v>
       </c>
       <c r="E66">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66" t="s">
-        <v>337</v>
-      </c>
-      <c r="H66">
-        <v>27763242</v>
+        <v>130</v>
+      </c>
+      <c r="H66" t="s">
+        <v>131</v>
       </c>
       <c r="I66" t="s">
-        <v>370</v>
+        <v>164</v>
       </c>
       <c r="J66" t="s">
-        <v>371</v>
+        <v>165</v>
       </c>
       <c r="K66" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="L66" t="s">
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>372</v>
-      </c>
-      <c r="U66" t="s">
-        <v>342</v>
+        <v>166</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>373</v>
+        <v>167</v>
       </c>
       <c r="C67" t="s">
-        <v>374</v>
+        <v>168</v>
       </c>
       <c r="D67">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>337</v>
-      </c>
-      <c r="H67">
-        <v>27763242</v>
+        <v>130</v>
+      </c>
+      <c r="H67" t="s">
+        <v>131</v>
       </c>
       <c r="I67" t="s">
-        <v>375</v>
+        <v>169</v>
       </c>
       <c r="J67" t="s">
-        <v>376</v>
+        <v>170</v>
       </c>
       <c r="K67" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="L67" t="s">
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>377</v>
-      </c>
-      <c r="U67" t="s">
-        <v>342</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>378</v>
+        <v>172</v>
       </c>
       <c r="C68" t="s">
-        <v>379</v>
+        <v>173</v>
       </c>
       <c r="D68">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>337</v>
-      </c>
-      <c r="H68">
-        <v>27763242</v>
+        <v>130</v>
+      </c>
+      <c r="H68" t="s">
+        <v>131</v>
       </c>
       <c r="I68" t="s">
-        <v>380</v>
+        <v>174</v>
       </c>
       <c r="J68" t="s">
-        <v>381</v>
+        <v>175</v>
       </c>
       <c r="K68" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="L68" t="s">
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>382</v>
-      </c>
-      <c r="U68" t="s">
-        <v>342</v>
+        <v>176</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>383</v>
+        <v>177</v>
       </c>
       <c r="C69" t="s">
-        <v>384</v>
+        <v>178</v>
       </c>
       <c r="D69">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="E69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F69">
         <v>2</v>
       </c>
       <c r="G69" t="s">
-        <v>337</v>
-      </c>
-      <c r="H69">
-        <v>27763242</v>
+        <v>179</v>
+      </c>
+      <c r="H69" t="s">
+        <v>180</v>
       </c>
       <c r="I69" t="s">
-        <v>385</v>
+        <v>181</v>
       </c>
       <c r="J69" t="s">
-        <v>386</v>
+        <v>182</v>
       </c>
       <c r="K69" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="L69" t="s">
-        <v>340</v>
+        <v>183</v>
+      </c>
+      <c r="M69" t="s">
+        <v>184</v>
       </c>
       <c r="P69" t="s">
-        <v>387</v>
+        <v>185</v>
       </c>
       <c r="U69" t="s">
-        <v>342</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>388</v>
+        <v>187</v>
       </c>
       <c r="C70" t="s">
-        <v>389</v>
+        <v>188</v>
       </c>
       <c r="D70">
         <v>2025</v>
       </c>
       <c r="E70">
+        <v>14</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70" t="s">
+        <v>179</v>
+      </c>
+      <c r="H70" t="s">
+        <v>180</v>
+      </c>
+      <c r="I70" t="s">
+        <v>189</v>
+      </c>
+      <c r="J70" t="s">
+        <v>190</v>
+      </c>
+      <c r="K70" t="s">
+        <v>107</v>
+      </c>
+      <c r="L70" t="s">
+        <v>183</v>
+      </c>
+      <c r="P70" t="s">
+        <v>191</v>
+      </c>
+      <c r="U70" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>192</v>
+      </c>
+      <c r="C71" t="s">
+        <v>193</v>
+      </c>
+      <c r="D71">
+        <v>2023</v>
+      </c>
+      <c r="E71">
+        <v>8</v>
+      </c>
+      <c r="F71">
+        <v>2</v>
+      </c>
+      <c r="G71" t="s">
+        <v>194</v>
+      </c>
+      <c r="H71" t="s">
+        <v>195</v>
+      </c>
+      <c r="I71" t="s">
+        <v>196</v>
+      </c>
+      <c r="J71" t="s">
+        <v>197</v>
+      </c>
+      <c r="K71" t="s">
+        <v>107</v>
+      </c>
+      <c r="L71" t="s">
+        <v>198</v>
+      </c>
+      <c r="M71" t="s">
+        <v>199</v>
+      </c>
+      <c r="P71" t="s">
+        <v>200</v>
+      </c>
+      <c r="U71" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>202</v>
+      </c>
+      <c r="C72" t="s">
+        <v>203</v>
+      </c>
+      <c r="D72">
+        <v>2019</v>
+      </c>
+      <c r="E72">
+        <v>4</v>
+      </c>
+      <c r="F72">
+        <v>2</v>
+      </c>
+      <c r="G72" t="s">
+        <v>194</v>
+      </c>
+      <c r="H72" t="s">
+        <v>195</v>
+      </c>
+      <c r="I72" t="s">
+        <v>204</v>
+      </c>
+      <c r="J72" t="s">
+        <v>205</v>
+      </c>
+      <c r="K72" t="s">
+        <v>107</v>
+      </c>
+      <c r="L72" t="s">
+        <v>198</v>
+      </c>
+      <c r="M72" t="s">
+        <v>184</v>
+      </c>
+      <c r="P72" t="s">
+        <v>206</v>
+      </c>
+      <c r="U72" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>207</v>
+      </c>
+      <c r="C73" t="s">
+        <v>208</v>
+      </c>
+      <c r="D73">
+        <v>2021</v>
+      </c>
+      <c r="E73">
+        <v>6</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+      <c r="G73" t="s">
+        <v>194</v>
+      </c>
+      <c r="H73" t="s">
+        <v>195</v>
+      </c>
+      <c r="I73" t="s">
+        <v>209</v>
+      </c>
+      <c r="J73" t="s">
+        <v>210</v>
+      </c>
+      <c r="K73" t="s">
+        <v>107</v>
+      </c>
+      <c r="L73" t="s">
+        <v>198</v>
+      </c>
+      <c r="M73" t="s">
+        <v>211</v>
+      </c>
+      <c r="P73" t="s">
+        <v>212</v>
+      </c>
+      <c r="U73" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>213</v>
+      </c>
+      <c r="C74" t="s">
+        <v>214</v>
+      </c>
+      <c r="D74">
+        <v>2025</v>
+      </c>
+      <c r="E74">
+        <v>10</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74" t="s">
+        <v>194</v>
+      </c>
+      <c r="H74" t="s">
+        <v>195</v>
+      </c>
+      <c r="I74" t="s">
+        <v>215</v>
+      </c>
+      <c r="J74" t="s">
+        <v>216</v>
+      </c>
+      <c r="K74" t="s">
+        <v>107</v>
+      </c>
+      <c r="L74" t="s">
+        <v>198</v>
+      </c>
+      <c r="P74" t="s">
+        <v>217</v>
+      </c>
+      <c r="U74" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>218</v>
+      </c>
+      <c r="C75" t="s">
+        <v>219</v>
+      </c>
+      <c r="D75">
+        <v>2020</v>
+      </c>
+      <c r="E75">
         <v>5</v>
       </c>
-      <c r="F70">
+      <c r="F75">
+        <v>2</v>
+      </c>
+      <c r="G75" t="s">
+        <v>194</v>
+      </c>
+      <c r="H75" t="s">
+        <v>195</v>
+      </c>
+      <c r="I75" t="s">
+        <v>220</v>
+      </c>
+      <c r="J75" t="s">
+        <v>221</v>
+      </c>
+      <c r="K75" t="s">
+        <v>107</v>
+      </c>
+      <c r="L75" t="s">
+        <v>198</v>
+      </c>
+      <c r="P75" t="s">
+        <v>222</v>
+      </c>
+      <c r="U75" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>243</v>
+      </c>
+      <c r="C76" t="s">
+        <v>244</v>
+      </c>
+      <c r="D76">
+        <v>2023</v>
+      </c>
+      <c r="E76">
+        <v>6</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+      <c r="G76" t="s">
+        <v>245</v>
+      </c>
+      <c r="H76" t="s">
+        <v>246</v>
+      </c>
+      <c r="I76" t="s">
+        <v>247</v>
+      </c>
+      <c r="J76" t="s">
+        <v>248</v>
+      </c>
+      <c r="K76" t="s">
+        <v>249</v>
+      </c>
+      <c r="L76" t="s">
+        <v>250</v>
+      </c>
+      <c r="P76" t="s">
+        <v>251</v>
+      </c>
+      <c r="U76" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>253</v>
+      </c>
+      <c r="C77" t="s">
+        <v>254</v>
+      </c>
+      <c r="D77">
+        <v>2022</v>
+      </c>
+      <c r="E77">
+        <v>5</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77" t="s">
+        <v>245</v>
+      </c>
+      <c r="H77" t="s">
+        <v>246</v>
+      </c>
+      <c r="I77" t="s">
+        <v>255</v>
+      </c>
+      <c r="J77" t="s">
+        <v>256</v>
+      </c>
+      <c r="K77" t="s">
+        <v>249</v>
+      </c>
+      <c r="L77" t="s">
+        <v>250</v>
+      </c>
+      <c r="P77" t="s">
+        <v>257</v>
+      </c>
+      <c r="U77" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>268</v>
+      </c>
+      <c r="C78" t="s">
+        <v>269</v>
+      </c>
+      <c r="D78">
+        <v>2025</v>
+      </c>
+      <c r="E78">
+        <v>6</v>
+      </c>
+      <c r="F78">
+        <v>2</v>
+      </c>
+      <c r="G78" t="s">
+        <v>270</v>
+      </c>
+      <c r="H78" t="s">
+        <v>271</v>
+      </c>
+      <c r="I78" t="s">
+        <v>272</v>
+      </c>
+      <c r="J78" t="s">
+        <v>273</v>
+      </c>
+      <c r="K78" t="s">
+        <v>249</v>
+      </c>
+      <c r="L78" t="s">
+        <v>274</v>
+      </c>
+      <c r="P78" t="s">
+        <v>275</v>
+      </c>
+      <c r="U78" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>277</v>
+      </c>
+      <c r="C79" t="s">
+        <v>278</v>
+      </c>
+      <c r="D79">
+        <v>2024</v>
+      </c>
+      <c r="E79">
+        <v>5</v>
+      </c>
+      <c r="F79">
+        <v>2</v>
+      </c>
+      <c r="G79" t="s">
+        <v>279</v>
+      </c>
+      <c r="H79" t="s">
+        <v>280</v>
+      </c>
+      <c r="I79" t="s">
+        <v>281</v>
+      </c>
+      <c r="J79" t="s">
+        <v>282</v>
+      </c>
+      <c r="K79" t="s">
+        <v>134</v>
+      </c>
+      <c r="L79" t="s">
+        <v>283</v>
+      </c>
+      <c r="P79" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>503</v>
+      </c>
+      <c r="C80" t="s">
+        <v>504</v>
+      </c>
+      <c r="D80">
+        <v>2023</v>
+      </c>
+      <c r="E80">
+        <v>4</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80" t="s">
+        <v>505</v>
+      </c>
+      <c r="H80" t="s">
+        <v>506</v>
+      </c>
+      <c r="I80" t="s">
+        <v>507</v>
+      </c>
+      <c r="J80" t="s">
+        <v>508</v>
+      </c>
+      <c r="K80" t="s">
+        <v>107</v>
+      </c>
+      <c r="L80" t="s">
+        <v>509</v>
+      </c>
+      <c r="P80" t="s">
+        <v>510</v>
+      </c>
+      <c r="U80" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>512</v>
+      </c>
+      <c r="C81" t="s">
+        <v>513</v>
+      </c>
+      <c r="D81">
+        <v>2020</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="F81">
+        <v>2</v>
+      </c>
+      <c r="G81" t="s">
+        <v>505</v>
+      </c>
+      <c r="H81" t="s">
+        <v>506</v>
+      </c>
+      <c r="I81" t="s">
+        <v>514</v>
+      </c>
+      <c r="J81" t="s">
+        <v>515</v>
+      </c>
+      <c r="K81" t="s">
+        <v>107</v>
+      </c>
+      <c r="L81" t="s">
+        <v>509</v>
+      </c>
+      <c r="P81" t="s">
+        <v>516</v>
+      </c>
+      <c r="U81" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>517</v>
+      </c>
+      <c r="C82" t="s">
+        <v>518</v>
+      </c>
+      <c r="D82">
+        <v>2024</v>
+      </c>
+      <c r="E82">
+        <v>5</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82" t="s">
+        <v>505</v>
+      </c>
+      <c r="H82" t="s">
+        <v>506</v>
+      </c>
+      <c r="I82" t="s">
+        <v>519</v>
+      </c>
+      <c r="J82" t="s">
+        <v>520</v>
+      </c>
+      <c r="K82" t="s">
+        <v>107</v>
+      </c>
+      <c r="L82" t="s">
+        <v>509</v>
+      </c>
+      <c r="P82" t="s">
+        <v>521</v>
+      </c>
+      <c r="U82" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>522</v>
+      </c>
+      <c r="C83" t="s">
+        <v>523</v>
+      </c>
+      <c r="D83">
+        <v>2025</v>
+      </c>
+      <c r="E83">
+        <v>6</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+      <c r="G83" t="s">
+        <v>524</v>
+      </c>
+      <c r="H83" t="s">
+        <v>525</v>
+      </c>
+      <c r="I83" t="s">
+        <v>526</v>
+      </c>
+      <c r="J83" t="s">
+        <v>523</v>
+      </c>
+      <c r="K83" t="s">
+        <v>249</v>
+      </c>
+      <c r="L83" t="s">
+        <v>527</v>
+      </c>
+      <c r="P83" t="s">
+        <v>528</v>
+      </c>
+      <c r="U83" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>530</v>
+      </c>
+      <c r="C84" t="s">
+        <v>531</v>
+      </c>
+      <c r="D84">
+        <v>2026</v>
+      </c>
+      <c r="E84">
+        <v>6</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84" t="s">
+        <v>532</v>
+      </c>
+      <c r="H84" t="s">
+        <v>533</v>
+      </c>
+      <c r="I84" t="s">
+        <v>534</v>
+      </c>
+      <c r="J84" t="s">
+        <v>535</v>
+      </c>
+      <c r="K84" t="s">
+        <v>107</v>
+      </c>
+      <c r="L84" t="s">
+        <v>536</v>
+      </c>
+      <c r="P84" t="s">
+        <v>537</v>
+      </c>
+      <c r="U84" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>539</v>
+      </c>
+      <c r="C85" t="s">
+        <v>540</v>
+      </c>
+      <c r="D85">
+        <v>2023</v>
+      </c>
+      <c r="E85">
         <v>3</v>
       </c>
-      <c r="G70" t="s">
-        <v>337</v>
-      </c>
-      <c r="H70">
-        <v>27763242</v>
-      </c>
-      <c r="I70" t="s">
-        <v>390</v>
-      </c>
-      <c r="J70" t="s">
-        <v>391</v>
-      </c>
-      <c r="K70" t="s">
-        <v>74</v>
-      </c>
-      <c r="L70" t="s">
-        <v>340</v>
-      </c>
-      <c r="P70" t="s">
-        <v>392</v>
-      </c>
-      <c r="U70" t="s">
-        <v>342</v>
+      <c r="F85">
+        <v>2</v>
+      </c>
+      <c r="G85" t="s">
+        <v>532</v>
+      </c>
+      <c r="H85" t="s">
+        <v>533</v>
+      </c>
+      <c r="I85" t="s">
+        <v>541</v>
+      </c>
+      <c r="J85" t="s">
+        <v>542</v>
+      </c>
+      <c r="K85" t="s">
+        <v>107</v>
+      </c>
+      <c r="L85" t="s">
+        <v>536</v>
+      </c>
+      <c r="P85" t="s">
+        <v>543</v>
+      </c>
+      <c r="U85" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>544</v>
+      </c>
+      <c r="C86" t="s">
+        <v>545</v>
+      </c>
+      <c r="D86">
+        <v>2024</v>
+      </c>
+      <c r="E86">
+        <v>4</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86" t="s">
+        <v>532</v>
+      </c>
+      <c r="H86" t="s">
+        <v>533</v>
+      </c>
+      <c r="I86" t="s">
+        <v>546</v>
+      </c>
+      <c r="J86" t="s">
+        <v>547</v>
+      </c>
+      <c r="K86" t="s">
+        <v>107</v>
+      </c>
+      <c r="L86" t="s">
+        <v>536</v>
+      </c>
+      <c r="P86" t="s">
+        <v>548</v>
+      </c>
+      <c r="U86" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>549</v>
+      </c>
+      <c r="C87" t="s">
+        <v>550</v>
+      </c>
+      <c r="D87">
+        <v>2024</v>
+      </c>
+      <c r="E87">
+        <v>4</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87" t="s">
+        <v>532</v>
+      </c>
+      <c r="H87" t="s">
+        <v>533</v>
+      </c>
+      <c r="I87" t="s">
+        <v>551</v>
+      </c>
+      <c r="J87" t="s">
+        <v>552</v>
+      </c>
+      <c r="K87" t="s">
+        <v>107</v>
+      </c>
+      <c r="L87" t="s">
+        <v>536</v>
+      </c>
+      <c r="P87" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>554</v>
+      </c>
+      <c r="C88" t="s">
+        <v>555</v>
+      </c>
+      <c r="D88">
+        <v>2025</v>
+      </c>
+      <c r="E88">
+        <v>5</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88" t="s">
+        <v>532</v>
+      </c>
+      <c r="H88" t="s">
+        <v>533</v>
+      </c>
+      <c r="I88" t="s">
+        <v>556</v>
+      </c>
+      <c r="J88" t="s">
+        <v>557</v>
+      </c>
+      <c r="K88" t="s">
+        <v>107</v>
+      </c>
+      <c r="L88" t="s">
+        <v>536</v>
+      </c>
+      <c r="P88" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>569</v>
+      </c>
+      <c r="C89" t="s">
+        <v>570</v>
+      </c>
+      <c r="D89">
+        <v>2021</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89" t="s">
+        <v>571</v>
+      </c>
+      <c r="H89" t="s">
+        <v>572</v>
+      </c>
+      <c r="I89" t="s">
+        <v>573</v>
+      </c>
+      <c r="J89" t="s">
+        <v>574</v>
+      </c>
+      <c r="K89" t="s">
+        <v>107</v>
+      </c>
+      <c r="L89" t="s">
+        <v>575</v>
+      </c>
+      <c r="P89" t="s">
+        <v>576</v>
+      </c>
+      <c r="U89" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>578</v>
+      </c>
+      <c r="C90" t="s">
+        <v>579</v>
+      </c>
+      <c r="D90">
+        <v>2023</v>
+      </c>
+      <c r="E90">
+        <v>3</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90" t="s">
+        <v>571</v>
+      </c>
+      <c r="H90" t="s">
+        <v>572</v>
+      </c>
+      <c r="I90" t="s">
+        <v>580</v>
+      </c>
+      <c r="J90" t="s">
+        <v>581</v>
+      </c>
+      <c r="K90" t="s">
+        <v>107</v>
+      </c>
+      <c r="L90" t="s">
+        <v>575</v>
+      </c>
+      <c r="P90" t="s">
+        <v>582</v>
+      </c>
+      <c r="U90" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>583</v>
+      </c>
+      <c r="C91" t="s">
+        <v>584</v>
+      </c>
+      <c r="D91">
+        <v>2023</v>
+      </c>
+      <c r="E91">
+        <v>3</v>
+      </c>
+      <c r="F91">
+        <v>2</v>
+      </c>
+      <c r="G91" t="s">
+        <v>571</v>
+      </c>
+      <c r="H91" t="s">
+        <v>572</v>
+      </c>
+      <c r="I91" t="s">
+        <v>585</v>
+      </c>
+      <c r="J91" t="s">
+        <v>586</v>
+      </c>
+      <c r="K91" t="s">
+        <v>107</v>
+      </c>
+      <c r="L91" t="s">
+        <v>575</v>
+      </c>
+      <c r="P91" t="s">
+        <v>587</v>
+      </c>
+      <c r="U91" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>588</v>
+      </c>
+      <c r="C92" t="s">
+        <v>589</v>
+      </c>
+      <c r="D92">
+        <v>2024</v>
+      </c>
+      <c r="E92">
+        <v>4</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92" t="s">
+        <v>571</v>
+      </c>
+      <c r="H92" t="s">
+        <v>572</v>
+      </c>
+      <c r="I92" t="s">
+        <v>590</v>
+      </c>
+      <c r="J92" t="s">
+        <v>591</v>
+      </c>
+      <c r="K92" t="s">
+        <v>107</v>
+      </c>
+      <c r="L92" t="s">
+        <v>575</v>
+      </c>
+      <c r="P92" t="s">
+        <v>592</v>
+      </c>
+      <c r="U92" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>593</v>
+      </c>
+      <c r="C93" t="s">
+        <v>594</v>
+      </c>
+      <c r="D93">
+        <v>2024</v>
+      </c>
+      <c r="E93">
+        <v>4</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93" t="s">
+        <v>571</v>
+      </c>
+      <c r="H93" t="s">
+        <v>572</v>
+      </c>
+      <c r="I93" t="s">
+        <v>595</v>
+      </c>
+      <c r="J93" t="s">
+        <v>596</v>
+      </c>
+      <c r="K93" t="s">
+        <v>107</v>
+      </c>
+      <c r="L93" t="s">
+        <v>575</v>
+      </c>
+      <c r="P93" t="s">
+        <v>597</v>
+      </c>
+      <c r="U93" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>598</v>
+      </c>
+      <c r="C94" t="s">
+        <v>599</v>
+      </c>
+      <c r="D94">
+        <v>2024</v>
+      </c>
+      <c r="E94">
+        <v>4</v>
+      </c>
+      <c r="F94">
+        <v>2</v>
+      </c>
+      <c r="G94" t="s">
+        <v>571</v>
+      </c>
+      <c r="H94" t="s">
+        <v>572</v>
+      </c>
+      <c r="I94" t="s">
+        <v>600</v>
+      </c>
+      <c r="J94" t="s">
+        <v>601</v>
+      </c>
+      <c r="K94" t="s">
+        <v>107</v>
+      </c>
+      <c r="L94" t="s">
+        <v>575</v>
+      </c>
+      <c r="P94" t="s">
+        <v>602</v>
+      </c>
+      <c r="U94" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>603</v>
+      </c>
+      <c r="C95" t="s">
+        <v>604</v>
+      </c>
+      <c r="D95">
+        <v>2024</v>
+      </c>
+      <c r="E95">
+        <v>4</v>
+      </c>
+      <c r="F95">
+        <v>3</v>
+      </c>
+      <c r="G95" t="s">
+        <v>571</v>
+      </c>
+      <c r="H95" t="s">
+        <v>572</v>
+      </c>
+      <c r="I95" t="s">
+        <v>605</v>
+      </c>
+      <c r="J95" t="s">
+        <v>606</v>
+      </c>
+      <c r="K95" t="s">
+        <v>107</v>
+      </c>
+      <c r="L95" t="s">
+        <v>575</v>
+      </c>
+      <c r="P95" t="s">
+        <v>607</v>
+      </c>
+      <c r="U95" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>608</v>
+      </c>
+      <c r="C96" t="s">
+        <v>609</v>
+      </c>
+      <c r="D96">
+        <v>2024</v>
+      </c>
+      <c r="E96">
+        <v>4</v>
+      </c>
+      <c r="F96">
+        <v>3</v>
+      </c>
+      <c r="G96" t="s">
+        <v>571</v>
+      </c>
+      <c r="H96" t="s">
+        <v>572</v>
+      </c>
+      <c r="I96" t="s">
+        <v>610</v>
+      </c>
+      <c r="J96" t="s">
+        <v>611</v>
+      </c>
+      <c r="K96" t="s">
+        <v>107</v>
+      </c>
+      <c r="L96" t="s">
+        <v>575</v>
+      </c>
+      <c r="P96" t="s">
+        <v>612</v>
+      </c>
+      <c r="U96" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>613</v>
+      </c>
+      <c r="C97" t="s">
+        <v>614</v>
+      </c>
+      <c r="D97">
+        <v>2024</v>
+      </c>
+      <c r="E97">
+        <v>4</v>
+      </c>
+      <c r="F97">
+        <v>3</v>
+      </c>
+      <c r="G97" t="s">
+        <v>571</v>
+      </c>
+      <c r="H97" t="s">
+        <v>572</v>
+      </c>
+      <c r="I97" t="s">
+        <v>615</v>
+      </c>
+      <c r="J97" t="s">
+        <v>616</v>
+      </c>
+      <c r="K97" t="s">
+        <v>107</v>
+      </c>
+      <c r="L97" t="s">
+        <v>575</v>
+      </c>
+      <c r="P97" t="s">
+        <v>617</v>
+      </c>
+      <c r="U97" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>618</v>
+      </c>
+      <c r="C98" t="s">
+        <v>619</v>
+      </c>
+      <c r="D98">
+        <v>2024</v>
+      </c>
+      <c r="E98">
+        <v>4</v>
+      </c>
+      <c r="F98">
+        <v>3</v>
+      </c>
+      <c r="G98" t="s">
+        <v>571</v>
+      </c>
+      <c r="H98" t="s">
+        <v>572</v>
+      </c>
+      <c r="I98" t="s">
+        <v>620</v>
+      </c>
+      <c r="J98" t="s">
+        <v>621</v>
+      </c>
+      <c r="K98" t="s">
+        <v>107</v>
+      </c>
+      <c r="L98" t="s">
+        <v>575</v>
+      </c>
+      <c r="P98" t="s">
+        <v>622</v>
+      </c>
+      <c r="U98" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>623</v>
+      </c>
+      <c r="C99" t="s">
+        <v>624</v>
+      </c>
+      <c r="D99">
+        <v>2024</v>
+      </c>
+      <c r="E99">
+        <v>4</v>
+      </c>
+      <c r="F99">
+        <v>4</v>
+      </c>
+      <c r="G99" t="s">
+        <v>571</v>
+      </c>
+      <c r="H99" t="s">
+        <v>572</v>
+      </c>
+      <c r="I99" t="s">
+        <v>625</v>
+      </c>
+      <c r="J99" t="s">
+        <v>626</v>
+      </c>
+      <c r="K99" t="s">
+        <v>107</v>
+      </c>
+      <c r="L99" t="s">
+        <v>575</v>
+      </c>
+      <c r="P99" t="s">
+        <v>627</v>
+      </c>
+      <c r="U99" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>628</v>
+      </c>
+      <c r="C100" t="s">
+        <v>629</v>
+      </c>
+      <c r="D100">
+        <v>2024</v>
+      </c>
+      <c r="E100">
+        <v>4</v>
+      </c>
+      <c r="F100">
+        <v>4</v>
+      </c>
+      <c r="G100" t="s">
+        <v>571</v>
+      </c>
+      <c r="H100" t="s">
+        <v>572</v>
+      </c>
+      <c r="I100" t="s">
+        <v>630</v>
+      </c>
+      <c r="J100" t="s">
+        <v>631</v>
+      </c>
+      <c r="K100" t="s">
+        <v>107</v>
+      </c>
+      <c r="L100" t="s">
+        <v>575</v>
+      </c>
+      <c r="P100" t="s">
+        <v>632</v>
+      </c>
+      <c r="U100" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>633</v>
+      </c>
+      <c r="C101" t="s">
+        <v>634</v>
+      </c>
+      <c r="D101">
+        <v>2024</v>
+      </c>
+      <c r="E101">
+        <v>4</v>
+      </c>
+      <c r="F101">
+        <v>4</v>
+      </c>
+      <c r="G101" t="s">
+        <v>571</v>
+      </c>
+      <c r="H101" t="s">
+        <v>572</v>
+      </c>
+      <c r="I101" t="s">
+        <v>635</v>
+      </c>
+      <c r="J101" t="s">
+        <v>636</v>
+      </c>
+      <c r="K101" t="s">
+        <v>107</v>
+      </c>
+      <c r="L101" t="s">
+        <v>575</v>
+      </c>
+      <c r="P101" t="s">
+        <v>637</v>
+      </c>
+      <c r="U101" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>638</v>
+      </c>
+      <c r="C102" t="s">
+        <v>639</v>
+      </c>
+      <c r="D102">
+        <v>2024</v>
+      </c>
+      <c r="E102">
+        <v>4</v>
+      </c>
+      <c r="F102">
+        <v>4</v>
+      </c>
+      <c r="G102" t="s">
+        <v>571</v>
+      </c>
+      <c r="H102" t="s">
+        <v>572</v>
+      </c>
+      <c r="I102" t="s">
+        <v>640</v>
+      </c>
+      <c r="J102" t="s">
+        <v>641</v>
+      </c>
+      <c r="K102" t="s">
+        <v>107</v>
+      </c>
+      <c r="L102" t="s">
+        <v>575</v>
+      </c>
+      <c r="P102" t="s">
+        <v>642</v>
+      </c>
+      <c r="U102" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>643</v>
+      </c>
+      <c r="C103" t="s">
+        <v>644</v>
+      </c>
+      <c r="D103">
+        <v>2024</v>
+      </c>
+      <c r="E103">
+        <v>4</v>
+      </c>
+      <c r="F103">
+        <v>4</v>
+      </c>
+      <c r="G103" t="s">
+        <v>571</v>
+      </c>
+      <c r="H103" t="s">
+        <v>572</v>
+      </c>
+      <c r="I103" t="s">
+        <v>645</v>
+      </c>
+      <c r="J103" t="s">
+        <v>646</v>
+      </c>
+      <c r="K103" t="s">
+        <v>107</v>
+      </c>
+      <c r="L103" t="s">
+        <v>575</v>
+      </c>
+      <c r="P103" t="s">
+        <v>647</v>
+      </c>
+      <c r="U103" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>648</v>
+      </c>
+      <c r="C104" t="s">
+        <v>649</v>
+      </c>
+      <c r="D104">
+        <v>2024</v>
+      </c>
+      <c r="E104">
+        <v>4</v>
+      </c>
+      <c r="F104">
+        <v>4</v>
+      </c>
+      <c r="G104" t="s">
+        <v>571</v>
+      </c>
+      <c r="H104" t="s">
+        <v>572</v>
+      </c>
+      <c r="I104" t="s">
+        <v>650</v>
+      </c>
+      <c r="J104" t="s">
+        <v>651</v>
+      </c>
+      <c r="K104" t="s">
+        <v>107</v>
+      </c>
+      <c r="L104" t="s">
+        <v>575</v>
+      </c>
+      <c r="P104" t="s">
+        <v>652</v>
+      </c>
+      <c r="U104" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>653</v>
+      </c>
+      <c r="C105" t="s">
+        <v>654</v>
+      </c>
+      <c r="D105">
+        <v>2025</v>
+      </c>
+      <c r="E105">
+        <v>5</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="G105" t="s">
+        <v>571</v>
+      </c>
+      <c r="H105" t="s">
+        <v>572</v>
+      </c>
+      <c r="I105" t="s">
+        <v>655</v>
+      </c>
+      <c r="J105" t="s">
+        <v>656</v>
+      </c>
+      <c r="K105" t="s">
+        <v>107</v>
+      </c>
+      <c r="L105" t="s">
+        <v>575</v>
+      </c>
+      <c r="P105" t="s">
+        <v>657</v>
+      </c>
+      <c r="U105" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>658</v>
+      </c>
+      <c r="C106" t="s">
+        <v>659</v>
+      </c>
+      <c r="D106">
+        <v>2025</v>
+      </c>
+      <c r="E106">
+        <v>5</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+      <c r="G106" t="s">
+        <v>571</v>
+      </c>
+      <c r="H106" t="s">
+        <v>572</v>
+      </c>
+      <c r="I106" t="s">
+        <v>660</v>
+      </c>
+      <c r="J106" t="s">
+        <v>661</v>
+      </c>
+      <c r="K106" t="s">
+        <v>107</v>
+      </c>
+      <c r="L106" t="s">
+        <v>575</v>
+      </c>
+      <c r="P106" t="s">
+        <v>662</v>
+      </c>
+      <c r="U106" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>663</v>
+      </c>
+      <c r="C107" t="s">
+        <v>664</v>
+      </c>
+      <c r="D107">
+        <v>2025</v>
+      </c>
+      <c r="E107">
+        <v>5</v>
+      </c>
+      <c r="F107">
+        <v>2</v>
+      </c>
+      <c r="G107" t="s">
+        <v>571</v>
+      </c>
+      <c r="H107" t="s">
+        <v>572</v>
+      </c>
+      <c r="I107" t="s">
+        <v>665</v>
+      </c>
+      <c r="J107" t="s">
+        <v>666</v>
+      </c>
+      <c r="K107" t="s">
+        <v>107</v>
+      </c>
+      <c r="L107" t="s">
+        <v>575</v>
+      </c>
+      <c r="P107" t="s">
+        <v>667</v>
+      </c>
+      <c r="U107" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>668</v>
+      </c>
+      <c r="C108" t="s">
+        <v>669</v>
+      </c>
+      <c r="D108">
+        <v>2025</v>
+      </c>
+      <c r="E108">
+        <v>5</v>
+      </c>
+      <c r="F108">
+        <v>2</v>
+      </c>
+      <c r="G108" t="s">
+        <v>571</v>
+      </c>
+      <c r="H108" t="s">
+        <v>572</v>
+      </c>
+      <c r="I108" t="s">
+        <v>670</v>
+      </c>
+      <c r="J108" t="s">
+        <v>671</v>
+      </c>
+      <c r="K108" t="s">
+        <v>107</v>
+      </c>
+      <c r="L108" t="s">
+        <v>575</v>
+      </c>
+      <c r="P108" t="s">
+        <v>672</v>
+      </c>
+      <c r="U108" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>673</v>
+      </c>
+      <c r="C109" t="s">
+        <v>674</v>
+      </c>
+      <c r="D109">
+        <v>2025</v>
+      </c>
+      <c r="E109">
+        <v>5</v>
+      </c>
+      <c r="F109">
+        <v>2</v>
+      </c>
+      <c r="G109" t="s">
+        <v>571</v>
+      </c>
+      <c r="H109" t="s">
+        <v>572</v>
+      </c>
+      <c r="I109" t="s">
+        <v>675</v>
+      </c>
+      <c r="J109" t="s">
+        <v>676</v>
+      </c>
+      <c r="K109" t="s">
+        <v>107</v>
+      </c>
+      <c r="L109" t="s">
+        <v>575</v>
+      </c>
+      <c r="P109" t="s">
+        <v>677</v>
+      </c>
+      <c r="U109" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>678</v>
+      </c>
+      <c r="C110" t="s">
+        <v>679</v>
+      </c>
+      <c r="D110">
+        <v>2025</v>
+      </c>
+      <c r="E110">
+        <v>5</v>
+      </c>
+      <c r="F110">
+        <v>3</v>
+      </c>
+      <c r="G110" t="s">
+        <v>571</v>
+      </c>
+      <c r="H110" t="s">
+        <v>572</v>
+      </c>
+      <c r="I110" t="s">
+        <v>680</v>
+      </c>
+      <c r="J110" t="s">
+        <v>681</v>
+      </c>
+      <c r="K110" t="s">
+        <v>107</v>
+      </c>
+      <c r="L110" t="s">
+        <v>575</v>
+      </c>
+      <c r="P110" t="s">
+        <v>682</v>
+      </c>
+      <c r="U110" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>683</v>
+      </c>
+      <c r="C111" t="s">
+        <v>684</v>
+      </c>
+      <c r="D111">
+        <v>2025</v>
+      </c>
+      <c r="E111">
+        <v>5</v>
+      </c>
+      <c r="F111">
+        <v>3</v>
+      </c>
+      <c r="G111" t="s">
+        <v>571</v>
+      </c>
+      <c r="H111" t="s">
+        <v>572</v>
+      </c>
+      <c r="I111" t="s">
+        <v>685</v>
+      </c>
+      <c r="J111" t="s">
+        <v>686</v>
+      </c>
+      <c r="K111" t="s">
+        <v>107</v>
+      </c>
+      <c r="L111" t="s">
+        <v>575</v>
+      </c>
+      <c r="P111" t="s">
+        <v>687</v>
+      </c>
+      <c r="U111" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>688</v>
+      </c>
+      <c r="C112" t="s">
+        <v>689</v>
+      </c>
+      <c r="D112">
+        <v>2025</v>
+      </c>
+      <c r="E112">
+        <v>5</v>
+      </c>
+      <c r="F112">
+        <v>3</v>
+      </c>
+      <c r="G112" t="s">
+        <v>571</v>
+      </c>
+      <c r="H112" t="s">
+        <v>572</v>
+      </c>
+      <c r="I112" t="s">
+        <v>690</v>
+      </c>
+      <c r="J112" t="s">
+        <v>691</v>
+      </c>
+      <c r="K112" t="s">
+        <v>107</v>
+      </c>
+      <c r="L112" t="s">
+        <v>575</v>
+      </c>
+      <c r="P112" t="s">
+        <v>692</v>
+      </c>
+      <c r="U112" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>693</v>
+      </c>
+      <c r="C113" t="s">
+        <v>694</v>
+      </c>
+      <c r="D113">
+        <v>2025</v>
+      </c>
+      <c r="E113">
+        <v>5</v>
+      </c>
+      <c r="F113">
+        <v>3</v>
+      </c>
+      <c r="G113" t="s">
+        <v>571</v>
+      </c>
+      <c r="H113" t="s">
+        <v>572</v>
+      </c>
+      <c r="I113" t="s">
+        <v>695</v>
+      </c>
+      <c r="J113" t="s">
+        <v>696</v>
+      </c>
+      <c r="K113" t="s">
+        <v>107</v>
+      </c>
+      <c r="L113" t="s">
+        <v>575</v>
+      </c>
+      <c r="P113" t="s">
+        <v>697</v>
+      </c>
+      <c r="U113" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>698</v>
+      </c>
+      <c r="C114" t="s">
+        <v>699</v>
+      </c>
+      <c r="D114">
+        <v>2025</v>
+      </c>
+      <c r="E114">
+        <v>5</v>
+      </c>
+      <c r="F114">
+        <v>4</v>
+      </c>
+      <c r="G114" t="s">
+        <v>571</v>
+      </c>
+      <c r="H114" t="s">
+        <v>572</v>
+      </c>
+      <c r="I114" t="s">
+        <v>700</v>
+      </c>
+      <c r="J114" t="s">
+        <v>701</v>
+      </c>
+      <c r="K114" t="s">
+        <v>107</v>
+      </c>
+      <c r="L114" t="s">
+        <v>575</v>
+      </c>
+      <c r="P114" t="s">
+        <v>702</v>
+      </c>
+      <c r="U114" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>703</v>
+      </c>
+      <c r="C115" t="s">
+        <v>704</v>
+      </c>
+      <c r="D115">
+        <v>2025</v>
+      </c>
+      <c r="E115">
+        <v>5</v>
+      </c>
+      <c r="F115">
+        <v>4</v>
+      </c>
+      <c r="G115" t="s">
+        <v>571</v>
+      </c>
+      <c r="H115" t="s">
+        <v>572</v>
+      </c>
+      <c r="I115" t="s">
+        <v>705</v>
+      </c>
+      <c r="J115" t="s">
+        <v>706</v>
+      </c>
+      <c r="K115" t="s">
+        <v>107</v>
+      </c>
+      <c r="L115" t="s">
+        <v>575</v>
+      </c>
+      <c r="P115" t="s">
+        <v>707</v>
+      </c>
+      <c r="U115" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>708</v>
+      </c>
+      <c r="C116" t="s">
+        <v>709</v>
+      </c>
+      <c r="D116">
+        <v>2025</v>
+      </c>
+      <c r="E116">
+        <v>5</v>
+      </c>
+      <c r="F116">
+        <v>4</v>
+      </c>
+      <c r="G116" t="s">
+        <v>571</v>
+      </c>
+      <c r="H116" t="s">
+        <v>572</v>
+      </c>
+      <c r="I116" t="s">
+        <v>710</v>
+      </c>
+      <c r="J116" t="s">
+        <v>711</v>
+      </c>
+      <c r="K116" t="s">
+        <v>107</v>
+      </c>
+      <c r="L116" t="s">
+        <v>575</v>
+      </c>
+      <c r="P116" t="s">
+        <v>712</v>
+      </c>
+      <c r="U116" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>713</v>
+      </c>
+      <c r="C117" t="s">
+        <v>714</v>
+      </c>
+      <c r="D117">
+        <v>2025</v>
+      </c>
+      <c r="E117">
+        <v>5</v>
+      </c>
+      <c r="F117">
+        <v>4</v>
+      </c>
+      <c r="G117" t="s">
+        <v>571</v>
+      </c>
+      <c r="H117" t="s">
+        <v>572</v>
+      </c>
+      <c r="I117" t="s">
+        <v>715</v>
+      </c>
+      <c r="J117" t="s">
+        <v>716</v>
+      </c>
+      <c r="K117" t="s">
+        <v>107</v>
+      </c>
+      <c r="L117" t="s">
+        <v>575</v>
+      </c>
+      <c r="P117" t="s">
+        <v>717</v>
+      </c>
+      <c r="U117" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>718</v>
+      </c>
+      <c r="C118" t="s">
+        <v>719</v>
+      </c>
+      <c r="D118">
+        <v>2026</v>
+      </c>
+      <c r="E118">
+        <v>6</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118" t="s">
+        <v>571</v>
+      </c>
+      <c r="H118" t="s">
+        <v>572</v>
+      </c>
+      <c r="I118" t="s">
+        <v>720</v>
+      </c>
+      <c r="J118" t="s">
+        <v>721</v>
+      </c>
+      <c r="K118" t="s">
+        <v>107</v>
+      </c>
+      <c r="L118" t="s">
+        <v>575</v>
+      </c>
+      <c r="P118" t="s">
+        <v>722</v>
+      </c>
+      <c r="U118" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>723</v>
+      </c>
+      <c r="C119" t="s">
+        <v>724</v>
+      </c>
+      <c r="D119">
+        <v>2026</v>
+      </c>
+      <c r="E119">
+        <v>6</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119" t="s">
+        <v>571</v>
+      </c>
+      <c r="H119" t="s">
+        <v>572</v>
+      </c>
+      <c r="I119" t="s">
+        <v>725</v>
+      </c>
+      <c r="J119" t="s">
+        <v>726</v>
+      </c>
+      <c r="K119" t="s">
+        <v>107</v>
+      </c>
+      <c r="L119" t="s">
+        <v>575</v>
+      </c>
+      <c r="P119" t="s">
+        <v>727</v>
+      </c>
+      <c r="U119" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>728</v>
+      </c>
+      <c r="C120" t="s">
+        <v>729</v>
+      </c>
+      <c r="D120">
+        <v>2023</v>
+      </c>
+      <c r="E120">
+        <v>3</v>
+      </c>
+      <c r="F120">
+        <v>3</v>
+      </c>
+      <c r="G120" t="s">
+        <v>730</v>
+      </c>
+      <c r="H120" t="s">
+        <v>731</v>
+      </c>
+      <c r="I120" t="s">
+        <v>732</v>
+      </c>
+      <c r="J120" t="s">
+        <v>733</v>
+      </c>
+      <c r="K120" t="s">
+        <v>107</v>
+      </c>
+      <c r="L120" t="s">
+        <v>734</v>
+      </c>
+      <c r="P120" t="s">
+        <v>735</v>
+      </c>
+      <c r="U120" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>737</v>
+      </c>
+      <c r="C121" t="s">
+        <v>738</v>
+      </c>
+      <c r="D121">
+        <v>2024</v>
+      </c>
+      <c r="E121">
+        <v>4</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121" t="s">
+        <v>730</v>
+      </c>
+      <c r="H121" t="s">
+        <v>731</v>
+      </c>
+      <c r="I121" t="s">
+        <v>739</v>
+      </c>
+      <c r="J121" t="s">
+        <v>740</v>
+      </c>
+      <c r="K121" t="s">
+        <v>107</v>
+      </c>
+      <c r="L121" t="s">
+        <v>734</v>
+      </c>
+      <c r="P121" t="s">
+        <v>741</v>
+      </c>
+      <c r="U121" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>742</v>
+      </c>
+      <c r="C122" t="s">
+        <v>743</v>
+      </c>
+      <c r="D122">
+        <v>2024</v>
+      </c>
+      <c r="E122">
+        <v>4</v>
+      </c>
+      <c r="F122">
+        <v>2</v>
+      </c>
+      <c r="G122" t="s">
+        <v>730</v>
+      </c>
+      <c r="H122" t="s">
+        <v>731</v>
+      </c>
+      <c r="I122" t="s">
+        <v>744</v>
+      </c>
+      <c r="J122" t="s">
+        <v>745</v>
+      </c>
+      <c r="K122" t="s">
+        <v>107</v>
+      </c>
+      <c r="L122" t="s">
+        <v>734</v>
+      </c>
+      <c r="P122" t="s">
+        <v>746</v>
+      </c>
+      <c r="U122" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>747</v>
+      </c>
+      <c r="C123" t="s">
+        <v>748</v>
+      </c>
+      <c r="D123">
+        <v>2024</v>
+      </c>
+      <c r="E123">
+        <v>4</v>
+      </c>
+      <c r="F123">
+        <v>3</v>
+      </c>
+      <c r="G123" t="s">
+        <v>730</v>
+      </c>
+      <c r="H123" t="s">
+        <v>731</v>
+      </c>
+      <c r="I123" t="s">
+        <v>749</v>
+      </c>
+      <c r="J123" t="s">
+        <v>750</v>
+      </c>
+      <c r="K123" t="s">
+        <v>107</v>
+      </c>
+      <c r="L123" t="s">
+        <v>734</v>
+      </c>
+      <c r="P123" t="s">
+        <v>751</v>
+      </c>
+      <c r="U123" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>752</v>
+      </c>
+      <c r="C124" t="s">
+        <v>753</v>
+      </c>
+      <c r="D124">
+        <v>2024</v>
+      </c>
+      <c r="E124">
+        <v>4</v>
+      </c>
+      <c r="F124">
+        <v>3</v>
+      </c>
+      <c r="G124" t="s">
+        <v>730</v>
+      </c>
+      <c r="H124" t="s">
+        <v>731</v>
+      </c>
+      <c r="I124" t="s">
+        <v>754</v>
+      </c>
+      <c r="J124" t="s">
+        <v>755</v>
+      </c>
+      <c r="K124" t="s">
+        <v>107</v>
+      </c>
+      <c r="L124" t="s">
+        <v>734</v>
+      </c>
+      <c r="P124" t="s">
+        <v>756</v>
+      </c>
+      <c r="U124" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>757</v>
+      </c>
+      <c r="C125" t="s">
+        <v>758</v>
+      </c>
+      <c r="D125">
+        <v>2024</v>
+      </c>
+      <c r="E125">
+        <v>4</v>
+      </c>
+      <c r="F125">
+        <v>3</v>
+      </c>
+      <c r="G125" t="s">
+        <v>730</v>
+      </c>
+      <c r="H125" t="s">
+        <v>731</v>
+      </c>
+      <c r="I125" t="s">
+        <v>759</v>
+      </c>
+      <c r="J125" t="s">
+        <v>760</v>
+      </c>
+      <c r="K125" t="s">
+        <v>107</v>
+      </c>
+      <c r="L125" t="s">
+        <v>734</v>
+      </c>
+      <c r="P125" t="s">
+        <v>761</v>
+      </c>
+      <c r="U125" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>762</v>
+      </c>
+      <c r="C126" t="s">
+        <v>763</v>
+      </c>
+      <c r="D126">
+        <v>2025</v>
+      </c>
+      <c r="E126">
+        <v>5</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126" t="s">
+        <v>730</v>
+      </c>
+      <c r="H126" t="s">
+        <v>731</v>
+      </c>
+      <c r="I126" t="s">
+        <v>764</v>
+      </c>
+      <c r="J126" t="s">
+        <v>765</v>
+      </c>
+      <c r="K126" t="s">
+        <v>107</v>
+      </c>
+      <c r="L126" t="s">
+        <v>734</v>
+      </c>
+      <c r="P126" t="s">
+        <v>766</v>
+      </c>
+      <c r="U126" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>767</v>
+      </c>
+      <c r="C127" t="s">
+        <v>768</v>
+      </c>
+      <c r="D127">
+        <v>2025</v>
+      </c>
+      <c r="E127">
+        <v>5</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127" t="s">
+        <v>730</v>
+      </c>
+      <c r="H127" t="s">
+        <v>731</v>
+      </c>
+      <c r="I127" t="s">
+        <v>769</v>
+      </c>
+      <c r="J127" t="s">
+        <v>770</v>
+      </c>
+      <c r="K127" t="s">
+        <v>107</v>
+      </c>
+      <c r="L127" t="s">
+        <v>734</v>
+      </c>
+      <c r="P127" t="s">
+        <v>771</v>
+      </c>
+      <c r="U127" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>772</v>
+      </c>
+      <c r="C128" t="s">
+        <v>773</v>
+      </c>
+      <c r="D128">
+        <v>2025</v>
+      </c>
+      <c r="E128">
+        <v>5</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128" t="s">
+        <v>730</v>
+      </c>
+      <c r="H128" t="s">
+        <v>731</v>
+      </c>
+      <c r="I128" t="s">
+        <v>774</v>
+      </c>
+      <c r="J128" t="s">
+        <v>775</v>
+      </c>
+      <c r="K128" t="s">
+        <v>107</v>
+      </c>
+      <c r="L128" t="s">
+        <v>734</v>
+      </c>
+      <c r="P128" t="s">
+        <v>776</v>
+      </c>
+      <c r="U128" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>777</v>
+      </c>
+      <c r="C129" t="s">
+        <v>778</v>
+      </c>
+      <c r="D129">
+        <v>2025</v>
+      </c>
+      <c r="E129">
+        <v>5</v>
+      </c>
+      <c r="F129">
+        <v>2</v>
+      </c>
+      <c r="G129" t="s">
+        <v>730</v>
+      </c>
+      <c r="H129" t="s">
+        <v>731</v>
+      </c>
+      <c r="I129" t="s">
+        <v>779</v>
+      </c>
+      <c r="J129" t="s">
+        <v>780</v>
+      </c>
+      <c r="K129" t="s">
+        <v>107</v>
+      </c>
+      <c r="L129" t="s">
+        <v>734</v>
+      </c>
+      <c r="P129" t="s">
+        <v>781</v>
+      </c>
+      <c r="U129" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>782</v>
+      </c>
+      <c r="C130" t="s">
+        <v>783</v>
+      </c>
+      <c r="D130">
+        <v>2025</v>
+      </c>
+      <c r="E130">
+        <v>5</v>
+      </c>
+      <c r="F130">
+        <v>3</v>
+      </c>
+      <c r="G130" t="s">
+        <v>730</v>
+      </c>
+      <c r="H130" t="s">
+        <v>731</v>
+      </c>
+      <c r="I130" t="s">
+        <v>784</v>
+      </c>
+      <c r="J130" t="s">
+        <v>785</v>
+      </c>
+      <c r="K130" t="s">
+        <v>107</v>
+      </c>
+      <c r="L130" t="s">
+        <v>734</v>
+      </c>
+      <c r="P130" t="s">
+        <v>786</v>
+      </c>
+      <c r="U130" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>787</v>
+      </c>
+      <c r="C131" t="s">
+        <v>788</v>
+      </c>
+      <c r="D131">
+        <v>2025</v>
+      </c>
+      <c r="E131">
+        <v>4</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131" t="s">
+        <v>789</v>
+      </c>
+      <c r="H131" t="s">
+        <v>790</v>
+      </c>
+      <c r="I131" t="s">
+        <v>791</v>
+      </c>
+      <c r="J131" t="s">
+        <v>788</v>
+      </c>
+      <c r="K131" t="s">
+        <v>249</v>
+      </c>
+      <c r="L131" t="s">
+        <v>792</v>
+      </c>
+      <c r="P131" t="s">
+        <v>793</v>
+      </c>
+      <c r="U131" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>795</v>
+      </c>
+      <c r="C132" t="s">
+        <v>796</v>
+      </c>
+      <c r="D132">
+        <v>2025</v>
+      </c>
+      <c r="E132">
+        <v>4</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="G132" t="s">
+        <v>789</v>
+      </c>
+      <c r="H132" t="s">
+        <v>790</v>
+      </c>
+      <c r="I132" t="s">
+        <v>797</v>
+      </c>
+      <c r="J132" t="s">
+        <v>796</v>
+      </c>
+      <c r="K132" t="s">
+        <v>249</v>
+      </c>
+      <c r="L132" t="s">
+        <v>792</v>
+      </c>
+      <c r="P132" t="s">
+        <v>798</v>
+      </c>
+      <c r="U132" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>799</v>
+      </c>
+      <c r="C133" t="s">
+        <v>800</v>
+      </c>
+      <c r="D133">
+        <v>2026</v>
+      </c>
+      <c r="E133">
+        <v>5</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="G133" t="s">
+        <v>789</v>
+      </c>
+      <c r="H133" t="s">
+        <v>790</v>
+      </c>
+      <c r="I133" t="s">
+        <v>801</v>
+      </c>
+      <c r="J133" t="s">
+        <v>802</v>
+      </c>
+      <c r="K133" t="s">
+        <v>249</v>
+      </c>
+      <c r="L133" t="s">
+        <v>792</v>
+      </c>
+      <c r="P133" t="s">
+        <v>803</v>
+      </c>
+      <c r="U133" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>804</v>
+      </c>
+      <c r="C134" t="s">
+        <v>805</v>
+      </c>
+      <c r="D134">
+        <v>2025</v>
+      </c>
+      <c r="E134">
+        <v>4</v>
+      </c>
+      <c r="F134">
+        <v>2</v>
+      </c>
+      <c r="G134" t="s">
+        <v>789</v>
+      </c>
+      <c r="H134" t="s">
+        <v>790</v>
+      </c>
+      <c r="I134" t="s">
+        <v>806</v>
+      </c>
+      <c r="J134" t="s">
+        <v>807</v>
+      </c>
+      <c r="K134" t="s">
+        <v>249</v>
+      </c>
+      <c r="L134" t="s">
+        <v>792</v>
+      </c>
+      <c r="P134" t="s">
+        <v>808</v>
+      </c>
+      <c r="U134" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>809</v>
+      </c>
+      <c r="C135" t="s">
+        <v>810</v>
+      </c>
+      <c r="D135">
+        <v>2026</v>
+      </c>
+      <c r="E135">
+        <v>5</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135" t="s">
+        <v>789</v>
+      </c>
+      <c r="H135" t="s">
+        <v>790</v>
+      </c>
+      <c r="I135" t="s">
+        <v>811</v>
+      </c>
+      <c r="J135" t="s">
+        <v>812</v>
+      </c>
+      <c r="K135" t="s">
+        <v>249</v>
+      </c>
+      <c r="L135" t="s">
+        <v>792</v>
+      </c>
+      <c r="P135" t="s">
+        <v>813</v>
+      </c>
+      <c r="U135" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>814</v>
+      </c>
+      <c r="C136" t="s">
+        <v>815</v>
+      </c>
+      <c r="D136">
+        <v>2023</v>
+      </c>
+      <c r="E136">
+        <v>2</v>
+      </c>
+      <c r="F136">
+        <v>2</v>
+      </c>
+      <c r="G136" t="s">
+        <v>789</v>
+      </c>
+      <c r="H136" t="s">
+        <v>790</v>
+      </c>
+      <c r="I136" t="s">
+        <v>816</v>
+      </c>
+      <c r="J136" t="s">
+        <v>817</v>
+      </c>
+      <c r="K136" t="s">
+        <v>249</v>
+      </c>
+      <c r="L136" t="s">
+        <v>792</v>
+      </c>
+      <c r="P136" t="s">
+        <v>818</v>
+      </c>
+      <c r="U136" t="s">
+        <v>794</v>
       </c>
     </row>
   </sheetData>

--- a/myapp/data_idx_gabung.xlsx
+++ b/myapp/data_idx_gabung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SENTIMENT ANALYSIS UGI AQIS 2026\PROJECT SHINY DASHBOARD ANALISIS SENTIMEN 2026 TERBARU\myapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8944BB26-DE2F-4096-BBBB-C84EA7E524AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45DDB59D-82D4-4578-A62A-0649F5AEB78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="963">
   <si>
     <t>No</t>
   </si>
@@ -85,12 +85,45 @@
     <t>Journal Information</t>
   </si>
   <si>
+    <t>Comparative Sentiment Analysis of Shopee and Tokopedia in Indonesia: Insights from Twitter Data</t>
+  </si>
+  <si>
+    <t>Sentiment analysis; E-commerce; Twitter data; User satisfaction; Social media analytics</t>
+  </si>
+  <si>
+    <t>5b</t>
+  </si>
+  <si>
+    <t>Paper Asia</t>
+  </si>
+  <si>
+    <t>0218-4540</t>
+  </si>
+  <si>
+    <t>https://compendiumpaperasia.com/index.php/cpa/article/view/697</t>
+  </si>
+  <si>
+    <t>Understanding user sentiment is essential for strengthening platform competitiveness in Southeast Asia's rapidly evolving e-commerce landscape. This study presents a comparative sentiment analysis of Indonesia's two leading e-commerce platforms, Shopee and Tokopedia, based on 6,336 tweets collected from Twitter (X) between 10 and 17 January 2024. A lexicon-based sentiment analysis, complemented by keyword analysis, was employed to classify user sentiments using a five-star scale, thereby capturing nuanced emotional expressions. The results indicate that 47% of Shopee-related tweets conveyed positive sentiment, whereas only 15.6% of Tokopedia-related tweets were positive. In contrast, Tokopedia demonstrated a significantly higher proportion of negative sentiment at 64.3%, indicating notable user dissatisfaction. Keyword analysis revealed that Shopee users focused on affordability, promotions, and product discovery, while Tokopedia discussions emphasized transactional reliability, peer-topeer selling, and financial services. These findings suggest that Shopee should continue leveraging promotional strategies while addressing technical reliability to maintain user trust and loyalty. Meanwhile, Tokopedia must enhance logistical performance, strengthen seller accountability, and improve financial services governance to rebuild user confidence. This study contributes to the e-commerce and social media analytics literature by integrating sentiment intensity and thematic keyword analysis, offering actionable recommendations for enhancing user engagement in Indonesia's competitive digital marketplace. Future research should consider more extended observation periods and cross-platform analyses to capture evolving sentiment trends and inform strategic decision-making</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=56171&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/56171?origin=resultslist</t>
+  </si>
+  <si>
+    <t>IPMEDIA SDN BHD</t>
+  </si>
+  <si>
     <t>Investigating the Role of Logistics Delivery Services in Shaping Customer Satisfaction: LLM-Aspect-Based Sentiment Analysis of Perceived Quality in Indonesian E-Commerce</t>
   </si>
   <si>
     <t>Arbi Setiyawan; Youshi He; Ray Sastri</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>Journal of Theoretical and Applied Electronic Commerce Research</t>
   </si>
   <si>
@@ -115,6 +148,69 @@
     <t>Multidisciplinary Digital Publishing Institute (MDPI)</t>
   </si>
   <si>
+    <t>Analyzing Halal Concerns on Korean Food Using Text-Mining: Perspectives from Indonesian Social Media Users</t>
+  </si>
+  <si>
+    <t>Ekasari Nugraheni; Andria Arisal; Andri Fachrur Rozie; Dianadewi Riswantini; Purnomo Husnul Khotimah; Wiwin Suwarningsih</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>International Journal on Food System Dynamics</t>
+  </si>
+  <si>
+    <t>1869-6945</t>
+  </si>
+  <si>
+    <t>https://brill.com/view/journals/fsd/16/2/article-p181_5.xml?ebody=full%20html-copy1</t>
+  </si>
+  <si>
+    <t>Korean food; text mining; halal concern; social media; sentiment analysis; topic analysis; word network analysis</t>
+  </si>
+  <si>
+    <t>This study examines Indonesian consumers’ perceptions of the halal status of Korean food utilising Twitter data. The analysis employs text mining methods to extract insights from 1936 tweets, including sentiment, word frequency, topic, and word co-occurrence. Findings revealed that 59.50% of tweets expressed positive sentiment toward halal Korean food. This discussion focuses on three main topics: Korean drinks (soju), halal recommendations for Korean snacks, and concerns regarding haram ingredients. While research on halal concerns in Korean food through social media remains limited, this study offers insights into Indonesian consumer perspectives, supports market optimization, and informs culturally aligned marketing strategies for Korean food in Indonesia</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100456788&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21100456788?origin=resultslist</t>
+  </si>
+  <si>
+    <t>CentMa GmbH</t>
+  </si>
+  <si>
+    <t>Analyzing public discourse on photovoltaic (PV) adoption in Indonesia: A topic-based sentiment analysis of news articles and social media</t>
+  </si>
+  <si>
+    <t>Yun Prihantina Mulyani; Anas Saifurrahman; Hilya Mudrika Arini; Arwindra Rizqiawan; Budi Hartono; Dhanan Sarwo Utomo; Agnessa Spanellis; Macarena Beltran; Kevin; Marojahan Banjar Nahor; Dhyana Paramita; Wira Dranata Harefa</t>
+  </si>
+  <si>
+    <t>Journal of Cleaner Production</t>
+  </si>
+  <si>
+    <t>1879-1786</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0959652623043913</t>
+  </si>
+  <si>
+    <t>Solar PV; Discourse; Perception; Mainstream media; Social media</t>
+  </si>
+  <si>
+    <t>The importance of integrating renewable energy, such as solar PV, in the global energy mix for mitigating carbon emissions is increasing. Despite the global drive towards renewable energy, the limited uptake of solar PV particularly in developing nations, such as Indonesia, poses significant challenges for transition to sustainable energy. This study analyses public discourse to comprehend the obstacles for widespread adoption of solar PV technologies. This study employs topic modelling and sentiment analysis of mainstream and social media data to comprehensively capture public discourse and perceptions concerning PV and residential PV adoption in Indonesia. The findings reveal shared thematic areas in both mainstream and social media. Nonetheless, the two media types diverge significantly in their focal points. Our findings support previous survey-based research while introducing three new topics found in both media channels. These topics are: (1) knowledge, misconceptions, and skepticism, (2) economically viable alternative PV technologies; and (3) government regulations and policies. Social and visual impressions such as aesthetics, hedonic motivation, and social influence are notably absent. Public perception varies, with mainstream media portraying PV technology more positively than social media. From both media, the public generally holds favorable views of PV, particularly in terms of its practicality, installation, safety, and information accessibility. Nevertheless, negative perceptions arise regarding investment costs, regulations, governmental policies, and the adequacy of government support</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=19167&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/19167</t>
+  </si>
+  <si>
+    <t>Elsevier</t>
+  </si>
+  <si>
     <t>A hybrid stacked ensemble learning framework for multilabel text emotion detection</t>
   </si>
   <si>
@@ -145,12 +241,48 @@
     <t>Nature Research</t>
   </si>
   <si>
+    <t>Revitalizing Tax Revenue: Tax Incentive Indonesia and Overcoming Negative Sentiment</t>
+  </si>
+  <si>
+    <t>Muhamad Taqi; Aam Slamet Rusydiana; Aisyah As-Salafiyah; Nawang Kalbuana; Mamay Mayyizah</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>International Journal of Economics and Financial Issues</t>
+  </si>
+  <si>
+    <t>2146-4138</t>
+  </si>
+  <si>
+    <t>https://econjournals.com/index.php/ijefi/article/view/17057</t>
+  </si>
+  <si>
+    <t>Policy; Tax Incentive; Sentiment Analysis; Indonesia</t>
+  </si>
+  <si>
+    <t>This study aims to test the effectiveness of the Policy implemented by the Indonesian government to increase national tax revenues through tax incentive programs and solutions to negative sentiment and see the progress of research on “Tax Incentives in Indonesia” around the world published by journals on that theme. This research uses qualitative methods with bibliometric analysis and sentiment analysis approaches. The data used is secondary data with the theme “Tax Incentive Indonesia” from the Dimension database of 80 published journals. Then, the data is processed and analyzed using the VOSviewer application to know the bibliometric map of research development “Tax Incentive Indonesia” in this world. Apart from that, the data was also analyzed using the SentiStrength application to find out positive sentiment, negative, and neutral sentiment regarding the tax incentive policy that has been implemented in Indonesia. The results of the research found that the tax incentive program has proven effective in increasing national tax revenues and the solution to negative sentiment is to create activities that can increase taxpayers’ awareness of paying taxes, and trust in the government as well as direct benefit programs for taxes that have been paid. Then based on sentiment analysis, neutral sentiment is the highest result with a percentage of 50%, followed by positive and negative sentiment with each having a percentage of 25%. Meanwhile, based on bibliometric keyword mapping, 5 clusters can become research paths.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100373226&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105003548205?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Econjournals</t>
+  </si>
+  <si>
     <t>Dynamic Sentiment Analysis on the Emergence of Pre-Trained Generative Model-Based Applications in Indonesia</t>
   </si>
   <si>
     <t>Frans Mikael Sinaga; Jefri Junifer Pangaribuan; Kelvin; Ferawaty; Andree Emmanuel Widjaja</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>International Journal of Advanced Computer Science and Applications</t>
   </si>
   <si>
@@ -175,12 +307,42 @@
     <t>Science and Information Organization</t>
   </si>
   <si>
+    <t>Data-driven public policy for electric vehicles (EV) through open innovation and dynamic consumer preferences: A time-series social media analysis using integrated IPA-product improvability model</t>
+  </si>
+  <si>
+    <t>Dwi Adi Purnama; Distian Pingkan Lumi; Atik Febriani; Ar Royyan Utama T; Samaya Dhiya Salindri; Adhe Rizky Anugerah; Nashtiti Aliafari</t>
+  </si>
+  <si>
+    <t>Journal of Open Innovation: Technology, Market, and Complexity</t>
+  </si>
+  <si>
+    <t>2199-8531</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S2199853125001180?via%3Dihub</t>
+  </si>
+  <si>
+    <t>D-PII-IPA model; Data-driven open innovation; Dynamic consumer preferences; Electric vehicle; Social media</t>
+  </si>
+  <si>
+    <t>Transport emissions play a crucial role in the accumulation of greenhouse gases (GHG) and the progression of climate change. Electric vehicles (EV) present a viable solution to this issue, aligning with the sustainable development goal through affordable and clean energy. However, in numerous countries, electric vehicle adoption accounts for only around 1 % of total sales. Investigating open innovation and surveys on electric vehicle adoption and public policy development is essential. This study proposes a data-driven public policy for EV through open innovation and dynamic consumer preferences using the macrolevel (big data social media) for decision making. The case study on the adoption of electric vehicles in Indonesia, a populous developing nation with significant transportation ownership, demonstrates the method’s feasibility and effectiveness. Textual big data modeling and dynamic analysis were developed using the Latent Dirichlet Allocation (LDA), Sentiment Analysis, and a time series analysis. Then, open innovation strategies and public policy development were developed by integrating the Dynamic-Product Improvability Index-Importance Performance Analysis (D-PIIIPA), a novel method. Finally, this study discovers improvement ideas and innovation priorities consist of always-priority attributes (battery), changing attributes (EV cost/price and comfortable facilities), and unique attributes, such as entertainment events of EVs and electricity for online drivers. The government can enhance this public policy by offering incentives, improving battery and charging infrastructure, investing in user-friendly facilities, and streamlining the distribution of electric vehicles. These insights could offer significant direction to the government and industry stakeholders concerning the issues related to dynamic EV adoption.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100887502&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21100887502?origin=resultslist</t>
+  </si>
+  <si>
     <t>Multilabel classification sentiment analysis on Indonesian mobile app reviews</t>
   </si>
   <si>
     <t>Riccosan Riccosan; Karen Etania Saputra</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>IAES International Journal of Artificial Intelligence</t>
   </si>
   <si>
@@ -205,6 +367,21 @@
     <t>Institute of Advanced Engineering and Science</t>
   </si>
   <si>
+    <t>Modeling sentiment analysis of Indonesian biodiversity policy Tweets using IndoBERTweet</t>
+  </si>
+  <si>
+    <t>Mohammad Teduh Uliniansyah; Asril Jarin; Agung Santosa; Gunarso Gunarso</t>
+  </si>
+  <si>
+    <t>https://ijai.iaescore.com/index.php/IJAI/article/view/26816</t>
+  </si>
+  <si>
+    <t>BERT embeddings; Biodiversity policy; IndoBERTweet; Sentiment analysis; Twitter data</t>
+  </si>
+  <si>
+    <t>This study develops and evaluates a sentiment analysis model using IndoBERTweet to analyze Twitter data on Indonesia’s biodiversity policy. Twitter data focusing on topics such as food security, health, and environmental management were collected, with a representative subset of 13,435 tweets annotated from a larger dataset of 500,000 to ensure reliable sentiment labels through majority voting. IndoBERTweet was compared to seven traditional machine-learning classifiers using TF-IDF and BERT embeddings for feature extraction. Model performance was assessed using mean accuracy, mean F1 score, and statistical significance (p-values). Additionally, sentiment analysis included word attribution techniques with BERT embeddings, enhancing relevance, interpretability, and consistent attribution to deliver accurate insights. IndoBERTweet models consistently outperformed traditional methods in both accuracy and F1 score. While BERT embeddings boosted performance for conventional models, IndoBERTweet delivered superior results, with p-values below 0.05 confirming statistical significance. This approach demonstrates that the model’s outputs are explainable and align with human understanding. Findings underscore IndoBERTweet’s substantial impact on advancing sentiment analysis technology, showcasing its potential to drive innovation and elevate practices in the field.</t>
+  </si>
+  <si>
     <t>Public Opinion in Political Dynamics: The Role of Political Parties through Social Media in Indonesia</t>
   </si>
   <si>
@@ -293,6 +470,34 @@
   </si>
   <si>
     <t>Redfame Publishing Inc.</t>
+  </si>
+  <si>
+    <t>Enhancing telemedicine service quality through sentiment analysis of user review dataset in Indonesia</t>
+  </si>
+  <si>
+    <t>Edi Sutoyo; Muhammad Cekas Permana</t>
+  </si>
+  <si>
+    <t>Data in Brief</t>
+  </si>
+  <si>
+    <t>2352-3409</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S235234092500602X?via%3Dihub</t>
+  </si>
+  <si>
+    <t>Sentiment analysis; Telemedicine; Deep learning; Imbalanced data; Data augmentation</t>
+  </si>
+  <si>
+    <t>Sentiment analysis, a field within natural language processing, text mining, and computational linguistics, evaluates user opinions and product ratings. This article describes a dataset of user reviews collected from telemedicine applications in Indonesia to understand sentiments related to service quality. The dataset comprises 255,679 textual reviews containing positive and negative feedback, offering valuable input for analyzing user experiences. Reviews were sourced from publicly available platforms, ensuring diversity in user perspectives.
+The dataset exhibits significant class imbalance, with negative reviews constituting a small proportion compared to positive reviews (ratio exceeding 1:14). To address this imbalance, advanced resampling techniques, including Easy Data Augmentation (EDA), were applied. The dataset underwent rigorous preprocessing to remove noise, standardize content, and tokenize reviews for compatibility with deep learning models. This dataset has been utilized with architectures such as SRNN, 1D-CNN, 1L-LSTM, and BiLSTM for sentiment classification. Generated word clouds highlight frequently mentioned terms, enabling exploratory analysis. The dataset is publicly available, providing a resource for benchmarking sentiment classification algorithms and studying the impact of imbalanced data handling on model performance. This work contributes to enhancing telemedicine service quality and advancing Indonesian natural language processing research.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100372856&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21100372856?origin=resultslist</t>
   </si>
   <si>
     <t>Exploring the Icarus Paradox in Indonesia's Specialist Medical Education System Using the Public Perspective From Online Media: Convergent Mixed Methods Study</t>
@@ -334,6 +539,70 @@
     <t>JMIR Publications Inc.</t>
   </si>
   <si>
+    <t>Deep learning-based application for multilevel sentiment analysis of Indonesian hotel reviews</t>
+  </si>
+  <si>
+    <t>Retno Kusumaningrum; Iffa Zainan Nisa; Rahmat Jayanto; Rizka Putri Nawangsari; Adi Wibowo</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Heliyon</t>
+  </si>
+  <si>
+    <t>2405-8440</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S2405844023043554</t>
+  </si>
+  <si>
+    <t>Sentiment analysis; Deep learning; Convolutional neural network; Long short-term memory; Sentiment visualization</t>
+  </si>
+  <si>
+    <t>Purpose: In this study, we present a web-based application that retrieves hotel review documents in Indonesian languages from an online travel agent (OTA) and analyses their sentiments from the coarse-grained document to the fine-grained aspect level. Design: /Methodology/Approach: There are four main stages in this study: development of sentiment analysis model at the document level based on a convolutional neural network (CNN), development of sentiment analysis model at the aspect level based on an improved long shortterm memory (LSTM), model deployment for multilevel sentiment analysis in a web-based application, and its performance evaluation. The developed application uses several sentiment visualizations types at coarse-grained and fine-grained levels, such as pie charts, line charts, and bar charts. Finding: The application’s functionality was demonstrated in practice based on three datasets from three OTA websites, which were analyzed and evaluated based on several matrices, namely, the precision, recall, and F1-score. The results revealed that the performance for the F1-score was 0.95 ± 0.03, 0.87 ± 0.02, and 0.92 ± 0.07 for document-level sentiment analysis, aspect-level sentiment analysis, and aspect-polarity detection, respectively. Originality: The developed application (Sentilytics 1.0) can analyze sentiment at document and aspect levels. The two levels of sentiment analysis are based on two models generated by finetuning CNN and LSTM models using specific architectures and domain data (Indonesian hotel
+reviews).</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100411756&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21100411756</t>
+  </si>
+  <si>
+    <t>A Sentiment Analysis Study of Banning Single-Use Plastic Bags Based on X Users’ Attitude</t>
+  </si>
+  <si>
+    <t>Zulwelly Murti; Soen Steven; Riana Y. H. Sinaga; Mulyono Mulyono; Arief A. R. Setiawan; Geby Otivriyanti; Maya L. D; Wardani; Nurus S. Laili; Anita Yustisia; Asep Bustanil Aripin; Ernie S. A. Soekotjo; Muhammad Sudiono; Vionita Lukitari; Dharmawan Dharmawan; Adik A. Soedarsono</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>2432-5953</t>
+  </si>
+  <si>
+    <t>https://catalog.lib.kyushu-u.ac.jp/opac_detail_md/?lang=1&amp;amode=MD100000&amp;bibid=7363473</t>
+  </si>
+  <si>
+    <t>algorithm; machine learning; Naïve Bayes; sentiment; single-use plastic</t>
+  </si>
+  <si>
+    <t>Single-use plastics have become an urgent global environmental concern. The Indonesian government has attempted to introduce a policy that bans the use of single-use plastics as an initial step toward overcoming this issue. However, policy implementation often faces challenges from stakeholders. Therefore, this study aims to analyze public sentiment expressed on the X platform (formerly known as “Twitter”) regarding the policy of banning single-use plastic bags in Indonesia. The methods used in this study include data collection, pre-processing (cleaning and transforming), labeling, modeling, and analysis using RapidMiner software. Tweet data were then analyzed using three machine learning methods, i.e., Naïve Bayes, K-Nearest Neighbors (KNN), and Decision Tree. Data were divided into training and test sets with a ratio of 60:40, 70:30, and 80:20. As many as 1038 refined datasets from 2019-2023 with related keywords were obtained. Based on the performance evaluation, the Naïve Bayes algorithm can improve its performance as the amount of training data increases, without overfitting. This algorithm achieves the highest accuracy of 89.73% at an 80:20 ratio. Furthermore, the classification results of the majority (70.6%) of the tweets showed positive support for the policy, 19.6% were negative, and 9.8% were neutral. In other words, the results of this sentiment classification can be used to monitor public responses and formulate environmentally friendly policies that are effective and supported by the majority</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100812868&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21100812868?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Joint Journal of Novel Carbon Resource Sciences and Green Asia Strategy</t>
+  </si>
+  <si>
     <t>Analisis Sentimen Terhadap Film Sri Asih Dengan CNN, KNN, dan Logistic Regression</t>
   </si>
   <si>
@@ -731,12 +1000,45 @@
     <t>Politeknik Negeri Padang</t>
   </si>
   <si>
+    <t>Exploring the Public Opinion on Celebrity Fad Diets: Twitter Sentiment and Netnographic Analysis</t>
+  </si>
+  <si>
+    <t>Ardyanisa Raihan Kusuma; Sheila Amara Putri; Anisah Firdaus Rahmawati; Mutiara Arsya Wijanarko; Shintia Yunita Arini; Dominikus Raditya Atmaka; Norfezah Md Nor; Nadiatul Syima Mohd Shahid; Sa’idah Zahrotul Jannah</t>
+  </si>
+  <si>
+    <t>Amerta Nutrition</t>
+  </si>
+  <si>
+    <t>2580-9776</t>
+  </si>
+  <si>
+    <t>https://e-journal.unair.ac.id/AMNT/article/view/56788</t>
+  </si>
+  <si>
+    <t>Opinion; Celebrity; Fad Diets; Twitter; Sentiment; Netnographic</t>
+  </si>
+  <si>
+    <t>Background: Celebrity fad diets have garnered significant attention in recent years. Celebrity diets often gain popularity through social media, particularly Twitter, where users engage in discussions, debates, and promotions of various diet trends. Objectives: To analyze Indonesian’s public sentiment surrounding celebrity fad diets on Twitter social media using netnographic from twitter. Methods: This research used a mixed-methods approach with both qualitative and quantitative methods to find the public sentiments of the 5 chosen diets. The data were obtained through snscrape from GitHub, a Python-based tool that enables users to access various types of Twitter data, such as user profiles, hashtags, live tweets, top tweets, users, single or threaded tweets, list posts, communities, and trends. Results: Positive sentiment was found to be more prevalent than negative sentiment over the years, and the number of tweets increased each year. Intermittent fasting emerged as the most discussed diet on social media, likely due to its resemblance to fasting practices observed by Indonesia's Muslim population. On the other hand, the Atkins diet was the least talked-about, possibly because of its complex nature. Conclusions: The prevalence of Ketogenic and Very Low-Calorie Diet discussions in the context of Indonesian and K-Pop culture underscores the need for a nuanced understanding of these diets and their potential implications for health. Future research should consider diverse data sources, expand sample sizes, and collaborate with experts to gain a more comprehensive understanding of public opinions on diets.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21101201215&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21101201215?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Airlangga University Faculty of Public Health</t>
+  </si>
+  <si>
     <t>Assessing Indonesian Islamic schools’ readiness for the independent curriculum using text analytics</t>
   </si>
   <si>
     <t>Dian Sa'adillah Maylawatia; Rohmat Mulyana; Naufal Rizqullah; Ilham Nurjaman; Muhammad Ali Ramdhani</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>Multidisciplinary Reviews</t>
   </si>
   <si>
@@ -761,6 +1063,36 @@
     <t>Malque Publishing</t>
   </si>
   <si>
+    <t>Analyzing Public Sentiment on Indonesia's Constitutional Court Post-2024 Election Ruling: Insights from Appraisal Theory and Data Mining</t>
+  </si>
+  <si>
+    <t>Ai Yeni Yuliyanti; Ponia Mega Septiana; Wiwi Widuri Sintia Putri Sari; Titania Sari</t>
+  </si>
+  <si>
+    <t>Traduction et Langues</t>
+  </si>
+  <si>
+    <t>2600-6235</t>
+  </si>
+  <si>
+    <t>https://revue.univ-oran2.dz/revuetranslang/index.php/translang/article/view/1027</t>
+  </si>
+  <si>
+    <t>Appraisal System Theory; Institutional Accountability; Political Discourse; Public Sentiment; Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>This study examines public sentiment toward Indonesia’s Constitutional Court (Mahkamah Konstitusi, MK) following its 2024 regional election ruling. Using sentiment analysis and Martin and White’s (2005) Appraisal Theory, the research investigates emotional, evaluative, and dialogic patterns in public discourse through YouTube comments. A mixed-method approach was adopted by combining qualitative appraisal interpretation with quantitative categorization and machine learning-based sentiment classification, all conducted using the Orange data mining application. Orange was chosen for its visual programming interface, ease of integration between linguistic theory and machine learning workflows, and accessibility for researchers working across disciplines. From 4,010 YouTube comments, 223 relevant entries were filtered and analysed according to the three domains of Appraisal Theory: Attitude (affect, judgment, appreciation), Engagement (monogloss and heterogloss), and Graduation (force and focus), enabling a structured evaluation of public responses. Three machine learning models were employed for sentiment classification within Orange: Naive Bayes, for its speed and efficiency in text classification; Logistic Regression, for its interpretability and robust baseline performance; and Neural Network, for its ability to capture nuanced emotional expressions. Among these, the Neural Network achieved the highest performance (AUC: 0.958; F1 score: 0.853), followed by Logistic Regression (AUC: 0.931; F1: 0.807), and Naive Bayes (AUC: 0.925; F1: 0.802). Each model offered distinct strengths: Neural Network revealed deeper emotional intensity, Logistic Regression emphasized positive affect, and Naive Bayes captured dominant monoglossic tendencies in discourse. The findings reveal a predominance of neutral and moderately positive sentiments, with joy, fear, surprise, and dissatisfaction emerging as key affective responses. The integration of Appraisal Theory and sentiment modeling through Orange demonstrates a systematic and scalable method for interpreting public discourse in digital environments. This research contributes methodologically by bridging qualitative linguistic analysis with accessible data mining tools, and substantively by offering insight into how digital publics engage with constitutional authority. It advances the literature on institutional trust by illustrating how social media serves as a platform for democratic evaluations of judicial decisions.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21101196450&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21101196450?origin=resultslist</t>
+  </si>
+  <si>
+    <t>University of Oran 2 Mohamed Ben Ahmed</t>
+  </si>
+  <si>
     <t>Sentiment Analysis of BNI Mobile Application Using The K-Nearest Neighbor Algorithm (KNN) With Particle Swarm Optimization (PSO) Feature Selection</t>
   </si>
   <si>
@@ -834,6 +1166,108 @@
   </si>
   <si>
     <t>Pandawan Sejahtera</t>
+  </si>
+  <si>
+    <t>Exploring electric vehicle adoption in Indonesia using zero-shot aspect-based sentiment analysis</t>
+  </si>
+  <si>
+    <t>Sinung Adi Nugroho; Sunu Widianto</t>
+  </si>
+  <si>
+    <t>Sustainable Operations and Computers</t>
+  </si>
+  <si>
+    <t>2666-4127</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S2666412724000151</t>
+  </si>
+  <si>
+    <t>Electric vehicle; Technology adoption; Consumer acceptance; Aspect-based sentiment analysis; Zero-shot learning</t>
+  </si>
+  <si>
+    <t>Transportation emissions significantly contribute to greenhouse gases (GHG) and climate change. Electric vehicles (EVs) offer a promising solution to this problem. Despite the noteworthy adoption of EVs in emerging economies like China and Europe, the pace of EV rollout in Indonesia remains sluggish. Currently, the country’s rate of EV adoption is below 0.3 %, leading to stagnation in the Indonesian electric vehicle market. Several factors have impeded the adoption of EVs in Indonesia. Previous studies have investigated consumer acceptance of EV adoption in specific countries using sentiment analysis. Various data analytics and machine learning techniques have been implemented in those studies. However, those studies predominantly rely on the traditional sentiment analysis method, which assigns a single sentiment classification to each document or sentence. On the other hand, this study aims to investigate consumer acceptance of electric vehicle adoption in Indonesia through Twitter conversations. It utilises the Zero-Shot Aspect-Based Sentiment Analysis (ABSA) approach, which can provide a more fine-grained analysis of the aspects discussed and their corresponding sentiments. The findings demonstrate the effectiveness of this approach in identifying discussed aspects within tweets, though its sentiment classification performance is limited. The research also uncovers crucial aspects of electric vehicle adoption and public sentiments on Twitter. These insights could provide valuable guidance to the government and other stakeholders regarding the concerns associated with EV adoption in Indonesia.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21101107945&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21101107945</t>
+  </si>
+  <si>
+    <t>KeAi Communications Co.</t>
+  </si>
+  <si>
+    <t>Exploring public sentiment toward Islamic banking apps: A case study of BSI mobile in Indonesia</t>
+  </si>
+  <si>
+    <t>Amir Rumra; Teguh Arie Sandy; Akbar Sarif; Koerniawan Dwi Wibawa; Darman; Ahmad Chafid Alwif; Tri Septianto</t>
+  </si>
+  <si>
+    <t>Multidisciplinary Science Journal</t>
+  </si>
+  <si>
+    <t>2675-1240</t>
+  </si>
+  <si>
+    <t>https://malque.pub/ojs/index.php/msj/article/view/10470</t>
+  </si>
+  <si>
+    <t>public sentiment; islamic digital banking; BSI mobile; sentiment analysis</t>
+  </si>
+  <si>
+    <t>Abstract Islamic banking in Indonesia has experienced significant growth since its introduction in the early 1990s, with digital transformation becoming a critical driver of financial inclusion and service accessibility. The establishment of Bank Syariah Indonesia (BSI) in 2021, formed through the merger of several state-owned Islamic banks, marked a pivotal moment in the sector's development. BSI Mobile, as the bank's primary digital platform, serves as a crucial interface for delivering Sharia-compliant financial services to millions of users. However, despite rapid technological advancement, questions remain regarding user satisfaction, trust, and the effectiveness of digital Islamic banking services. This study explores public sentiment toward BSI Mobile by analyzing 25,592 user reviews collected from the Google Play Store using Natural Language Processing (NLP) and Machine Learning techniques. Sentiment classification was conducted based on Ekman's Six Basic Emotions framework, categorizing user feedback into Joy, Surprise, Fear, Sadness, Disgust, and Anger. Two supervised machine learning models—Naïve Bayes and Logistic Regression—were employed to classify reviews into four key aspects: App Performance, Security &amp; Privacy, App Functionality, and User Interaction. Both models demonstrated high accuracy (89.7%) with equivalent performance metrics (AUC: 0.948, F1: 0.898). The findings reveal a highly polarized user experience, with 10,618 one-star ratings and 10,554 five-star ratings, indicating that users have either very positive or very negative experiences. While Joy (11,180 cases) and Surprise (9,943 cases) dominated positive sentiments, Fear (3,072 cases) emerged as a significant concern, primarily related to security and transaction reliability. App Performance and Security &amp; Privacy were identified as the most critical factors influencing user satisfaction. The study provides actionable insights for improving digital Islamic banking services, emphasizing the need for enhanced system stability, robust security measures, and continuous feature optimization. These findings contribute to the broader understanding of digital transformation in Islamic finance and offer practical recommendations for banking institutions, policymakers, and FinTech developers to strengthen user trust and promote wider adoption of Sharia-compliant financial technology solutions.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21101133576&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21101133576?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Marketing insights from social media discourse on islamic banking in Indonesia: A social network analysis</t>
+  </si>
+  <si>
+    <t>Muhamad Subhi Apriantoro; Pristika Yuniarti</t>
+  </si>
+  <si>
+    <t>https://malque.pub/ojs/index.php/msj/article/view/6095</t>
+  </si>
+  <si>
+    <t>social network analysis; islamic banking; financial institutions; government involvement; consumer behavior</t>
+  </si>
+  <si>
+    <t>This research examines Twitter conversations about Islamic banking in Indonesia to better understand the prevailing discourse. The Indonesian populace displays notable interest in Islamic banking as an alternative financial system; however, the perspectives surrounding Islamic finance exhibit multifaceted nuances. This study uses social network analysis to scrutinize Twitter users engaged in discussions about Islamic banking, exploring their discourse dynamics and opinion formation processes. The research began by collecting a large dataset of Indonesian Islamic banking conversations on Twitter, with 7,289 tweets recorded in August 2022, using centrality, density, and community detection metrics to analyze discussions and identify prominent actors and communities. DEA, an NLP-based social network analysis service, facilitated data collection. This investigation unveils distinct communities characterized by diverse perspectives and stances surrounding Islamic banking in Indonesia on Twitter, focusing on key individuals, or thought leaders, who shape the narrative and influence their peers. Findings provide a comprehensive overview of dominant sentiments, issues, and attitudes in online discourse, offering invaluable insights for government bodies, financial entities, and marketing professionals to engage the public effectively. Additionally, these findings enrich academic perspectives on social media interactions in Islamic banking, paving the way for further scholarly inquiries. To strengthen Islamic banking's presence and trust within the digital community, it is recommended that financial institutions and government agencies collaborate with key influencers identified in this study to amplify awareness and address prevalent concerns. Future research should incorporate longitudinal analysis to track changes in sentiment and opinion trends over time, providing a dynamic understanding of public discourse that can inform policies and marketing strategies aligned with the values and preferences of Indonesia's Muslim population.</t>
+  </si>
+  <si>
+    <t>Assessing Political Communication Reform in Digital Age: Case of 2024 Indonesia Presidential Elections</t>
+  </si>
+  <si>
+    <t>Nabila Ridwan Mohamad; Ali Sahab; Aribowo Aribowo; Rizky Bangun Wibisono; Mohammad Asfar</t>
+  </si>
+  <si>
+    <t>Journal of Law and Legal Reform</t>
+  </si>
+  <si>
+    <t>2715-0968</t>
+  </si>
+  <si>
+    <t>https://journal.unnes.ac.id/journals/jllr/article/view/20491</t>
+  </si>
+  <si>
+    <t>Political Perception; Media; Presidential Election; Political Behavior</t>
+  </si>
+  <si>
+    <t>This research examines the role of Metro TV media in shaping the political image of Anies Baswedan and Muhaimin Iskandar for the 2024 Presidential Election. The study focuses on how Surya Paloh, a member of the Democratic National Party (Nasdem), biasedly reported on the candidates, affecting their electability in the 2024 General Election contestation. The research uses a qualitative content analysis method, a systematic approach to understanding and interpreting text data, to identify themes, patterns, and deep meaning. The study uses content analysis techniques to analyze narratives and framing strategies used in YouTube videos, while quantitative data, such as views, likes, dislikes, and comments, is analyzed to understand public sentiment and response to the political actors studied. The research provides a deeper understanding of Metro TV’s media alignment and the construction of the political image of Anies Baswedan and Muhaimin Iskandar on YouTube, ultimately impacting public perception and increasing their electability in the context of democracy and participation politics in the 2024 presidential election.</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21101209979&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/sourceid/21101209979?origin=resultslist</t>
+  </si>
+  <si>
+    <t>Universitas Negeri Semarang</t>
   </si>
   <si>
     <t>Twitter Sentiment Analysis on the Iran-Israel Conflict Using the Naïve Bayes Classification Algorithm</t>
@@ -2543,10 +2977,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:U136" totalsRowShown="0">
-  <autoFilter ref="A1:U136" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U136">
-    <sortCondition ref="R2:R136"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:U151" totalsRowShown="0">
+  <autoFilter ref="A1:U151" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U151">
+    <sortCondition ref="R2:R151"/>
   </sortState>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No"/>
@@ -2854,7 +3288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U136"/>
+  <dimension ref="A1:U151"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
@@ -2927,43 +3361,43 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E2">
-        <v>16</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="J2" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="P2" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="Q2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="R2" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="S2" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -2971,46 +3405,43 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>285</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>286</v>
+        <v>54</v>
       </c>
       <c r="D3">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="E3">
-        <v>8</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
+        <v>434</v>
+      </c>
+      <c r="F3" t="s">
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>287</v>
+        <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>288</v>
+        <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>289</v>
+        <v>57</v>
       </c>
       <c r="J3" t="s">
-        <v>290</v>
-      </c>
-      <c r="K3" t="s">
-        <v>122</v>
-      </c>
-      <c r="L3" t="s">
-        <v>291</v>
+        <v>58</v>
       </c>
       <c r="P3" t="s">
-        <v>292</v>
+        <v>59</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>60</v>
       </c>
       <c r="R3" t="s">
-        <v>293</v>
-      </c>
-      <c r="U3" t="s">
-        <v>294</v>
+        <v>61</v>
+      </c>
+      <c r="S3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -3018,46 +3449,43 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>295</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>296</v>
+        <v>64</v>
       </c>
       <c r="D4">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="E4">
-        <v>8</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>44</v>
       </c>
       <c r="G4" t="s">
-        <v>287</v>
+        <v>65</v>
       </c>
       <c r="H4" t="s">
-        <v>288</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>297</v>
+        <v>67</v>
       </c>
       <c r="J4" t="s">
-        <v>298</v>
-      </c>
-      <c r="K4" t="s">
-        <v>122</v>
-      </c>
-      <c r="L4" t="s">
-        <v>291</v>
+        <v>68</v>
       </c>
       <c r="P4" t="s">
-        <v>299</v>
+        <v>69</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>70</v>
       </c>
       <c r="R4" t="s">
-        <v>293</v>
-      </c>
-      <c r="U4" t="s">
-        <v>294</v>
+        <v>71</v>
+      </c>
+      <c r="S4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -3065,46 +3493,43 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>301</v>
+        <v>151</v>
       </c>
       <c r="D5">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
+        <v>61</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>287</v>
+        <v>152</v>
       </c>
       <c r="H5" t="s">
-        <v>288</v>
+        <v>153</v>
       </c>
       <c r="I5" t="s">
-        <v>302</v>
+        <v>154</v>
       </c>
       <c r="J5" t="s">
-        <v>303</v>
-      </c>
-      <c r="K5" t="s">
-        <v>122</v>
-      </c>
-      <c r="L5" t="s">
-        <v>291</v>
+        <v>155</v>
       </c>
       <c r="P5" t="s">
-        <v>304</v>
+        <v>156</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>157</v>
       </c>
       <c r="R5" t="s">
-        <v>293</v>
-      </c>
-      <c r="U5" t="s">
-        <v>294</v>
+        <v>158</v>
+      </c>
+      <c r="S5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -3112,46 +3537,46 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>305</v>
+        <v>429</v>
       </c>
       <c r="C6" t="s">
-        <v>306</v>
+        <v>430</v>
       </c>
       <c r="D6">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>106</v>
       </c>
       <c r="G6" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H6" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I6" t="s">
-        <v>307</v>
+        <v>433</v>
       </c>
       <c r="J6" t="s">
-        <v>308</v>
+        <v>434</v>
       </c>
       <c r="K6" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L6" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P6" t="s">
-        <v>309</v>
+        <v>436</v>
       </c>
       <c r="R6" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U6" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -3159,46 +3584,46 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>310</v>
+        <v>439</v>
       </c>
       <c r="C7" t="s">
-        <v>301</v>
+        <v>440</v>
       </c>
       <c r="D7">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E7">
-        <v>9</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>171</v>
       </c>
       <c r="G7" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H7" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I7" t="s">
-        <v>311</v>
+        <v>441</v>
       </c>
       <c r="J7" t="s">
-        <v>312</v>
+        <v>442</v>
       </c>
       <c r="K7" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L7" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P7" t="s">
-        <v>313</v>
+        <v>443</v>
       </c>
       <c r="R7" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U7" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -3206,10 +3631,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>314</v>
+        <v>444</v>
       </c>
       <c r="C8" t="s">
-        <v>315</v>
+        <v>445</v>
       </c>
       <c r="D8">
         <v>2019</v>
@@ -3217,35 +3642,35 @@
       <c r="E8">
         <v>9</v>
       </c>
-      <c r="F8">
-        <v>4</v>
+      <c r="F8" t="s">
+        <v>44</v>
       </c>
       <c r="G8" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H8" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I8" t="s">
-        <v>316</v>
+        <v>446</v>
       </c>
       <c r="J8" t="s">
-        <v>317</v>
+        <v>447</v>
       </c>
       <c r="K8" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L8" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P8" t="s">
-        <v>318</v>
+        <v>448</v>
       </c>
       <c r="R8" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U8" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -3253,46 +3678,46 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>319</v>
+        <v>449</v>
       </c>
       <c r="C9" t="s">
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="D9">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E9">
-        <v>10</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H9" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I9" t="s">
-        <v>321</v>
+        <v>451</v>
       </c>
       <c r="J9" t="s">
-        <v>322</v>
+        <v>452</v>
       </c>
       <c r="K9" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L9" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P9" t="s">
-        <v>323</v>
+        <v>453</v>
       </c>
       <c r="R9" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U9" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -3300,46 +3725,46 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>324</v>
+        <v>454</v>
       </c>
       <c r="C10" t="s">
-        <v>325</v>
+        <v>445</v>
       </c>
       <c r="D10">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E10">
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H10" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I10" t="s">
-        <v>326</v>
+        <v>455</v>
       </c>
       <c r="J10" t="s">
-        <v>327</v>
+        <v>456</v>
       </c>
       <c r="K10" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L10" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P10" t="s">
-        <v>328</v>
+        <v>457</v>
       </c>
       <c r="R10" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U10" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -3347,46 +3772,46 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>329</v>
+        <v>458</v>
       </c>
       <c r="C11" t="s">
-        <v>330</v>
+        <v>459</v>
       </c>
       <c r="D11">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E11">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H11" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I11" t="s">
-        <v>331</v>
+        <v>460</v>
       </c>
       <c r="J11" t="s">
-        <v>332</v>
+        <v>461</v>
       </c>
       <c r="K11" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L11" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P11" t="s">
-        <v>333</v>
+        <v>462</v>
       </c>
       <c r="R11" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U11" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -3394,46 +3819,46 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>334</v>
+        <v>463</v>
       </c>
       <c r="C12" t="s">
-        <v>335</v>
+        <v>464</v>
       </c>
       <c r="D12">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E12">
-        <v>11</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>106</v>
       </c>
       <c r="G12" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H12" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I12" t="s">
-        <v>336</v>
+        <v>465</v>
       </c>
       <c r="J12" t="s">
-        <v>337</v>
+        <v>466</v>
       </c>
       <c r="K12" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L12" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P12" t="s">
-        <v>338</v>
+        <v>467</v>
       </c>
       <c r="R12" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U12" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -3441,46 +3866,46 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>339</v>
+        <v>468</v>
       </c>
       <c r="C13" t="s">
-        <v>335</v>
+        <v>469</v>
       </c>
       <c r="D13">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E13">
-        <v>11</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>171</v>
       </c>
       <c r="G13" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H13" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I13" t="s">
-        <v>340</v>
+        <v>470</v>
       </c>
       <c r="J13" t="s">
-        <v>341</v>
+        <v>471</v>
       </c>
       <c r="K13" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L13" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P13" t="s">
-        <v>342</v>
+        <v>472</v>
       </c>
       <c r="R13" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U13" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -3488,46 +3913,46 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>343</v>
+        <v>473</v>
       </c>
       <c r="C14" t="s">
-        <v>344</v>
+        <v>474</v>
       </c>
       <c r="D14">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E14">
-        <v>11</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>171</v>
       </c>
       <c r="G14" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H14" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I14" t="s">
-        <v>345</v>
+        <v>475</v>
       </c>
       <c r="J14" t="s">
-        <v>346</v>
+        <v>476</v>
       </c>
       <c r="K14" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L14" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P14" t="s">
-        <v>347</v>
+        <v>477</v>
       </c>
       <c r="R14" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U14" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -3535,10 +3960,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>348</v>
+        <v>478</v>
       </c>
       <c r="C15" t="s">
-        <v>349</v>
+        <v>479</v>
       </c>
       <c r="D15">
         <v>2021</v>
@@ -3546,35 +3971,35 @@
       <c r="E15">
         <v>11</v>
       </c>
-      <c r="F15">
-        <v>3</v>
+      <c r="F15" t="s">
+        <v>44</v>
       </c>
       <c r="G15" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H15" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I15" t="s">
-        <v>350</v>
+        <v>480</v>
       </c>
       <c r="J15" t="s">
-        <v>351</v>
+        <v>481</v>
       </c>
       <c r="K15" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L15" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P15" t="s">
-        <v>352</v>
+        <v>482</v>
       </c>
       <c r="R15" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U15" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -3582,10 +4007,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>353</v>
+        <v>483</v>
       </c>
       <c r="C16" t="s">
-        <v>354</v>
+        <v>479</v>
       </c>
       <c r="D16">
         <v>2021</v>
@@ -3593,35 +4018,35 @@
       <c r="E16">
         <v>11</v>
       </c>
-      <c r="F16">
-        <v>3</v>
+      <c r="F16" t="s">
+        <v>44</v>
       </c>
       <c r="G16" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H16" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I16" t="s">
-        <v>355</v>
+        <v>484</v>
       </c>
       <c r="J16" t="s">
-        <v>356</v>
+        <v>485</v>
       </c>
       <c r="K16" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L16" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P16" t="s">
-        <v>357</v>
+        <v>486</v>
       </c>
       <c r="R16" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U16" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -3629,10 +4054,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>358</v>
+        <v>487</v>
       </c>
       <c r="C17" t="s">
-        <v>359</v>
+        <v>488</v>
       </c>
       <c r="D17">
         <v>2021</v>
@@ -3640,35 +4065,35 @@
       <c r="E17">
         <v>11</v>
       </c>
-      <c r="F17">
-        <v>4</v>
+      <c r="F17" t="s">
+        <v>181</v>
       </c>
       <c r="G17" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H17" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I17" t="s">
-        <v>360</v>
+        <v>489</v>
       </c>
       <c r="J17" t="s">
-        <v>361</v>
+        <v>490</v>
       </c>
       <c r="K17" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L17" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P17" t="s">
-        <v>362</v>
+        <v>491</v>
       </c>
       <c r="R17" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U17" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -3676,46 +4101,46 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>363</v>
+        <v>492</v>
       </c>
       <c r="C18" t="s">
-        <v>364</v>
+        <v>493</v>
       </c>
       <c r="D18">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E18">
-        <v>12</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
+        <v>75</v>
       </c>
       <c r="G18" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H18" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I18" t="s">
-        <v>365</v>
+        <v>494</v>
       </c>
       <c r="J18" t="s">
-        <v>366</v>
+        <v>495</v>
       </c>
       <c r="K18" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L18" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P18" t="s">
-        <v>367</v>
+        <v>496</v>
       </c>
       <c r="R18" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U18" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -3723,46 +4148,46 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>368</v>
+        <v>497</v>
       </c>
       <c r="C19" t="s">
-        <v>369</v>
+        <v>498</v>
       </c>
       <c r="D19">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E19">
-        <v>12</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
+        <v>75</v>
       </c>
       <c r="G19" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H19" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I19" t="s">
-        <v>370</v>
+        <v>499</v>
       </c>
       <c r="J19" t="s">
-        <v>371</v>
+        <v>500</v>
       </c>
       <c r="K19" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L19" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P19" t="s">
-        <v>372</v>
+        <v>501</v>
       </c>
       <c r="R19" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U19" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -3770,46 +4195,46 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>373</v>
+        <v>502</v>
       </c>
       <c r="C20" t="s">
-        <v>374</v>
+        <v>503</v>
       </c>
       <c r="D20">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E20">
-        <v>12</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
+        <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H20" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I20" t="s">
-        <v>375</v>
+        <v>504</v>
       </c>
       <c r="J20" t="s">
-        <v>376</v>
+        <v>505</v>
       </c>
       <c r="K20" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L20" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P20" t="s">
-        <v>377</v>
+        <v>506</v>
       </c>
       <c r="R20" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U20" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -3817,10 +4242,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>378</v>
+        <v>507</v>
       </c>
       <c r="C21" t="s">
-        <v>379</v>
+        <v>508</v>
       </c>
       <c r="D21">
         <v>2022</v>
@@ -3828,35 +4253,35 @@
       <c r="E21">
         <v>12</v>
       </c>
-      <c r="F21">
-        <v>3</v>
+      <c r="F21" t="s">
+        <v>44</v>
       </c>
       <c r="G21" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H21" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I21" t="s">
-        <v>380</v>
+        <v>509</v>
       </c>
       <c r="J21" t="s">
-        <v>381</v>
+        <v>510</v>
       </c>
       <c r="K21" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P21" t="s">
-        <v>382</v>
+        <v>511</v>
       </c>
       <c r="R21" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U21" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -3864,10 +4289,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>383</v>
+        <v>512</v>
       </c>
       <c r="C22" t="s">
-        <v>384</v>
+        <v>513</v>
       </c>
       <c r="D22">
         <v>2022</v>
@@ -3875,35 +4300,35 @@
       <c r="E22">
         <v>12</v>
       </c>
-      <c r="F22">
-        <v>3</v>
+      <c r="F22" t="s">
+        <v>44</v>
       </c>
       <c r="G22" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H22" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I22" t="s">
-        <v>385</v>
+        <v>514</v>
       </c>
       <c r="J22" t="s">
-        <v>386</v>
+        <v>515</v>
       </c>
       <c r="K22" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L22" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P22" t="s">
-        <v>387</v>
+        <v>516</v>
       </c>
       <c r="R22" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U22" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -3911,10 +4336,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>388</v>
+        <v>517</v>
       </c>
       <c r="C23" t="s">
-        <v>389</v>
+        <v>518</v>
       </c>
       <c r="D23">
         <v>2022</v>
@@ -3922,35 +4347,35 @@
       <c r="E23">
         <v>12</v>
       </c>
-      <c r="F23">
-        <v>4</v>
+      <c r="F23" t="s">
+        <v>181</v>
       </c>
       <c r="G23" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H23" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I23" t="s">
-        <v>390</v>
+        <v>519</v>
       </c>
       <c r="J23" t="s">
-        <v>391</v>
+        <v>520</v>
       </c>
       <c r="K23" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L23" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P23" t="s">
-        <v>392</v>
+        <v>521</v>
       </c>
       <c r="R23" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U23" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -3958,10 +4383,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>393</v>
+        <v>522</v>
       </c>
       <c r="C24" t="s">
-        <v>394</v>
+        <v>523</v>
       </c>
       <c r="D24">
         <v>2022</v>
@@ -3969,35 +4394,35 @@
       <c r="E24">
         <v>12</v>
       </c>
-      <c r="F24">
-        <v>4</v>
+      <c r="F24" t="s">
+        <v>75</v>
       </c>
       <c r="G24" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H24" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I24" t="s">
-        <v>395</v>
+        <v>524</v>
       </c>
       <c r="J24" t="s">
-        <v>396</v>
+        <v>525</v>
       </c>
       <c r="K24" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L24" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P24" t="s">
-        <v>397</v>
+        <v>526</v>
       </c>
       <c r="R24" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U24" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -4005,10 +4430,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>398</v>
+        <v>527</v>
       </c>
       <c r="C25" t="s">
-        <v>399</v>
+        <v>528</v>
       </c>
       <c r="D25">
         <v>2022</v>
@@ -4016,35 +4441,35 @@
       <c r="E25">
         <v>12</v>
       </c>
-      <c r="F25">
-        <v>4</v>
+      <c r="F25" t="s">
+        <v>75</v>
       </c>
       <c r="G25" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H25" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I25" t="s">
-        <v>400</v>
+        <v>529</v>
       </c>
       <c r="J25" t="s">
-        <v>401</v>
+        <v>530</v>
       </c>
       <c r="K25" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L25" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P25" t="s">
-        <v>402</v>
+        <v>531</v>
       </c>
       <c r="R25" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U25" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -4052,10 +4477,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>403</v>
+        <v>532</v>
       </c>
       <c r="C26" t="s">
-        <v>404</v>
+        <v>533</v>
       </c>
       <c r="D26">
         <v>2022</v>
@@ -4063,35 +4488,35 @@
       <c r="E26">
         <v>12</v>
       </c>
-      <c r="F26">
-        <v>5</v>
+      <c r="F26" t="s">
+        <v>33</v>
       </c>
       <c r="G26" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H26" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I26" t="s">
-        <v>405</v>
+        <v>534</v>
       </c>
       <c r="J26" t="s">
-        <v>406</v>
+        <v>535</v>
       </c>
       <c r="K26" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L26" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P26" t="s">
-        <v>407</v>
+        <v>536</v>
       </c>
       <c r="R26" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U26" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -4099,10 +4524,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>408</v>
+        <v>537</v>
       </c>
       <c r="C27" t="s">
-        <v>409</v>
+        <v>538</v>
       </c>
       <c r="D27">
         <v>2022</v>
@@ -4110,35 +4535,35 @@
       <c r="E27">
         <v>12</v>
       </c>
-      <c r="F27">
-        <v>6</v>
+      <c r="F27" t="s">
+        <v>33</v>
       </c>
       <c r="G27" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H27" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I27" t="s">
-        <v>410</v>
+        <v>539</v>
       </c>
       <c r="J27" t="s">
-        <v>411</v>
+        <v>540</v>
       </c>
       <c r="K27" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L27" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P27" t="s">
-        <v>412</v>
+        <v>541</v>
       </c>
       <c r="R27" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U27" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -4146,46 +4571,46 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>413</v>
+        <v>542</v>
       </c>
       <c r="C28" t="s">
-        <v>414</v>
+        <v>543</v>
       </c>
       <c r="D28">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E28">
-        <v>13</v>
-      </c>
-      <c r="F28">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>33</v>
       </c>
       <c r="G28" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H28" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I28" t="s">
-        <v>415</v>
+        <v>544</v>
       </c>
       <c r="J28" t="s">
-        <v>416</v>
+        <v>545</v>
       </c>
       <c r="K28" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L28" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P28" t="s">
-        <v>417</v>
+        <v>546</v>
       </c>
       <c r="R28" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U28" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -4193,46 +4618,46 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>418</v>
+        <v>547</v>
       </c>
       <c r="C29" t="s">
-        <v>419</v>
+        <v>548</v>
       </c>
       <c r="D29">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E29">
-        <v>13</v>
-      </c>
-      <c r="F29">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>106</v>
       </c>
       <c r="G29" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H29" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I29" t="s">
-        <v>420</v>
+        <v>549</v>
       </c>
       <c r="J29" t="s">
-        <v>421</v>
+        <v>550</v>
       </c>
       <c r="K29" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L29" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P29" t="s">
-        <v>422</v>
+        <v>551</v>
       </c>
       <c r="R29" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U29" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -4240,46 +4665,46 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>423</v>
+        <v>552</v>
       </c>
       <c r="C30" t="s">
-        <v>424</v>
+        <v>553</v>
       </c>
       <c r="D30">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E30">
-        <v>13</v>
-      </c>
-      <c r="F30">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>171</v>
       </c>
       <c r="G30" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H30" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I30" t="s">
-        <v>425</v>
+        <v>554</v>
       </c>
       <c r="J30" t="s">
-        <v>426</v>
+        <v>555</v>
       </c>
       <c r="K30" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L30" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P30" t="s">
-        <v>427</v>
+        <v>556</v>
       </c>
       <c r="R30" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U30" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -4287,10 +4712,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>428</v>
+        <v>557</v>
       </c>
       <c r="C31" t="s">
-        <v>429</v>
+        <v>558</v>
       </c>
       <c r="D31">
         <v>2023</v>
@@ -4298,35 +4723,35 @@
       <c r="E31">
         <v>13</v>
       </c>
-      <c r="F31">
-        <v>6</v>
+      <c r="F31" t="s">
+        <v>181</v>
       </c>
       <c r="G31" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H31" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I31" t="s">
-        <v>430</v>
+        <v>559</v>
       </c>
       <c r="J31" t="s">
-        <v>431</v>
+        <v>560</v>
       </c>
       <c r="K31" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L31" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P31" t="s">
-        <v>432</v>
+        <v>561</v>
       </c>
       <c r="R31" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U31" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -4334,46 +4759,46 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>433</v>
+        <v>562</v>
       </c>
       <c r="C32" t="s">
-        <v>434</v>
+        <v>563</v>
       </c>
       <c r="D32">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E32">
-        <v>14</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="F32" t="s">
+        <v>75</v>
       </c>
       <c r="G32" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H32" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I32" t="s">
+        <v>564</v>
+      </c>
+      <c r="J32" t="s">
+        <v>565</v>
+      </c>
+      <c r="K32" t="s">
+        <v>211</v>
+      </c>
+      <c r="L32" t="s">
         <v>435</v>
       </c>
-      <c r="J32" t="s">
-        <v>436</v>
-      </c>
-      <c r="K32" t="s">
-        <v>122</v>
-      </c>
-      <c r="L32" t="s">
-        <v>291</v>
-      </c>
       <c r="P32" t="s">
+        <v>566</v>
+      </c>
+      <c r="R32" t="s">
         <v>437</v>
       </c>
-      <c r="R32" t="s">
-        <v>293</v>
-      </c>
       <c r="U32" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -4381,46 +4806,46 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>567</v>
+      </c>
+      <c r="C33" t="s">
+        <v>568</v>
+      </c>
+      <c r="D33">
+        <v>2023</v>
+      </c>
+      <c r="E33">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" t="s">
+        <v>431</v>
+      </c>
+      <c r="H33" t="s">
+        <v>432</v>
+      </c>
+      <c r="I33" t="s">
+        <v>569</v>
+      </c>
+      <c r="J33" t="s">
+        <v>570</v>
+      </c>
+      <c r="K33" t="s">
+        <v>211</v>
+      </c>
+      <c r="L33" t="s">
+        <v>435</v>
+      </c>
+      <c r="P33" t="s">
+        <v>571</v>
+      </c>
+      <c r="R33" t="s">
+        <v>437</v>
+      </c>
+      <c r="U33" t="s">
         <v>438</v>
-      </c>
-      <c r="C33" t="s">
-        <v>439</v>
-      </c>
-      <c r="D33">
-        <v>2024</v>
-      </c>
-      <c r="E33">
-        <v>14</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33" t="s">
-        <v>287</v>
-      </c>
-      <c r="H33" t="s">
-        <v>288</v>
-      </c>
-      <c r="I33" t="s">
-        <v>440</v>
-      </c>
-      <c r="J33" t="s">
-        <v>441</v>
-      </c>
-      <c r="K33" t="s">
-        <v>122</v>
-      </c>
-      <c r="L33" t="s">
-        <v>291</v>
-      </c>
-      <c r="P33" t="s">
-        <v>442</v>
-      </c>
-      <c r="R33" t="s">
-        <v>293</v>
-      </c>
-      <c r="U33" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -4428,46 +4853,46 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>443</v>
+        <v>572</v>
       </c>
       <c r="C34" t="s">
-        <v>444</v>
+        <v>573</v>
       </c>
       <c r="D34">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E34">
-        <v>14</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="F34" t="s">
+        <v>171</v>
       </c>
       <c r="G34" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H34" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I34" t="s">
-        <v>445</v>
+        <v>574</v>
       </c>
       <c r="J34" t="s">
-        <v>446</v>
+        <v>575</v>
       </c>
       <c r="K34" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L34" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P34" t="s">
-        <v>447</v>
+        <v>576</v>
       </c>
       <c r="R34" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U34" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -4475,10 +4900,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>448</v>
+        <v>577</v>
       </c>
       <c r="C35" t="s">
-        <v>449</v>
+        <v>578</v>
       </c>
       <c r="D35">
         <v>2024</v>
@@ -4486,35 +4911,35 @@
       <c r="E35">
         <v>14</v>
       </c>
-      <c r="F35">
-        <v>1</v>
+      <c r="F35" t="s">
+        <v>44</v>
       </c>
       <c r="G35" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H35" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I35" t="s">
-        <v>450</v>
+        <v>579</v>
       </c>
       <c r="J35" t="s">
-        <v>451</v>
+        <v>580</v>
       </c>
       <c r="K35" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L35" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P35" t="s">
-        <v>452</v>
+        <v>581</v>
       </c>
       <c r="R35" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U35" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -4522,10 +4947,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>453</v>
+        <v>582</v>
       </c>
       <c r="C36" t="s">
-        <v>454</v>
+        <v>583</v>
       </c>
       <c r="D36">
         <v>2024</v>
@@ -4533,35 +4958,35 @@
       <c r="E36">
         <v>14</v>
       </c>
-      <c r="F36">
-        <v>2</v>
+      <c r="F36" t="s">
+        <v>44</v>
       </c>
       <c r="G36" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H36" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I36" t="s">
-        <v>455</v>
+        <v>584</v>
       </c>
       <c r="J36" t="s">
-        <v>456</v>
+        <v>585</v>
       </c>
       <c r="K36" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L36" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P36" t="s">
-        <v>457</v>
+        <v>586</v>
       </c>
       <c r="R36" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U36" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4569,10 +4994,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>458</v>
+        <v>587</v>
       </c>
       <c r="C37" t="s">
-        <v>459</v>
+        <v>588</v>
       </c>
       <c r="D37">
         <v>2024</v>
@@ -4580,35 +5005,35 @@
       <c r="E37">
         <v>14</v>
       </c>
-      <c r="F37">
-        <v>3</v>
+      <c r="F37" t="s">
+        <v>44</v>
       </c>
       <c r="G37" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H37" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I37" t="s">
-        <v>460</v>
+        <v>589</v>
       </c>
       <c r="J37" t="s">
-        <v>461</v>
+        <v>590</v>
       </c>
       <c r="K37" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L37" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P37" t="s">
-        <v>462</v>
+        <v>591</v>
       </c>
       <c r="R37" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U37" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -4616,10 +5041,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>463</v>
+        <v>592</v>
       </c>
       <c r="C38" t="s">
-        <v>464</v>
+        <v>593</v>
       </c>
       <c r="D38">
         <v>2024</v>
@@ -4627,35 +5052,35 @@
       <c r="E38">
         <v>14</v>
       </c>
-      <c r="F38">
-        <v>3</v>
+      <c r="F38" t="s">
+        <v>44</v>
       </c>
       <c r="G38" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H38" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I38" t="s">
-        <v>465</v>
+        <v>594</v>
       </c>
       <c r="J38" t="s">
-        <v>466</v>
+        <v>595</v>
       </c>
       <c r="K38" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L38" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P38" t="s">
-        <v>467</v>
+        <v>596</v>
       </c>
       <c r="R38" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U38" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -4663,10 +5088,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>468</v>
+        <v>597</v>
       </c>
       <c r="C39" t="s">
-        <v>469</v>
+        <v>598</v>
       </c>
       <c r="D39">
         <v>2024</v>
@@ -4674,35 +5099,35 @@
       <c r="E39">
         <v>14</v>
       </c>
-      <c r="F39">
-        <v>3</v>
+      <c r="F39" t="s">
+        <v>181</v>
       </c>
       <c r="G39" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H39" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I39" t="s">
-        <v>470</v>
+        <v>599</v>
       </c>
       <c r="J39" t="s">
-        <v>471</v>
+        <v>600</v>
       </c>
       <c r="K39" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L39" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P39" t="s">
-        <v>472</v>
+        <v>601</v>
       </c>
       <c r="R39" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U39" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4710,10 +5135,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>473</v>
+        <v>602</v>
       </c>
       <c r="C40" t="s">
-        <v>474</v>
+        <v>603</v>
       </c>
       <c r="D40">
         <v>2024</v>
@@ -4721,35 +5146,35 @@
       <c r="E40">
         <v>14</v>
       </c>
-      <c r="F40">
-        <v>4</v>
+      <c r="F40" t="s">
+        <v>75</v>
       </c>
       <c r="G40" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H40" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I40" t="s">
-        <v>475</v>
+        <v>604</v>
       </c>
       <c r="J40" t="s">
-        <v>476</v>
+        <v>605</v>
       </c>
       <c r="K40" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L40" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P40" t="s">
-        <v>477</v>
+        <v>606</v>
       </c>
       <c r="R40" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U40" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -4757,10 +5182,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>478</v>
+        <v>607</v>
       </c>
       <c r="C41" t="s">
-        <v>479</v>
+        <v>608</v>
       </c>
       <c r="D41">
         <v>2024</v>
@@ -4768,35 +5193,35 @@
       <c r="E41">
         <v>14</v>
       </c>
-      <c r="F41">
-        <v>4</v>
+      <c r="F41" t="s">
+        <v>75</v>
       </c>
       <c r="G41" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H41" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I41" t="s">
-        <v>480</v>
+        <v>609</v>
       </c>
       <c r="J41" t="s">
-        <v>481</v>
+        <v>610</v>
       </c>
       <c r="K41" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L41" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P41" t="s">
-        <v>482</v>
+        <v>611</v>
       </c>
       <c r="R41" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U41" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4804,10 +5229,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>483</v>
+        <v>612</v>
       </c>
       <c r="C42" t="s">
-        <v>484</v>
+        <v>613</v>
       </c>
       <c r="D42">
         <v>2024</v>
@@ -4815,35 +5240,35 @@
       <c r="E42">
         <v>14</v>
       </c>
-      <c r="F42">
-        <v>4</v>
+      <c r="F42" t="s">
+        <v>75</v>
       </c>
       <c r="G42" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H42" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I42" t="s">
-        <v>485</v>
+        <v>614</v>
       </c>
       <c r="J42" t="s">
-        <v>486</v>
+        <v>615</v>
       </c>
       <c r="K42" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L42" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P42" t="s">
-        <v>487</v>
+        <v>616</v>
       </c>
       <c r="R42" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U42" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4851,10 +5276,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>488</v>
+        <v>617</v>
       </c>
       <c r="C43" t="s">
-        <v>489</v>
+        <v>618</v>
       </c>
       <c r="D43">
         <v>2024</v>
@@ -4862,35 +5287,35 @@
       <c r="E43">
         <v>14</v>
       </c>
-      <c r="F43">
-        <v>6</v>
+      <c r="F43" t="s">
+        <v>33</v>
       </c>
       <c r="G43" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H43" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I43" t="s">
-        <v>490</v>
+        <v>619</v>
       </c>
       <c r="J43" t="s">
-        <v>491</v>
+        <v>620</v>
       </c>
       <c r="K43" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L43" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P43" t="s">
-        <v>492</v>
+        <v>621</v>
       </c>
       <c r="R43" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U43" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4898,46 +5323,46 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>493</v>
+        <v>622</v>
       </c>
       <c r="C44" t="s">
-        <v>494</v>
+        <v>623</v>
       </c>
       <c r="D44">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E44">
-        <v>15</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="F44" t="s">
+        <v>33</v>
       </c>
       <c r="G44" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H44" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I44" t="s">
-        <v>495</v>
+        <v>624</v>
       </c>
       <c r="J44" t="s">
-        <v>496</v>
+        <v>625</v>
       </c>
       <c r="K44" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L44" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P44" t="s">
-        <v>497</v>
+        <v>626</v>
       </c>
       <c r="R44" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U44" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4945,46 +5370,46 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>498</v>
+        <v>627</v>
       </c>
       <c r="C45" t="s">
-        <v>499</v>
+        <v>628</v>
       </c>
       <c r="D45">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E45">
-        <v>15</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="F45" t="s">
+        <v>33</v>
       </c>
       <c r="G45" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="H45" t="s">
-        <v>288</v>
+        <v>432</v>
       </c>
       <c r="I45" t="s">
-        <v>500</v>
+        <v>629</v>
       </c>
       <c r="J45" t="s">
-        <v>501</v>
+        <v>630</v>
       </c>
       <c r="K45" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L45" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="P45" t="s">
-        <v>502</v>
+        <v>631</v>
       </c>
       <c r="R45" t="s">
-        <v>293</v>
+        <v>437</v>
       </c>
       <c r="U45" t="s">
-        <v>294</v>
+        <v>438</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4992,49 +5417,46 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>116</v>
+        <v>632</v>
       </c>
       <c r="C46" t="s">
-        <v>117</v>
+        <v>633</v>
       </c>
       <c r="D46">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E46">
-        <v>40</v>
-      </c>
-      <c r="F46">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="F46" t="s">
+        <v>171</v>
       </c>
       <c r="G46" t="s">
-        <v>118</v>
+        <v>431</v>
       </c>
       <c r="H46" t="s">
-        <v>119</v>
+        <v>432</v>
       </c>
       <c r="I46" t="s">
-        <v>120</v>
+        <v>634</v>
       </c>
       <c r="J46" t="s">
-        <v>121</v>
+        <v>635</v>
       </c>
       <c r="K46" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="L46" t="s">
-        <v>123</v>
+        <v>435</v>
       </c>
       <c r="P46" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>125</v>
+        <v>636</v>
       </c>
       <c r="R46" t="s">
-        <v>126</v>
+        <v>437</v>
       </c>
       <c r="U46" t="s">
-        <v>127</v>
+        <v>438</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -5042,43 +5464,46 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>41</v>
+        <v>637</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>638</v>
       </c>
       <c r="D47">
         <v>2025</v>
       </c>
       <c r="E47">
-        <v>16</v>
-      </c>
-      <c r="F47">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="F47" t="s">
+        <v>44</v>
       </c>
       <c r="G47" t="s">
-        <v>43</v>
+        <v>431</v>
       </c>
       <c r="H47" t="s">
-        <v>44</v>
+        <v>432</v>
       </c>
       <c r="I47" t="s">
-        <v>45</v>
+        <v>639</v>
       </c>
       <c r="J47" t="s">
-        <v>46</v>
+        <v>640</v>
+      </c>
+      <c r="K47" t="s">
+        <v>211</v>
+      </c>
+      <c r="L47" t="s">
+        <v>435</v>
       </c>
       <c r="P47" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>48</v>
+        <v>641</v>
       </c>
       <c r="R47" t="s">
-        <v>49</v>
-      </c>
-      <c r="S47" t="s">
-        <v>50</v>
+        <v>437</v>
+      </c>
+      <c r="U47" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -5086,43 +5511,46 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>642</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>643</v>
       </c>
       <c r="D48">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E48">
-        <v>14</v>
-      </c>
-      <c r="F48">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="F48" t="s">
+        <v>44</v>
       </c>
       <c r="G48" t="s">
-        <v>63</v>
+        <v>431</v>
       </c>
       <c r="H48" t="s">
-        <v>64</v>
+        <v>432</v>
       </c>
       <c r="I48" t="s">
-        <v>65</v>
+        <v>644</v>
       </c>
       <c r="J48" t="s">
-        <v>66</v>
+        <v>645</v>
+      </c>
+      <c r="K48" t="s">
+        <v>211</v>
+      </c>
+      <c r="L48" t="s">
+        <v>435</v>
       </c>
       <c r="P48" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>68</v>
+        <v>646</v>
       </c>
       <c r="R48" t="s">
-        <v>69</v>
-      </c>
-      <c r="S48" t="s">
-        <v>70</v>
+        <v>437</v>
+      </c>
+      <c r="U48" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -5130,43 +5558,43 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="C49" t="s">
-        <v>52</v>
+        <v>170</v>
       </c>
       <c r="D49">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E49">
-        <v>14</v>
-      </c>
-      <c r="F49">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="F49" t="s">
+        <v>171</v>
       </c>
       <c r="G49" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="H49" t="s">
-        <v>54</v>
+        <v>173</v>
       </c>
       <c r="I49" t="s">
-        <v>55</v>
+        <v>174</v>
       </c>
       <c r="J49" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="P49" t="s">
-        <v>57</v>
+        <v>176</v>
       </c>
       <c r="Q49" t="s">
-        <v>58</v>
+        <v>177</v>
       </c>
       <c r="R49" t="s">
-        <v>59</v>
+        <v>178</v>
       </c>
       <c r="S49" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -5174,43 +5602,43 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="C50" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="D50">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E50">
-        <v>12</v>
-      </c>
-      <c r="F50">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="F50" t="s">
+        <v>44</v>
       </c>
       <c r="G50" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="H50" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="I50" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="J50" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="P50" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="Q50" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="R50" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="S50" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -5218,43 +5646,49 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="C51" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="D51">
         <v>2025</v>
       </c>
       <c r="E51">
-        <v>9</v>
-      </c>
-      <c r="F51">
-        <v>5</v>
+        <v>40</v>
+      </c>
+      <c r="F51" t="s">
+        <v>75</v>
       </c>
       <c r="G51" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="H51" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="I51" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="J51" t="s">
-        <v>228</v>
+        <v>210</v>
+      </c>
+      <c r="K51" t="s">
+        <v>211</v>
+      </c>
+      <c r="L51" t="s">
+        <v>212</v>
       </c>
       <c r="P51" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="Q51" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="R51" t="s">
-        <v>231</v>
-      </c>
-      <c r="S51" t="s">
-        <v>232</v>
+        <v>215</v>
+      </c>
+      <c r="U51" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -5262,43 +5696,43 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>179</v>
       </c>
       <c r="C52" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="D52">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E52">
-        <v>10</v>
-      </c>
-      <c r="F52">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="F52" t="s">
+        <v>181</v>
       </c>
       <c r="G52" t="s">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="H52" t="s">
-        <v>74</v>
+        <v>183</v>
       </c>
       <c r="I52" t="s">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="J52" t="s">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="P52" t="s">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="Q52" t="s">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="R52" t="s">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="S52" t="s">
-        <v>80</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -5306,43 +5740,43 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D53">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E53">
-        <v>14</v>
-      </c>
-      <c r="F53">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="F53" t="s">
+        <v>86</v>
       </c>
       <c r="G53" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I53" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J53" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="Q53" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="R53" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="S53" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -5350,43 +5784,43 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>233</v>
+        <v>95</v>
       </c>
       <c r="C54" t="s">
-        <v>234</v>
+        <v>96</v>
       </c>
       <c r="D54">
         <v>2025</v>
       </c>
       <c r="E54">
-        <v>8</v>
-      </c>
-      <c r="F54">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F54" t="s">
+        <v>75</v>
       </c>
       <c r="G54" t="s">
-        <v>235</v>
+        <v>97</v>
       </c>
       <c r="H54" t="s">
-        <v>236</v>
+        <v>98</v>
       </c>
       <c r="I54" t="s">
-        <v>237</v>
+        <v>99</v>
       </c>
       <c r="J54" t="s">
-        <v>238</v>
+        <v>100</v>
       </c>
       <c r="P54" t="s">
-        <v>239</v>
+        <v>101</v>
       </c>
       <c r="Q54" t="s">
-        <v>240</v>
+        <v>102</v>
       </c>
       <c r="R54" t="s">
-        <v>241</v>
+        <v>103</v>
       </c>
       <c r="S54" t="s">
-        <v>242</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -5394,43 +5828,43 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>258</v>
+        <v>120</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>121</v>
       </c>
       <c r="D55">
         <v>2026</v>
       </c>
       <c r="E55">
-        <v>8</v>
-      </c>
-      <c r="F55">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="F55" t="s">
+        <v>44</v>
       </c>
       <c r="G55" t="s">
-        <v>260</v>
+        <v>122</v>
       </c>
       <c r="H55" t="s">
-        <v>261</v>
+        <v>123</v>
       </c>
       <c r="I55" t="s">
-        <v>262</v>
+        <v>124</v>
       </c>
       <c r="J55" t="s">
-        <v>263</v>
+        <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>264</v>
+        <v>126</v>
       </c>
       <c r="Q55" t="s">
-        <v>265</v>
+        <v>127</v>
       </c>
       <c r="R55" t="s">
-        <v>266</v>
+        <v>128</v>
       </c>
       <c r="S55" t="s">
-        <v>267</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -5438,43 +5872,43 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>559</v>
+        <v>104</v>
       </c>
       <c r="C56" t="s">
-        <v>560</v>
+        <v>105</v>
       </c>
       <c r="D56">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E56">
-        <v>6</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="F56" t="s">
+        <v>106</v>
       </c>
       <c r="G56" t="s">
-        <v>561</v>
+        <v>107</v>
       </c>
       <c r="H56" t="s">
-        <v>562</v>
+        <v>108</v>
       </c>
       <c r="I56" t="s">
-        <v>563</v>
+        <v>109</v>
       </c>
       <c r="J56" t="s">
-        <v>564</v>
+        <v>110</v>
       </c>
       <c r="P56" t="s">
-        <v>565</v>
+        <v>111</v>
       </c>
       <c r="Q56" t="s">
-        <v>566</v>
+        <v>112</v>
       </c>
       <c r="R56" t="s">
-        <v>567</v>
+        <v>113</v>
       </c>
       <c r="S56" t="s">
-        <v>568</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -5482,43 +5916,43 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="C57" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="D57">
         <v>2025</v>
       </c>
       <c r="E57">
-        <v>20</v>
-      </c>
-      <c r="F57">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="F57" t="s">
+        <v>75</v>
       </c>
       <c r="G57" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="H57" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="I57" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="J57" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="P57" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
       <c r="Q57" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="R57" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="S57" t="s">
-        <v>30</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5526,43 +5960,43 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="C58" t="s">
-        <v>102</v>
+        <v>160</v>
       </c>
       <c r="D58">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="E58">
-        <v>15</v>
-      </c>
-      <c r="F58">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="F58" t="s">
+        <v>44</v>
       </c>
       <c r="G58" t="s">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="H58" t="s">
-        <v>104</v>
+        <v>162</v>
       </c>
       <c r="I58" t="s">
-        <v>105</v>
+        <v>163</v>
       </c>
       <c r="J58" t="s">
-        <v>106</v>
-      </c>
-      <c r="K58" t="s">
-        <v>107</v>
-      </c>
-      <c r="L58" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="P58" t="s">
-        <v>109</v>
-      </c>
-      <c r="U58" t="s">
-        <v>110</v>
+        <v>165</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>166</v>
+      </c>
+      <c r="R58" t="s">
+        <v>167</v>
+      </c>
+      <c r="S58" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5570,43 +6004,43 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>312</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>313</v>
       </c>
       <c r="D59">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E59">
-        <v>16</v>
-      </c>
-      <c r="F59">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="F59" t="s">
+        <v>106</v>
       </c>
       <c r="G59" t="s">
-        <v>103</v>
+        <v>314</v>
       </c>
       <c r="H59" t="s">
-        <v>104</v>
+        <v>315</v>
       </c>
       <c r="I59" t="s">
-        <v>113</v>
+        <v>316</v>
       </c>
       <c r="J59" t="s">
-        <v>114</v>
-      </c>
-      <c r="K59" t="s">
-        <v>107</v>
-      </c>
-      <c r="L59" t="s">
-        <v>108</v>
+        <v>317</v>
       </c>
       <c r="P59" t="s">
-        <v>115</v>
-      </c>
-      <c r="U59" t="s">
-        <v>110</v>
+        <v>318</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>319</v>
+      </c>
+      <c r="R59" t="s">
+        <v>320</v>
+      </c>
+      <c r="S59" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5614,40 +6048,43 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C60" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D60">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="E60">
-        <v>3</v>
-      </c>
-      <c r="F60">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="F60" t="s">
+        <v>44</v>
       </c>
       <c r="G60" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H60" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I60" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J60" t="s">
-        <v>133</v>
-      </c>
-      <c r="K60" t="s">
-        <v>134</v>
-      </c>
-      <c r="L60" t="s">
         <v>135</v>
       </c>
       <c r="P60" t="s">
         <v>136</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>137</v>
+      </c>
+      <c r="R60" t="s">
+        <v>138</v>
+      </c>
+      <c r="S60" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5655,40 +6092,43 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D61">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="E61">
-        <v>8</v>
-      </c>
-      <c r="F61">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="F61" t="s">
+        <v>44</v>
       </c>
       <c r="G61" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="H61" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="I61" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J61" t="s">
-        <v>140</v>
-      </c>
-      <c r="K61" t="s">
-        <v>134</v>
-      </c>
-      <c r="L61" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="P61" t="s">
-        <v>141</v>
+        <v>146</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>147</v>
+      </c>
+      <c r="R61" t="s">
+        <v>148</v>
+      </c>
+      <c r="S61" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5696,40 +6136,43 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>142</v>
+        <v>378</v>
       </c>
       <c r="C62" t="s">
-        <v>143</v>
+        <v>379</v>
       </c>
       <c r="D62">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E62">
-        <v>10</v>
-      </c>
-      <c r="F62">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F62" t="s">
+        <v>44</v>
       </c>
       <c r="G62" t="s">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="H62" t="s">
-        <v>131</v>
+        <v>381</v>
       </c>
       <c r="I62" t="s">
-        <v>144</v>
+        <v>382</v>
       </c>
       <c r="J62" t="s">
-        <v>145</v>
-      </c>
-      <c r="K62" t="s">
-        <v>134</v>
-      </c>
-      <c r="L62" t="s">
-        <v>135</v>
+        <v>383</v>
       </c>
       <c r="P62" t="s">
-        <v>146</v>
+        <v>384</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>385</v>
+      </c>
+      <c r="R62" t="s">
+        <v>386</v>
+      </c>
+      <c r="S62" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5737,40 +6180,43 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>147</v>
+        <v>388</v>
       </c>
       <c r="C63" t="s">
-        <v>148</v>
+        <v>389</v>
       </c>
       <c r="D63">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="E63">
-        <v>6</v>
-      </c>
-      <c r="F63">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="F63" t="s">
+        <v>171</v>
       </c>
       <c r="G63" t="s">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="H63" t="s">
-        <v>131</v>
+        <v>391</v>
       </c>
       <c r="I63" t="s">
-        <v>149</v>
+        <v>392</v>
       </c>
       <c r="J63" t="s">
-        <v>150</v>
-      </c>
-      <c r="K63" t="s">
-        <v>134</v>
-      </c>
-      <c r="L63" t="s">
-        <v>135</v>
+        <v>393</v>
       </c>
       <c r="P63" t="s">
-        <v>151</v>
+        <v>394</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>395</v>
+      </c>
+      <c r="R63" t="s">
+        <v>396</v>
+      </c>
+      <c r="S63" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5778,40 +6224,43 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>152</v>
+        <v>397</v>
       </c>
       <c r="C64" t="s">
-        <v>153</v>
+        <v>398</v>
       </c>
       <c r="D64">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E64">
-        <v>10</v>
-      </c>
-      <c r="F64">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="F64" t="s">
+        <v>106</v>
       </c>
       <c r="G64" t="s">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="H64" t="s">
-        <v>131</v>
+        <v>391</v>
       </c>
       <c r="I64" t="s">
-        <v>154</v>
+        <v>399</v>
       </c>
       <c r="J64" t="s">
-        <v>155</v>
-      </c>
-      <c r="K64" t="s">
-        <v>134</v>
-      </c>
-      <c r="L64" t="s">
-        <v>135</v>
+        <v>400</v>
       </c>
       <c r="P64" t="s">
-        <v>156</v>
+        <v>401</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>395</v>
+      </c>
+      <c r="R64" t="s">
+        <v>396</v>
+      </c>
+      <c r="S64" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5819,40 +6268,43 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>157</v>
+        <v>332</v>
       </c>
       <c r="C65" t="s">
-        <v>158</v>
+        <v>333</v>
       </c>
       <c r="D65">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="E65">
-        <v>6</v>
-      </c>
-      <c r="F65">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="F65" t="s">
+        <v>334</v>
       </c>
       <c r="G65" t="s">
-        <v>130</v>
+        <v>335</v>
       </c>
       <c r="H65" t="s">
-        <v>131</v>
+        <v>336</v>
       </c>
       <c r="I65" t="s">
-        <v>159</v>
+        <v>337</v>
       </c>
       <c r="J65" t="s">
-        <v>160</v>
-      </c>
-      <c r="K65" t="s">
-        <v>134</v>
-      </c>
-      <c r="L65" t="s">
-        <v>135</v>
+        <v>338</v>
       </c>
       <c r="P65" t="s">
-        <v>161</v>
+        <v>339</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>340</v>
+      </c>
+      <c r="R65" t="s">
+        <v>341</v>
+      </c>
+      <c r="S65" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5860,40 +6312,43 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>162</v>
+        <v>343</v>
       </c>
       <c r="C66" t="s">
-        <v>163</v>
+        <v>344</v>
       </c>
       <c r="D66">
         <v>2025</v>
       </c>
       <c r="E66">
-        <v>10</v>
-      </c>
-      <c r="F66">
-        <v>3</v>
+        <v>24</v>
+      </c>
+      <c r="F66" t="s">
+        <v>44</v>
       </c>
       <c r="G66" t="s">
-        <v>130</v>
+        <v>345</v>
       </c>
       <c r="H66" t="s">
-        <v>131</v>
+        <v>346</v>
       </c>
       <c r="I66" t="s">
-        <v>164</v>
+        <v>347</v>
       </c>
       <c r="J66" t="s">
-        <v>165</v>
-      </c>
-      <c r="K66" t="s">
-        <v>134</v>
-      </c>
-      <c r="L66" t="s">
-        <v>135</v>
+        <v>348</v>
       </c>
       <c r="P66" t="s">
-        <v>166</v>
+        <v>349</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>350</v>
+      </c>
+      <c r="R66" t="s">
+        <v>351</v>
+      </c>
+      <c r="S66" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5901,40 +6356,43 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>167</v>
+        <v>368</v>
       </c>
       <c r="C67" t="s">
-        <v>168</v>
+        <v>369</v>
       </c>
       <c r="D67">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="E67">
-        <v>6</v>
-      </c>
-      <c r="F67">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="F67" t="s">
+        <v>44</v>
       </c>
       <c r="G67" t="s">
-        <v>130</v>
+        <v>370</v>
       </c>
       <c r="H67" t="s">
-        <v>131</v>
+        <v>371</v>
       </c>
       <c r="I67" t="s">
-        <v>169</v>
+        <v>372</v>
       </c>
       <c r="J67" t="s">
-        <v>170</v>
-      </c>
-      <c r="K67" t="s">
-        <v>134</v>
-      </c>
-      <c r="L67" t="s">
-        <v>135</v>
+        <v>373</v>
       </c>
       <c r="P67" t="s">
-        <v>171</v>
+        <v>374</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>375</v>
+      </c>
+      <c r="R67" t="s">
+        <v>376</v>
+      </c>
+      <c r="S67" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5942,40 +6400,43 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>172</v>
+        <v>703</v>
       </c>
       <c r="C68" t="s">
-        <v>173</v>
+        <v>704</v>
       </c>
       <c r="D68">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="E68">
         <v>6</v>
       </c>
-      <c r="F68">
-        <v>1</v>
+      <c r="F68" t="s">
+        <v>44</v>
       </c>
       <c r="G68" t="s">
-        <v>130</v>
+        <v>705</v>
       </c>
       <c r="H68" t="s">
-        <v>131</v>
+        <v>706</v>
       </c>
       <c r="I68" t="s">
-        <v>174</v>
+        <v>707</v>
       </c>
       <c r="J68" t="s">
-        <v>175</v>
-      </c>
-      <c r="K68" t="s">
-        <v>134</v>
-      </c>
-      <c r="L68" t="s">
-        <v>135</v>
+        <v>708</v>
       </c>
       <c r="P68" t="s">
-        <v>176</v>
+        <v>709</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>710</v>
+      </c>
+      <c r="R68" t="s">
+        <v>711</v>
+      </c>
+      <c r="S68" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5983,46 +6444,43 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
       <c r="C69" t="s">
-        <v>178</v>
+        <v>323</v>
       </c>
       <c r="D69">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="E69">
-        <v>6</v>
-      </c>
-      <c r="F69">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="F69" t="s">
+        <v>75</v>
       </c>
       <c r="G69" t="s">
-        <v>179</v>
+        <v>324</v>
       </c>
       <c r="H69" t="s">
-        <v>180</v>
+        <v>325</v>
       </c>
       <c r="I69" t="s">
-        <v>181</v>
+        <v>326</v>
       </c>
       <c r="J69" t="s">
-        <v>182</v>
-      </c>
-      <c r="K69" t="s">
-        <v>107</v>
-      </c>
-      <c r="L69" t="s">
-        <v>183</v>
-      </c>
-      <c r="M69" t="s">
-        <v>184</v>
+        <v>327</v>
       </c>
       <c r="P69" t="s">
-        <v>185</v>
-      </c>
-      <c r="U69" t="s">
-        <v>186</v>
+        <v>328</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>329</v>
+      </c>
+      <c r="R69" t="s">
+        <v>330</v>
+      </c>
+      <c r="S69" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -6030,43 +6488,43 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>187</v>
+        <v>402</v>
       </c>
       <c r="C70" t="s">
-        <v>188</v>
+        <v>403</v>
       </c>
       <c r="D70">
         <v>2025</v>
       </c>
       <c r="E70">
-        <v>14</v>
-      </c>
-      <c r="F70">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F70" t="s">
+        <v>75</v>
       </c>
       <c r="G70" t="s">
-        <v>179</v>
+        <v>404</v>
       </c>
       <c r="H70" t="s">
-        <v>180</v>
+        <v>405</v>
       </c>
       <c r="I70" t="s">
-        <v>189</v>
+        <v>406</v>
       </c>
       <c r="J70" t="s">
-        <v>190</v>
-      </c>
-      <c r="K70" t="s">
-        <v>107</v>
-      </c>
-      <c r="L70" t="s">
-        <v>183</v>
+        <v>407</v>
       </c>
       <c r="P70" t="s">
-        <v>191</v>
-      </c>
-      <c r="U70" t="s">
-        <v>186</v>
+        <v>408</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>409</v>
+      </c>
+      <c r="R70" t="s">
+        <v>410</v>
+      </c>
+      <c r="S70" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -6074,46 +6532,43 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="C71" t="s">
-        <v>193</v>
+        <v>22</v>
       </c>
       <c r="D71">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E71">
-        <v>8</v>
-      </c>
-      <c r="F71">
-        <v>2</v>
+        <v>41</v>
+      </c>
+      <c r="F71" t="s">
+        <v>23</v>
       </c>
       <c r="G71" t="s">
-        <v>194</v>
+        <v>24</v>
       </c>
       <c r="H71" t="s">
-        <v>195</v>
+        <v>25</v>
       </c>
       <c r="I71" t="s">
-        <v>196</v>
+        <v>26</v>
       </c>
       <c r="J71" t="s">
-        <v>197</v>
-      </c>
-      <c r="K71" t="s">
-        <v>107</v>
-      </c>
-      <c r="L71" t="s">
-        <v>198</v>
-      </c>
-      <c r="M71" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="P71" t="s">
-        <v>200</v>
-      </c>
-      <c r="U71" t="s">
-        <v>201</v>
+        <v>27</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>28</v>
+      </c>
+      <c r="R71" t="s">
+        <v>29</v>
+      </c>
+      <c r="S71" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -6121,46 +6576,43 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>202</v>
+        <v>31</v>
       </c>
       <c r="C72" t="s">
-        <v>203</v>
+        <v>32</v>
       </c>
       <c r="D72">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="E72">
-        <v>4</v>
-      </c>
-      <c r="F72">
-        <v>2</v>
+        <v>20</v>
+      </c>
+      <c r="F72" t="s">
+        <v>33</v>
       </c>
       <c r="G72" t="s">
-        <v>194</v>
+        <v>34</v>
       </c>
       <c r="H72" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="I72" t="s">
-        <v>204</v>
+        <v>36</v>
       </c>
       <c r="J72" t="s">
-        <v>205</v>
-      </c>
-      <c r="K72" t="s">
-        <v>107</v>
-      </c>
-      <c r="L72" t="s">
-        <v>198</v>
-      </c>
-      <c r="M72" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="P72" t="s">
-        <v>206</v>
-      </c>
-      <c r="U72" t="s">
-        <v>201</v>
+        <v>38</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>39</v>
+      </c>
+      <c r="R72" t="s">
+        <v>40</v>
+      </c>
+      <c r="S72" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -6168,46 +6620,43 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="C73" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D73">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E73">
-        <v>6</v>
-      </c>
-      <c r="F73">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="F73" t="s">
+        <v>75</v>
       </c>
       <c r="G73" t="s">
+        <v>192</v>
+      </c>
+      <c r="H73" t="s">
+        <v>193</v>
+      </c>
+      <c r="I73" t="s">
         <v>194</v>
       </c>
-      <c r="H73" t="s">
+      <c r="J73" t="s">
         <v>195</v>
       </c>
-      <c r="I73" t="s">
-        <v>209</v>
-      </c>
-      <c r="J73" t="s">
-        <v>210</v>
-      </c>
       <c r="K73" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L73" t="s">
+        <v>197</v>
+      </c>
+      <c r="P73" t="s">
         <v>198</v>
       </c>
-      <c r="M73" t="s">
-        <v>211</v>
-      </c>
-      <c r="P73" t="s">
-        <v>212</v>
-      </c>
       <c r="U73" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -6215,43 +6664,43 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="C74" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="D74">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E74">
-        <v>10</v>
-      </c>
-      <c r="F74">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="F74" t="s">
+        <v>181</v>
       </c>
       <c r="G74" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H74" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I74" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="J74" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="K74" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L74" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P74" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="U74" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6259,43 +6708,40 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>217</v>
+      </c>
+      <c r="C75" t="s">
         <v>218</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75">
+        <v>2018</v>
+      </c>
+      <c r="E75">
+        <v>3</v>
+      </c>
+      <c r="F75" t="s">
+        <v>181</v>
+      </c>
+      <c r="G75" t="s">
         <v>219</v>
       </c>
-      <c r="D75">
-        <v>2020</v>
-      </c>
-      <c r="E75">
-        <v>5</v>
-      </c>
-      <c r="F75">
-        <v>2</v>
-      </c>
-      <c r="G75" t="s">
-        <v>194</v>
-      </c>
       <c r="H75" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="I75" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J75" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K75" t="s">
-        <v>107</v>
+        <v>223</v>
       </c>
       <c r="L75" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="P75" t="s">
-        <v>222</v>
-      </c>
-      <c r="U75" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6303,43 +6749,40 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="C76" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="D76">
         <v>2023</v>
       </c>
       <c r="E76">
-        <v>6</v>
-      </c>
-      <c r="F76">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="F76" t="s">
+        <v>44</v>
       </c>
       <c r="G76" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="H76" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="I76" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="J76" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="K76" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="L76" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="P76" t="s">
-        <v>251</v>
-      </c>
-      <c r="U76" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6347,43 +6790,40 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="C77" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="D77">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="E77">
-        <v>5</v>
-      </c>
-      <c r="F77">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="F77" t="s">
+        <v>75</v>
       </c>
       <c r="G77" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="H77" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="I77" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="J77" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="K77" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="L77" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="P77" t="s">
-        <v>257</v>
-      </c>
-      <c r="U77" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6391,43 +6831,40 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="C78" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="D78">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E78">
         <v>6</v>
       </c>
-      <c r="F78">
-        <v>2</v>
+      <c r="F78" t="s">
+        <v>75</v>
       </c>
       <c r="G78" t="s">
-        <v>270</v>
+        <v>219</v>
       </c>
       <c r="H78" t="s">
-        <v>271</v>
+        <v>220</v>
       </c>
       <c r="I78" t="s">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="J78" t="s">
-        <v>273</v>
+        <v>239</v>
       </c>
       <c r="K78" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="L78" t="s">
-        <v>274</v>
+        <v>224</v>
       </c>
       <c r="P78" t="s">
-        <v>275</v>
-      </c>
-      <c r="U78" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6435,40 +6872,40 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
       <c r="C79" t="s">
-        <v>278</v>
+        <v>242</v>
       </c>
       <c r="D79">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E79">
-        <v>5</v>
-      </c>
-      <c r="F79">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="F79" t="s">
+        <v>44</v>
       </c>
       <c r="G79" t="s">
-        <v>279</v>
+        <v>219</v>
       </c>
       <c r="H79" t="s">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="I79" t="s">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="J79" t="s">
-        <v>282</v>
+        <v>244</v>
       </c>
       <c r="K79" t="s">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="L79" t="s">
-        <v>283</v>
+        <v>224</v>
       </c>
       <c r="P79" t="s">
-        <v>284</v>
+        <v>245</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6476,43 +6913,40 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>503</v>
+        <v>246</v>
       </c>
       <c r="C80" t="s">
-        <v>504</v>
+        <v>247</v>
       </c>
       <c r="D80">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E80">
-        <v>4</v>
-      </c>
-      <c r="F80">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F80" t="s">
+        <v>181</v>
       </c>
       <c r="G80" t="s">
-        <v>505</v>
+        <v>219</v>
       </c>
       <c r="H80" t="s">
-        <v>506</v>
+        <v>220</v>
       </c>
       <c r="I80" t="s">
-        <v>507</v>
+        <v>248</v>
       </c>
       <c r="J80" t="s">
-        <v>508</v>
+        <v>249</v>
       </c>
       <c r="K80" t="s">
-        <v>107</v>
+        <v>223</v>
       </c>
       <c r="L80" t="s">
-        <v>509</v>
+        <v>224</v>
       </c>
       <c r="P80" t="s">
-        <v>510</v>
-      </c>
-      <c r="U80" t="s">
-        <v>511</v>
+        <v>250</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6520,43 +6954,40 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>512</v>
+        <v>251</v>
       </c>
       <c r="C81" t="s">
-        <v>513</v>
+        <v>252</v>
       </c>
       <c r="D81">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="E81">
-        <v>1</v>
-      </c>
-      <c r="F81">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="F81" t="s">
+        <v>75</v>
       </c>
       <c r="G81" t="s">
-        <v>505</v>
+        <v>219</v>
       </c>
       <c r="H81" t="s">
-        <v>506</v>
+        <v>220</v>
       </c>
       <c r="I81" t="s">
-        <v>514</v>
+        <v>253</v>
       </c>
       <c r="J81" t="s">
-        <v>515</v>
+        <v>254</v>
       </c>
       <c r="K81" t="s">
-        <v>107</v>
+        <v>223</v>
       </c>
       <c r="L81" t="s">
-        <v>509</v>
+        <v>224</v>
       </c>
       <c r="P81" t="s">
-        <v>516</v>
-      </c>
-      <c r="U81" t="s">
-        <v>511</v>
+        <v>255</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6564,43 +6995,40 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>517</v>
+        <v>256</v>
       </c>
       <c r="C82" t="s">
-        <v>518</v>
+        <v>257</v>
       </c>
       <c r="D82">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E82">
-        <v>5</v>
-      </c>
-      <c r="F82">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F82" t="s">
+        <v>44</v>
       </c>
       <c r="G82" t="s">
-        <v>505</v>
+        <v>219</v>
       </c>
       <c r="H82" t="s">
-        <v>506</v>
+        <v>220</v>
       </c>
       <c r="I82" t="s">
-        <v>519</v>
+        <v>258</v>
       </c>
       <c r="J82" t="s">
-        <v>520</v>
+        <v>259</v>
       </c>
       <c r="K82" t="s">
-        <v>107</v>
+        <v>223</v>
       </c>
       <c r="L82" t="s">
-        <v>509</v>
+        <v>224</v>
       </c>
       <c r="P82" t="s">
-        <v>521</v>
-      </c>
-      <c r="U82" t="s">
-        <v>511</v>
+        <v>260</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6608,43 +7036,40 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>522</v>
+        <v>261</v>
       </c>
       <c r="C83" t="s">
-        <v>523</v>
+        <v>262</v>
       </c>
       <c r="D83">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E83">
         <v>6</v>
       </c>
-      <c r="F83">
-        <v>2</v>
+      <c r="F83" t="s">
+        <v>44</v>
       </c>
       <c r="G83" t="s">
-        <v>524</v>
+        <v>219</v>
       </c>
       <c r="H83" t="s">
-        <v>525</v>
+        <v>220</v>
       </c>
       <c r="I83" t="s">
-        <v>526</v>
+        <v>263</v>
       </c>
       <c r="J83" t="s">
-        <v>523</v>
+        <v>264</v>
       </c>
       <c r="K83" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="L83" t="s">
-        <v>527</v>
+        <v>224</v>
       </c>
       <c r="P83" t="s">
-        <v>528</v>
-      </c>
-      <c r="U83" t="s">
-        <v>529</v>
+        <v>265</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6652,43 +7077,46 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>530</v>
+        <v>266</v>
       </c>
       <c r="C84" t="s">
-        <v>531</v>
+        <v>267</v>
       </c>
       <c r="D84">
-        <v>2026</v>
+        <v>2017</v>
       </c>
       <c r="E84">
         <v>6</v>
       </c>
-      <c r="F84">
-        <v>1</v>
+      <c r="F84" t="s">
+        <v>181</v>
       </c>
       <c r="G84" t="s">
-        <v>532</v>
+        <v>268</v>
       </c>
       <c r="H84" t="s">
-        <v>533</v>
+        <v>269</v>
       </c>
       <c r="I84" t="s">
-        <v>534</v>
+        <v>270</v>
       </c>
       <c r="J84" t="s">
-        <v>535</v>
+        <v>271</v>
       </c>
       <c r="K84" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L84" t="s">
-        <v>536</v>
+        <v>272</v>
+      </c>
+      <c r="M84" t="s">
+        <v>273</v>
       </c>
       <c r="P84" t="s">
-        <v>537</v>
+        <v>274</v>
       </c>
       <c r="U84" t="s">
-        <v>538</v>
+        <v>275</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6696,43 +7124,43 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>539</v>
+        <v>276</v>
       </c>
       <c r="C85" t="s">
-        <v>540</v>
+        <v>277</v>
       </c>
       <c r="D85">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E85">
-        <v>3</v>
-      </c>
-      <c r="F85">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="F85" t="s">
+        <v>44</v>
       </c>
       <c r="G85" t="s">
-        <v>532</v>
+        <v>268</v>
       </c>
       <c r="H85" t="s">
-        <v>533</v>
+        <v>269</v>
       </c>
       <c r="I85" t="s">
-        <v>541</v>
+        <v>278</v>
       </c>
       <c r="J85" t="s">
-        <v>542</v>
+        <v>279</v>
       </c>
       <c r="K85" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L85" t="s">
-        <v>536</v>
+        <v>272</v>
       </c>
       <c r="P85" t="s">
-        <v>543</v>
+        <v>280</v>
       </c>
       <c r="U85" t="s">
-        <v>538</v>
+        <v>275</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6740,43 +7168,46 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>544</v>
+        <v>281</v>
       </c>
       <c r="C86" t="s">
-        <v>545</v>
+        <v>282</v>
       </c>
       <c r="D86">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E86">
-        <v>4</v>
-      </c>
-      <c r="F86">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="F86" t="s">
+        <v>181</v>
       </c>
       <c r="G86" t="s">
-        <v>532</v>
+        <v>283</v>
       </c>
       <c r="H86" t="s">
-        <v>533</v>
+        <v>284</v>
       </c>
       <c r="I86" t="s">
-        <v>546</v>
+        <v>285</v>
       </c>
       <c r="J86" t="s">
-        <v>547</v>
+        <v>286</v>
       </c>
       <c r="K86" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L86" t="s">
-        <v>536</v>
+        <v>287</v>
+      </c>
+      <c r="M86" t="s">
+        <v>288</v>
       </c>
       <c r="P86" t="s">
-        <v>548</v>
+        <v>289</v>
       </c>
       <c r="U86" t="s">
-        <v>538</v>
+        <v>290</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6784,40 +7215,46 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>549</v>
+        <v>291</v>
       </c>
       <c r="C87" t="s">
-        <v>550</v>
+        <v>292</v>
       </c>
       <c r="D87">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="E87">
         <v>4</v>
       </c>
-      <c r="F87">
-        <v>1</v>
+      <c r="F87" t="s">
+        <v>181</v>
       </c>
       <c r="G87" t="s">
-        <v>532</v>
+        <v>283</v>
       </c>
       <c r="H87" t="s">
-        <v>533</v>
+        <v>284</v>
       </c>
       <c r="I87" t="s">
-        <v>551</v>
+        <v>293</v>
       </c>
       <c r="J87" t="s">
-        <v>552</v>
+        <v>294</v>
       </c>
       <c r="K87" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L87" t="s">
-        <v>536</v>
+        <v>287</v>
+      </c>
+      <c r="M87" t="s">
+        <v>273</v>
       </c>
       <c r="P87" t="s">
-        <v>553</v>
+        <v>295</v>
+      </c>
+      <c r="U87" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6825,40 +7262,46 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>554</v>
+        <v>296</v>
       </c>
       <c r="C88" t="s">
-        <v>555</v>
+        <v>297</v>
       </c>
       <c r="D88">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E88">
-        <v>5</v>
-      </c>
-      <c r="F88">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F88" t="s">
+        <v>181</v>
       </c>
       <c r="G88" t="s">
-        <v>532</v>
+        <v>283</v>
       </c>
       <c r="H88" t="s">
-        <v>533</v>
+        <v>284</v>
       </c>
       <c r="I88" t="s">
-        <v>556</v>
+        <v>298</v>
       </c>
       <c r="J88" t="s">
-        <v>557</v>
+        <v>299</v>
       </c>
       <c r="K88" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L88" t="s">
-        <v>536</v>
+        <v>287</v>
+      </c>
+      <c r="M88" t="s">
+        <v>300</v>
       </c>
       <c r="P88" t="s">
-        <v>558</v>
+        <v>301</v>
+      </c>
+      <c r="U88" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6866,43 +7309,43 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>569</v>
+        <v>302</v>
       </c>
       <c r="C89" t="s">
-        <v>570</v>
+        <v>303</v>
       </c>
       <c r="D89">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="E89">
-        <v>1</v>
-      </c>
-      <c r="F89">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="F89" t="s">
+        <v>44</v>
       </c>
       <c r="G89" t="s">
-        <v>571</v>
+        <v>283</v>
       </c>
       <c r="H89" t="s">
-        <v>572</v>
+        <v>284</v>
       </c>
       <c r="I89" t="s">
-        <v>573</v>
+        <v>304</v>
       </c>
       <c r="J89" t="s">
-        <v>574</v>
+        <v>305</v>
       </c>
       <c r="K89" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L89" t="s">
-        <v>575</v>
+        <v>287</v>
       </c>
       <c r="P89" t="s">
-        <v>576</v>
+        <v>306</v>
       </c>
       <c r="U89" t="s">
-        <v>577</v>
+        <v>290</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6910,43 +7353,43 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>578</v>
+        <v>307</v>
       </c>
       <c r="C90" t="s">
-        <v>579</v>
+        <v>308</v>
       </c>
       <c r="D90">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="E90">
-        <v>3</v>
-      </c>
-      <c r="F90">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F90" t="s">
+        <v>181</v>
       </c>
       <c r="G90" t="s">
-        <v>571</v>
+        <v>283</v>
       </c>
       <c r="H90" t="s">
-        <v>572</v>
+        <v>284</v>
       </c>
       <c r="I90" t="s">
-        <v>580</v>
+        <v>309</v>
       </c>
       <c r="J90" t="s">
-        <v>581</v>
+        <v>310</v>
       </c>
       <c r="K90" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L90" t="s">
-        <v>575</v>
+        <v>287</v>
       </c>
       <c r="P90" t="s">
-        <v>582</v>
+        <v>311</v>
       </c>
       <c r="U90" t="s">
-        <v>577</v>
+        <v>290</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
@@ -6954,43 +7397,43 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>583</v>
+        <v>353</v>
       </c>
       <c r="C91" t="s">
-        <v>584</v>
+        <v>354</v>
       </c>
       <c r="D91">
         <v>2023</v>
       </c>
       <c r="E91">
-        <v>3</v>
-      </c>
-      <c r="F91">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="F91" t="s">
+        <v>181</v>
       </c>
       <c r="G91" t="s">
-        <v>571</v>
+        <v>355</v>
       </c>
       <c r="H91" t="s">
-        <v>572</v>
+        <v>356</v>
       </c>
       <c r="I91" t="s">
-        <v>585</v>
+        <v>357</v>
       </c>
       <c r="J91" t="s">
-        <v>586</v>
+        <v>358</v>
       </c>
       <c r="K91" t="s">
-        <v>107</v>
+        <v>359</v>
       </c>
       <c r="L91" t="s">
-        <v>575</v>
+        <v>360</v>
       </c>
       <c r="P91" t="s">
-        <v>587</v>
+        <v>361</v>
       </c>
       <c r="U91" t="s">
-        <v>577</v>
+        <v>362</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6998,43 +7441,43 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>588</v>
+        <v>363</v>
       </c>
       <c r="C92" t="s">
-        <v>589</v>
+        <v>364</v>
       </c>
       <c r="D92">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E92">
-        <v>4</v>
-      </c>
-      <c r="F92">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F92" t="s">
+        <v>44</v>
       </c>
       <c r="G92" t="s">
-        <v>571</v>
+        <v>355</v>
       </c>
       <c r="H92" t="s">
-        <v>572</v>
+        <v>356</v>
       </c>
       <c r="I92" t="s">
-        <v>590</v>
+        <v>365</v>
       </c>
       <c r="J92" t="s">
-        <v>591</v>
+        <v>366</v>
       </c>
       <c r="K92" t="s">
-        <v>107</v>
+        <v>359</v>
       </c>
       <c r="L92" t="s">
-        <v>575</v>
+        <v>360</v>
       </c>
       <c r="P92" t="s">
-        <v>592</v>
+        <v>367</v>
       </c>
       <c r="U92" t="s">
-        <v>577</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7042,43 +7485,43 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>593</v>
+        <v>412</v>
       </c>
       <c r="C93" t="s">
-        <v>594</v>
+        <v>413</v>
       </c>
       <c r="D93">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E93">
-        <v>4</v>
-      </c>
-      <c r="F93">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F93" t="s">
+        <v>181</v>
       </c>
       <c r="G93" t="s">
-        <v>571</v>
+        <v>414</v>
       </c>
       <c r="H93" t="s">
-        <v>572</v>
+        <v>415</v>
       </c>
       <c r="I93" t="s">
-        <v>595</v>
+        <v>416</v>
       </c>
       <c r="J93" t="s">
-        <v>596</v>
+        <v>417</v>
       </c>
       <c r="K93" t="s">
-        <v>107</v>
+        <v>359</v>
       </c>
       <c r="L93" t="s">
-        <v>575</v>
+        <v>418</v>
       </c>
       <c r="P93" t="s">
-        <v>597</v>
+        <v>419</v>
       </c>
       <c r="U93" t="s">
-        <v>577</v>
+        <v>420</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7086,43 +7529,40 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>598</v>
+        <v>421</v>
       </c>
       <c r="C94" t="s">
-        <v>599</v>
+        <v>422</v>
       </c>
       <c r="D94">
         <v>2024</v>
       </c>
       <c r="E94">
-        <v>4</v>
-      </c>
-      <c r="F94">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F94" t="s">
+        <v>181</v>
       </c>
       <c r="G94" t="s">
-        <v>571</v>
+        <v>423</v>
       </c>
       <c r="H94" t="s">
-        <v>572</v>
+        <v>424</v>
       </c>
       <c r="I94" t="s">
-        <v>600</v>
+        <v>425</v>
       </c>
       <c r="J94" t="s">
-        <v>601</v>
+        <v>426</v>
       </c>
       <c r="K94" t="s">
-        <v>107</v>
+        <v>223</v>
       </c>
       <c r="L94" t="s">
-        <v>575</v>
+        <v>427</v>
       </c>
       <c r="P94" t="s">
-        <v>602</v>
-      </c>
-      <c r="U94" t="s">
-        <v>577</v>
+        <v>428</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7130,43 +7570,43 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>603</v>
+        <v>647</v>
       </c>
       <c r="C95" t="s">
-        <v>604</v>
+        <v>648</v>
       </c>
       <c r="D95">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E95">
         <v>4</v>
       </c>
-      <c r="F95">
-        <v>3</v>
+      <c r="F95" t="s">
+        <v>44</v>
       </c>
       <c r="G95" t="s">
-        <v>571</v>
+        <v>649</v>
       </c>
       <c r="H95" t="s">
-        <v>572</v>
+        <v>650</v>
       </c>
       <c r="I95" t="s">
-        <v>605</v>
+        <v>651</v>
       </c>
       <c r="J95" t="s">
-        <v>606</v>
+        <v>652</v>
       </c>
       <c r="K95" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L95" t="s">
-        <v>575</v>
+        <v>653</v>
       </c>
       <c r="P95" t="s">
-        <v>607</v>
+        <v>654</v>
       </c>
       <c r="U95" t="s">
-        <v>577</v>
+        <v>655</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7174,43 +7614,43 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>608</v>
+        <v>656</v>
       </c>
       <c r="C96" t="s">
-        <v>609</v>
+        <v>657</v>
       </c>
       <c r="D96">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="E96">
-        <v>4</v>
-      </c>
-      <c r="F96">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F96" t="s">
+        <v>181</v>
       </c>
       <c r="G96" t="s">
-        <v>571</v>
+        <v>649</v>
       </c>
       <c r="H96" t="s">
-        <v>572</v>
+        <v>650</v>
       </c>
       <c r="I96" t="s">
-        <v>610</v>
+        <v>658</v>
       </c>
       <c r="J96" t="s">
-        <v>611</v>
+        <v>659</v>
       </c>
       <c r="K96" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L96" t="s">
-        <v>575</v>
+        <v>653</v>
       </c>
       <c r="P96" t="s">
-        <v>612</v>
+        <v>660</v>
       </c>
       <c r="U96" t="s">
-        <v>577</v>
+        <v>655</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7218,43 +7658,43 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>613</v>
+        <v>661</v>
       </c>
       <c r="C97" t="s">
-        <v>614</v>
+        <v>662</v>
       </c>
       <c r="D97">
         <v>2024</v>
       </c>
       <c r="E97">
-        <v>4</v>
-      </c>
-      <c r="F97">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F97" t="s">
+        <v>44</v>
       </c>
       <c r="G97" t="s">
-        <v>571</v>
+        <v>649</v>
       </c>
       <c r="H97" t="s">
-        <v>572</v>
+        <v>650</v>
       </c>
       <c r="I97" t="s">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="J97" t="s">
-        <v>616</v>
+        <v>664</v>
       </c>
       <c r="K97" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L97" t="s">
-        <v>575</v>
+        <v>653</v>
       </c>
       <c r="P97" t="s">
-        <v>617</v>
+        <v>665</v>
       </c>
       <c r="U97" t="s">
-        <v>577</v>
+        <v>655</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7262,43 +7702,43 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>618</v>
+        <v>666</v>
       </c>
       <c r="C98" t="s">
-        <v>619</v>
+        <v>667</v>
       </c>
       <c r="D98">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E98">
-        <v>4</v>
-      </c>
-      <c r="F98">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="F98" t="s">
+        <v>181</v>
       </c>
       <c r="G98" t="s">
-        <v>571</v>
+        <v>668</v>
       </c>
       <c r="H98" t="s">
-        <v>572</v>
+        <v>669</v>
       </c>
       <c r="I98" t="s">
-        <v>620</v>
+        <v>670</v>
       </c>
       <c r="J98" t="s">
-        <v>621</v>
+        <v>667</v>
       </c>
       <c r="K98" t="s">
-        <v>107</v>
+        <v>359</v>
       </c>
       <c r="L98" t="s">
-        <v>575</v>
+        <v>671</v>
       </c>
       <c r="P98" t="s">
-        <v>622</v>
+        <v>672</v>
       </c>
       <c r="U98" t="s">
-        <v>577</v>
+        <v>673</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7306,43 +7746,43 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>623</v>
+        <v>674</v>
       </c>
       <c r="C99" t="s">
-        <v>624</v>
+        <v>675</v>
       </c>
       <c r="D99">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="E99">
-        <v>4</v>
-      </c>
-      <c r="F99">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="F99" t="s">
+        <v>44</v>
       </c>
       <c r="G99" t="s">
-        <v>571</v>
+        <v>676</v>
       </c>
       <c r="H99" t="s">
-        <v>572</v>
+        <v>677</v>
       </c>
       <c r="I99" t="s">
-        <v>625</v>
+        <v>678</v>
       </c>
       <c r="J99" t="s">
-        <v>626</v>
+        <v>679</v>
       </c>
       <c r="K99" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L99" t="s">
-        <v>575</v>
+        <v>680</v>
       </c>
       <c r="P99" t="s">
-        <v>627</v>
+        <v>681</v>
       </c>
       <c r="U99" t="s">
-        <v>577</v>
+        <v>682</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -7350,43 +7790,43 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>628</v>
+        <v>683</v>
       </c>
       <c r="C100" t="s">
-        <v>629</v>
+        <v>684</v>
       </c>
       <c r="D100">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E100">
-        <v>4</v>
-      </c>
-      <c r="F100">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F100" t="s">
+        <v>181</v>
       </c>
       <c r="G100" t="s">
-        <v>571</v>
+        <v>676</v>
       </c>
       <c r="H100" t="s">
-        <v>572</v>
+        <v>677</v>
       </c>
       <c r="I100" t="s">
-        <v>630</v>
+        <v>685</v>
       </c>
       <c r="J100" t="s">
-        <v>631</v>
+        <v>686</v>
       </c>
       <c r="K100" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L100" t="s">
-        <v>575</v>
+        <v>680</v>
       </c>
       <c r="P100" t="s">
-        <v>632</v>
+        <v>687</v>
       </c>
       <c r="U100" t="s">
-        <v>577</v>
+        <v>682</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7394,10 +7834,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>633</v>
+        <v>688</v>
       </c>
       <c r="C101" t="s">
-        <v>634</v>
+        <v>689</v>
       </c>
       <c r="D101">
         <v>2024</v>
@@ -7405,32 +7845,32 @@
       <c r="E101">
         <v>4</v>
       </c>
-      <c r="F101">
-        <v>4</v>
+      <c r="F101" t="s">
+        <v>44</v>
       </c>
       <c r="G101" t="s">
-        <v>571</v>
+        <v>676</v>
       </c>
       <c r="H101" t="s">
-        <v>572</v>
+        <v>677</v>
       </c>
       <c r="I101" t="s">
-        <v>635</v>
+        <v>690</v>
       </c>
       <c r="J101" t="s">
-        <v>636</v>
+        <v>691</v>
       </c>
       <c r="K101" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L101" t="s">
-        <v>575</v>
+        <v>680</v>
       </c>
       <c r="P101" t="s">
-        <v>637</v>
+        <v>692</v>
       </c>
       <c r="U101" t="s">
-        <v>577</v>
+        <v>682</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7438,10 +7878,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>638</v>
+        <v>693</v>
       </c>
       <c r="C102" t="s">
-        <v>639</v>
+        <v>694</v>
       </c>
       <c r="D102">
         <v>2024</v>
@@ -7449,32 +7889,29 @@
       <c r="E102">
         <v>4</v>
       </c>
-      <c r="F102">
-        <v>4</v>
+      <c r="F102" t="s">
+        <v>44</v>
       </c>
       <c r="G102" t="s">
-        <v>571</v>
+        <v>676</v>
       </c>
       <c r="H102" t="s">
-        <v>572</v>
+        <v>677</v>
       </c>
       <c r="I102" t="s">
-        <v>640</v>
+        <v>695</v>
       </c>
       <c r="J102" t="s">
-        <v>641</v>
+        <v>696</v>
       </c>
       <c r="K102" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L102" t="s">
-        <v>575</v>
+        <v>680</v>
       </c>
       <c r="P102" t="s">
-        <v>642</v>
-      </c>
-      <c r="U102" t="s">
-        <v>577</v>
+        <v>697</v>
       </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
@@ -7482,43 +7919,40 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>643</v>
+        <v>698</v>
       </c>
       <c r="C103" t="s">
-        <v>644</v>
+        <v>699</v>
       </c>
       <c r="D103">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E103">
-        <v>4</v>
-      </c>
-      <c r="F103">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="F103" t="s">
+        <v>44</v>
       </c>
       <c r="G103" t="s">
-        <v>571</v>
+        <v>676</v>
       </c>
       <c r="H103" t="s">
-        <v>572</v>
+        <v>677</v>
       </c>
       <c r="I103" t="s">
-        <v>645</v>
+        <v>700</v>
       </c>
       <c r="J103" t="s">
-        <v>646</v>
+        <v>701</v>
       </c>
       <c r="K103" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L103" t="s">
-        <v>575</v>
+        <v>680</v>
       </c>
       <c r="P103" t="s">
-        <v>647</v>
-      </c>
-      <c r="U103" t="s">
-        <v>577</v>
+        <v>702</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -7526,43 +7960,43 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>648</v>
+        <v>713</v>
       </c>
       <c r="C104" t="s">
-        <v>649</v>
+        <v>714</v>
       </c>
       <c r="D104">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E104">
-        <v>4</v>
-      </c>
-      <c r="F104">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="F104" t="s">
+        <v>44</v>
       </c>
       <c r="G104" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H104" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I104" t="s">
-        <v>650</v>
+        <v>717</v>
       </c>
       <c r="J104" t="s">
-        <v>651</v>
+        <v>718</v>
       </c>
       <c r="K104" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L104" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P104" t="s">
-        <v>652</v>
+        <v>720</v>
       </c>
       <c r="U104" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7570,43 +8004,43 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>653</v>
+        <v>722</v>
       </c>
       <c r="C105" t="s">
-        <v>654</v>
+        <v>723</v>
       </c>
       <c r="D105">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E105">
-        <v>5</v>
-      </c>
-      <c r="F105">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F105" t="s">
+        <v>44</v>
       </c>
       <c r="G105" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H105" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I105" t="s">
-        <v>655</v>
+        <v>724</v>
       </c>
       <c r="J105" t="s">
-        <v>656</v>
+        <v>725</v>
       </c>
       <c r="K105" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L105" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P105" t="s">
-        <v>657</v>
+        <v>726</v>
       </c>
       <c r="U105" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -7614,43 +8048,43 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>658</v>
+        <v>727</v>
       </c>
       <c r="C106" t="s">
-        <v>659</v>
+        <v>728</v>
       </c>
       <c r="D106">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E106">
-        <v>5</v>
-      </c>
-      <c r="F106">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F106" t="s">
+        <v>181</v>
       </c>
       <c r="G106" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H106" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I106" t="s">
-        <v>660</v>
+        <v>729</v>
       </c>
       <c r="J106" t="s">
-        <v>661</v>
+        <v>730</v>
       </c>
       <c r="K106" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L106" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P106" t="s">
-        <v>662</v>
+        <v>731</v>
       </c>
       <c r="U106" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -7658,43 +8092,43 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>663</v>
+        <v>732</v>
       </c>
       <c r="C107" t="s">
-        <v>664</v>
+        <v>733</v>
       </c>
       <c r="D107">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E107">
-        <v>5</v>
-      </c>
-      <c r="F107">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="F107" t="s">
+        <v>44</v>
       </c>
       <c r="G107" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H107" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I107" t="s">
-        <v>665</v>
+        <v>734</v>
       </c>
       <c r="J107" t="s">
-        <v>666</v>
+        <v>735</v>
       </c>
       <c r="K107" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L107" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P107" t="s">
-        <v>667</v>
+        <v>736</v>
       </c>
       <c r="U107" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
@@ -7702,43 +8136,43 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>668</v>
+        <v>737</v>
       </c>
       <c r="C108" t="s">
-        <v>669</v>
+        <v>738</v>
       </c>
       <c r="D108">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E108">
-        <v>5</v>
-      </c>
-      <c r="F108">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="F108" t="s">
+        <v>44</v>
       </c>
       <c r="G108" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H108" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I108" t="s">
-        <v>670</v>
+        <v>739</v>
       </c>
       <c r="J108" t="s">
-        <v>671</v>
+        <v>740</v>
       </c>
       <c r="K108" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L108" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P108" t="s">
-        <v>672</v>
+        <v>741</v>
       </c>
       <c r="U108" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -7746,43 +8180,43 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>673</v>
+        <v>742</v>
       </c>
       <c r="C109" t="s">
-        <v>674</v>
+        <v>743</v>
       </c>
       <c r="D109">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E109">
-        <v>5</v>
-      </c>
-      <c r="F109">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="F109" t="s">
+        <v>181</v>
       </c>
       <c r="G109" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H109" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I109" t="s">
-        <v>675</v>
+        <v>744</v>
       </c>
       <c r="J109" t="s">
-        <v>676</v>
+        <v>745</v>
       </c>
       <c r="K109" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L109" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P109" t="s">
-        <v>677</v>
+        <v>746</v>
       </c>
       <c r="U109" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -7790,43 +8224,43 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>678</v>
+        <v>747</v>
       </c>
       <c r="C110" t="s">
-        <v>679</v>
+        <v>748</v>
       </c>
       <c r="D110">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E110">
-        <v>5</v>
-      </c>
-      <c r="F110">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="F110" t="s">
+        <v>75</v>
       </c>
       <c r="G110" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H110" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I110" t="s">
-        <v>680</v>
+        <v>749</v>
       </c>
       <c r="J110" t="s">
-        <v>681</v>
+        <v>750</v>
       </c>
       <c r="K110" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L110" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P110" t="s">
-        <v>682</v>
+        <v>751</v>
       </c>
       <c r="U110" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
@@ -7834,43 +8268,43 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>683</v>
+        <v>752</v>
       </c>
       <c r="C111" t="s">
-        <v>684</v>
+        <v>753</v>
       </c>
       <c r="D111">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E111">
-        <v>5</v>
-      </c>
-      <c r="F111">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="F111" t="s">
+        <v>75</v>
       </c>
       <c r="G111" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H111" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I111" t="s">
-        <v>685</v>
+        <v>754</v>
       </c>
       <c r="J111" t="s">
-        <v>686</v>
+        <v>755</v>
       </c>
       <c r="K111" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L111" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P111" t="s">
-        <v>687</v>
+        <v>756</v>
       </c>
       <c r="U111" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
@@ -7878,43 +8312,43 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>688</v>
+        <v>757</v>
       </c>
       <c r="C112" t="s">
-        <v>689</v>
+        <v>758</v>
       </c>
       <c r="D112">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E112">
-        <v>5</v>
-      </c>
-      <c r="F112">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="F112" t="s">
+        <v>75</v>
       </c>
       <c r="G112" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H112" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I112" t="s">
-        <v>690</v>
+        <v>759</v>
       </c>
       <c r="J112" t="s">
-        <v>691</v>
+        <v>760</v>
       </c>
       <c r="K112" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L112" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P112" t="s">
-        <v>692</v>
+        <v>761</v>
       </c>
       <c r="U112" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -7922,43 +8356,43 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>693</v>
+        <v>762</v>
       </c>
       <c r="C113" t="s">
-        <v>694</v>
+        <v>763</v>
       </c>
       <c r="D113">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E113">
-        <v>5</v>
-      </c>
-      <c r="F113">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="F113" t="s">
+        <v>75</v>
       </c>
       <c r="G113" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H113" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I113" t="s">
-        <v>695</v>
+        <v>764</v>
       </c>
       <c r="J113" t="s">
-        <v>696</v>
+        <v>765</v>
       </c>
       <c r="K113" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L113" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P113" t="s">
-        <v>697</v>
+        <v>766</v>
       </c>
       <c r="U113" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
@@ -7966,43 +8400,43 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>698</v>
+        <v>767</v>
       </c>
       <c r="C114" t="s">
-        <v>699</v>
+        <v>768</v>
       </c>
       <c r="D114">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E114">
-        <v>5</v>
-      </c>
-      <c r="F114">
         <v>4</v>
       </c>
+      <c r="F114" t="s">
+        <v>33</v>
+      </c>
       <c r="G114" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H114" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I114" t="s">
-        <v>700</v>
+        <v>769</v>
       </c>
       <c r="J114" t="s">
-        <v>701</v>
+        <v>770</v>
       </c>
       <c r="K114" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L114" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P114" t="s">
-        <v>702</v>
+        <v>771</v>
       </c>
       <c r="U114" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -8010,43 +8444,43 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>703</v>
+        <v>772</v>
       </c>
       <c r="C115" t="s">
-        <v>704</v>
+        <v>773</v>
       </c>
       <c r="D115">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E115">
-        <v>5</v>
-      </c>
-      <c r="F115">
         <v>4</v>
       </c>
+      <c r="F115" t="s">
+        <v>33</v>
+      </c>
       <c r="G115" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H115" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I115" t="s">
-        <v>705</v>
+        <v>774</v>
       </c>
       <c r="J115" t="s">
-        <v>706</v>
+        <v>775</v>
       </c>
       <c r="K115" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L115" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P115" t="s">
-        <v>707</v>
+        <v>776</v>
       </c>
       <c r="U115" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
@@ -8054,43 +8488,43 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>708</v>
+        <v>777</v>
       </c>
       <c r="C116" t="s">
-        <v>709</v>
+        <v>778</v>
       </c>
       <c r="D116">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E116">
-        <v>5</v>
-      </c>
-      <c r="F116">
         <v>4</v>
       </c>
+      <c r="F116" t="s">
+        <v>33</v>
+      </c>
       <c r="G116" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H116" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I116" t="s">
-        <v>710</v>
+        <v>779</v>
       </c>
       <c r="J116" t="s">
-        <v>711</v>
+        <v>780</v>
       </c>
       <c r="K116" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L116" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P116" t="s">
-        <v>712</v>
+        <v>781</v>
       </c>
       <c r="U116" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -8098,43 +8532,43 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>713</v>
+        <v>782</v>
       </c>
       <c r="C117" t="s">
-        <v>714</v>
+        <v>783</v>
       </c>
       <c r="D117">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E117">
-        <v>5</v>
-      </c>
-      <c r="F117">
         <v>4</v>
       </c>
+      <c r="F117" t="s">
+        <v>33</v>
+      </c>
       <c r="G117" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H117" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I117" t="s">
-        <v>715</v>
+        <v>784</v>
       </c>
       <c r="J117" t="s">
-        <v>716</v>
+        <v>785</v>
       </c>
       <c r="K117" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L117" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P117" t="s">
-        <v>717</v>
+        <v>786</v>
       </c>
       <c r="U117" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -8142,43 +8576,43 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>718</v>
+        <v>787</v>
       </c>
       <c r="C118" t="s">
+        <v>788</v>
+      </c>
+      <c r="D118">
+        <v>2024</v>
+      </c>
+      <c r="E118">
+        <v>4</v>
+      </c>
+      <c r="F118" t="s">
+        <v>33</v>
+      </c>
+      <c r="G118" t="s">
+        <v>715</v>
+      </c>
+      <c r="H118" t="s">
+        <v>716</v>
+      </c>
+      <c r="I118" t="s">
+        <v>789</v>
+      </c>
+      <c r="J118" t="s">
+        <v>790</v>
+      </c>
+      <c r="K118" t="s">
+        <v>196</v>
+      </c>
+      <c r="L118" t="s">
         <v>719</v>
       </c>
-      <c r="D118">
-        <v>2026</v>
-      </c>
-      <c r="E118">
-        <v>6</v>
-      </c>
-      <c r="F118">
-        <v>1</v>
-      </c>
-      <c r="G118" t="s">
-        <v>571</v>
-      </c>
-      <c r="H118" t="s">
-        <v>572</v>
-      </c>
-      <c r="I118" t="s">
-        <v>720</v>
-      </c>
-      <c r="J118" t="s">
+      <c r="P118" t="s">
+        <v>791</v>
+      </c>
+      <c r="U118" t="s">
         <v>721</v>
-      </c>
-      <c r="K118" t="s">
-        <v>107</v>
-      </c>
-      <c r="L118" t="s">
-        <v>575</v>
-      </c>
-      <c r="P118" t="s">
-        <v>722</v>
-      </c>
-      <c r="U118" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -8186,43 +8620,43 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>723</v>
+        <v>792</v>
       </c>
       <c r="C119" t="s">
-        <v>724</v>
+        <v>793</v>
       </c>
       <c r="D119">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="E119">
-        <v>6</v>
-      </c>
-      <c r="F119">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F119" t="s">
+        <v>33</v>
       </c>
       <c r="G119" t="s">
-        <v>571</v>
+        <v>715</v>
       </c>
       <c r="H119" t="s">
-        <v>572</v>
+        <v>716</v>
       </c>
       <c r="I119" t="s">
-        <v>725</v>
+        <v>794</v>
       </c>
       <c r="J119" t="s">
-        <v>726</v>
+        <v>795</v>
       </c>
       <c r="K119" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L119" t="s">
-        <v>575</v>
+        <v>719</v>
       </c>
       <c r="P119" t="s">
-        <v>727</v>
+        <v>796</v>
       </c>
       <c r="U119" t="s">
-        <v>577</v>
+        <v>721</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -8230,43 +8664,43 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>728</v>
+        <v>797</v>
       </c>
       <c r="C120" t="s">
-        <v>729</v>
+        <v>798</v>
       </c>
       <c r="D120">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E120">
-        <v>3</v>
-      </c>
-      <c r="F120">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F120" t="s">
+        <v>44</v>
       </c>
       <c r="G120" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="H120" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="I120" t="s">
-        <v>732</v>
+        <v>799</v>
       </c>
       <c r="J120" t="s">
-        <v>733</v>
+        <v>800</v>
       </c>
       <c r="K120" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L120" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="P120" t="s">
-        <v>735</v>
+        <v>801</v>
       </c>
       <c r="U120" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
@@ -8274,43 +8708,43 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>737</v>
+        <v>802</v>
       </c>
       <c r="C121" t="s">
-        <v>738</v>
+        <v>803</v>
       </c>
       <c r="D121">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E121">
-        <v>4</v>
-      </c>
-      <c r="F121">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F121" t="s">
+        <v>44</v>
       </c>
       <c r="G121" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="H121" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="I121" t="s">
-        <v>739</v>
+        <v>804</v>
       </c>
       <c r="J121" t="s">
-        <v>740</v>
+        <v>805</v>
       </c>
       <c r="K121" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L121" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="P121" t="s">
-        <v>741</v>
+        <v>806</v>
       </c>
       <c r="U121" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
@@ -8318,43 +8752,43 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>742</v>
+        <v>807</v>
       </c>
       <c r="C122" t="s">
-        <v>743</v>
+        <v>808</v>
       </c>
       <c r="D122">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E122">
-        <v>4</v>
-      </c>
-      <c r="F122">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F122" t="s">
+        <v>181</v>
       </c>
       <c r="G122" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="H122" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="I122" t="s">
-        <v>744</v>
+        <v>809</v>
       </c>
       <c r="J122" t="s">
-        <v>745</v>
+        <v>810</v>
       </c>
       <c r="K122" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L122" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="P122" t="s">
-        <v>746</v>
+        <v>811</v>
       </c>
       <c r="U122" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
@@ -8362,43 +8796,43 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>747</v>
+        <v>812</v>
       </c>
       <c r="C123" t="s">
-        <v>748</v>
+        <v>813</v>
       </c>
       <c r="D123">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E123">
-        <v>4</v>
-      </c>
-      <c r="F123">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F123" t="s">
+        <v>181</v>
       </c>
       <c r="G123" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="H123" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="I123" t="s">
-        <v>749</v>
+        <v>814</v>
       </c>
       <c r="J123" t="s">
-        <v>750</v>
+        <v>815</v>
       </c>
       <c r="K123" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L123" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="P123" t="s">
-        <v>751</v>
+        <v>816</v>
       </c>
       <c r="U123" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
@@ -8406,43 +8840,43 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>752</v>
+        <v>817</v>
       </c>
       <c r="C124" t="s">
-        <v>753</v>
+        <v>818</v>
       </c>
       <c r="D124">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E124">
-        <v>4</v>
-      </c>
-      <c r="F124">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F124" t="s">
+        <v>181</v>
       </c>
       <c r="G124" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="H124" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="I124" t="s">
-        <v>754</v>
+        <v>819</v>
       </c>
       <c r="J124" t="s">
-        <v>755</v>
+        <v>820</v>
       </c>
       <c r="K124" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L124" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="P124" t="s">
-        <v>756</v>
+        <v>821</v>
       </c>
       <c r="U124" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
@@ -8450,43 +8884,43 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>757</v>
+        <v>822</v>
       </c>
       <c r="C125" t="s">
-        <v>758</v>
+        <v>823</v>
       </c>
       <c r="D125">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E125">
-        <v>4</v>
-      </c>
-      <c r="F125">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F125" t="s">
+        <v>75</v>
       </c>
       <c r="G125" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="H125" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="I125" t="s">
-        <v>759</v>
+        <v>824</v>
       </c>
       <c r="J125" t="s">
-        <v>760</v>
+        <v>825</v>
       </c>
       <c r="K125" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L125" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="P125" t="s">
-        <v>761</v>
+        <v>826</v>
       </c>
       <c r="U125" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
@@ -8494,10 +8928,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>762</v>
+        <v>827</v>
       </c>
       <c r="C126" t="s">
-        <v>763</v>
+        <v>828</v>
       </c>
       <c r="D126">
         <v>2025</v>
@@ -8505,32 +8939,32 @@
       <c r="E126">
         <v>5</v>
       </c>
-      <c r="F126">
-        <v>1</v>
+      <c r="F126" t="s">
+        <v>75</v>
       </c>
       <c r="G126" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="H126" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="I126" t="s">
-        <v>764</v>
+        <v>829</v>
       </c>
       <c r="J126" t="s">
-        <v>765</v>
+        <v>830</v>
       </c>
       <c r="K126" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L126" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="P126" t="s">
-        <v>766</v>
+        <v>831</v>
       </c>
       <c r="U126" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
@@ -8538,10 +8972,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>767</v>
+        <v>832</v>
       </c>
       <c r="C127" t="s">
-        <v>768</v>
+        <v>833</v>
       </c>
       <c r="D127">
         <v>2025</v>
@@ -8549,32 +8983,32 @@
       <c r="E127">
         <v>5</v>
       </c>
-      <c r="F127">
-        <v>1</v>
+      <c r="F127" t="s">
+        <v>75</v>
       </c>
       <c r="G127" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="H127" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="I127" t="s">
-        <v>769</v>
+        <v>834</v>
       </c>
       <c r="J127" t="s">
-        <v>770</v>
+        <v>835</v>
       </c>
       <c r="K127" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L127" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="P127" t="s">
-        <v>771</v>
+        <v>836</v>
       </c>
       <c r="U127" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
@@ -8582,10 +9016,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>772</v>
+        <v>837</v>
       </c>
       <c r="C128" t="s">
-        <v>773</v>
+        <v>838</v>
       </c>
       <c r="D128">
         <v>2025</v>
@@ -8593,32 +9027,32 @@
       <c r="E128">
         <v>5</v>
       </c>
-      <c r="F128">
-        <v>1</v>
+      <c r="F128" t="s">
+        <v>75</v>
       </c>
       <c r="G128" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="H128" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="I128" t="s">
-        <v>774</v>
+        <v>839</v>
       </c>
       <c r="J128" t="s">
-        <v>775</v>
+        <v>840</v>
       </c>
       <c r="K128" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L128" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="P128" t="s">
-        <v>776</v>
+        <v>841</v>
       </c>
       <c r="U128" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
@@ -8626,10 +9060,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>777</v>
+        <v>842</v>
       </c>
       <c r="C129" t="s">
-        <v>778</v>
+        <v>843</v>
       </c>
       <c r="D129">
         <v>2025</v>
@@ -8637,32 +9071,32 @@
       <c r="E129">
         <v>5</v>
       </c>
-      <c r="F129">
-        <v>2</v>
+      <c r="F129" t="s">
+        <v>33</v>
       </c>
       <c r="G129" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="H129" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="I129" t="s">
-        <v>779</v>
+        <v>844</v>
       </c>
       <c r="J129" t="s">
-        <v>780</v>
+        <v>845</v>
       </c>
       <c r="K129" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L129" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="P129" t="s">
-        <v>781</v>
+        <v>846</v>
       </c>
       <c r="U129" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
@@ -8670,10 +9104,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>782</v>
+        <v>847</v>
       </c>
       <c r="C130" t="s">
-        <v>783</v>
+        <v>848</v>
       </c>
       <c r="D130">
         <v>2025</v>
@@ -8681,32 +9115,32 @@
       <c r="E130">
         <v>5</v>
       </c>
-      <c r="F130">
-        <v>3</v>
+      <c r="F130" t="s">
+        <v>33</v>
       </c>
       <c r="G130" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="H130" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="I130" t="s">
-        <v>784</v>
+        <v>849</v>
       </c>
       <c r="J130" t="s">
-        <v>785</v>
+        <v>850</v>
       </c>
       <c r="K130" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="L130" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="P130" t="s">
-        <v>786</v>
+        <v>851</v>
       </c>
       <c r="U130" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
@@ -8714,43 +9148,43 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>787</v>
+        <v>852</v>
       </c>
       <c r="C131" t="s">
-        <v>788</v>
+        <v>853</v>
       </c>
       <c r="D131">
         <v>2025</v>
       </c>
       <c r="E131">
-        <v>4</v>
-      </c>
-      <c r="F131">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F131" t="s">
+        <v>33</v>
       </c>
       <c r="G131" t="s">
-        <v>789</v>
+        <v>715</v>
       </c>
       <c r="H131" t="s">
-        <v>790</v>
+        <v>716</v>
       </c>
       <c r="I131" t="s">
-        <v>791</v>
+        <v>854</v>
       </c>
       <c r="J131" t="s">
-        <v>788</v>
+        <v>855</v>
       </c>
       <c r="K131" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="L131" t="s">
-        <v>792</v>
+        <v>719</v>
       </c>
       <c r="P131" t="s">
-        <v>793</v>
+        <v>856</v>
       </c>
       <c r="U131" t="s">
-        <v>794</v>
+        <v>721</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
@@ -8758,43 +9192,43 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>795</v>
+        <v>857</v>
       </c>
       <c r="C132" t="s">
-        <v>796</v>
+        <v>858</v>
       </c>
       <c r="D132">
         <v>2025</v>
       </c>
       <c r="E132">
-        <v>4</v>
-      </c>
-      <c r="F132">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F132" t="s">
+        <v>33</v>
       </c>
       <c r="G132" t="s">
-        <v>789</v>
+        <v>715</v>
       </c>
       <c r="H132" t="s">
-        <v>790</v>
+        <v>716</v>
       </c>
       <c r="I132" t="s">
-        <v>797</v>
+        <v>859</v>
       </c>
       <c r="J132" t="s">
-        <v>796</v>
+        <v>860</v>
       </c>
       <c r="K132" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="L132" t="s">
-        <v>792</v>
+        <v>719</v>
       </c>
       <c r="P132" t="s">
-        <v>798</v>
+        <v>861</v>
       </c>
       <c r="U132" t="s">
-        <v>794</v>
+        <v>721</v>
       </c>
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
@@ -8802,43 +9236,43 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>799</v>
+        <v>862</v>
       </c>
       <c r="C133" t="s">
-        <v>800</v>
+        <v>863</v>
       </c>
       <c r="D133">
         <v>2026</v>
       </c>
       <c r="E133">
-        <v>5</v>
-      </c>
-      <c r="F133">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F133" t="s">
+        <v>44</v>
       </c>
       <c r="G133" t="s">
-        <v>789</v>
+        <v>715</v>
       </c>
       <c r="H133" t="s">
-        <v>790</v>
+        <v>716</v>
       </c>
       <c r="I133" t="s">
-        <v>801</v>
+        <v>864</v>
       </c>
       <c r="J133" t="s">
-        <v>802</v>
+        <v>865</v>
       </c>
       <c r="K133" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="L133" t="s">
-        <v>792</v>
+        <v>719</v>
       </c>
       <c r="P133" t="s">
-        <v>803</v>
+        <v>866</v>
       </c>
       <c r="U133" t="s">
-        <v>794</v>
+        <v>721</v>
       </c>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
@@ -8846,43 +9280,43 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>804</v>
+        <v>867</v>
       </c>
       <c r="C134" t="s">
-        <v>805</v>
+        <v>868</v>
       </c>
       <c r="D134">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E134">
-        <v>4</v>
-      </c>
-      <c r="F134">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="F134" t="s">
+        <v>44</v>
       </c>
       <c r="G134" t="s">
-        <v>789</v>
+        <v>715</v>
       </c>
       <c r="H134" t="s">
-        <v>790</v>
+        <v>716</v>
       </c>
       <c r="I134" t="s">
-        <v>806</v>
+        <v>869</v>
       </c>
       <c r="J134" t="s">
-        <v>807</v>
+        <v>870</v>
       </c>
       <c r="K134" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="L134" t="s">
-        <v>792</v>
+        <v>719</v>
       </c>
       <c r="P134" t="s">
-        <v>808</v>
+        <v>871</v>
       </c>
       <c r="U134" t="s">
-        <v>794</v>
+        <v>721</v>
       </c>
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
@@ -8890,43 +9324,43 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>809</v>
+        <v>872</v>
       </c>
       <c r="C135" t="s">
-        <v>810</v>
+        <v>873</v>
       </c>
       <c r="D135">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="E135">
-        <v>5</v>
-      </c>
-      <c r="F135">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F135" t="s">
+        <v>75</v>
       </c>
       <c r="G135" t="s">
-        <v>789</v>
+        <v>874</v>
       </c>
       <c r="H135" t="s">
-        <v>790</v>
+        <v>875</v>
       </c>
       <c r="I135" t="s">
-        <v>811</v>
+        <v>876</v>
       </c>
       <c r="J135" t="s">
-        <v>812</v>
+        <v>877</v>
       </c>
       <c r="K135" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="L135" t="s">
-        <v>792</v>
+        <v>878</v>
       </c>
       <c r="P135" t="s">
-        <v>813</v>
+        <v>879</v>
       </c>
       <c r="U135" t="s">
-        <v>794</v>
+        <v>880</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -8934,43 +9368,703 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>814</v>
+        <v>881</v>
       </c>
       <c r="C136" t="s">
-        <v>815</v>
+        <v>882</v>
       </c>
       <c r="D136">
+        <v>2024</v>
+      </c>
+      <c r="E136">
+        <v>4</v>
+      </c>
+      <c r="F136" t="s">
+        <v>44</v>
+      </c>
+      <c r="G136" t="s">
+        <v>874</v>
+      </c>
+      <c r="H136" t="s">
+        <v>875</v>
+      </c>
+      <c r="I136" t="s">
+        <v>883</v>
+      </c>
+      <c r="J136" t="s">
+        <v>884</v>
+      </c>
+      <c r="K136" t="s">
+        <v>196</v>
+      </c>
+      <c r="L136" t="s">
+        <v>878</v>
+      </c>
+      <c r="P136" t="s">
+        <v>885</v>
+      </c>
+      <c r="U136" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>886</v>
+      </c>
+      <c r="C137" t="s">
+        <v>887</v>
+      </c>
+      <c r="D137">
+        <v>2024</v>
+      </c>
+      <c r="E137">
+        <v>4</v>
+      </c>
+      <c r="F137" t="s">
+        <v>181</v>
+      </c>
+      <c r="G137" t="s">
+        <v>874</v>
+      </c>
+      <c r="H137" t="s">
+        <v>875</v>
+      </c>
+      <c r="I137" t="s">
+        <v>888</v>
+      </c>
+      <c r="J137" t="s">
+        <v>889</v>
+      </c>
+      <c r="K137" t="s">
+        <v>196</v>
+      </c>
+      <c r="L137" t="s">
+        <v>878</v>
+      </c>
+      <c r="P137" t="s">
+        <v>890</v>
+      </c>
+      <c r="U137" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>891</v>
+      </c>
+      <c r="C138" t="s">
+        <v>892</v>
+      </c>
+      <c r="D138">
+        <v>2024</v>
+      </c>
+      <c r="E138">
+        <v>4</v>
+      </c>
+      <c r="F138" t="s">
+        <v>75</v>
+      </c>
+      <c r="G138" t="s">
+        <v>874</v>
+      </c>
+      <c r="H138" t="s">
+        <v>875</v>
+      </c>
+      <c r="I138" t="s">
+        <v>893</v>
+      </c>
+      <c r="J138" t="s">
+        <v>894</v>
+      </c>
+      <c r="K138" t="s">
+        <v>196</v>
+      </c>
+      <c r="L138" t="s">
+        <v>878</v>
+      </c>
+      <c r="P138" t="s">
+        <v>895</v>
+      </c>
+      <c r="U138" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>896</v>
+      </c>
+      <c r="C139" t="s">
+        <v>897</v>
+      </c>
+      <c r="D139">
+        <v>2024</v>
+      </c>
+      <c r="E139">
+        <v>4</v>
+      </c>
+      <c r="F139" t="s">
+        <v>75</v>
+      </c>
+      <c r="G139" t="s">
+        <v>874</v>
+      </c>
+      <c r="H139" t="s">
+        <v>875</v>
+      </c>
+      <c r="I139" t="s">
+        <v>898</v>
+      </c>
+      <c r="J139" t="s">
+        <v>899</v>
+      </c>
+      <c r="K139" t="s">
+        <v>196</v>
+      </c>
+      <c r="L139" t="s">
+        <v>878</v>
+      </c>
+      <c r="P139" t="s">
+        <v>900</v>
+      </c>
+      <c r="U139" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>901</v>
+      </c>
+      <c r="C140" t="s">
+        <v>902</v>
+      </c>
+      <c r="D140">
+        <v>2024</v>
+      </c>
+      <c r="E140">
+        <v>4</v>
+      </c>
+      <c r="F140" t="s">
+        <v>75</v>
+      </c>
+      <c r="G140" t="s">
+        <v>874</v>
+      </c>
+      <c r="H140" t="s">
+        <v>875</v>
+      </c>
+      <c r="I140" t="s">
+        <v>903</v>
+      </c>
+      <c r="J140" t="s">
+        <v>904</v>
+      </c>
+      <c r="K140" t="s">
+        <v>196</v>
+      </c>
+      <c r="L140" t="s">
+        <v>878</v>
+      </c>
+      <c r="P140" t="s">
+        <v>905</v>
+      </c>
+      <c r="U140" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>906</v>
+      </c>
+      <c r="C141" t="s">
+        <v>907</v>
+      </c>
+      <c r="D141">
+        <v>2025</v>
+      </c>
+      <c r="E141">
+        <v>5</v>
+      </c>
+      <c r="F141" t="s">
+        <v>44</v>
+      </c>
+      <c r="G141" t="s">
+        <v>874</v>
+      </c>
+      <c r="H141" t="s">
+        <v>875</v>
+      </c>
+      <c r="I141" t="s">
+        <v>908</v>
+      </c>
+      <c r="J141" t="s">
+        <v>909</v>
+      </c>
+      <c r="K141" t="s">
+        <v>196</v>
+      </c>
+      <c r="L141" t="s">
+        <v>878</v>
+      </c>
+      <c r="P141" t="s">
+        <v>910</v>
+      </c>
+      <c r="U141" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>911</v>
+      </c>
+      <c r="C142" t="s">
+        <v>912</v>
+      </c>
+      <c r="D142">
+        <v>2025</v>
+      </c>
+      <c r="E142">
+        <v>5</v>
+      </c>
+      <c r="F142" t="s">
+        <v>44</v>
+      </c>
+      <c r="G142" t="s">
+        <v>874</v>
+      </c>
+      <c r="H142" t="s">
+        <v>875</v>
+      </c>
+      <c r="I142" t="s">
+        <v>913</v>
+      </c>
+      <c r="J142" t="s">
+        <v>914</v>
+      </c>
+      <c r="K142" t="s">
+        <v>196</v>
+      </c>
+      <c r="L142" t="s">
+        <v>878</v>
+      </c>
+      <c r="P142" t="s">
+        <v>915</v>
+      </c>
+      <c r="U142" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>916</v>
+      </c>
+      <c r="C143" t="s">
+        <v>917</v>
+      </c>
+      <c r="D143">
+        <v>2025</v>
+      </c>
+      <c r="E143">
+        <v>5</v>
+      </c>
+      <c r="F143" t="s">
+        <v>44</v>
+      </c>
+      <c r="G143" t="s">
+        <v>874</v>
+      </c>
+      <c r="H143" t="s">
+        <v>875</v>
+      </c>
+      <c r="I143" t="s">
+        <v>918</v>
+      </c>
+      <c r="J143" t="s">
+        <v>919</v>
+      </c>
+      <c r="K143" t="s">
+        <v>196</v>
+      </c>
+      <c r="L143" t="s">
+        <v>878</v>
+      </c>
+      <c r="P143" t="s">
+        <v>920</v>
+      </c>
+      <c r="U143" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>921</v>
+      </c>
+      <c r="C144" t="s">
+        <v>922</v>
+      </c>
+      <c r="D144">
+        <v>2025</v>
+      </c>
+      <c r="E144">
+        <v>5</v>
+      </c>
+      <c r="F144" t="s">
+        <v>181</v>
+      </c>
+      <c r="G144" t="s">
+        <v>874</v>
+      </c>
+      <c r="H144" t="s">
+        <v>875</v>
+      </c>
+      <c r="I144" t="s">
+        <v>923</v>
+      </c>
+      <c r="J144" t="s">
+        <v>924</v>
+      </c>
+      <c r="K144" t="s">
+        <v>196</v>
+      </c>
+      <c r="L144" t="s">
+        <v>878</v>
+      </c>
+      <c r="P144" t="s">
+        <v>925</v>
+      </c>
+      <c r="U144" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>926</v>
+      </c>
+      <c r="C145" t="s">
+        <v>927</v>
+      </c>
+      <c r="D145">
+        <v>2025</v>
+      </c>
+      <c r="E145">
+        <v>5</v>
+      </c>
+      <c r="F145" t="s">
+        <v>75</v>
+      </c>
+      <c r="G145" t="s">
+        <v>874</v>
+      </c>
+      <c r="H145" t="s">
+        <v>875</v>
+      </c>
+      <c r="I145" t="s">
+        <v>928</v>
+      </c>
+      <c r="J145" t="s">
+        <v>929</v>
+      </c>
+      <c r="K145" t="s">
+        <v>196</v>
+      </c>
+      <c r="L145" t="s">
+        <v>878</v>
+      </c>
+      <c r="P145" t="s">
+        <v>930</v>
+      </c>
+      <c r="U145" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>931</v>
+      </c>
+      <c r="C146" t="s">
+        <v>932</v>
+      </c>
+      <c r="D146">
+        <v>2025</v>
+      </c>
+      <c r="E146">
+        <v>4</v>
+      </c>
+      <c r="F146" t="s">
+        <v>44</v>
+      </c>
+      <c r="G146" t="s">
+        <v>933</v>
+      </c>
+      <c r="H146" t="s">
+        <v>934</v>
+      </c>
+      <c r="I146" t="s">
+        <v>935</v>
+      </c>
+      <c r="J146" t="s">
+        <v>932</v>
+      </c>
+      <c r="K146" t="s">
+        <v>359</v>
+      </c>
+      <c r="L146" t="s">
+        <v>936</v>
+      </c>
+      <c r="P146" t="s">
+        <v>937</v>
+      </c>
+      <c r="U146" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>939</v>
+      </c>
+      <c r="C147" t="s">
+        <v>940</v>
+      </c>
+      <c r="D147">
+        <v>2025</v>
+      </c>
+      <c r="E147">
+        <v>4</v>
+      </c>
+      <c r="F147" t="s">
+        <v>44</v>
+      </c>
+      <c r="G147" t="s">
+        <v>933</v>
+      </c>
+      <c r="H147" t="s">
+        <v>934</v>
+      </c>
+      <c r="I147" t="s">
+        <v>941</v>
+      </c>
+      <c r="J147" t="s">
+        <v>940</v>
+      </c>
+      <c r="K147" t="s">
+        <v>359</v>
+      </c>
+      <c r="L147" t="s">
+        <v>936</v>
+      </c>
+      <c r="P147" t="s">
+        <v>942</v>
+      </c>
+      <c r="U147" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>943</v>
+      </c>
+      <c r="C148" t="s">
+        <v>944</v>
+      </c>
+      <c r="D148">
+        <v>2026</v>
+      </c>
+      <c r="E148">
+        <v>5</v>
+      </c>
+      <c r="F148" t="s">
+        <v>44</v>
+      </c>
+      <c r="G148" t="s">
+        <v>933</v>
+      </c>
+      <c r="H148" t="s">
+        <v>934</v>
+      </c>
+      <c r="I148" t="s">
+        <v>945</v>
+      </c>
+      <c r="J148" t="s">
+        <v>946</v>
+      </c>
+      <c r="K148" t="s">
+        <v>359</v>
+      </c>
+      <c r="L148" t="s">
+        <v>936</v>
+      </c>
+      <c r="P148" t="s">
+        <v>947</v>
+      </c>
+      <c r="U148" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>948</v>
+      </c>
+      <c r="C149" t="s">
+        <v>949</v>
+      </c>
+      <c r="D149">
+        <v>2025</v>
+      </c>
+      <c r="E149">
+        <v>4</v>
+      </c>
+      <c r="F149" t="s">
+        <v>181</v>
+      </c>
+      <c r="G149" t="s">
+        <v>933</v>
+      </c>
+      <c r="H149" t="s">
+        <v>934</v>
+      </c>
+      <c r="I149" t="s">
+        <v>950</v>
+      </c>
+      <c r="J149" t="s">
+        <v>951</v>
+      </c>
+      <c r="K149" t="s">
+        <v>359</v>
+      </c>
+      <c r="L149" t="s">
+        <v>936</v>
+      </c>
+      <c r="P149" t="s">
+        <v>952</v>
+      </c>
+      <c r="U149" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>953</v>
+      </c>
+      <c r="C150" t="s">
+        <v>954</v>
+      </c>
+      <c r="D150">
+        <v>2026</v>
+      </c>
+      <c r="E150">
+        <v>5</v>
+      </c>
+      <c r="F150" t="s">
+        <v>44</v>
+      </c>
+      <c r="G150" t="s">
+        <v>933</v>
+      </c>
+      <c r="H150" t="s">
+        <v>934</v>
+      </c>
+      <c r="I150" t="s">
+        <v>955</v>
+      </c>
+      <c r="J150" t="s">
+        <v>956</v>
+      </c>
+      <c r="K150" t="s">
+        <v>359</v>
+      </c>
+      <c r="L150" t="s">
+        <v>936</v>
+      </c>
+      <c r="P150" t="s">
+        <v>957</v>
+      </c>
+      <c r="U150" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>958</v>
+      </c>
+      <c r="C151" t="s">
+        <v>959</v>
+      </c>
+      <c r="D151">
         <v>2023</v>
       </c>
-      <c r="E136">
+      <c r="E151">
         <v>2</v>
       </c>
-      <c r="F136">
-        <v>2</v>
-      </c>
-      <c r="G136" t="s">
-        <v>789</v>
-      </c>
-      <c r="H136" t="s">
-        <v>790</v>
-      </c>
-      <c r="I136" t="s">
-        <v>816</v>
-      </c>
-      <c r="J136" t="s">
-        <v>817</v>
-      </c>
-      <c r="K136" t="s">
-        <v>249</v>
-      </c>
-      <c r="L136" t="s">
-        <v>792</v>
-      </c>
-      <c r="P136" t="s">
-        <v>818</v>
-      </c>
-      <c r="U136" t="s">
-        <v>794</v>
+      <c r="F151" t="s">
+        <v>181</v>
+      </c>
+      <c r="G151" t="s">
+        <v>933</v>
+      </c>
+      <c r="H151" t="s">
+        <v>934</v>
+      </c>
+      <c r="I151" t="s">
+        <v>960</v>
+      </c>
+      <c r="J151" t="s">
+        <v>961</v>
+      </c>
+      <c r="K151" t="s">
+        <v>359</v>
+      </c>
+      <c r="L151" t="s">
+        <v>936</v>
+      </c>
+      <c r="P151" t="s">
+        <v>962</v>
+      </c>
+      <c r="U151" t="s">
+        <v>938</v>
       </c>
     </row>
   </sheetData>
